--- a/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
+++ b/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
@@ -166,7 +166,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -243,6 +243,11 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -277,7 +282,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="184">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -500,6 +505,26 @@
     <xf numFmtId="167" fontId="6" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="6" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="169" fontId="5" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="5" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="169" fontId="7" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="7" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="9" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -904,7 +929,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="n"/>
       <c r="B5" s="112" t="inlineStr">
@@ -1087,7 +1111,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
@@ -1112,27 +1135,27 @@
       </c>
       <c r="F10" s="119">
         <f>IF(E$8=1,E59,D58)</f>
-        <v>423090.99999999994</v>
+        <v>300315.52999999997</v>
       </c>
       <c r="G10" s="119">
         <f>F10</f>
-        <v>423090.99999999994</v>
+        <v>300315.52999999997</v>
       </c>
       <c r="H10" s="119">
         <f>IF(G$8=1,G59,F58)</f>
-        <v>459456.67666666664</v>
+        <v>534919.8166666667</v>
       </c>
       <c r="I10" s="119">
         <f>H10</f>
-        <v>459456.67666666664</v>
+        <v>534919.8166666667</v>
       </c>
       <c r="J10" s="119">
         <f>IF(I$8=1,I59,H58)</f>
-        <v>194490.60933333333</v>
+        <v>269953.74933333334</v>
       </c>
       <c r="K10" s="119">
         <f>J10</f>
-        <v>194490.60933333333</v>
+        <v>269953.74933333334</v>
       </c>
       <c r="L10" s="119">
         <f>B10</f>
@@ -1145,7 +1168,6 @@
       <c r="N10" s="16" t="n"/>
       <c r="O10" s="77" t="n"/>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
@@ -1174,39 +1196,39 @@
         </is>
       </c>
       <c r="B13" s="120">
-        <f>SUMIFS(Receivables!$F$5:$F$52,Receivables!$H$5:$H$52,"&gt;="&amp;Assumptions!$B$44,Receivables!$H$5:$H$52,"&lt;="&amp;Assumptions!$C$44)</f>
-        <v>158974.55</v>
+        <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$44,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$44)</f>
+        <v>134590.91999999998</v>
       </c>
       <c r="C13" s="121">
         <f>41925.4+6172.39+58024.76+1975.51+1092.3+13046.62+4352.45+13156</f>
         <v>139745.43</v>
       </c>
       <c r="D13" s="120">
-        <f>SUMIFS(Receivables!$F$5:$F$52,Receivables!$H$5:$H$52,"&gt;="&amp;Assumptions!$B$45,Receivables!$H$5:$H$52,"&lt;="&amp;Assumptions!$C$45)</f>
-        <v>263138.69999999995</v>
+        <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$45,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$45)</f>
+        <v>142696.27</v>
       </c>
       <c r="E13" s="121">
         <f>112683.22+18891.66+9086.39+1661+506+374</f>
         <v>143202.27000000002</v>
       </c>
       <c r="F13" s="120">
-        <f>SUMIFS(Receivables!$F$5:$F$52,Receivables!$H$5:$H$52,"&gt;="&amp;Assumptions!$B$46,Receivables!$H$5:$H$52,"&lt;="&amp;Assumptions!$C$46)+Assumptions!$B$39/3</f>
-        <v>90207.73666666666</v>
+        <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$46,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$46)+Assumptions!$B$39/3</f>
+        <v>234604.28666666668</v>
       </c>
       <c r="G13" s="121" t="n"/>
       <c r="H13" s="120">
-        <f>SUMIFS(Receivables!$F$5:$F$52,Receivables!$H$5:$H$52,"&gt;="&amp;Assumptions!$B$47,Receivables!$H$5:$H$52,"&lt;="&amp;Assumptions!$C$47)+Assumptions!$B$39/3</f>
+        <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$47,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$47)+Assumptions!$B$39/3</f>
         <v>12626.466666666667</v>
       </c>
       <c r="I13" s="121" t="n"/>
       <c r="J13" s="120">
-        <f>SUMIFS(Receivables!$F$5:$F$52,Receivables!$H$5:$H$52,"&gt;="&amp;Assumptions!$B$48,Receivables!$H$5:$H$52,"&lt;="&amp;Assumptions!$C$48)+Assumptions!$B$39/3</f>
-        <v>29899.056666666667</v>
+        <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$48,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$48)+Assumptions!$B$39/3</f>
+        <v>91870.13666666666</v>
       </c>
       <c r="K13" s="121" t="n"/>
       <c r="L13" s="120">
         <f>SUM(B13,D13,F13,H13,J13)</f>
-        <v>554846.5099999999</v>
+        <v>616388.0799999998</v>
       </c>
       <c r="M13" s="120">
         <f>SUM(C13,E13,G13,I13,K13)</f>
@@ -1214,7 +1236,7 @@
       </c>
       <c r="N13" s="120">
         <f>(C13-B13)*C$8+(E13-D13)*E$8+(G13-F13)*G$8+(I13-H13)*I$8+(K13-J13)*K$8</f>
-        <v>-19229.119999999995</v>
+        <v>5154.510000000009</v>
       </c>
       <c r="O13" s="108" t="inlineStr">
         <is>
@@ -1283,7 +1305,7 @@
       </c>
       <c r="B15" s="122">
         <f>B13+B14</f>
-        <v>158974.55</v>
+        <v>134590.91999999998</v>
       </c>
       <c r="C15" s="122">
         <f>C13+C14</f>
@@ -1291,7 +1313,7 @@
       </c>
       <c r="D15" s="122">
         <f>D13+D14</f>
-        <v>263138.69999999995</v>
+        <v>142696.27</v>
       </c>
       <c r="E15" s="122">
         <f>E13+E14</f>
@@ -1299,7 +1321,7 @@
       </c>
       <c r="F15" s="122">
         <f>F13+F14</f>
-        <v>90207.73666666666</v>
+        <v>234604.28666666668</v>
       </c>
       <c r="G15" s="122">
         <f>G13+G14</f>
@@ -1315,7 +1337,7 @@
       </c>
       <c r="J15" s="122">
         <f>J13+J14</f>
-        <v>30499.056666666667</v>
+        <v>92470.13666666666</v>
       </c>
       <c r="K15" s="122">
         <f>K13+K14</f>
@@ -1323,7 +1345,7 @@
       </c>
       <c r="L15" s="122">
         <f>L13+L14</f>
-        <v>555446.5099999999</v>
+        <v>616988.0799999998</v>
       </c>
       <c r="M15" s="122">
         <f>M13+M14</f>
@@ -1331,11 +1353,10 @@
       </c>
       <c r="N15" s="122">
         <f>N13+N14</f>
-        <v>-18798.949999999997</v>
+        <v>5584.680000000009</v>
       </c>
       <c r="O15" s="16" t="n"/>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
@@ -1673,7 +1694,6 @@
       </c>
       <c r="O24" s="12" t="n"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="22" t="inlineStr">
         <is>
@@ -1847,12 +1867,12 @@
       </c>
       <c r="B30" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
-        <v>9955.84</v>
+        <v>6328.8</v>
       </c>
       <c r="C30" s="121" t="n"/>
       <c r="D30" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
-        <v>2085</v>
+        <v>5712.04</v>
       </c>
       <c r="E30" s="121">
         <f>ROUND(18837.31*1.1,2)</f>
@@ -1883,7 +1903,7 @@
       </c>
       <c r="N30" s="120">
         <f>(C30-B30)*C$8+(E30-D30)*E$8+(G30-F30)*G$8+(I30-H30)*I$8+(K30-J30)*K$8</f>
-        <v>-9955.84</v>
+        <v>-6328.8</v>
       </c>
       <c r="O30" s="108" t="inlineStr">
         <is>
@@ -1951,7 +1971,7 @@
       </c>
       <c r="B32" s="123">
         <f>B27+B28+B29+B30+B31</f>
-        <v>193150.27</v>
+        <v>189523.22999999998</v>
       </c>
       <c r="C32" s="123">
         <f>C27+C28+C29+C30+C31</f>
@@ -1959,7 +1979,7 @@
       </c>
       <c r="D32" s="123">
         <f>D27+D28+D29+D30+D31</f>
-        <v>21485</v>
+        <v>25112.04</v>
       </c>
       <c r="E32" s="123">
         <f>E27+E28+E29+E30+E31</f>
@@ -1999,11 +2019,10 @@
       </c>
       <c r="N32" s="123">
         <f>N27+N28+N29+N30+N31</f>
-        <v>-54064.03999999998</v>
+        <v>-50436.999999999985</v>
       </c>
       <c r="O32" s="12" t="n"/>
     </row>
-    <row r="33"/>
     <row r="34">
       <c r="A34" s="22" t="inlineStr">
         <is>
@@ -2172,19 +2191,19 @@
       </c>
       <c r="B38" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
-        <v>6410</v>
+        <v>1680</v>
       </c>
       <c r="C38" s="121" t="n"/>
       <c r="D38" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
-        <v>800</v>
+        <v>1680</v>
       </c>
       <c r="E38" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
-        <v>800</v>
+        <v>4650</v>
       </c>
       <c r="G38" s="121" t="n"/>
       <c r="H38" s="120">
@@ -2207,7 +2226,7 @@
       </c>
       <c r="N38" s="120">
         <f>(C38-B38)*C$8+(E38-D38)*E$8+(G38-F38)*G$8+(I38-H38)*I$8+(K38-J38)*K$8</f>
-        <v>-6410</v>
+        <v>-1680</v>
       </c>
       <c r="O38" s="108" t="inlineStr">
         <is>
@@ -2228,14 +2247,14 @@
       <c r="C39" s="121" t="n"/>
       <c r="D39" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
-        <v>2310</v>
+        <v>0</v>
       </c>
       <c r="E39" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
-        <v>0</v>
+        <v>2310</v>
       </c>
       <c r="G39" s="121" t="n"/>
       <c r="H39" s="120">
@@ -2279,7 +2298,7 @@
       <c r="C40" s="121" t="n"/>
       <c r="D40" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
-        <v>804.11</v>
+        <v>940.11</v>
       </c>
       <c r="E40" s="121">
         <f>804.11+136</f>
@@ -2297,12 +2316,12 @@
       <c r="I40" s="121" t="n"/>
       <c r="J40" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K40" s="121" t="n"/>
       <c r="L40" s="120">
         <f>SUM(B40,D40,F40,H40,J40)</f>
-        <v>1035.31</v>
+        <v>1041.31</v>
       </c>
       <c r="M40" s="120">
         <f>SUM(C40,E40,G40,I40,K40)</f>
@@ -2710,7 +2729,7 @@
       </c>
       <c r="B49" s="123">
         <f>B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47</f>
-        <v>19845.6</v>
+        <v>15115.6</v>
       </c>
       <c r="C49" s="123">
         <f>C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C47+C48</f>
@@ -2718,7 +2737,7 @@
       </c>
       <c r="D49" s="123">
         <f>D35+D36+D37+D38+D39+D40+D41+D42+D43+D44+D45+D46+D47</f>
-        <v>77690.93</v>
+        <v>76396.93</v>
       </c>
       <c r="E49" s="123">
         <f>E35+E36+E37+E38+E39+E40+E41+E42+E43+E44+E45+E46+E47</f>
@@ -2726,7 +2745,7 @@
       </c>
       <c r="F49" s="123">
         <f>F35+F36+F37+F38+F39+F40+F41+F42+F43+F44+F45+F46+F47</f>
-        <v>26738.8</v>
+        <v>32898.8</v>
       </c>
       <c r="G49" s="123">
         <f>G35+G36+G37+G38+G39+G40+G41+G42+G43+G44+G45+G46+G47</f>
@@ -2742,7 +2761,7 @@
       </c>
       <c r="J49" s="123">
         <f>J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47</f>
-        <v>16496.2</v>
+        <v>16366.2</v>
       </c>
       <c r="K49" s="123">
         <f>K35+K36+K37+K38+K39+K40+K41+K42+K43+K44+K45+K46+K47</f>
@@ -2750,7 +2769,7 @@
       </c>
       <c r="L49" s="123">
         <f>L35+L36+L37+L38+L39+L40+L41+L42+L43+L44+L45+L46+L47</f>
-        <v>177452.24999999997</v>
+        <v>177458.24999999997</v>
       </c>
       <c r="M49" s="123">
         <f>M35+M36+M37+M38+M39+M40+M41+M42+M43+M44+M45+M46+M47</f>
@@ -2758,11 +2777,10 @@
       </c>
       <c r="N49" s="123">
         <f>N35+N36+N37+N38+N39+N40+N41+N42+N43+N44+N45+N46+N47</f>
-        <v>-19600</v>
+        <v>-14870</v>
       </c>
       <c r="O49" s="12" t="n"/>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="22" t="inlineStr">
         <is>
@@ -2880,7 +2898,6 @@
       </c>
       <c r="O53" s="12" t="n"/>
     </row>
-    <row r="54"/>
     <row r="55">
       <c r="A55" s="13" t="inlineStr">
         <is>
@@ -2889,7 +2906,7 @@
       </c>
       <c r="B55" s="122">
         <f>B24+B32+B49+B53</f>
-        <v>221990.87</v>
+        <v>213633.83</v>
       </c>
       <c r="C55" s="122">
         <f>C24+C32+C49+C53</f>
@@ -2897,15 +2914,15 @@
       </c>
       <c r="D55" s="122">
         <f>D24+D32+D49+D53</f>
-        <v>198743.93</v>
+        <v>201076.97</v>
       </c>
       <c r="E55" s="122">
         <f>E24+E32+E49+E53</f>
         <v>80029.05</v>
       </c>
       <c r="F55" s="122">
-        <f>F24+F32+F49+F53</f>
-        <v>53842.06</v>
+        <f>F24+F32+F49+F66</f>
+        <v>60002.060000000005</v>
       </c>
       <c r="G55" s="122">
         <f>G24+G32+G49+G53</f>
@@ -2921,7 +2938,7 @@
       </c>
       <c r="J55" s="122">
         <f>J24+J32+J49+J53</f>
-        <v>52780.92</v>
+        <v>52650.92</v>
       </c>
       <c r="K55" s="122">
         <f>K24+K32+K49+K53</f>
@@ -2929,7 +2946,7 @@
       </c>
       <c r="L55" s="122">
         <f>L24+L32+L49+L53</f>
-        <v>804950.3139999999</v>
+        <v>804956.3139999999</v>
       </c>
       <c r="M55" s="122">
         <f>M24+M32+M49+M53</f>
@@ -2937,11 +2954,10 @@
       </c>
       <c r="N55" s="122">
         <f>N24+N32+N49+N53</f>
-        <v>-82659.03999999998</v>
+        <v>-74301.99999999999</v>
       </c>
       <c r="O55" s="16" t="n"/>
     </row>
-    <row r="56"/>
     <row r="57">
       <c r="A57" s="13" t="inlineStr">
         <is>
@@ -2950,7 +2966,7 @@
       </c>
       <c r="B57" s="122">
         <f>B15-B55</f>
-        <v>-63016.32000000001</v>
+        <v>-79042.91</v>
       </c>
       <c r="C57" s="122">
         <f>C15-C55</f>
@@ -2958,15 +2974,15 @@
       </c>
       <c r="D57" s="122">
         <f>D15-D55</f>
-        <v>64394.76999999996</v>
+        <v>-58380.70000000001</v>
       </c>
       <c r="E57" s="122">
         <f>E15-E55</f>
         <v>63173.220000000016</v>
       </c>
       <c r="F57" s="122">
-        <f>F15-F55</f>
-        <v>36365.676666666666</v>
+        <f>F15-F68</f>
+        <v>234604.28666666668</v>
       </c>
       <c r="G57" s="122">
         <f>G15-G55</f>
@@ -2982,7 +2998,7 @@
       </c>
       <c r="J57" s="122">
         <f>J15-J55</f>
-        <v>-22281.86333333333</v>
+        <v>39819.21666666666</v>
       </c>
       <c r="K57" s="122">
         <f>K15-K55</f>
@@ -2990,7 +3006,7 @@
       </c>
       <c r="L57" s="122">
         <f>L15-L55</f>
-        <v>-249503.804</v>
+        <v>-187968.23400000005</v>
       </c>
       <c r="M57" s="122">
         <f>M15-M55</f>
@@ -2998,7 +3014,7 @@
       </c>
       <c r="N57" s="122">
         <f>N15-N55</f>
-        <v>63860.08999999998</v>
+        <v>79886.68</v>
       </c>
       <c r="O57" s="16" t="n"/>
     </row>
@@ -3010,7 +3026,7 @@
       </c>
       <c r="B58" s="125">
         <f>B10+B57</f>
-        <v>372138.68</v>
+        <v>356112.08999999997</v>
       </c>
       <c r="C58" s="125">
         <f>C10+C57</f>
@@ -3018,7 +3034,7 @@
       </c>
       <c r="D58" s="125">
         <f>D10+D57</f>
-        <v>423090.99999999994</v>
+        <v>300315.52999999997</v>
       </c>
       <c r="E58" s="125" t="str">
         <f>IF(E$8=1,E10+E57,"")</f>
@@ -3026,7 +3042,7 @@
       </c>
       <c r="F58" s="125">
         <f>F10+F57</f>
-        <v>459456.67666666664</v>
+        <v>534919.8166666667</v>
       </c>
       <c r="G58" s="125" t="str">
         <f>IF(G$8=1,G10+G57,"")</f>
@@ -3034,7 +3050,7 @@
       </c>
       <c r="H58" s="125">
         <f>H10+H57</f>
-        <v>194490.60933333333</v>
+        <v>269953.74933333334</v>
       </c>
       <c r="I58" s="125" t="str">
         <f>IF(I$8=1,I10+I57,"")</f>
@@ -3042,7 +3058,7 @@
       </c>
       <c r="J58" s="125">
         <f>J10+J57</f>
-        <v>172208.74599999998</v>
+        <v>309772.966</v>
       </c>
       <c r="K58" s="125" t="str">
         <f>IF(K$8=1,K10+K57,"")</f>
@@ -3050,7 +3066,7 @@
       </c>
       <c r="L58" s="125">
         <f>J58</f>
-        <v>172208.74599999998</v>
+        <v>309772.966</v>
       </c>
       <c r="M58" s="125">
         <f>IF(K$8=1,K58,IF(I$8=1,I58,IF(G$8=1,G58,IF(E$8=1,E58,IF(C$8=1,C58,"")))))</f>
@@ -3131,7 +3147,6 @@
         </is>
       </c>
     </row>
-    <row r="61"/>
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
@@ -3189,23 +3204,23 @@
       </c>
       <c r="B64" s="127">
         <f>IF(Payroll!$I$5=0,0,B58/(Payroll!$I$5/2))</f>
-        <v>7.475065884621565</v>
+        <v>7.153143379399003</v>
       </c>
       <c r="D64" s="127">
         <f>IF(Payroll!$I$5=0,0,D58/(Payroll!$I$5/2))</f>
-        <v>8.498533665434676</v>
+        <v>6.032370440302104</v>
       </c>
       <c r="F64" s="127">
         <f>IF(Payroll!$I$5=0,0,F58/(Payroll!$I$5/2))</f>
-        <v>9.229002825539665</v>
+        <v>10.744813929508812</v>
       </c>
       <c r="H64" s="127">
         <f>IF(Payroll!$I$5=0,0,H58/(Payroll!$I$5/2))</f>
-        <v>3.9066890835074184</v>
+        <v>5.422500187476565</v>
       </c>
       <c r="J64" s="127">
         <f>IF(Payroll!$I$5=0,0,J58/(Payroll!$I$5/2))</f>
-        <v>3.459118311103969</v>
+        <v>6.2223398280572075</v>
       </c>
       <c r="O64" s="108" t="n"/>
     </row>
@@ -3216,8 +3231,8 @@
         </is>
       </c>
       <c r="L65" s="120">
-        <f>SUMIFS(Receivables!$F$5:$F$52,Receivables!$H$5:$H$52,"&gt;"&amp;Assumptions!$C$48)</f>
-        <v>271658.62</v>
+        <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;"&amp;Assumptions!$C$48)</f>
+        <v>264323.60000000003</v>
       </c>
       <c r="O65" s="80" t="inlineStr">
         <is>
@@ -3241,7 +3256,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
@@ -3266,7 +3280,7 @@
     <row r="69" ht="15.75" customHeight="1" s="109">
       <c r="A69" s="110" t="inlineStr">
         <is>
-          <t>1. Aware Super $225,887 (INV-10596, due 9 Oct) is the big one. We're paying Complete AV materials $136,163 this week (30 Sep), ahead of it landing - if Aware slip, the held labour stays held and we watch the cheque account. Build-up on the Complete AV tab.</t>
+          <t>1. Aware Super $225,887 (INV-10596) is the big one - still not paid at 12 Oct and now expected 9 Nov, after this forecast. Complete AV materials $133,246 went out 29 Sep. If Aware slip again the held labour stays held and we watch the cheque account. Build-up on the Complete AV tab.</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3294,7 @@
     <row r="71" ht="15.75" customHeight="1" s="109">
       <c r="A71" s="110" t="inlineStr">
         <is>
-          <t>3. Ventia $58,025 is a month overdue and their other three ($36,677) are assumed 2-3 weeks late. PwC, Gen-e and Microsoft each have a month-old one too. Chase this week.</t>
+          <t>3. Ventia's $58,025 landed 29 Sep. Still chasing their other three ($36,677), Downer ($39,664 - both overdue), Gen-e, Microsoft and ON24 - all a month or more old. Chase this week.</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" style="109" min="1" max="1"/>
@@ -4578,7 +4592,7 @@
     <row r="2">
       <c r="A2" s="29" t="inlineStr">
         <is>
-          <t>Xero aged receivables at 28 Sep ($580,292.39, 38 invoices) plus the Sep contract invoices we still have to raise (from the repeating templates). Expected date (blue) is my call based on how each customer has been paying - change it and the forecast moves.</t>
+          <t>Xero aged receivables at 28 Sep ($580,292.39, 38 invoices) plus the Sep contract invoices we still have to raise (from the repeating templates). Expected date (blue) is my call based on how each customer has been paying - change it and the forecast moves. Updated 12 Oct: paid invoices are greyed out with the date they landed, the Sep contract invoices (raised 30 Sep) replace the "to be raised" rows, and the expected date has been moved on anything that has not come in.</t>
         </is>
       </c>
     </row>
@@ -4640,143 +4654,143 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="170" t="inlineStr">
         <is>
           <t>APT Management Services (APA)</t>
         </is>
       </c>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="170" t="inlineStr">
         <is>
           <t>INV-10622</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="170" t="inlineStr">
         <is>
           <t>PO-00030884</t>
         </is>
       </c>
-      <c r="D5" s="137" t="n">
+      <c r="D5" s="171" t="n">
         <v>46275</v>
       </c>
-      <c r="E5" s="137" t="n">
+      <c r="E5" s="171" t="n">
         <v>46305</v>
       </c>
-      <c r="F5" s="138" t="n">
+      <c r="F5" s="172" t="n">
         <v>4352.45</v>
       </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H5" s="137" t="n">
-        <v>46304</v>
-      </c>
-      <c r="I5" s="45">
+      <c r="G5" s="173" t="inlineStr">
+        <is>
+          <t>Paid 2 Oct</t>
+        </is>
+      </c>
+      <c r="H5" s="171" t="n">
+        <v>46297</v>
+      </c>
+      <c r="I5" s="174">
         <f>H5-E5</f>
-        <v>-1</v>
-      </c>
-      <c r="J5" s="18">
+        <v>-8</v>
+      </c>
+      <c r="J5" s="170">
         <f>IF(H5&lt;Assumptions!$B$5,"Before",IF(H5&gt;Assumptions!$C$48,"After",INT((H5-Assumptions!$B$5)/7)+1))</f>
+        <v>1</v>
+      </c>
+      <c r="K5" s="175" t="inlineStr">
+        <is>
+          <t>Paid 2 Oct - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="170" t="inlineStr">
+        <is>
+          <t>APT Management Services (APA)</t>
+        </is>
+      </c>
+      <c r="B6" s="170" t="inlineStr">
+        <is>
+          <t>INV-10628</t>
+        </is>
+      </c>
+      <c r="C6" s="170" t="inlineStr">
+        <is>
+          <t>APA RUOK Event 10.09.2026</t>
+        </is>
+      </c>
+      <c r="D6" s="171" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E6" s="171" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F6" s="172" t="n">
+        <v>627</v>
+      </c>
+      <c r="G6" s="173" t="inlineStr">
+        <is>
+          <t>Paid 7 Oct</t>
+        </is>
+      </c>
+      <c r="H6" s="171" t="n">
+        <v>46302</v>
+      </c>
+      <c r="I6" s="174">
+        <f>H6-E6</f>
+        <v>-9</v>
+      </c>
+      <c r="J6" s="170">
+        <f>IF(H6&lt;Assumptions!$B$5,"Before",IF(H6&gt;Assumptions!$C$48,"After",INT((H6-Assumptions!$B$5)/7)+1))</f>
         <v>2</v>
       </c>
-      <c r="K5" s="115" t="inlineStr">
-        <is>
-          <t>APA paid the last one the day after we sent it</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="18" t="inlineStr">
-        <is>
-          <t>APT Management Services (APA)</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="inlineStr">
-        <is>
-          <t>INV-10628</t>
-        </is>
-      </c>
-      <c r="C6" s="18" t="inlineStr">
-        <is>
-          <t>APA RUOK Event 10.09.2026</t>
-        </is>
-      </c>
-      <c r="D6" s="137" t="n">
-        <v>46281</v>
-      </c>
-      <c r="E6" s="137" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F6" s="138" t="n">
-        <v>627</v>
-      </c>
-      <c r="G6" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H6" s="137" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I6" s="45">
-        <f>H6-E6</f>
-        <v>0</v>
-      </c>
-      <c r="J6" s="18">
-        <f>IF(H6&lt;Assumptions!$B$5,"Before",IF(H6&gt;Assumptions!$C$48,"After",INT((H6-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="K6" s="115" t="inlineStr">
-        <is>
-          <t>On the due date</t>
+      <c r="K6" s="175" t="inlineStr">
+        <is>
+          <t>Paid 7 Oct - in the bank, in the actuals.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="170" t="inlineStr">
         <is>
           <t>ASX Operations</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="170" t="inlineStr">
         <is>
           <t>INV-10599</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="170" t="inlineStr">
         <is>
           <t>ASX Employee Town Hall 13.08.2026</t>
         </is>
       </c>
-      <c r="D7" s="137" t="n">
+      <c r="D7" s="171" t="n">
         <v>46261</v>
       </c>
-      <c r="E7" s="137" t="n">
+      <c r="E7" s="171" t="n">
         <v>46291</v>
       </c>
-      <c r="F7" s="138" t="n">
+      <c r="F7" s="172" t="n">
         <v>1661</v>
       </c>
-      <c r="G7" s="33" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H7" s="137" t="n">
-        <v>46297</v>
-      </c>
-      <c r="I7" s="45">
+      <c r="G7" s="173" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct</t>
+        </is>
+      </c>
+      <c r="H7" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="I7" s="174">
         <f>H7-E7</f>
-        <v>6</v>
-      </c>
-      <c r="J7" s="18">
+        <v>12</v>
+      </c>
+      <c r="J7" s="170">
         <f>IF(H7&lt;Assumptions!$B$5,"Before",IF(H7&gt;Assumptions!$C$48,"After",INT((H7-Assumptions!$B$5)/7)+1))</f>
-        <v>1</v>
-      </c>
-      <c r="K7" s="115" t="inlineStr">
-        <is>
-          <t>ASX paid the Aug ones ~4 days late</t>
+        <v>2</v>
+      </c>
+      <c r="K7" s="175" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct - in the bank, in the actuals.</t>
         </is>
       </c>
     </row>
@@ -4875,49 +4889,49 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="170" t="inlineStr">
         <is>
           <t>Australian Payments Network</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="170" t="inlineStr">
         <is>
           <t>INV-10574</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="170" t="inlineStr">
         <is>
           <t>Logitech room licence renewal</t>
         </is>
       </c>
-      <c r="D10" s="137" t="n">
+      <c r="D10" s="171" t="n">
         <v>46254</v>
       </c>
-      <c r="E10" s="137" t="n">
+      <c r="E10" s="171" t="n">
         <v>46284</v>
       </c>
-      <c r="F10" s="138" t="n">
+      <c r="F10" s="172" t="n">
         <v>1092.3</v>
       </c>
-      <c r="G10" s="33" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H10" s="137" t="n">
-        <v>46297</v>
-      </c>
-      <c r="I10" s="45">
+      <c r="G10" s="173" t="inlineStr">
+        <is>
+          <t>Paid 30 Sep</t>
+        </is>
+      </c>
+      <c r="H10" s="171" t="n">
+        <v>46295</v>
+      </c>
+      <c r="I10" s="174">
         <f>H10-E10</f>
-        <v>13</v>
-      </c>
-      <c r="J10" s="18">
+        <v>11</v>
+      </c>
+      <c r="J10" s="170">
         <f>IF(H10&lt;Assumptions!$B$5,"Before",IF(H10&gt;Assumptions!$C$48,"After",INT((H10-Assumptions!$B$5)/7)+1))</f>
         <v>1</v>
       </c>
-      <c r="K10" s="115" t="inlineStr">
-        <is>
-          <t>Small and overdue - chase this week</t>
+      <c r="K10" s="175" t="inlineStr">
+        <is>
+          <t>Paid 30 Sep - in the bank, in the actuals.</t>
         </is>
       </c>
     </row>
@@ -4948,23 +4962,23 @@
       </c>
       <c r="G11" s="33" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H11" s="137" t="n">
-        <v>46295</v>
+        <v>46311</v>
       </c>
       <c r="I11" s="45">
         <f>H11-E11</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="J11" s="18">
         <f>IF(H11&lt;Assumptions!$B$5,"Before",IF(H11&gt;Assumptions!$C$48,"After",INT((H11-Assumptions!$B$5)/7)+1))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" s="115" t="inlineStr">
         <is>
-          <t>Aware pay on the due date</t>
+          <t>Still unpaid at 12 Oct (due 30 Sep). Aware usually pay on the due date - call it Fri 16 Oct and chase with the big one.</t>
         </is>
       </c>
     </row>
@@ -5187,19 +5201,19 @@
         </is>
       </c>
       <c r="H16" s="137" t="n">
-        <v>46297</v>
+        <v>46311</v>
       </c>
       <c r="I16" s="45">
         <f>H16-E16</f>
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="J16" s="18">
         <f>IF(H16&lt;Assumptions!$B$5,"Before",IF(H16&gt;Assumptions!$C$48,"After",INT((H16-Assumptions!$B$5)/7)+1))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K16" s="115" t="inlineStr">
         <is>
-          <t>4 days overdue - should land this week</t>
+          <t>Still not in at 12 Oct - chase. Fri 16 Oct.</t>
         </is>
       </c>
     </row>
@@ -5230,23 +5244,23 @@
       </c>
       <c r="G17" s="33" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Overdue</t>
         </is>
       </c>
       <c r="H17" s="137" t="n">
-        <v>46302</v>
+        <v>46311</v>
       </c>
       <c r="I17" s="45">
         <f>H17-E17</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="J17" s="18">
         <f>IF(H17&lt;Assumptions!$B$5,"Before",IF(H17&gt;Assumptions!$C$48,"After",INT((H17-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K17" s="115" t="inlineStr">
         <is>
-          <t>Due 30 Sep, give it a week</t>
+          <t>Still not in at 12 Oct - chase with the other one. Fri 16 Oct.</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5287,7 @@
         <v>46264</v>
       </c>
       <c r="F18" s="138" t="n">
-        <v>13627.68</v>
+        <v>11850.16</v>
       </c>
       <c r="G18" s="33" t="inlineStr">
         <is>
@@ -5281,19 +5295,19 @@
         </is>
       </c>
       <c r="H18" s="137" t="n">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="I18" s="45">
         <f>H18-E18</f>
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J18" s="18">
         <f>IF(H18&lt;Assumptions!$B$5,"Before",IF(H18&gt;Assumptions!$C$48,"After",INT((H18-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18" s="115" t="inlineStr">
         <is>
-          <t>A month overdue - chase. Week 2.</t>
+          <t>Six weeks overdue at 12 Oct. Xero shows $11,850.16 left on this one (a $1,777.52 credit has been applied), so the three Gen-e invoices total $39,106. Chase. Week 3.</t>
         </is>
       </c>
     </row>
@@ -5345,96 +5359,96 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="170" t="inlineStr">
         <is>
           <t>ICC Sydney</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="170" t="inlineStr">
         <is>
           <t>INV-10630</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="170" t="inlineStr">
         <is>
           <t>Speaker presentation technicians - ICAS 2026</t>
         </is>
       </c>
-      <c r="D20" s="137" t="n">
+      <c r="D20" s="171" t="n">
         <v>46281</v>
       </c>
-      <c r="E20" s="137" t="n">
+      <c r="E20" s="171" t="n">
         <v>46311</v>
       </c>
-      <c r="F20" s="138" t="n">
+      <c r="F20" s="172" t="n">
         <v>1040.88</v>
       </c>
-      <c r="G20" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H20" s="137" t="n">
+      <c r="G20" s="173" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep</t>
+        </is>
+      </c>
+      <c r="H20" s="171" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I20" s="174">
+        <f>H20-E20</f>
+        <v>-17</v>
+      </c>
+      <c r="J20" s="170">
+        <f>IF(H20&lt;Assumptions!$B$5,"Before",IF(H20&gt;Assumptions!$C$48,"After",INT((H20-Assumptions!$B$5)/7)+1))</f>
+        <v>1</v>
+      </c>
+      <c r="K20" s="175" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="170" t="inlineStr">
+        <is>
+          <t>ICC Sydney</t>
+        </is>
+      </c>
+      <c r="B21" s="170" t="inlineStr">
+        <is>
+          <t>INV-10633</t>
+        </is>
+      </c>
+      <c r="C21" s="170" t="inlineStr">
+        <is>
+          <t>Speaker presentation technicians - ISE</t>
+        </is>
+      </c>
+      <c r="D21" s="171" t="n">
+        <v>46281</v>
+      </c>
+      <c r="E21" s="171" t="n">
         <v>46311</v>
       </c>
-      <c r="I20" s="45">
-        <f>H20-E20</f>
-        <v>0</v>
-      </c>
-      <c r="J20" s="18">
-        <f>IF(H20&lt;Assumptions!$B$5,"Before",IF(H20&gt;Assumptions!$C$48,"After",INT((H20-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="K20" s="115" t="inlineStr">
-        <is>
-          <t>On the due date</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="inlineStr">
-        <is>
-          <t>ICC Sydney</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>INV-10633</t>
-        </is>
-      </c>
-      <c r="C21" s="18" t="inlineStr">
-        <is>
-          <t>Speaker presentation technicians - ISE</t>
-        </is>
-      </c>
-      <c r="D21" s="137" t="n">
-        <v>46281</v>
-      </c>
-      <c r="E21" s="137" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F21" s="138" t="n">
+      <c r="F21" s="172" t="n">
         <v>5131.51</v>
       </c>
-      <c r="G21" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H21" s="137" t="n">
-        <v>46311</v>
-      </c>
-      <c r="I21" s="45">
+      <c r="G21" s="173" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep</t>
+        </is>
+      </c>
+      <c r="H21" s="171" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I21" s="174">
         <f>H21-E21</f>
-        <v>0</v>
-      </c>
-      <c r="J21" s="18">
+        <v>-17</v>
+      </c>
+      <c r="J21" s="170">
         <f>IF(H21&lt;Assumptions!$B$5,"Before",IF(H21&gt;Assumptions!$C$48,"After",INT((H21-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="K21" s="115" t="inlineStr">
-        <is>
-          <t>On the due date</t>
+        <v>1</v>
+      </c>
+      <c r="K21" s="175" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep - in the bank, in the actuals.</t>
         </is>
       </c>
     </row>
@@ -5465,23 +5479,23 @@
       </c>
       <c r="G22" s="33" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Open</t>
         </is>
       </c>
       <c r="H22" s="137" t="n">
-        <v>46301</v>
+        <v>46325</v>
       </c>
       <c r="I22" s="45">
         <f>H22-E22</f>
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="J22" s="18">
         <f>IF(H22&lt;Assumptions!$B$5,"Before",IF(H22&gt;Assumptions!$C$48,"After",INT((H22-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K22" s="115" t="inlineStr">
         <is>
-          <t>Staff recovery - probably through payroll</t>
+          <t>Staff recovery - goes through payroll, no cash. Pushed to end of month.</t>
         </is>
       </c>
     </row>
@@ -5563,19 +5577,19 @@
         </is>
       </c>
       <c r="H24" s="137" t="n">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="I24" s="45">
         <f>H24-E24</f>
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J24" s="18">
         <f>IF(H24&lt;Assumptions!$B$5,"Before",IF(H24&gt;Assumptions!$C$48,"After",INT((H24-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K24" s="115" t="inlineStr">
         <is>
-          <t>A month overdue - usually a PO / portal issue. Week 2.</t>
+          <t>Six weeks overdue at 12 Oct - usually a PO / portal issue. Week 3.</t>
         </is>
       </c>
     </row>
@@ -5610,19 +5624,19 @@
         </is>
       </c>
       <c r="H25" s="137" t="n">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="I25" s="45">
         <f>H25-E25</f>
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="J25" s="18">
         <f>IF(H25&lt;Assumptions!$B$5,"Before",IF(H25&gt;Assumptions!$C$48,"After",INT((H25-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K25" s="115" t="inlineStr">
         <is>
-          <t>A month overdue - chase</t>
+          <t>Six weeks overdue at 12 Oct - chase. Week 3.</t>
         </is>
       </c>
     </row>
@@ -5657,19 +5671,19 @@
         </is>
       </c>
       <c r="H26" s="137" t="n">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="I26" s="45">
         <f>H26-E26</f>
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J26" s="18">
         <f>IF(H26&lt;Assumptions!$B$5,"Before",IF(H26&gt;Assumptions!$C$48,"After",INT((H26-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K26" s="115" t="inlineStr">
         <is>
-          <t>Assume it comes with the July one</t>
+          <t>Assume it comes with the Aug one. Week 3.</t>
         </is>
       </c>
     </row>
@@ -5721,378 +5735,378 @@
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" s="109">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="170" t="inlineStr">
         <is>
           <t>PwC Services</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="170" t="inlineStr">
         <is>
           <t>INV-10535</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="170" t="inlineStr">
         <is>
           <t>PO2601702104 (Jul)</t>
         </is>
       </c>
-      <c r="D28" s="137" t="n">
+      <c r="D28" s="171" t="n">
         <v>46234</v>
       </c>
-      <c r="E28" s="137" t="n">
+      <c r="E28" s="171" t="n">
         <v>46264</v>
       </c>
-      <c r="F28" s="138" t="n">
+      <c r="F28" s="172" t="n">
         <v>13097.7</v>
       </c>
-      <c r="G28" s="33" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H28" s="137" t="n">
-        <v>46302</v>
-      </c>
-      <c r="I28" s="45">
+      <c r="G28" s="173" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep</t>
+        </is>
+      </c>
+      <c r="H28" s="171" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I28" s="174">
         <f>H28-E28</f>
-        <v>38</v>
-      </c>
-      <c r="J28" s="18">
+        <v>30</v>
+      </c>
+      <c r="J28" s="170">
         <f>IF(H28&lt;Assumptions!$B$5,"Before",IF(H28&gt;Assumptions!$C$48,"After",INT((H28-Assumptions!$B$5)/7)+1))</f>
+        <v>1</v>
+      </c>
+      <c r="K28" s="175" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="170" t="inlineStr">
+        <is>
+          <t>PwC Services</t>
+        </is>
+      </c>
+      <c r="B29" s="170" t="inlineStr">
+        <is>
+          <t>INV-10531</t>
+        </is>
+      </c>
+      <c r="C29" s="170" t="inlineStr">
+        <is>
+          <t>PO2601702371 (Jul)</t>
+        </is>
+      </c>
+      <c r="D29" s="171" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E29" s="171" t="n">
+        <v>46264</v>
+      </c>
+      <c r="F29" s="172" t="n">
+        <v>7865</v>
+      </c>
+      <c r="G29" s="173" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep</t>
+        </is>
+      </c>
+      <c r="H29" s="171" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I29" s="174">
+        <f>H29-E29</f>
+        <v>30</v>
+      </c>
+      <c r="J29" s="170">
+        <f>IF(H29&lt;Assumptions!$B$5,"Before",IF(H29&gt;Assumptions!$C$48,"After",INT((H29-Assumptions!$B$5)/7)+1))</f>
+        <v>1</v>
+      </c>
+      <c r="K29" s="175" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="170" t="inlineStr">
+        <is>
+          <t>PwC Services</t>
+        </is>
+      </c>
+      <c r="B30" s="170" t="inlineStr">
+        <is>
+          <t>INV-10598</t>
+        </is>
+      </c>
+      <c r="C30" s="170" t="inlineStr">
+        <is>
+          <t>PO2601703509</t>
+        </is>
+      </c>
+      <c r="D30" s="171" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E30" s="171" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F30" s="172" t="n">
+        <v>9350</v>
+      </c>
+      <c r="G30" s="173" t="inlineStr">
+        <is>
+          <t>Paid 6 Oct</t>
+        </is>
+      </c>
+      <c r="H30" s="171" t="n">
+        <v>46301</v>
+      </c>
+      <c r="I30" s="174">
+        <f>H30-E30</f>
+        <v>6</v>
+      </c>
+      <c r="J30" s="170">
+        <f>IF(H30&lt;Assumptions!$B$5,"Before",IF(H30&gt;Assumptions!$C$48,"After",INT((H30-Assumptions!$B$5)/7)+1))</f>
         <v>2</v>
       </c>
-      <c r="K28" s="115" t="inlineStr">
-        <is>
-          <t>A month overdue. PwC paid INV-10577 on the day, so these two look like PO issues - chase</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="K30" s="175" t="inlineStr">
+        <is>
+          <t>Paid 6 Oct - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="170" t="inlineStr">
         <is>
           <t>PwC Services</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>INV-10531</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>PO2601702371 (Jul)</t>
-        </is>
-      </c>
-      <c r="D29" s="137" t="n">
-        <v>46234</v>
-      </c>
-      <c r="E29" s="137" t="n">
-        <v>46264</v>
-      </c>
-      <c r="F29" s="138" t="n">
+      <c r="B31" s="170" t="inlineStr">
+        <is>
+          <t>INV-10572</t>
+        </is>
+      </c>
+      <c r="C31" s="170" t="inlineStr">
+        <is>
+          <t>PO2601702371 (Aug)</t>
+        </is>
+      </c>
+      <c r="D31" s="171" t="n">
+        <v>46265</v>
+      </c>
+      <c r="E31" s="171" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F31" s="172" t="n">
         <v>7865</v>
       </c>
-      <c r="G29" s="33" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H29" s="137" t="n">
-        <v>46302</v>
-      </c>
-      <c r="I29" s="45">
-        <f>H29-E29</f>
-        <v>38</v>
-      </c>
-      <c r="J29" s="18">
-        <f>IF(H29&lt;Assumptions!$B$5,"Before",IF(H29&gt;Assumptions!$C$48,"After",INT((H29-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
-      </c>
-      <c r="K29" s="115" t="inlineStr">
-        <is>
-          <t>Same</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="G31" s="173" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep</t>
+        </is>
+      </c>
+      <c r="H31" s="171" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I31" s="174">
+        <f>H31-E31</f>
+        <v>-1</v>
+      </c>
+      <c r="J31" s="170">
+        <f>IF(H31&lt;Assumptions!$B$5,"Before",IF(H31&gt;Assumptions!$C$48,"After",INT((H31-Assumptions!$B$5)/7)+1))</f>
+        <v>1</v>
+      </c>
+      <c r="K31" s="175" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="170" t="inlineStr">
         <is>
           <t>PwC Services</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>INV-10598</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="inlineStr">
-        <is>
-          <t>PO2601703509</t>
-        </is>
-      </c>
-      <c r="D30" s="137" t="n">
+      <c r="B32" s="170" t="inlineStr">
+        <is>
+          <t>INV-10585</t>
+        </is>
+      </c>
+      <c r="C32" s="170" t="inlineStr">
+        <is>
+          <t>PO2601702104 (Aug)</t>
+        </is>
+      </c>
+      <c r="D32" s="171" t="n">
         <v>46265</v>
       </c>
-      <c r="E30" s="137" t="n">
+      <c r="E32" s="171" t="n">
         <v>46295</v>
       </c>
-      <c r="F30" s="138" t="n">
-        <v>9350</v>
-      </c>
-      <c r="G30" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H30" s="137" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I30" s="45">
-        <f>H30-E30</f>
-        <v>14</v>
-      </c>
-      <c r="J30" s="18">
-        <f>IF(H30&lt;Assumptions!$B$5,"Before",IF(H30&gt;Assumptions!$C$48,"After",INT((H30-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="K30" s="115" t="inlineStr">
-        <is>
-          <t>Give it two weeks after due</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>PwC Services</t>
-        </is>
-      </c>
-      <c r="B31" s="18" t="inlineStr">
-        <is>
-          <t>INV-10572</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="inlineStr">
-        <is>
-          <t>PO2601702371 (Aug)</t>
-        </is>
-      </c>
-      <c r="D31" s="137" t="n">
+      <c r="F32" s="172" t="n">
+        <v>13097.7</v>
+      </c>
+      <c r="G32" s="173" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep</t>
+        </is>
+      </c>
+      <c r="H32" s="171" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I32" s="174">
+        <f>H32-E32</f>
+        <v>-1</v>
+      </c>
+      <c r="J32" s="170">
+        <f>IF(H32&lt;Assumptions!$B$5,"Before",IF(H32&gt;Assumptions!$C$48,"After",INT((H32-Assumptions!$B$5)/7)+1))</f>
+        <v>1</v>
+      </c>
+      <c r="K32" s="175" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="170" t="inlineStr">
+        <is>
+          <t>Ricoh Australia</t>
+        </is>
+      </c>
+      <c r="B33" s="170" t="inlineStr">
+        <is>
+          <t>INV-10618</t>
+        </is>
+      </c>
+      <c r="C33" s="170" t="inlineStr">
+        <is>
+          <t>CONTRACT (Aug)</t>
+        </is>
+      </c>
+      <c r="D33" s="171" t="n">
         <v>46265</v>
       </c>
-      <c r="E31" s="137" t="n">
+      <c r="E33" s="171" t="n">
         <v>46295</v>
       </c>
-      <c r="F31" s="138" t="n">
-        <v>7865</v>
-      </c>
-      <c r="G31" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H31" s="137" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I31" s="45">
-        <f>H31-E31</f>
-        <v>14</v>
-      </c>
-      <c r="J31" s="18">
-        <f>IF(H31&lt;Assumptions!$B$5,"Before",IF(H31&gt;Assumptions!$C$48,"After",INT((H31-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="K31" s="115" t="inlineStr">
-        <is>
-          <t>Give it two weeks after due</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>PwC Services</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>INV-10585</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="inlineStr">
-        <is>
-          <t>PO2601702104 (Aug)</t>
-        </is>
-      </c>
-      <c r="D32" s="137" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E32" s="137" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F32" s="138" t="n">
-        <v>13097.7</v>
-      </c>
-      <c r="G32" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H32" s="137" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I32" s="45">
-        <f>H32-E32</f>
-        <v>14</v>
-      </c>
-      <c r="J32" s="18">
-        <f>IF(H32&lt;Assumptions!$B$5,"Before",IF(H32&gt;Assumptions!$C$48,"After",INT((H32-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="K32" s="115" t="inlineStr">
-        <is>
-          <t>Give it two weeks after due</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="F33" s="172" t="n">
+        <v>13046.62</v>
+      </c>
+      <c r="G33" s="173" t="inlineStr">
+        <is>
+          <t>Paid 1 Oct</t>
+        </is>
+      </c>
+      <c r="H33" s="171" t="n">
+        <v>46296</v>
+      </c>
+      <c r="I33" s="174">
+        <f>H33-E33</f>
+        <v>1</v>
+      </c>
+      <c r="J33" s="170">
+        <f>IF(H33&lt;Assumptions!$B$5,"Before",IF(H33&gt;Assumptions!$C$48,"After",INT((H33-Assumptions!$B$5)/7)+1))</f>
+        <v>1</v>
+      </c>
+      <c r="K33" s="175" t="inlineStr">
+        <is>
+          <t>Paid 1 Oct - in the bank, in the actuals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="170" t="inlineStr">
         <is>
           <t>Ricoh Australia</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>INV-10618</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="inlineStr">
-        <is>
-          <t>CONTRACT (Aug)</t>
-        </is>
-      </c>
-      <c r="D33" s="137" t="n">
-        <v>46265</v>
-      </c>
-      <c r="E33" s="137" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F33" s="138" t="n">
-        <v>13046.62</v>
-      </c>
-      <c r="G33" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H33" s="137" t="n">
-        <v>46302</v>
-      </c>
-      <c r="I33" s="45">
-        <f>H33-E33</f>
-        <v>7</v>
-      </c>
-      <c r="J33" s="18">
-        <f>IF(H33&lt;Assumptions!$B$5,"Before",IF(H33&gt;Assumptions!$C$48,"After",INT((H33-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
-      </c>
-      <c r="K33" s="115" t="inlineStr">
-        <is>
-          <t>Give it a week</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="18" t="inlineStr">
-        <is>
-          <t>Ricoh Australia</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="170" t="inlineStr">
         <is>
           <t>INV-10620</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="170" t="inlineStr">
         <is>
           <t>SHELL AV Support</t>
         </is>
       </c>
-      <c r="D34" s="137" t="n">
+      <c r="D34" s="171" t="n">
         <v>46268</v>
       </c>
-      <c r="E34" s="137" t="n">
+      <c r="E34" s="171" t="n">
         <v>46298</v>
       </c>
-      <c r="F34" s="138" t="n">
+      <c r="F34" s="172" t="n">
         <v>374</v>
       </c>
-      <c r="G34" s="33" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="H34" s="137" t="n">
-        <v>46302</v>
-      </c>
-      <c r="I34" s="45">
+      <c r="G34" s="173" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct</t>
+        </is>
+      </c>
+      <c r="H34" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="I34" s="174">
         <f>H34-E34</f>
-        <v>4</v>
-      </c>
-      <c r="J34" s="18">
+        <v>5</v>
+      </c>
+      <c r="J34" s="170">
         <f>IF(H34&lt;Assumptions!$B$5,"Before",IF(H34&gt;Assumptions!$C$48,"After",INT((H34-Assumptions!$B$5)/7)+1))</f>
         <v>2</v>
       </c>
-      <c r="K34" s="115" t="inlineStr">
-        <is>
-          <t>Give it a week</t>
+      <c r="K34" s="175" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct - in the bank, in the actuals.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="170" t="inlineStr">
         <is>
           <t>The CEO Institute</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="170" t="inlineStr">
         <is>
           <t>INV-10581</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="170" t="inlineStr">
         <is>
           <t>CEO Connect 2026 11.8.26</t>
         </is>
       </c>
-      <c r="D35" s="137" t="n">
+      <c r="D35" s="171" t="n">
         <v>46255</v>
       </c>
-      <c r="E35" s="137" t="n">
+      <c r="E35" s="171" t="n">
         <v>46285</v>
       </c>
-      <c r="F35" s="138" t="n">
+      <c r="F35" s="172" t="n">
         <v>9086.389999999999</v>
       </c>
-      <c r="G35" s="33" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H35" s="137" t="n">
-        <v>46297</v>
-      </c>
-      <c r="I35" s="45">
+      <c r="G35" s="173" t="inlineStr">
+        <is>
+          <t>Paid 9 Oct</t>
+        </is>
+      </c>
+      <c r="H35" s="171" t="n">
+        <v>46304</v>
+      </c>
+      <c r="I35" s="174">
         <f>H35-E35</f>
-        <v>12</v>
-      </c>
-      <c r="J35" s="18">
+        <v>19</v>
+      </c>
+      <c r="J35" s="170">
         <f>IF(H35&lt;Assumptions!$B$5,"Before",IF(H35&gt;Assumptions!$C$48,"After",INT((H35-Assumptions!$B$5)/7)+1))</f>
-        <v>1</v>
-      </c>
-      <c r="K35" s="115" t="inlineStr">
-        <is>
-          <t>8 days overdue - this week</t>
+        <v>2</v>
+      </c>
+      <c r="K35" s="175" t="inlineStr">
+        <is>
+          <t>Paid 9 Oct - in the bank, in the actuals.</t>
         </is>
       </c>
     </row>
@@ -6144,49 +6158,49 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="170" t="inlineStr">
         <is>
           <t>Ventia</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="170" t="inlineStr">
         <is>
           <t>INV-10557</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="170" t="inlineStr">
         <is>
           <t>Ventia Awards 29-30.7.2026 (PO4701355678)</t>
         </is>
       </c>
-      <c r="D37" s="137" t="n">
+      <c r="D37" s="171" t="n">
         <v>46234</v>
       </c>
-      <c r="E37" s="137" t="n">
+      <c r="E37" s="171" t="n">
         <v>46264</v>
       </c>
-      <c r="F37" s="138" t="n">
+      <c r="F37" s="172" t="n">
         <v>58024.76</v>
       </c>
-      <c r="G37" s="33" t="inlineStr">
-        <is>
-          <t>Overdue</t>
-        </is>
-      </c>
-      <c r="H37" s="141" t="n">
-        <v>46304</v>
-      </c>
-      <c r="I37" s="45">
+      <c r="G37" s="173" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep</t>
+        </is>
+      </c>
+      <c r="H37" s="171" t="n">
+        <v>46294</v>
+      </c>
+      <c r="I37" s="174">
         <f>H37-E37</f>
-        <v>40</v>
-      </c>
-      <c r="J37" s="18">
+        <v>30</v>
+      </c>
+      <c r="J37" s="170">
         <f>IF(H37&lt;Assumptions!$B$5,"Before",IF(H37&gt;Assumptions!$C$48,"After",INT((H37-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
-      </c>
-      <c r="K37" s="115" t="inlineStr">
-        <is>
-          <t>BIGGEST OVERDUE - a month late. Chase now. Week 2.</t>
+        <v>1</v>
+      </c>
+      <c r="K37" s="175" t="inlineStr">
+        <is>
+          <t>Paid 29 Sep - in the bank, in the actuals.</t>
         </is>
       </c>
     </row>
@@ -6362,19 +6376,19 @@
         </is>
       </c>
       <c r="H41" s="137" t="n">
-        <v>46297</v>
+        <v>46311</v>
       </c>
       <c r="I41" s="45">
         <f>H41-E41</f>
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="J41" s="18">
         <f>IF(H41&lt;Assumptions!$B$5,"Before",IF(H41&gt;Assumptions!$C$48,"After",INT((H41-Assumptions!$B$5)/7)+1))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K41" s="115" t="inlineStr">
         <is>
-          <t>2 days overdue - this week</t>
+          <t>Still not in at 12 Oct - chase. Fri 16 Oct.</t>
         </is>
       </c>
     </row>
@@ -6426,113 +6440,113 @@
       </c>
     </row>
     <row r="43" ht="24" customHeight="1" s="109">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="170" t="inlineStr">
         <is>
           <t>Deloitte Services Trust</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>TBR</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="inlineStr">
-        <is>
-          <t>CONTRACT - September technicians</t>
-        </is>
-      </c>
-      <c r="D43" s="137" t="n">
+      <c r="B43" s="170" t="inlineStr">
+        <is>
+          <t>INV-10638</t>
+        </is>
+      </c>
+      <c r="C43" s="170" t="inlineStr">
+        <is>
+          <t>DTTL Sep contract (PO) - raised 30 Sep</t>
+        </is>
+      </c>
+      <c r="D43" s="171" t="n">
         <v>46295</v>
       </c>
-      <c r="E43" s="137" t="n">
+      <c r="E43" s="171" t="n">
         <v>46325</v>
       </c>
-      <c r="F43" s="138" t="n">
-        <v>113987.99</v>
-      </c>
-      <c r="G43" s="33" t="inlineStr">
-        <is>
-          <t>To be raised</t>
-        </is>
-      </c>
-      <c r="H43" s="141" t="n">
-        <v>46309</v>
-      </c>
-      <c r="I43" s="45">
+      <c r="F43" s="172" t="n">
+        <v>112683.22</v>
+      </c>
+      <c r="G43" s="173" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct</t>
+        </is>
+      </c>
+      <c r="H43" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="I43" s="174">
         <f>H43-E43</f>
-        <v>-16</v>
-      </c>
-      <c r="J43" s="18">
+        <v>-22</v>
+      </c>
+      <c r="J43" s="170">
         <f>IF(H43&lt;Assumptions!$B$5,"Before",IF(H43&gt;Assumptions!$C$48,"After",INT((H43-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="K43" s="115" t="inlineStr">
-        <is>
-          <t>Aug invoice (31 Aug) paid 14 Sep - Deloitte pay ~2 weeks after we invoice. Template $113,987.99 a month</t>
+        <v>2</v>
+      </c>
+      <c r="K43" s="175" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct - Deloitte pay about a week after we invoice.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
-        <is>
-          <t>Commonwealth Bank (CBA Place South)</t>
-        </is>
-      </c>
-      <c r="B44" s="18" t="inlineStr">
-        <is>
-          <t>TBR</t>
-        </is>
-      </c>
-      <c r="C44" s="18" t="inlineStr">
-        <is>
-          <t>85720001CBPSCSJUN27 - September</t>
-        </is>
-      </c>
-      <c r="D44" s="137" t="n">
+      <c r="A44" s="170" t="inlineStr">
+        <is>
+          <t>Deloitte Services Trust</t>
+        </is>
+      </c>
+      <c r="B44" s="170" t="inlineStr">
+        <is>
+          <t>INV-10665</t>
+        </is>
+      </c>
+      <c r="C44" s="170" t="inlineStr">
+        <is>
+          <t>DTTL Sep additionals - raised 30 Sep</t>
+        </is>
+      </c>
+      <c r="D44" s="171" t="n">
         <v>46295</v>
       </c>
-      <c r="E44" s="137" t="n">
+      <c r="E44" s="171" t="n">
         <v>46325</v>
       </c>
-      <c r="F44" s="138" t="n">
-        <v>24978.8</v>
-      </c>
-      <c r="G44" s="33" t="inlineStr">
-        <is>
-          <t>To be raised</t>
-        </is>
-      </c>
-      <c r="H44" s="137" t="n">
+      <c r="F44" s="172" t="n">
+        <v>18891.66</v>
+      </c>
+      <c r="G44" s="173" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct</t>
+        </is>
+      </c>
+      <c r="H44" s="171" t="n">
         <v>46303</v>
       </c>
-      <c r="I44" s="45">
+      <c r="I44" s="174">
         <f>H44-E44</f>
         <v>-22</v>
       </c>
-      <c r="J44" s="18">
+      <c r="J44" s="170">
         <f>IF(H44&lt;Assumptions!$B$5,"Before",IF(H44&gt;Assumptions!$C$48,"After",INT((H44-Assumptions!$B$5)/7)+1))</f>
         <v>2</v>
       </c>
-      <c r="K44" s="115" t="inlineStr">
-        <is>
-          <t>Aug invoices (31 Aug) paid 8 Sep - CBA pay ~8 days after invoice</t>
+      <c r="K44" s="175" t="inlineStr">
+        <is>
+          <t>Paid 8 Oct with the contract one.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
         <is>
-          <t>Commonwealth Bank (CBA Square)</t>
+          <t>Commonwealth Bank (CBA Place South)</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10643</t>
         </is>
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>85720001CBSCSJUN27 - September</t>
+          <t>85720001CBPSCSJUN27 - Sep contract</t>
         </is>
       </c>
       <c r="D45" s="137" t="n">
@@ -6542,44 +6556,44 @@
         <v>46325</v>
       </c>
       <c r="F45" s="138" t="n">
-        <v>11792</v>
+        <v>24619.84</v>
       </c>
       <c r="G45" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H45" s="137" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="I45" s="45">
         <f>H45-E45</f>
-        <v>-22</v>
+        <v>-14</v>
       </c>
       <c r="J45" s="18">
         <f>IF(H45&lt;Assumptions!$B$5,"Before",IF(H45&gt;Assumptions!$C$48,"After",INT((H45-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K45" s="115" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>Aug one was paid 8 days after invoice. Not in yet at 12 Oct - call it Fri 16 Oct.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
         <is>
-          <t>Commonwealth Bank (CBA Melbourne)</t>
+          <t>Commonwealth Bank (CBA Place South)</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10657 to 10662</t>
         </is>
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>85720001MEL435CSJUN27 - September</t>
+          <t>Sep dedicated tech + after hours (6 small invoices)</t>
         </is>
       </c>
       <c r="D46" s="137" t="n">
@@ -6589,44 +6603,44 @@
         <v>46325</v>
       </c>
       <c r="F46" s="138" t="n">
-        <v>13156</v>
+        <v>3432</v>
       </c>
       <c r="G46" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H46" s="137" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="I46" s="45">
         <f>H46-E46</f>
-        <v>-22</v>
+        <v>-14</v>
       </c>
       <c r="J46" s="18">
         <f>IF(H46&lt;Assumptions!$B$5,"Before",IF(H46&gt;Assumptions!$C$48,"After",INT((H46-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K46" s="115" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>$1,188 + 4 x $467.50 + $374. With the contract one.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
         <is>
-          <t>Commonwealth Bank (CBA Brisbane)</t>
+          <t>Commonwealth Bank (CBA Place South)</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10675</t>
         </is>
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>85720001BRISCSJUN27 - September</t>
+          <t>Live event support Sep (PO3317501)</t>
         </is>
       </c>
       <c r="D47" s="137" t="n">
@@ -6636,44 +6650,44 @@
         <v>46325</v>
       </c>
       <c r="F47" s="138" t="n">
-        <v>6534</v>
+        <v>5398.25</v>
       </c>
       <c r="G47" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H47" s="137" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="I47" s="45">
         <f>H47-E47</f>
-        <v>-22</v>
+        <v>-14</v>
       </c>
       <c r="J47" s="18">
         <f>IF(H47&lt;Assumptions!$B$5,"Before",IF(H47&gt;Assumptions!$C$48,"After",INT((H47-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K47" s="115" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>With the contract one.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
         <is>
-          <t>Bankwest</t>
+          <t>Commonwealth Bank (CBA Square)</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10637</t>
         </is>
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>85720001BWPCSJUN27 - September</t>
+          <t>85720001CBSCSJUN27 - Sep contract</t>
         </is>
       </c>
       <c r="D48" s="137" t="n">
@@ -6683,44 +6697,44 @@
         <v>46325</v>
       </c>
       <c r="F48" s="138" t="n">
-        <v>21210.75</v>
+        <v>11792</v>
       </c>
       <c r="G48" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H48" s="137" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="I48" s="45">
         <f>H48-E48</f>
-        <v>-25</v>
+        <v>-14</v>
       </c>
       <c r="J48" s="18">
         <f>IF(H48&lt;Assumptions!$B$5,"Before",IF(H48&gt;Assumptions!$C$48,"After",INT((H48-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K48" s="115" t="inlineStr">
         <is>
-          <t>Aug invoice (31 Aug) paid 3 Sep - Bankwest pay within days</t>
+          <t>Same as Place South.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="18" t="inlineStr">
         <is>
-          <t>Bankwest</t>
+          <t>Commonwealth Bank (CBA Melbourne)</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10644</t>
         </is>
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>85720001BWPCSJUN27 Additionals - September</t>
+          <t>85720001MEL435CSJUN27 - Sep contract</t>
         </is>
       </c>
       <c r="D49" s="137" t="n">
@@ -6730,44 +6744,44 @@
         <v>46325</v>
       </c>
       <c r="F49" s="138" t="n">
-        <v>1490.5</v>
+        <v>12995.72</v>
       </c>
       <c r="G49" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H49" s="137" t="n">
-        <v>46300</v>
+        <v>46311</v>
       </c>
       <c r="I49" s="45">
         <f>H49-E49</f>
-        <v>-25</v>
+        <v>-14</v>
       </c>
       <c r="J49" s="18">
         <f>IF(H49&lt;Assumptions!$B$5,"Before",IF(H49&gt;Assumptions!$C$48,"After",INT((H49-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K49" s="115" t="inlineStr">
         <is>
-          <t>Same (template amount, actual varies)</t>
+          <t>Same. (Their $93.50 one was paid 6 Oct.)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="inlineStr">
         <is>
-          <t>PwC Services</t>
+          <t>Bankwest</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10640</t>
         </is>
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>PO2601702104 - Sydney AV support September</t>
+          <t>85720001BWPCSJUN27 - Sep additionals</t>
         </is>
       </c>
       <c r="D50" s="137" t="n">
@@ -6777,27 +6791,27 @@
         <v>46325</v>
       </c>
       <c r="F50" s="138" t="n">
-        <v>13097.7</v>
+        <v>4752</v>
       </c>
       <c r="G50" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H50" s="137" t="n">
-        <v>46340</v>
+        <v>46311</v>
       </c>
       <c r="I50" s="45">
         <f>H50-E50</f>
-        <v>15</v>
-      </c>
-      <c r="J50" s="18" t="str">
+        <v>-14</v>
+      </c>
+      <c r="J50" s="18">
         <f>IF(H50&lt;Assumptions!$B$5,"Before",IF(H50&gt;Assumptions!$C$48,"After",INT((H50-Assumptions!$B$5)/7)+1))</f>
-        <v>After</v>
+        <v>3</v>
       </c>
       <c r="K50" s="115" t="inlineStr">
         <is>
-          <t>PwC's July contract invoices are still unpaid - assume Nov</t>
+          <t>Bankwest paid the Sep contract one ($13,156) on 2 Oct. This is the additionals - give it to Fri 16 Oct.</t>
         </is>
       </c>
     </row>
@@ -6809,12 +6823,12 @@
       </c>
       <c r="B51" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10655</t>
         </is>
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>PO2601702371 - Brisbane AV support September</t>
+          <t>PO2601702104 - Sep contract</t>
         </is>
       </c>
       <c r="D51" s="137" t="n">
@@ -6824,44 +6838,44 @@
         <v>46325</v>
       </c>
       <c r="F51" s="138" t="n">
-        <v>7865</v>
+        <v>13097.7</v>
       </c>
       <c r="G51" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H51" s="137" t="n">
-        <v>46340</v>
+        <v>46325</v>
       </c>
       <c r="I51" s="45">
         <f>H51-E51</f>
-        <v>15</v>
-      </c>
-      <c r="J51" s="18" t="str">
+        <v>0</v>
+      </c>
+      <c r="J51" s="18">
         <f>IF(H51&lt;Assumptions!$B$5,"Before",IF(H51&gt;Assumptions!$C$48,"After",INT((H51-Assumptions!$B$5)/7)+1))</f>
-        <v>After</v>
+        <v>5</v>
       </c>
       <c r="K51" s="115" t="inlineStr">
         <is>
-          <t>Same</t>
+          <t>PwC paid the Aug ones on 29 Sep (the due date). On the due date, week 5.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="18" t="inlineStr">
         <is>
-          <t>Aware Super</t>
+          <t>PwC Services</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
         <is>
-          <t>TBR</t>
+          <t>INV-10654</t>
         </is>
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>Annual National Maintenance - September</t>
+          <t>PO2601703509 - Sep</t>
         </is>
       </c>
       <c r="D52" s="137" t="n">
@@ -6871,11 +6885,11 @@
         <v>46325</v>
       </c>
       <c r="F52" s="138" t="n">
-        <v>12100</v>
+        <v>8415</v>
       </c>
       <c r="G52" s="33" t="inlineStr">
         <is>
-          <t>To be raised</t>
+          <t>Current</t>
         </is>
       </c>
       <c r="H52" s="137" t="n">
@@ -6891,61 +6905,604 @@
       </c>
       <c r="K52" s="115" t="inlineStr">
         <is>
-          <t>Aware pay on the due date</t>
+          <t>On the due date, week 5.</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="13" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
+        <is>
+          <t>PwC Services</t>
+        </is>
+      </c>
+      <c r="B53" s="18" t="inlineStr">
+        <is>
+          <t>INV-10641</t>
+        </is>
+      </c>
+      <c r="C53" s="18" t="inlineStr">
+        <is>
+          <t>PO2601702371 - Sep contract</t>
+        </is>
+      </c>
+      <c r="D53" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E53" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F53" s="138" t="n">
+        <v>7865</v>
+      </c>
+      <c r="G53" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H53" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I53" s="45">
+        <f>H53-E53</f>
+        <v>0</v>
+      </c>
+      <c r="J53" s="18">
+        <f>IF(H53&lt;Assumptions!$B$5,"Before",IF(H53&gt;Assumptions!$C$48,"After",INT((H53-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K53" s="115" t="inlineStr">
+        <is>
+          <t>On the due date, week 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="inlineStr">
+        <is>
+          <t>Aware Super</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>INV-10652</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>Annual National Maintenance - September</t>
+        </is>
+      </c>
+      <c r="D54" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E54" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F54" s="138" t="n">
+        <v>12100</v>
+      </c>
+      <c r="G54" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H54" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I54" s="45">
+        <f>H54-E54</f>
+        <v>0</v>
+      </c>
+      <c r="J54" s="18">
+        <f>IF(H54&lt;Assumptions!$B$5,"Before",IF(H54&gt;Assumptions!$C$48,"After",INT((H54-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K54" s="115" t="inlineStr">
+        <is>
+          <t>Aware pay on the due date - but the Aug one is still sitting there, so watch it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="inlineStr">
+        <is>
+          <t>Generation-e Productivity Solutions</t>
+        </is>
+      </c>
+      <c r="B55" s="18" t="inlineStr">
+        <is>
+          <t>INV-10642</t>
+        </is>
+      </c>
+      <c r="C55" s="18" t="inlineStr">
+        <is>
+          <t>PAU26-407 - Sep</t>
+        </is>
+      </c>
+      <c r="D55" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E55" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F55" s="138" t="n">
+        <v>13627.68</v>
+      </c>
+      <c r="G55" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H55" s="137" t="n">
+        <v>46346</v>
+      </c>
+      <c r="I55" s="45">
+        <f>H55-E55</f>
+        <v>21</v>
+      </c>
+      <c r="J55" s="18" t="str">
+        <f>IF(H55&lt;Assumptions!$B$5,"Before",IF(H55&gt;Assumptions!$C$48,"After",INT((H55-Assumptions!$B$5)/7)+1))</f>
+        <v>After</v>
+      </c>
+      <c r="K55" s="115" t="inlineStr">
+        <is>
+          <t>Slow payers - 3 weeks after due, so after this forecast.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="inlineStr">
+        <is>
+          <t>Automic Group</t>
+        </is>
+      </c>
+      <c r="B56" s="18" t="inlineStr">
+        <is>
+          <t>INV-10663</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>September All Hands 25.9.26</t>
+        </is>
+      </c>
+      <c r="D56" s="137" t="n">
+        <v>46294</v>
+      </c>
+      <c r="E56" s="137" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F56" s="138" t="n">
+        <v>8775.799999999999</v>
+      </c>
+      <c r="G56" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H56" s="137" t="n">
+        <v>46324</v>
+      </c>
+      <c r="I56" s="45">
+        <f>H56-E56</f>
+        <v>0</v>
+      </c>
+      <c r="J56" s="18">
+        <f>IF(H56&lt;Assumptions!$B$5,"Before",IF(H56&gt;Assumptions!$C$48,"After",INT((H56-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K56" s="115" t="inlineStr">
+        <is>
+          <t>New customer - on the due date, week 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="inlineStr">
+        <is>
+          <t>ASX Operations</t>
+        </is>
+      </c>
+      <c r="B57" s="18" t="inlineStr">
+        <is>
+          <t>INV-10668</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="inlineStr">
+        <is>
+          <t>External listing test days 29.9.26</t>
+        </is>
+      </c>
+      <c r="D57" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E57" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F57" s="138" t="n">
+        <v>5747.5</v>
+      </c>
+      <c r="G57" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H57" s="137" t="n">
+        <v>46328</v>
+      </c>
+      <c r="I57" s="45">
+        <f>H57-E57</f>
+        <v>3</v>
+      </c>
+      <c r="J57" s="18">
+        <f>IF(H57&lt;Assumptions!$B$5,"Before",IF(H57&gt;Assumptions!$C$48,"After",INT((H57-Assumptions!$B$5)/7)+1))</f>
+        <v>6</v>
+      </c>
+      <c r="K57" s="115" t="inlineStr">
+        <is>
+          <t>Due Fri 30 Oct, ASX run a day or two late - Mon 2 Nov.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="inlineStr">
+        <is>
+          <t>Global Philanthropic</t>
+        </is>
+      </c>
+      <c r="B58" s="18" t="inlineStr">
+        <is>
+          <t>INV-10669</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="inlineStr">
+        <is>
+          <t>Talking Philanthropy event B-roll</t>
+        </is>
+      </c>
+      <c r="D58" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E58" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F58" s="138" t="n">
+        <v>1373.9</v>
+      </c>
+      <c r="G58" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H58" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I58" s="45">
+        <f>H58-E58</f>
+        <v>0</v>
+      </c>
+      <c r="J58" s="18">
+        <f>IF(H58&lt;Assumptions!$B$5,"Before",IF(H58&gt;Assumptions!$C$48,"After",INT((H58-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K58" s="115" t="inlineStr">
+        <is>
+          <t>On the due date, week 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="inlineStr">
+        <is>
+          <t>Global Philanthropic</t>
+        </is>
+      </c>
+      <c r="B59" s="18" t="inlineStr">
+        <is>
+          <t>INV-10670</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>Talking Philanthropy Aus 18.09.2026</t>
+        </is>
+      </c>
+      <c r="D59" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E59" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F59" s="138" t="n">
+        <v>4343.9</v>
+      </c>
+      <c r="G59" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H59" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I59" s="45">
+        <f>H59-E59</f>
+        <v>0</v>
+      </c>
+      <c r="J59" s="18">
+        <f>IF(H59&lt;Assumptions!$B$5,"Before",IF(H59&gt;Assumptions!$C$48,"After",INT((H59-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K59" s="115" t="inlineStr">
+        <is>
+          <t>On the due date, week 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="inlineStr">
+        <is>
+          <t>Australian Payments Network</t>
+        </is>
+      </c>
+      <c r="B60" s="18" t="inlineStr">
+        <is>
+          <t>INV-10671</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="inlineStr">
+        <is>
+          <t>AV support 21-22 Sep</t>
+        </is>
+      </c>
+      <c r="D60" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E60" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F60" s="138" t="n">
+        <v>748</v>
+      </c>
+      <c r="G60" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H60" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I60" s="45">
+        <f>H60-E60</f>
+        <v>0</v>
+      </c>
+      <c r="J60" s="18">
+        <f>IF(H60&lt;Assumptions!$B$5,"Before",IF(H60&gt;Assumptions!$C$48,"After",INT((H60-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K60" s="115" t="inlineStr">
+        <is>
+          <t>Paid the last one 11 days late - may slip past the forecast. Left on the due date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="inlineStr">
+        <is>
+          <t>ICC Sydney</t>
+        </is>
+      </c>
+      <c r="B61" s="18" t="inlineStr">
+        <is>
+          <t>INV-10672</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="inlineStr">
+        <is>
+          <t>Speaker presentation technicians Sep (TTS)</t>
+        </is>
+      </c>
+      <c r="D61" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E61" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F61" s="138" t="n">
+        <v>4100.26</v>
+      </c>
+      <c r="G61" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H61" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I61" s="45">
+        <f>H61-E61</f>
+        <v>0</v>
+      </c>
+      <c r="J61" s="18">
+        <f>IF(H61&lt;Assumptions!$B$5,"Before",IF(H61&gt;Assumptions!$C$48,"After",INT((H61-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K61" s="115" t="inlineStr">
+        <is>
+          <t>ICC pay on the due date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="inlineStr">
+        <is>
+          <t>ICC Sydney</t>
+        </is>
+      </c>
+      <c r="B62" s="18" t="inlineStr">
+        <is>
+          <t>INV-10674</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>Speaker presentation technicians Sep (CommBio)</t>
+        </is>
+      </c>
+      <c r="D62" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E62" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F62" s="138" t="n">
+        <v>2448.88</v>
+      </c>
+      <c r="G62" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H62" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I62" s="45">
+        <f>H62-E62</f>
+        <v>0</v>
+      </c>
+      <c r="J62" s="18">
+        <f>IF(H62&lt;Assumptions!$B$5,"Before",IF(H62&gt;Assumptions!$C$48,"After",INT((H62-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K62" s="115" t="inlineStr">
+        <is>
+          <t>ICC pay on the due date.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="inlineStr">
+        <is>
+          <t>St Luke's Liverpool</t>
+        </is>
+      </c>
+      <c r="B63" s="18" t="inlineStr">
+        <is>
+          <t>INV-10676</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>Digital mixer equipment</t>
+        </is>
+      </c>
+      <c r="D63" s="137" t="n">
+        <v>46295</v>
+      </c>
+      <c r="E63" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="F63" s="138" t="n">
+        <v>4988.5</v>
+      </c>
+      <c r="G63" s="33" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="H63" s="137" t="n">
+        <v>46325</v>
+      </c>
+      <c r="I63" s="45">
+        <f>H63-E63</f>
+        <v>0</v>
+      </c>
+      <c r="J63" s="18">
+        <f>IF(H63&lt;Assumptions!$B$5,"Before",IF(H63&gt;Assumptions!$C$48,"After",INT((H63-Assumptions!$B$5)/7)+1))</f>
+        <v>5</v>
+      </c>
+      <c r="K63" s="115" t="inlineStr">
+        <is>
+          <t>New - on the due date, week 5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="n"/>
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="137" t="n"/>
+      <c r="E64" s="137" t="n"/>
+      <c r="F64" s="138" t="n"/>
+      <c r="G64" s="33" t="n"/>
+      <c r="H64" s="137" t="n"/>
+      <c r="I64" s="45" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="115" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="n"/>
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="137" t="n"/>
+      <c r="E65" s="137" t="n"/>
+      <c r="F65" s="138" t="n"/>
+      <c r="G65" s="33" t="n"/>
+      <c r="H65" s="137" t="n"/>
+      <c r="I65" s="45" t="n"/>
+      <c r="J65" s="18" t="n"/>
+      <c r="K65" s="115" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="n"/>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="142">
-        <f>SUM(F5:F52)</f>
-        <v>806505.13</v>
-      </c>
-      <c r="G53" s="16" t="n"/>
-      <c r="H53" s="16" t="n"/>
-      <c r="I53" s="16" t="n"/>
-      <c r="J53" s="16" t="n"/>
-      <c r="K53" s="16" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="29" t="inlineStr">
-        <is>
-          <t>of which open in Xero at 28 Sep (should be $580,292.39)</t>
-        </is>
-      </c>
-      <c r="F54" s="143">
-        <f>SUMIFS(F5:F52,G5:G52,"&lt;&gt;To be raised")</f>
-        <v>580292.39</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="B66" s="16" t="n"/>
+      <c r="C66" s="16" t="n"/>
+      <c r="D66" s="16" t="n"/>
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="142">
+        <f>SUM(F5:F65)</f>
+        <v>860711.6799999999</v>
+      </c>
+      <c r="G66" s="16" t="n"/>
+      <c r="H66" s="16" t="n"/>
+      <c r="I66" s="16" t="n"/>
+      <c r="J66" s="16" t="n"/>
+      <c r="K66" s="16" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
+          <t>of which still open in Xero at 12 Oct (should be $583,424.49)</t>
+        </is>
+      </c>
+      <c r="F67" s="143">
+        <f>SUMPRODUCT((LEFT(G5:G65,4)&lt;&gt;"Paid")*F5:F65)</f>
+        <v>583424.4900000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="29" t="inlineStr">
         <is>
           <t>of which expected inside the forecast</t>
         </is>
       </c>
-      <c r="F55" s="143">
-        <f>SUMIFS(F5:F52,H5:H52,"&gt;="&amp;Assumptions!$B$5,H5:H52,"&lt;="&amp;Assumptions!$C$48)</f>
-        <v>534846.51</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="F68" s="143">
+        <f>SUMIFS(F5:F65,H5:H65,"&gt;="&amp;Assumptions!$B$5,H5:H65,"&lt;="&amp;Assumptions!$C$48)</f>
+        <v>596388.0800000001</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="29" t="inlineStr">
         <is>
           <t>of which pushed past the forecast (PwC Sep invoices, Meet Magic, Property NSW)</t>
         </is>
       </c>
-      <c r="F56" s="143">
-        <f>F53-F55</f>
-        <v>271658.62</v>
+      <c r="F69" s="143">
+        <f>F66-F68</f>
+        <v>264323.59999999986</v>
       </c>
     </row>
   </sheetData>
@@ -6990,11 +7547,10 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>PAYMENTS THIS WEEK (28 Sep - 7 Oct)</t>
+          <t>PAYMENTS THIS WEEK (8 - 14 Oct)</t>
         </is>
       </c>
       <c r="B4" s="114" t="n"/>
@@ -7052,63 +7608,64 @@
       </c>
     </row>
     <row r="6" ht="72" customHeight="1" s="109">
-      <c r="A6" s="48" t="str">
-        <f>A20</f>
-        <v>Complete AV Solutions</v>
-      </c>
-      <c r="B6" s="49" t="str">
-        <f>B20</f>
-        <v>INV41565 - Aware seminar room: MATERIALS portion (hardware, cables, freight, waste, net of the $4,848.68 claim-balance reduction)</v>
-      </c>
-      <c r="C6" s="144">
-        <f>C20</f>
-        <v>46291</v>
+      <c r="A6" s="48" t="inlineStr">
+        <is>
+          <t>Brookvale Insurance Brokers</t>
+        </is>
+      </c>
+      <c r="B6" s="49" t="inlineStr">
+        <is>
+          <t>Six annual renewals - INV1918462, 1918336, 1918436, 1920058, 1920113, 1914759</t>
+        </is>
+      </c>
+      <c r="C6" s="144" t="n">
+        <v>46309</v>
       </c>
       <c r="D6" s="145">
-        <f>D20</f>
-        <v>139086.22999999998</v>
-      </c>
-      <c r="E6" s="48" t="str">
-        <f>E20</f>
-        <v>EFT</v>
+        <f>SUM(D61:D66)</f>
+        <v>66238.98</v>
+      </c>
+      <c r="E6" s="48" t="inlineStr">
+        <is>
+          <t>EFT</t>
+        </is>
       </c>
       <c r="F6" s="52" t="inlineStr">
         <is>
           <t>AGREED - PAY</t>
         </is>
       </c>
-      <c r="G6" s="146">
-        <f>G20</f>
-        <v>46295</v>
+      <c r="G6" s="146" t="n">
+        <v>46309</v>
       </c>
       <c r="H6" s="54" t="n"/>
       <c r="I6" s="54" t="n"/>
       <c r="J6" s="55" t="inlineStr">
         <is>
-          <t>PAY NOW - $121,132.70 ex GST / $133,245.97 inc GST. Graham's verified figure (email 29 Sep): components delivered and installed, services excluded. PO 1/2 verified $140,320.33 less variations 1.1, 1.3, 1.4 credits plus 1.2 and the graphics card ($713.70). Excludes the $5,309.33 AW-SF501Z licence in Vary 1.1 until Complete AV verify it. Pay immediately per GC.</t>
+          <t>GC approved all six. One payment Wed 14 Oct - $66,238.98. Not in the 29 Sep forecast at all.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="56" t="str">
-        <f>A23</f>
-        <v>Employsure</v>
+        <f>A45</f>
+        <v>First Focus IT</v>
       </c>
       <c r="B7" s="57" t="str">
-        <f>B23</f>
-        <v>41 of 60</v>
+        <f>B45</f>
+        <v>INV180546 - Managed Services Azure October</v>
       </c>
       <c r="C7" s="147">
-        <f>C23</f>
-        <v>46271</v>
+        <f>C45</f>
+        <v>46309</v>
       </c>
       <c r="D7" s="148">
-        <f>D23</f>
-        <v>880</v>
+        <f>D45</f>
+        <v>692.84</v>
       </c>
       <c r="E7" s="56" t="str">
-        <f>E23</f>
-        <v>EFT</v>
+        <f>E45</f>
+        <v>DD</v>
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
@@ -7116,34 +7673,34 @@
         </is>
       </c>
       <c r="G7" s="149">
-        <f>G23</f>
-        <v>46296</v>
+        <f>G45</f>
+        <v>46309</v>
       </c>
       <c r="J7" s="115" t="inlineStr">
         <is>
-          <t>Routine - on the due date</t>
+          <t>First Focus Azure - DD on the due date</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="56" t="str">
-        <f>A26</f>
-        <v>Eptura Australia</v>
+        <f>A51</f>
+        <v>The CEO Institute</v>
       </c>
       <c r="B8" s="57" t="str">
-        <f>B26</f>
-        <v>INV-85230 - Proxyclick renewal APA VMS yr 2</v>
+        <f>B51</f>
+        <v>Syndicate membership (DL) - quarterly</v>
       </c>
       <c r="C8" s="147">
-        <f>C26</f>
-        <v>46296</v>
+        <f>C51</f>
+        <v>46303</v>
       </c>
       <c r="D8" s="148">
-        <f>D26</f>
-        <v>3627.04</v>
+        <f>D51</f>
+        <v>2310</v>
       </c>
       <c r="E8" s="56" t="str">
-        <f>E26</f>
+        <f>E51</f>
         <v>EFT</v>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -7152,12 +7709,12 @@
         </is>
       </c>
       <c r="G8" s="149">
-        <f>G26</f>
-        <v>46296</v>
+        <f>G51</f>
+        <v>46311</v>
       </c>
       <c r="J8" s="115" t="inlineStr">
         <is>
-          <t>Routine - on the due date</t>
+          <t>CEO Institute quarterly - no bill in Xero yet, check with DL</t>
         </is>
       </c>
       <c r="O8">
@@ -7166,40 +7723,38 @@
       </c>
     </row>
     <row r="9" ht="25.5" customHeight="1" s="109">
-      <c r="A9" s="61" t="str">
-        <f>A28</f>
-        <v>Fredon Technology</v>
-      </c>
-      <c r="B9" s="62" t="str">
-        <f>B28</f>
-        <v>INV11S-26080021 - DTTL 8PSQ Dream Big microphones</v>
-      </c>
-      <c r="C9" s="150">
-        <f>C28</f>
-        <v>46288</v>
-      </c>
-      <c r="D9" s="151">
-        <f>D28</f>
-        <v>24708.2</v>
-      </c>
-      <c r="E9" s="61" t="str">
-        <f>E28</f>
+      <c r="A9" s="56" t="str">
+        <f>A23</f>
+        <v>Employsure</v>
+      </c>
+      <c r="B9" s="57" t="str">
+        <f>B23</f>
+        <v>41 of 60</v>
+      </c>
+      <c r="C9" s="147">
+        <f>C23</f>
+        <v>46271</v>
+      </c>
+      <c r="D9" s="148">
+        <f>D23</f>
+        <v>880</v>
+      </c>
+      <c r="E9" s="56" t="str">
+        <f>E23</f>
         <v>EFT</v>
       </c>
-      <c r="F9" s="65" t="inlineStr">
-        <is>
-          <t>AWAITING DH</t>
-        </is>
-      </c>
-      <c r="G9" s="152">
-        <f>G28</f>
-        <v>46302</v>
-      </c>
-      <c r="H9" s="67" t="n"/>
-      <c r="I9" s="67" t="n"/>
-      <c r="J9" s="68" t="inlineStr">
-        <is>
-          <t>Bill says DH to confirm - don't pay until he does.</t>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Due this week</t>
+        </is>
+      </c>
+      <c r="G9" s="149">
+        <f>G23</f>
+        <v>46309</v>
+      </c>
+      <c r="J9" s="115" t="inlineStr">
+        <is>
+          <t>Employsure Sep (41 of 60) - still open, overdue</t>
         </is>
       </c>
       <c r="O9">
@@ -7208,38 +7763,40 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="56" t="str">
-        <f>A35</f>
-        <v>Ricoh Australia</v>
-      </c>
-      <c r="B10" s="57" t="str">
-        <f>B35</f>
-        <v>INV15759052 - printing Aug</v>
-      </c>
-      <c r="C10" s="147">
-        <f>C35</f>
-        <v>46295</v>
-      </c>
-      <c r="D10" s="148">
-        <f>D35</f>
-        <v>235.6</v>
-      </c>
-      <c r="E10" s="56" t="str">
-        <f>E35</f>
-        <v>DD</v>
-      </c>
-      <c r="F10" s="22" t="inlineStr">
-        <is>
-          <t>Due this week</t>
-        </is>
-      </c>
-      <c r="G10" s="149">
-        <f>G35</f>
-        <v>46295</v>
-      </c>
-      <c r="J10" s="115" t="inlineStr">
-        <is>
-          <t>Routine - on the due date</t>
+      <c r="A10" s="176" t="str">
+        <f>A26</f>
+        <v>Eptura Australia</v>
+      </c>
+      <c r="B10" s="177" t="str">
+        <f>B26</f>
+        <v>INV-85230 - Proxyclick renewal APA VMS yr 2</v>
+      </c>
+      <c r="C10" s="178">
+        <f>C26</f>
+        <v>46296</v>
+      </c>
+      <c r="D10" s="179">
+        <f>D26</f>
+        <v>3627.04</v>
+      </c>
+      <c r="E10" s="176" t="str">
+        <f>E26</f>
+        <v>EFT</v>
+      </c>
+      <c r="F10" s="180" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct</t>
+        </is>
+      </c>
+      <c r="G10" s="181">
+        <f>G26</f>
+        <v>46303</v>
+      </c>
+      <c r="H10" s="182" t="n"/>
+      <c r="I10" s="182" t="n"/>
+      <c r="J10" s="175" t="inlineStr">
+        <is>
+          <t>Eptura - paid</t>
         </is>
       </c>
       <c r="O10">
@@ -7248,76 +7805,78 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="61" t="str">
-        <f>A36</f>
-        <v>RJW Group Holdings</v>
-      </c>
-      <c r="B11" s="62" t="str">
-        <f>B36</f>
-        <v>INV-0048 - website design balance</v>
-      </c>
-      <c r="C11" s="150">
-        <f>C36</f>
-        <v>46295</v>
-      </c>
-      <c r="D11" s="151">
-        <f>D36</f>
-        <v>6600</v>
-      </c>
-      <c r="E11" s="61" t="str">
-        <f>E36</f>
+      <c r="A11" s="176" t="str">
+        <f>A49</f>
+        <v>LiveU</v>
+      </c>
+      <c r="B11" s="177" t="str">
+        <f>B49</f>
+        <v>INV-19664 - SOLO standard data pack October</v>
+      </c>
+      <c r="C11" s="178">
+        <f>C49</f>
+        <v>46309</v>
+      </c>
+      <c r="D11" s="179">
+        <f>D49</f>
+        <v>1485</v>
+      </c>
+      <c r="E11" s="176" t="str">
+        <f>E49</f>
         <v>EFT</v>
       </c>
-      <c r="F11" s="65" t="inlineStr">
-        <is>
-          <t>AWAITING DL</t>
-        </is>
-      </c>
-      <c r="G11" s="152">
-        <f>G36</f>
-        <v>46297</v>
-      </c>
-      <c r="H11" s="67" t="n"/>
-      <c r="I11" s="67" t="n"/>
-      <c r="J11" s="68" t="inlineStr">
-        <is>
-          <t>Bill says check with DL before paying.</t>
+      <c r="F11" s="180" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct</t>
+        </is>
+      </c>
+      <c r="G11" s="181">
+        <f>G49</f>
+        <v>46303</v>
+      </c>
+      <c r="H11" s="182" t="n"/>
+      <c r="I11" s="182" t="n"/>
+      <c r="J11" s="175" t="inlineStr">
+        <is>
+          <t>LiveU data pack - paid</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="56" t="str">
-        <f>A38</f>
-        <v>SPACERA</v>
-      </c>
-      <c r="B12" s="57" t="str">
-        <f>B38</f>
-        <v>INV-0056 - Aware Super national support (Sep)</v>
-      </c>
-      <c r="C12" s="147">
-        <f>C38</f>
-        <v>46296</v>
-      </c>
-      <c r="D12" s="148">
-        <f>D38</f>
-        <v>5728.8</v>
-      </c>
-      <c r="E12" s="56" t="str">
-        <f>E38</f>
-        <v>EFT</v>
-      </c>
-      <c r="F12" s="22" t="inlineStr">
-        <is>
-          <t>Due this week</t>
-        </is>
-      </c>
-      <c r="G12" s="149">
-        <f>G38</f>
-        <v>46296</v>
-      </c>
-      <c r="J12" s="115" t="inlineStr">
-        <is>
-          <t>Routine - on the due date</t>
+      <c r="A12" s="176" t="str">
+        <f>A32</f>
+        <v>Optus</v>
+      </c>
+      <c r="B12" s="177" t="str">
+        <f>B32</f>
+        <v>INV000594999543 - staff mobiles Sep</v>
+      </c>
+      <c r="C12" s="178">
+        <f>C32</f>
+        <v>46307</v>
+      </c>
+      <c r="D12" s="179">
+        <f>D32</f>
+        <v>804.11</v>
+      </c>
+      <c r="E12" s="176" t="str">
+        <f>E32</f>
+        <v>BPAY</v>
+      </c>
+      <c r="F12" s="180" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct</t>
+        </is>
+      </c>
+      <c r="G12" s="181">
+        <f>G32</f>
+        <v>46303</v>
+      </c>
+      <c r="H12" s="182" t="n"/>
+      <c r="I12" s="182" t="n"/>
+      <c r="J12" s="175" t="inlineStr">
+        <is>
+          <t>Optus mobiles - BPAY, paid</t>
         </is>
       </c>
       <c r="O12">
@@ -7326,74 +7885,78 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="56" t="str">
-        <f>A47</f>
-        <v>Cleveland Partners (8020 Advisors)</v>
-      </c>
-      <c r="B13" s="57" t="str">
-        <f>B47</f>
-        <v>Monthly advisory fees</v>
-      </c>
-      <c r="C13" s="147">
-        <f>C47</f>
-        <v>46302</v>
-      </c>
-      <c r="D13" s="148">
-        <f>D47</f>
-        <v>3850</v>
-      </c>
-      <c r="E13" s="56" t="str">
-        <f>E47</f>
+      <c r="A13" s="176" t="str">
+        <f>A52</f>
+        <v>Telstra</v>
+      </c>
+      <c r="B13" s="177" t="str">
+        <f>B52</f>
+        <v>TTI20227626284 - Nighthawk charges October</v>
+      </c>
+      <c r="C13" s="178">
+        <f>C52</f>
+        <v>46307</v>
+      </c>
+      <c r="D13" s="179">
+        <f>D52</f>
+        <v>136</v>
+      </c>
+      <c r="E13" s="176" t="str">
+        <f>E52</f>
         <v>EFT</v>
       </c>
-      <c r="F13" s="22" t="inlineStr">
-        <is>
-          <t>Due this week</t>
-        </is>
-      </c>
-      <c r="G13" s="149">
-        <f>G47</f>
-        <v>46302</v>
-      </c>
-      <c r="J13" s="115" t="inlineStr">
-        <is>
-          <t>Routine - on the due date</t>
+      <c r="F13" s="180" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct</t>
+        </is>
+      </c>
+      <c r="G13" s="181">
+        <f>G52</f>
+        <v>46303</v>
+      </c>
+      <c r="H13" s="182" t="n"/>
+      <c r="I13" s="182" t="n"/>
+      <c r="J13" s="175" t="inlineStr">
+        <is>
+          <t>Telstra Nighthawk - BPAY, paid</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="56" t="str">
-        <f>A50</f>
-        <v>Employsure</v>
-      </c>
-      <c r="B14" s="57" t="str">
-        <f>B50</f>
-        <v>42 of 60 - October</v>
-      </c>
-      <c r="C14" s="147">
-        <f>C50</f>
-        <v>46300</v>
-      </c>
-      <c r="D14" s="148">
-        <f>D50</f>
-        <v>880</v>
-      </c>
-      <c r="E14" s="56" t="str">
-        <f>E50</f>
+      <c r="A14" s="176" t="str">
+        <f>A34</f>
+        <v>Posh Services (Ambius)</v>
+      </c>
+      <c r="B14" s="177" t="str">
+        <f>B34</f>
+        <v>INV21736844 - indoor plants Sep</v>
+      </c>
+      <c r="C14" s="178">
+        <f>C34</f>
+        <v>46304</v>
+      </c>
+      <c r="D14" s="179">
+        <f>D34</f>
+        <v>245</v>
+      </c>
+      <c r="E14" s="176" t="str">
+        <f>E34</f>
         <v>EFT</v>
       </c>
-      <c r="F14" s="22" t="inlineStr">
-        <is>
-          <t>Due this week</t>
-        </is>
-      </c>
-      <c r="G14" s="149">
-        <f>G50</f>
-        <v>46300</v>
-      </c>
-      <c r="J14" s="115" t="inlineStr">
-        <is>
-          <t>Routine - on the due date</t>
+      <c r="F14" s="180" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct</t>
+        </is>
+      </c>
+      <c r="G14" s="181">
+        <f>G34</f>
+        <v>46303</v>
+      </c>
+      <c r="H14" s="182" t="n"/>
+      <c r="I14" s="182" t="n"/>
+      <c r="J14" s="175" t="inlineStr">
+        <is>
+          <t>Posh plants - paid</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7970,7 @@
       <c r="C15" s="16" t="n"/>
       <c r="D15" s="142">
         <f>SUM(D6:D14)</f>
-        <v>185595.86999999997</v>
+        <v>76418.96999999999</v>
       </c>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
@@ -7419,12 +7982,12 @@
     <row r="16">
       <c r="A16" s="29" t="inlineStr">
         <is>
-          <t>of which agreed / routine (excludes the two awaiting sign-off)</t>
+          <t>of which still to go out this week (agreed + due, excludes what is already paid)</t>
         </is>
       </c>
       <c r="D16" s="143">
         <f>SUMIFS(D6:D14,F6:F14,"AGREED - PAY")+SUMIFS(D6:D14,F6:F14,"Due this week")</f>
-        <v>154287.66999999998</v>
+        <v>70121.81999999999</v>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1" s="109">
@@ -7532,49 +8095,49 @@
       </c>
     </row>
     <row r="20" ht="38.25" customHeight="1" s="109">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="170" t="inlineStr">
         <is>
           <t>Complete AV Solutions</t>
         </is>
       </c>
-      <c r="B20" s="110" t="inlineStr">
+      <c r="B20" s="183" t="inlineStr">
         <is>
           <t>INV41565 - Aware seminar room: MATERIALS portion (hardware, cables, freight, waste, net of the $4,848.68 claim-balance reduction)</t>
         </is>
       </c>
-      <c r="C20" s="137" t="n">
+      <c r="C20" s="171" t="n">
         <v>46291</v>
       </c>
-      <c r="D20" s="148">
+      <c r="D20" s="179">
         <f>'Complete AV'!K19</f>
         <v>139086.22999999998</v>
       </c>
-      <c r="E20" s="33" t="inlineStr">
+      <c r="E20" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F20" s="33" t="inlineStr">
+      <c r="F20" s="173" t="inlineStr">
         <is>
           <t>Equipment purchases</t>
         </is>
       </c>
-      <c r="G20" s="153">
+      <c r="G20" s="178">
         <f>'Complete AV'!$D$46</f>
         <v>46295</v>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="170">
         <f>IF(G20&lt;Assumptions!$B$5,"Before",IF(G20&gt;Assumptions!$C$48,"After",INT((G20-Assumptions!$B$5)/7)+1))</f>
         <v>1</v>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="I20" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J20" s="115" t="inlineStr">
-        <is>
-          <t>AGREED 28 Sep (Graham / Jordan): pay the materials now, hold labour until Aware sign off. Build-up is on the Complete AV tab - amount and date come from there.</t>
+      <c r="J20" s="175" t="inlineStr">
+        <is>
+          <t>PAID 29 Sep (Xero shows the whole bill as paid 8 Oct - see note on the hold).</t>
         </is>
       </c>
     </row>
@@ -7620,7 +8183,7 @@
       </c>
       <c r="J21" s="115" t="inlineStr">
         <is>
-          <t>HELD - $40,793.90 ex GST / $44,873.28 inc GST. Balance of the Xero bill after the $133,245.97 payment. Labour and programming $37,137.65, rack cabling $691.60, graphics card install $1,440.00, lighting programming $1,064.00, less the Vary 1.1 licence query. Released once Aware sign off, we get the handover docs, and Complete AV verify the $5,840.26 (inc GST) Vary 1.1 charge. Dated past the forecast</t>
+          <t>HELD - agreed 28 Sep, released on Aware sign off and handover docs. Xero shows INV41565 fully paid on 8 Oct ($178,119.25) - if the $44,873 did go out, it needs to go into week 2 actuals.</t>
         </is>
       </c>
     </row>
@@ -7697,11 +8260,11 @@
         </is>
       </c>
       <c r="G23" s="137" t="n">
-        <v>46296</v>
+        <v>46309</v>
       </c>
       <c r="H23" s="18">
         <f>IF(G23&lt;Assumptions!$B$5,"Before",IF(G23&gt;Assumptions!$C$48,"After",INT((G23-Assumptions!$B$5)/7)+1))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I23" s="18" t="inlineStr">
         <is>
@@ -7710,52 +8273,52 @@
       </c>
       <c r="J23" s="115" t="inlineStr">
         <is>
-          <t>Overdue - pay this week</t>
+          <t>Still open in Xero at 12 Oct (the Oct one, 42 of 60, was paid 6 Oct). Pay this week.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="170" t="inlineStr">
         <is>
           <t>Energy Australia</t>
         </is>
       </c>
-      <c r="B24" s="110" t="inlineStr">
+      <c r="B24" s="183" t="inlineStr">
         <is>
           <t>INV260382065288 - energy 23 Jul-22 Aug</t>
         </is>
       </c>
-      <c r="C24" s="137" t="n">
+      <c r="C24" s="171" t="n">
         <v>46294</v>
       </c>
-      <c r="D24" s="138" t="n">
+      <c r="D24" s="172" t="n">
         <v>377.13</v>
       </c>
-      <c r="E24" s="33" t="inlineStr">
+      <c r="E24" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F24" s="33" t="inlineStr">
+      <c r="F24" s="173" t="inlineStr">
         <is>
           <t>Electricity</t>
         </is>
       </c>
-      <c r="G24" s="137" t="n">
+      <c r="G24" s="171" t="n">
         <v>46294</v>
       </c>
-      <c r="H24" s="18">
+      <c r="H24" s="170">
         <f>IF(G24&lt;Assumptions!$B$5,"Before",IF(G24&gt;Assumptions!$C$48,"After",INT((G24-Assumptions!$B$5)/7)+1))</f>
         <v>1</v>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I24" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J24" s="115" t="inlineStr">
-        <is>
-          <t>DD via the PL card</t>
+      <c r="J24" s="175" t="inlineStr">
+        <is>
+          <t>PAID 29 Sep - PL card</t>
         </is>
       </c>
     </row>
@@ -7805,137 +8368,137 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="170" t="inlineStr">
         <is>
           <t>Eptura Australia</t>
         </is>
       </c>
-      <c r="B26" s="110" t="inlineStr">
+      <c r="B26" s="183" t="inlineStr">
         <is>
           <t>INV-85230 - Proxyclick renewal APA VMS yr 2</t>
         </is>
       </c>
-      <c r="C26" s="137" t="n">
+      <c r="C26" s="171" t="n">
         <v>46296</v>
       </c>
-      <c r="D26" s="138" t="n">
+      <c r="D26" s="172" t="n">
         <v>3627.04</v>
       </c>
-      <c r="E26" s="33" t="inlineStr">
+      <c r="E26" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F26" s="33" t="inlineStr">
+      <c r="F26" s="173" t="inlineStr">
         <is>
           <t>Client subscriptions</t>
         </is>
       </c>
-      <c r="G26" s="137" t="n">
-        <v>46296</v>
-      </c>
-      <c r="H26" s="18">
+      <c r="G26" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H26" s="170">
         <f>IF(G26&lt;Assumptions!$B$5,"Before",IF(G26&gt;Assumptions!$C$48,"After",INT((G26-Assumptions!$B$5)/7)+1))</f>
-        <v>1</v>
-      </c>
-      <c r="I26" s="18" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I26" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J26" s="115" t="inlineStr">
-        <is>
-          <t>On the due date</t>
+      <c r="J26" s="175" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="170" t="inlineStr">
         <is>
           <t>Expedia</t>
         </is>
       </c>
-      <c r="B27" s="110" t="inlineStr">
+      <c r="B27" s="183" t="inlineStr">
         <is>
           <t>ITN73550041732636 - accommodation D Hurley</t>
         </is>
       </c>
-      <c r="C27" s="137" t="n">
+      <c r="C27" s="171" t="n">
         <v>46287</v>
       </c>
-      <c r="D27" s="138" t="n">
+      <c r="D27" s="172" t="n">
         <v>808.95</v>
       </c>
-      <c r="E27" s="33" t="inlineStr">
+      <c r="E27" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F27" s="33" t="inlineStr">
+      <c r="F27" s="173" t="inlineStr">
         <is>
           <t>Direct travel &amp; freight</t>
         </is>
       </c>
-      <c r="G27" s="137" t="n">
+      <c r="G27" s="171" t="n">
         <v>46287</v>
       </c>
-      <c r="H27" s="18" t="str">
+      <c r="H27" s="170" t="str">
         <f>IF(G27&lt;Assumptions!$B$5,"Before",IF(G27&gt;Assumptions!$C$48,"After",INT((G27-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I27" s="18" t="inlineStr">
+      <c r="I27" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J27" s="115" t="inlineStr">
-        <is>
-          <t>Went on the PL card last time</t>
+      <c r="J27" s="175" t="inlineStr">
+        <is>
+          <t>PAID 22 Sep - PL card</t>
         </is>
       </c>
     </row>
     <row r="28" ht="25.5" customHeight="1" s="109">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="170" t="inlineStr">
         <is>
           <t>Fredon Technology</t>
         </is>
       </c>
-      <c r="B28" s="110" t="inlineStr">
+      <c r="B28" s="183" t="inlineStr">
         <is>
           <t>INV11S-26080021 - DTTL 8PSQ Dream Big microphones</t>
         </is>
       </c>
-      <c r="C28" s="137" t="n">
+      <c r="C28" s="171" t="n">
         <v>46288</v>
       </c>
-      <c r="D28" s="138" t="n">
+      <c r="D28" s="172" t="n">
         <v>24708.2</v>
       </c>
-      <c r="E28" s="33" t="inlineStr">
+      <c r="E28" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F28" s="33" t="inlineStr">
+      <c r="F28" s="173" t="inlineStr">
         <is>
           <t>Equipment purchases</t>
         </is>
       </c>
-      <c r="G28" s="137" t="n">
-        <v>46302</v>
-      </c>
-      <c r="H28" s="18">
+      <c r="G28" s="171" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H28" s="170">
         <f>IF(G28&lt;Assumptions!$B$5,"Before",IF(G28&gt;Assumptions!$C$48,"After",INT((G28-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
-      </c>
-      <c r="I28" s="18" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="I28" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J28" s="115" t="inlineStr">
-        <is>
-          <t>Overdue - DH to confirm. Assume it's released week 2</t>
+      <c r="J28" s="175" t="inlineStr">
+        <is>
+          <t>PAID 1 Oct</t>
         </is>
       </c>
     </row>
@@ -7985,137 +8548,137 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="170" t="inlineStr">
         <is>
           <t>Mailchimp</t>
         </is>
       </c>
-      <c r="B30" s="110" t="inlineStr">
+      <c r="B30" s="183" t="inlineStr">
         <is>
           <t>MC27286583 - September</t>
         </is>
       </c>
-      <c r="C30" s="137" t="n">
+      <c r="C30" s="171" t="n">
         <v>46283</v>
       </c>
-      <c r="D30" s="138" t="n">
+      <c r="D30" s="172" t="n">
         <v>37.62</v>
       </c>
-      <c r="E30" s="33" t="inlineStr">
+      <c r="E30" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F30" s="33" t="inlineStr">
+      <c r="F30" s="173" t="inlineStr">
         <is>
           <t>Dues &amp; subscriptions</t>
         </is>
       </c>
-      <c r="G30" s="137" t="n">
+      <c r="G30" s="171" t="n">
         <v>46283</v>
       </c>
-      <c r="H30" s="18" t="str">
+      <c r="H30" s="170" t="str">
         <f>IF(G30&lt;Assumptions!$B$5,"Before",IF(G30&gt;Assumptions!$C$48,"After",INT((G30-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I30" s="18" t="inlineStr">
+      <c r="I30" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J30" s="115" t="inlineStr">
-        <is>
-          <t>PL card</t>
+      <c r="J30" s="175" t="inlineStr">
+        <is>
+          <t>PAID 18 Sep - card</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="170" t="inlineStr">
         <is>
           <t>Optus</t>
         </is>
       </c>
-      <c r="B31" s="110" t="inlineStr">
+      <c r="B31" s="183" t="inlineStr">
         <is>
           <t>INV000594614144 - office internet &amp; landline Sep</t>
         </is>
       </c>
-      <c r="C31" s="137" t="n">
+      <c r="C31" s="171" t="n">
         <v>46288</v>
       </c>
-      <c r="D31" s="138" t="n">
+      <c r="D31" s="172" t="n">
         <v>629.66</v>
       </c>
-      <c r="E31" s="33" t="inlineStr">
+      <c r="E31" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F31" s="33" t="inlineStr">
+      <c r="F31" s="173" t="inlineStr">
         <is>
           <t>Telephone &amp; internet</t>
         </is>
       </c>
-      <c r="G31" s="137" t="n">
+      <c r="G31" s="171" t="n">
         <v>46288</v>
       </c>
-      <c r="H31" s="18" t="str">
+      <c r="H31" s="170" t="str">
         <f>IF(G31&lt;Assumptions!$B$5,"Before",IF(G31&gt;Assumptions!$C$48,"After",INT((G31-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I31" s="18" t="inlineStr">
+      <c r="I31" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J31" s="115" t="inlineStr">
-        <is>
-          <t>PL card</t>
+      <c r="J31" s="175" t="inlineStr">
+        <is>
+          <t>PAID 23 Sep - card</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="170" t="inlineStr">
         <is>
           <t>Optus</t>
         </is>
       </c>
-      <c r="B32" s="110" t="inlineStr">
+      <c r="B32" s="183" t="inlineStr">
         <is>
           <t>INV000594999543 - staff mobiles Sep</t>
         </is>
       </c>
-      <c r="C32" s="137" t="n">
+      <c r="C32" s="171" t="n">
         <v>46307</v>
       </c>
-      <c r="D32" s="138" t="n">
+      <c r="D32" s="172" t="n">
         <v>804.11</v>
       </c>
-      <c r="E32" s="33" t="inlineStr">
+      <c r="E32" s="173" t="inlineStr">
         <is>
           <t>BPAY</t>
         </is>
       </c>
-      <c r="F32" s="33" t="inlineStr">
+      <c r="F32" s="173" t="inlineStr">
         <is>
           <t>Telephone &amp; internet</t>
         </is>
       </c>
-      <c r="G32" s="137" t="n">
-        <v>46307</v>
-      </c>
-      <c r="H32" s="18">
+      <c r="G32" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H32" s="170">
         <f>IF(G32&lt;Assumptions!$B$5,"Before",IF(G32&gt;Assumptions!$C$48,"After",INT((G32-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="I32" s="18" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I32" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J32" s="115" t="inlineStr">
-        <is>
-          <t>BPAY on the due date</t>
+      <c r="J32" s="175" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct - BPAY</t>
         </is>
       </c>
     </row>
@@ -8165,452 +8728,452 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="170" t="inlineStr">
         <is>
           <t>Posh Services (Ambius)</t>
         </is>
       </c>
-      <c r="B34" s="110" t="inlineStr">
+      <c r="B34" s="183" t="inlineStr">
         <is>
           <t>INV21736844 - indoor plants Sep</t>
         </is>
       </c>
-      <c r="C34" s="137" t="n">
+      <c r="C34" s="171" t="n">
         <v>46304</v>
       </c>
-      <c r="D34" s="138" t="n">
+      <c r="D34" s="172" t="n">
         <v>245</v>
       </c>
-      <c r="E34" s="33" t="inlineStr">
+      <c r="E34" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F34" s="33" t="inlineStr">
+      <c r="F34" s="173" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="G34" s="137" t="n">
-        <v>46304</v>
-      </c>
-      <c r="H34" s="18">
+      <c r="G34" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H34" s="170">
         <f>IF(G34&lt;Assumptions!$B$5,"Before",IF(G34&gt;Assumptions!$C$48,"After",INT((G34-Assumptions!$B$5)/7)+1))</f>
         <v>2</v>
       </c>
-      <c r="I34" s="18" t="inlineStr">
+      <c r="I34" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J34" s="115" t="inlineStr">
-        <is>
-          <t>On the due date</t>
+      <c r="J34" s="175" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="170" t="inlineStr">
         <is>
           <t>Ricoh Australia</t>
         </is>
       </c>
-      <c r="B35" s="110" t="inlineStr">
+      <c r="B35" s="183" t="inlineStr">
         <is>
           <t>INV15759052 - printing Aug</t>
         </is>
       </c>
-      <c r="C35" s="137" t="n">
+      <c r="C35" s="171" t="n">
         <v>46295</v>
       </c>
-      <c r="D35" s="138" t="n">
+      <c r="D35" s="172" t="n">
         <v>235.6</v>
       </c>
-      <c r="E35" s="33" t="inlineStr">
+      <c r="E35" s="173" t="inlineStr">
         <is>
           <t>DD</t>
         </is>
       </c>
-      <c r="F35" s="33" t="inlineStr">
+      <c r="F35" s="173" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="G35" s="137" t="n">
+      <c r="G35" s="171" t="n">
         <v>46295</v>
       </c>
-      <c r="H35" s="18">
+      <c r="H35" s="170">
         <f>IF(G35&lt;Assumptions!$B$5,"Before",IF(G35&gt;Assumptions!$C$48,"After",INT((G35-Assumptions!$B$5)/7)+1))</f>
         <v>1</v>
       </c>
-      <c r="I35" s="18" t="inlineStr">
+      <c r="I35" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J35" s="115" t="inlineStr">
-        <is>
-          <t>Direct debit</t>
+      <c r="J35" s="175" t="inlineStr">
+        <is>
+          <t>PAID 30 Sep - DD</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="170" t="inlineStr">
         <is>
           <t>RJW Group Holdings</t>
         </is>
       </c>
-      <c r="B36" s="110" t="inlineStr">
+      <c r="B36" s="183" t="inlineStr">
         <is>
           <t>INV-0048 - website design balance</t>
         </is>
       </c>
-      <c r="C36" s="137" t="n">
+      <c r="C36" s="171" t="n">
         <v>46295</v>
       </c>
-      <c r="D36" s="138" t="n">
+      <c r="D36" s="172" t="n">
         <v>6600</v>
       </c>
-      <c r="E36" s="33" t="inlineStr">
+      <c r="E36" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F36" s="33" t="inlineStr">
+      <c r="F36" s="173" t="inlineStr">
         <is>
           <t>Advertising</t>
         </is>
       </c>
-      <c r="G36" s="137" t="n">
-        <v>46297</v>
-      </c>
-      <c r="H36" s="18">
+      <c r="G36" s="171" t="n">
+        <v>46296</v>
+      </c>
+      <c r="H36" s="170">
         <f>IF(G36&lt;Assumptions!$B$5,"Before",IF(G36&gt;Assumptions!$C$48,"After",INT((G36-Assumptions!$B$5)/7)+1))</f>
         <v>1</v>
       </c>
-      <c r="I36" s="18" t="inlineStr">
+      <c r="I36" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J36" s="115" t="inlineStr">
-        <is>
-          <t>Check with DL before paying</t>
+      <c r="J36" s="175" t="inlineStr">
+        <is>
+          <t>PAID 1 Oct</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="170" t="inlineStr">
         <is>
           <t>Seek</t>
         </is>
       </c>
-      <c r="B37" s="110" t="inlineStr">
+      <c r="B37" s="183" t="inlineStr">
         <is>
           <t>INV702112646 - job ad casual AV concierge</t>
         </is>
       </c>
-      <c r="C37" s="137" t="n">
+      <c r="C37" s="171" t="n">
         <v>46283</v>
       </c>
-      <c r="D37" s="138" t="n">
+      <c r="D37" s="172" t="n">
         <v>550</v>
       </c>
-      <c r="E37" s="33" t="inlineStr">
+      <c r="E37" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F37" s="33" t="inlineStr">
+      <c r="F37" s="173" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
       </c>
-      <c r="G37" s="137" t="n">
+      <c r="G37" s="171" t="n">
         <v>46283</v>
       </c>
-      <c r="H37" s="18" t="str">
+      <c r="H37" s="170" t="str">
         <f>IF(G37&lt;Assumptions!$B$5,"Before",IF(G37&gt;Assumptions!$C$48,"After",INT((G37-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I37" s="18" t="inlineStr">
+      <c r="I37" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J37" s="115" t="inlineStr">
-        <is>
-          <t>PL card</t>
+      <c r="J37" s="175" t="inlineStr">
+        <is>
+          <t>PAID 18 Sep - card</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="170" t="inlineStr">
         <is>
           <t>SPACERA</t>
         </is>
       </c>
-      <c r="B38" s="110" t="inlineStr">
+      <c r="B38" s="183" t="inlineStr">
         <is>
           <t>INV-0056 - Aware Super national support (Sep)</t>
         </is>
       </c>
-      <c r="C38" s="137" t="n">
+      <c r="C38" s="171" t="n">
         <v>46296</v>
       </c>
-      <c r="D38" s="138" t="n">
+      <c r="D38" s="172" t="n">
         <v>5728.8</v>
       </c>
-      <c r="E38" s="33" t="inlineStr">
+      <c r="E38" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F38" s="33" t="inlineStr">
+      <c r="F38" s="173" t="inlineStr">
         <is>
           <t>Client subscriptions</t>
         </is>
       </c>
-      <c r="G38" s="137" t="n">
+      <c r="G38" s="171" t="n">
         <v>46296</v>
       </c>
-      <c r="H38" s="18">
+      <c r="H38" s="170">
         <f>IF(G38&lt;Assumptions!$B$5,"Before",IF(G38&gt;Assumptions!$C$48,"After",INT((G38-Assumptions!$B$5)/7)+1))</f>
         <v>1</v>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="I38" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J38" s="115" t="inlineStr">
-        <is>
-          <t>On the due date</t>
+      <c r="J38" s="175" t="inlineStr">
+        <is>
+          <t>PAID 1 Oct</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="170" t="inlineStr">
         <is>
           <t>Tec Art</t>
         </is>
       </c>
-      <c r="B39" s="110" t="inlineStr">
+      <c r="B39" s="183" t="inlineStr">
         <is>
           <t>INV136603 - PRD asset purchase</t>
         </is>
       </c>
-      <c r="C39" s="137" t="n">
+      <c r="C39" s="171" t="n">
         <v>46287</v>
       </c>
-      <c r="D39" s="138" t="n">
+      <c r="D39" s="172" t="n">
         <v>657.5</v>
       </c>
-      <c r="E39" s="33" t="inlineStr">
+      <c r="E39" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F39" s="33" t="inlineStr">
+      <c r="F39" s="173" t="inlineStr">
         <is>
           <t>Equipment purchases</t>
         </is>
       </c>
-      <c r="G39" s="137" t="n">
+      <c r="G39" s="171" t="n">
         <v>46287</v>
       </c>
-      <c r="H39" s="18" t="str">
+      <c r="H39" s="170" t="str">
         <f>IF(G39&lt;Assumptions!$B$5,"Before",IF(G39&gt;Assumptions!$C$48,"After",INT((G39-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I39" s="18" t="inlineStr">
+      <c r="I39" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J39" s="115" t="inlineStr">
-        <is>
-          <t>PL card</t>
+      <c r="J39" s="175" t="inlineStr">
+        <is>
+          <t>PAID 22 Sep - card</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="170" t="inlineStr">
         <is>
           <t>Tec Art</t>
         </is>
       </c>
-      <c r="B40" s="110" t="inlineStr">
+      <c r="B40" s="183" t="inlineStr">
         <is>
           <t>INV136603CR - refund</t>
         </is>
       </c>
-      <c r="C40" s="137" t="n">
+      <c r="C40" s="171" t="n">
         <v>46289</v>
       </c>
-      <c r="D40" s="138" t="n">
+      <c r="D40" s="172" t="n">
         <v>-657.5</v>
       </c>
-      <c r="E40" s="33" t="inlineStr">
+      <c r="E40" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F40" s="33" t="inlineStr">
+      <c r="F40" s="173" t="inlineStr">
         <is>
           <t>Equipment purchases</t>
         </is>
       </c>
-      <c r="G40" s="137" t="n">
+      <c r="G40" s="171" t="n">
         <v>46289</v>
       </c>
-      <c r="H40" s="18" t="str">
+      <c r="H40" s="170" t="str">
         <f>IF(G40&lt;Assumptions!$B$5,"Before",IF(G40&gt;Assumptions!$C$48,"After",INT((G40-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="I40" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J40" s="115" t="inlineStr">
-        <is>
-          <t>Refund back to the PL card</t>
+      <c r="J40" s="175" t="inlineStr">
+        <is>
+          <t>Refunded 24 Sep - card</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="170" t="inlineStr">
         <is>
           <t>Transport for NSW</t>
         </is>
       </c>
-      <c r="B41" s="110" t="inlineStr">
+      <c r="B41" s="183" t="inlineStr">
         <is>
           <t>Opal top-up T Wood</t>
         </is>
       </c>
-      <c r="C41" s="137" t="n">
+      <c r="C41" s="171" t="n">
         <v>46283</v>
       </c>
-      <c r="D41" s="138" t="n">
+      <c r="D41" s="172" t="n">
         <v>20</v>
       </c>
-      <c r="E41" s="33" t="inlineStr">
+      <c r="E41" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F41" s="33" t="inlineStr">
+      <c r="F41" s="173" t="inlineStr">
         <is>
           <t>Direct travel &amp; freight</t>
         </is>
       </c>
-      <c r="G41" s="137" t="n">
+      <c r="G41" s="171" t="n">
         <v>46283</v>
       </c>
-      <c r="H41" s="18" t="str">
+      <c r="H41" s="170" t="str">
         <f>IF(G41&lt;Assumptions!$B$5,"Before",IF(G41&gt;Assumptions!$C$48,"After",INT((G41-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I41" s="18" t="inlineStr">
+      <c r="I41" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J41" s="115" t="inlineStr">
+      <c r="J41" s="175" t="inlineStr">
+        <is>
+          <t>PAID - card</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="170" t="inlineStr">
+        <is>
+          <t>Virgin Australia</t>
+        </is>
+      </c>
+      <c r="B42" s="183" t="inlineStr">
+        <is>
+          <t>SYMUMZ-3 - rescheduled flights D Hurley</t>
+        </is>
+      </c>
+      <c r="C42" s="171" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D42" s="172" t="n">
+        <v>501.91</v>
+      </c>
+      <c r="E42" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="18" t="inlineStr">
-        <is>
-          <t>Virgin Australia</t>
-        </is>
-      </c>
-      <c r="B42" s="110" t="inlineStr">
-        <is>
-          <t>SYMUMZ-3 - rescheduled flights D Hurley</t>
-        </is>
-      </c>
-      <c r="C42" s="137" t="n">
+      <c r="F42" s="173" t="inlineStr">
+        <is>
+          <t>Direct travel &amp; freight</t>
+        </is>
+      </c>
+      <c r="G42" s="171" t="n">
         <v>46283</v>
       </c>
-      <c r="D42" s="138" t="n">
-        <v>501.91</v>
-      </c>
-      <c r="E42" s="33" t="inlineStr">
-        <is>
-          <t>Card</t>
-        </is>
-      </c>
-      <c r="F42" s="33" t="inlineStr">
-        <is>
-          <t>Direct travel &amp; freight</t>
-        </is>
-      </c>
-      <c r="G42" s="137" t="n">
-        <v>46283</v>
-      </c>
-      <c r="H42" s="18" t="str">
+      <c r="H42" s="170" t="str">
         <f>IF(G42&lt;Assumptions!$B$5,"Before",IF(G42&gt;Assumptions!$C$48,"After",INT((G42-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I42" s="18" t="inlineStr">
+      <c r="I42" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J42" s="115" t="inlineStr">
-        <is>
-          <t>Went on the PL card last time</t>
+      <c r="J42" s="175" t="inlineStr">
+        <is>
+          <t>PAID 17 Sep - card</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="170" t="inlineStr">
         <is>
           <t>Xero</t>
         </is>
       </c>
-      <c r="B43" s="110" t="inlineStr">
+      <c r="B43" s="183" t="inlineStr">
         <is>
           <t>INV-56302114 - subscription Sep</t>
         </is>
       </c>
-      <c r="C43" s="137" t="n">
+      <c r="C43" s="171" t="n">
         <v>46289</v>
       </c>
-      <c r="D43" s="138" t="n">
+      <c r="D43" s="172" t="n">
         <v>107</v>
       </c>
-      <c r="E43" s="33" t="inlineStr">
+      <c r="E43" s="173" t="inlineStr">
         <is>
           <t>Card</t>
         </is>
       </c>
-      <c r="F43" s="33" t="inlineStr">
+      <c r="F43" s="173" t="inlineStr">
         <is>
           <t>Dues &amp; subscriptions</t>
         </is>
       </c>
-      <c r="G43" s="137" t="n">
+      <c r="G43" s="171" t="n">
         <v>46289</v>
       </c>
-      <c r="H43" s="18" t="str">
+      <c r="H43" s="170" t="str">
         <f>IF(G43&lt;Assumptions!$B$5,"Before",IF(G43&gt;Assumptions!$C$48,"After",INT((G43-Assumptions!$B$5)/7)+1))</f>
         <v>Before</v>
       </c>
-      <c r="I43" s="18" t="inlineStr">
+      <c r="I43" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J43" s="115" t="inlineStr">
-        <is>
-          <t>PL card</t>
+      <c r="J43" s="175" t="inlineStr">
+        <is>
+          <t>PAID 24 Sep - card</t>
         </is>
       </c>
     </row>
@@ -8777,11 +9340,11 @@
         </is>
       </c>
       <c r="G47" s="137" t="n">
-        <v>46302</v>
+        <v>46311</v>
       </c>
       <c r="H47" s="18">
         <f>IF(G47&lt;Assumptions!$B$5,"Before",IF(G47&gt;Assumptions!$C$48,"After",INT((G47-Assumptions!$B$5)/7)+1))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I47" s="18" t="inlineStr">
         <is>
@@ -8790,7 +9353,7 @@
       </c>
       <c r="J47" s="115" t="inlineStr">
         <is>
-          <t>Template $3,850 a month (Sep cash P&amp;L had $5,000). Date assumed</t>
+          <t>Template $3,850 a month. Nothing paid in Xero to 12 Oct - check if the Oct invoice has come in.</t>
         </is>
       </c>
     </row>
@@ -8840,92 +9403,92 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="170" t="inlineStr">
         <is>
           <t>LiveU</t>
         </is>
       </c>
-      <c r="B49" s="110" t="inlineStr">
-        <is>
-          <t>SOLO standard data pack - October</t>
-        </is>
-      </c>
-      <c r="C49" s="137" t="n">
+      <c r="B49" s="183" t="inlineStr">
+        <is>
+          <t>INV-19664 - SOLO standard data pack October</t>
+        </is>
+      </c>
+      <c r="C49" s="171" t="n">
         <v>46309</v>
       </c>
-      <c r="D49" s="138" t="n">
+      <c r="D49" s="172" t="n">
         <v>1485</v>
       </c>
-      <c r="E49" s="33" t="inlineStr">
+      <c r="E49" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F49" s="33" t="inlineStr">
+      <c r="F49" s="173" t="inlineStr">
         <is>
           <t>Client subscriptions</t>
         </is>
       </c>
-      <c r="G49" s="137" t="n">
-        <v>46309</v>
-      </c>
-      <c r="H49" s="18">
+      <c r="G49" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H49" s="170">
         <f>IF(G49&lt;Assumptions!$B$5,"Before",IF(G49&gt;Assumptions!$C$48,"After",INT((G49-Assumptions!$B$5)/7)+1))</f>
-        <v>3</v>
-      </c>
-      <c r="I49" s="18" t="inlineStr">
-        <is>
-          <t>Repeating template</t>
-        </is>
-      </c>
-      <c r="J49" s="115" t="inlineStr">
-        <is>
-          <t>Template, due 14 Oct</t>
+        <v>2</v>
+      </c>
+      <c r="I49" s="170" t="inlineStr">
+        <is>
+          <t>Xero bill</t>
+        </is>
+      </c>
+      <c r="J49" s="175" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct (INV-19664)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="170" t="inlineStr">
         <is>
           <t>Employsure</t>
         </is>
       </c>
-      <c r="B50" s="110" t="inlineStr">
+      <c r="B50" s="183" t="inlineStr">
         <is>
           <t>42 of 60 - October</t>
         </is>
       </c>
-      <c r="C50" s="137" t="n">
+      <c r="C50" s="171" t="n">
         <v>46300</v>
       </c>
-      <c r="D50" s="138" t="n">
+      <c r="D50" s="172" t="n">
         <v>880</v>
       </c>
-      <c r="E50" s="33" t="inlineStr">
+      <c r="E50" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F50" s="33" t="inlineStr">
+      <c r="F50" s="173" t="inlineStr">
         <is>
           <t>Professional fees</t>
         </is>
       </c>
-      <c r="G50" s="137" t="n">
-        <v>46300</v>
-      </c>
-      <c r="H50" s="18">
+      <c r="G50" s="171" t="n">
+        <v>46301</v>
+      </c>
+      <c r="H50" s="170">
         <f>IF(G50&lt;Assumptions!$B$5,"Before",IF(G50&gt;Assumptions!$C$48,"After",INT((G50-Assumptions!$B$5)/7)+1))</f>
         <v>2</v>
       </c>
-      <c r="I50" s="18" t="inlineStr">
+      <c r="I50" s="170" t="inlineStr">
         <is>
           <t>Repeating template</t>
         </is>
       </c>
-      <c r="J50" s="115" t="inlineStr">
-        <is>
-          <t>Template, due 5 Oct</t>
+      <c r="J50" s="175" t="inlineStr">
+        <is>
+          <t>PAID 6 Oct</t>
         </is>
       </c>
     </row>
@@ -8957,65 +9520,65 @@
         </is>
       </c>
       <c r="G51" s="137" t="n">
-        <v>46303</v>
+        <v>46311</v>
       </c>
       <c r="H51" s="18">
         <f>IF(G51&lt;Assumptions!$B$5,"Before",IF(G51&gt;Assumptions!$C$48,"After",INT((G51-Assumptions!$B$5)/7)+1))</f>
+        <v>3</v>
+      </c>
+      <c r="I51" s="18" t="inlineStr">
+        <is>
+          <t>Repeating template</t>
+        </is>
+      </c>
+      <c r="J51" s="115" t="inlineStr">
+        <is>
+          <t>Quarterly, due 8 Oct. No bill in Xero at 12 Oct - check with DL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="170" t="inlineStr">
+        <is>
+          <t>Telstra</t>
+        </is>
+      </c>
+      <c r="B52" s="183" t="inlineStr">
+        <is>
+          <t>TTI20227626284 - Nighthawk charges October</t>
+        </is>
+      </c>
+      <c r="C52" s="171" t="n">
+        <v>46307</v>
+      </c>
+      <c r="D52" s="172" t="n">
+        <v>136</v>
+      </c>
+      <c r="E52" s="173" t="inlineStr">
+        <is>
+          <t>EFT</t>
+        </is>
+      </c>
+      <c r="F52" s="173" t="inlineStr">
+        <is>
+          <t>Telephone &amp; internet</t>
+        </is>
+      </c>
+      <c r="G52" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H52" s="170">
+        <f>IF(G52&lt;Assumptions!$B$5,"Before",IF(G52&gt;Assumptions!$C$48,"After",INT((G52-Assumptions!$B$5)/7)+1))</f>
         <v>2</v>
       </c>
-      <c r="I51" s="18" t="inlineStr">
-        <is>
-          <t>Repeating template</t>
-        </is>
-      </c>
-      <c r="J51" s="115" t="inlineStr">
-        <is>
-          <t>Quarterly, due 8 Oct</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="18" t="inlineStr">
-        <is>
-          <t>Telstra</t>
-        </is>
-      </c>
-      <c r="B52" s="110" t="inlineStr">
-        <is>
-          <t>Nighthawk data plans - October</t>
-        </is>
-      </c>
-      <c r="C52" s="137" t="n">
-        <v>46326</v>
-      </c>
-      <c r="D52" s="138" t="n">
-        <v>130</v>
-      </c>
-      <c r="E52" s="33" t="inlineStr">
-        <is>
-          <t>EFT</t>
-        </is>
-      </c>
-      <c r="F52" s="33" t="inlineStr">
-        <is>
-          <t>Telephone &amp; internet</t>
-        </is>
-      </c>
-      <c r="G52" s="137" t="n">
-        <v>46326</v>
-      </c>
-      <c r="H52" s="18">
-        <f>IF(G52&lt;Assumptions!$B$5,"Before",IF(G52&gt;Assumptions!$C$48,"After",INT((G52-Assumptions!$B$5)/7)+1))</f>
-        <v>5</v>
-      </c>
-      <c r="I52" s="18" t="inlineStr">
-        <is>
-          <t>Repeating template</t>
-        </is>
-      </c>
-      <c r="J52" s="115" t="inlineStr">
-        <is>
-          <t>Repeating bill</t>
+      <c r="I52" s="170" t="inlineStr">
+        <is>
+          <t>Xero bill</t>
+        </is>
+      </c>
+      <c r="J52" s="175" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct - BPAY (TTI20227626284, $136)</t>
         </is>
       </c>
     </row>
@@ -9060,7 +9623,7 @@
       </c>
       <c r="J53" s="115" t="inlineStr">
         <is>
-          <t>PL card - in the credit card line</t>
+          <t>Open - PL card, in the card line</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9668,7 @@
       </c>
       <c r="J54" s="115" t="inlineStr">
         <is>
-          <t>PL card - in the credit card line</t>
+          <t>Open - PL card, in the card line</t>
         </is>
       </c>
     </row>
@@ -9964,9 +10527,6 @@
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75"/>
-    <row r="76"/>
     <row r="77" s="109">
       <c r="A77" s="13" t="inlineStr">
         <is>
@@ -9977,7 +10537,7 @@
       <c r="C77" s="16" t="n"/>
       <c r="D77" s="142">
         <f>SUMIFS(D19:D75,I19:I75,"Xero bill")</f>
-        <v>396538.04000000004</v>
+        <v>398159.04</v>
       </c>
       <c r="E77" s="16" t="n"/>
       <c r="F77" s="16" t="n"/>
@@ -10005,7 +10565,7 @@
       </c>
       <c r="D79" s="143">
         <f>SUMIFS(D19:D75,I19:I75,"Repeating template",E19:E75,"&lt;&gt;Card",G19:G75,"&gt;="&amp;Assumptions!$B$5,G19:G75,"&lt;="&amp;Assumptions!$C$48)</f>
-        <v>8655</v>
+        <v>7040</v>
       </c>
     </row>
     <row r="80" s="109">

--- a/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
+++ b/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
@@ -1135,27 +1135,27 @@
       </c>
       <c r="F10" s="119">
         <f>IF(E$8=1,E59,D58)</f>
-        <v>300315.52999999997</v>
+        <v>261282.50999999998</v>
       </c>
       <c r="G10" s="119">
         <f>F10</f>
-        <v>300315.52999999997</v>
+        <v>261282.50999999998</v>
       </c>
       <c r="H10" s="119">
         <f>IF(G$8=1,G59,F58)</f>
-        <v>534919.8166666667</v>
+        <v>495886.79666666663</v>
       </c>
       <c r="I10" s="119">
         <f>H10</f>
-        <v>534919.8166666667</v>
+        <v>495886.79666666663</v>
       </c>
       <c r="J10" s="119">
         <f>IF(I$8=1,I59,H58)</f>
-        <v>269953.74933333334</v>
+        <v>230920.72933333332</v>
       </c>
       <c r="K10" s="119">
         <f>J10</f>
-        <v>269953.74933333334</v>
+        <v>230920.72933333332</v>
       </c>
       <c r="L10" s="119">
         <f>B10</f>
@@ -1716,11 +1716,11 @@
       </c>
       <c r="D27" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
-        <v>4000</v>
+        <v>43033.020000000004</v>
       </c>
       <c r="E27" s="121">
-        <f>ROUND(28736.64*1.1,2)</f>
-        <v>31610.3</v>
+        <f>ROUND(28736.64*1.1,2)+39033.02</f>
+        <v>70643.31999999999</v>
       </c>
       <c r="F27" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
@@ -1739,11 +1739,11 @@
       <c r="K27" s="121" t="n"/>
       <c r="L27" s="120">
         <f>SUM(B27,D27,F27,H27,J27)</f>
-        <v>201453.61000000002</v>
+        <v>240486.63000000003</v>
       </c>
       <c r="M27" s="120">
         <f>SUM(C27,E27,G27,I27,K27)</f>
-        <v>170696.53</v>
+        <v>209729.55</v>
       </c>
       <c r="N27" s="120">
         <f>(C27-B27)*C$8+(E27-D27)*E$8+(G27-F27)*G$8+(I27-H27)*I$8+(K27-J27)*K$8</f>
@@ -1751,7 +1751,7 @@
       </c>
       <c r="O27" s="108" t="inlineStr">
         <is>
-          <t>139k was paid on the 29/09/2026. Remittance (Complete AV) table  under GC approvals was send on the 29/09. Week 2 to 12 Oct: LiveU SDI/modems $26,004 plus small items ($28,737 ex GST per Xero cash P&amp;L).</t>
+          <t>139k was paid on the 29/09/2026. Remittance (Complete AV) table  under GC approvals was send on the 29/09. Week 2 to 12 Oct: LiveU SDI/modems $26,004 plus small items ($28,737 ex GST per Xero cash P&amp;L). Complete AV labour and programming $39,033.02 was released and paid 8 Oct - whole bill now paid.</t>
         </is>
       </c>
     </row>
@@ -1979,11 +1979,11 @@
       </c>
       <c r="D32" s="123">
         <f>D27+D28+D29+D30+D31</f>
-        <v>25112.04</v>
+        <v>64145.060000000005</v>
       </c>
       <c r="E32" s="123">
         <f>E27+E28+E29+E30+E31</f>
-        <v>78843.94</v>
+        <v>117876.95999999999</v>
       </c>
       <c r="F32" s="123">
         <f>F27+F28+F29+F30+F31</f>
@@ -2011,11 +2011,11 @@
       </c>
       <c r="L32" s="123">
         <f>L27+L28+L29+L30+L31</f>
-        <v>319008.68</v>
+        <v>358041.7</v>
       </c>
       <c r="M32" s="123">
         <f>M27+M28+M29+M30+M31</f>
-        <v>217930.16999999998</v>
+        <v>256963.18999999997</v>
       </c>
       <c r="N32" s="123">
         <f>N27+N28+N29+N30+N31</f>
@@ -2914,11 +2914,11 @@
       </c>
       <c r="D55" s="122">
         <f>D24+D32+D49+D53</f>
-        <v>201076.97</v>
+        <v>240109.99</v>
       </c>
       <c r="E55" s="122">
         <f>E24+E32+E49+E53</f>
-        <v>80029.05</v>
+        <v>119062.06999999999</v>
       </c>
       <c r="F55" s="122">
         <f>F24+F32+F49+F66</f>
@@ -2946,11 +2946,11 @@
       </c>
       <c r="L55" s="122">
         <f>L24+L32+L49+L53</f>
-        <v>804956.3139999999</v>
+        <v>843989.3339999999</v>
       </c>
       <c r="M55" s="122">
         <f>M24+M32+M49+M53</f>
-        <v>219360.87999999998</v>
+        <v>258393.89999999997</v>
       </c>
       <c r="N55" s="122">
         <f>N24+N32+N49+N53</f>
@@ -2974,11 +2974,11 @@
       </c>
       <c r="D57" s="122">
         <f>D15-D55</f>
-        <v>-58380.70000000001</v>
+        <v>-97413.72</v>
       </c>
       <c r="E57" s="122">
         <f>E15-E55</f>
-        <v>63173.220000000016</v>
+        <v>24140.200000000026</v>
       </c>
       <c r="F57" s="122">
         <f>F15-F68</f>
@@ -3006,11 +3006,11 @@
       </c>
       <c r="L57" s="122">
         <f>L15-L55</f>
-        <v>-187968.23400000005</v>
+        <v>-227001.25400000007</v>
       </c>
       <c r="M57" s="122">
         <f>M15-M55</f>
-        <v>64016.99000000002</v>
+        <v>24983.97000000003</v>
       </c>
       <c r="N57" s="122">
         <f>N15-N55</f>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="D58" s="125">
         <f>D10+D57</f>
-        <v>300315.52999999997</v>
+        <v>261282.50999999998</v>
       </c>
       <c r="E58" s="125" t="str">
         <f>IF(E$8=1,E10+E57,"")</f>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="F58" s="125">
         <f>F10+F57</f>
-        <v>534919.8166666667</v>
+        <v>495886.79666666663</v>
       </c>
       <c r="G58" s="125" t="str">
         <f>IF(G$8=1,G10+G57,"")</f>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H58" s="125">
         <f>H10+H57</f>
-        <v>269953.74933333334</v>
+        <v>230920.72933333332</v>
       </c>
       <c r="I58" s="125" t="str">
         <f>IF(I$8=1,I10+I57,"")</f>
@@ -3058,7 +3058,7 @@
       </c>
       <c r="J58" s="125">
         <f>J10+J57</f>
-        <v>309772.966</v>
+        <v>270739.946</v>
       </c>
       <c r="K58" s="125" t="str">
         <f>IF(K$8=1,K10+K57,"")</f>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="L58" s="125">
         <f>J58</f>
-        <v>309772.966</v>
+        <v>270739.946</v>
       </c>
       <c r="M58" s="125">
         <f>IF(K$8=1,K58,IF(I$8=1,I58,IF(G$8=1,G58,IF(E$8=1,E58,IF(C$8=1,C58,"")))))</f>
@@ -3208,19 +3208,19 @@
       </c>
       <c r="D64" s="127">
         <f>IF(Payroll!$I$5=0,0,D58/(Payroll!$I$5/2))</f>
-        <v>6.032370440302104</v>
+        <v>5.248322955166318</v>
       </c>
       <c r="F64" s="127">
         <f>IF(Payroll!$I$5=0,0,F58/(Payroll!$I$5/2))</f>
-        <v>10.744813929508812</v>
+        <v>9.960766444373023</v>
       </c>
       <c r="H64" s="127">
         <f>IF(Payroll!$I$5=0,0,H58/(Payroll!$I$5/2))</f>
-        <v>5.422500187476565</v>
+        <v>4.638452702340778</v>
       </c>
       <c r="J64" s="127">
         <f>IF(Payroll!$I$5=0,0,J58/(Payroll!$I$5/2))</f>
-        <v>6.2223398280572075</v>
+        <v>5.438292342921421</v>
       </c>
       <c r="O64" s="108" t="n"/>
     </row>
@@ -3248,11 +3248,11 @@
       </c>
       <c r="L66" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$G$19:$G$75,"&gt;"&amp;Assumptions!$C$48)</f>
-        <v>69117.8</v>
+        <v>30084.780000000002</v>
       </c>
       <c r="O66" s="108" t="inlineStr">
         <is>
-          <t>Complete AV labour $41,956 (held for Aware sign off), Oct rent, Oct mobiles.</t>
+          <t>Oct rent, Oct mobiles. (Complete AV labour was released and paid 8 Oct, so nothing held now.)</t>
         </is>
       </c>
     </row>
@@ -3280,14 +3280,14 @@
     <row r="69" ht="15.75" customHeight="1" s="109">
       <c r="A69" s="110" t="inlineStr">
         <is>
-          <t>1. Aware Super $225,887 (INV-10596) is the big one - still not paid at 12 Oct and now expected 9 Nov, after this forecast. Complete AV materials $133,246 went out 29 Sep. If Aware slip again the held labour stays held and we watch the cheque account. Build-up on the Complete AV tab.</t>
+          <t>1. Aware Super $225,887 (INV-10596) is the big one - still not paid at 12 Oct and now expected 9 Nov, after this forecast. The whole Complete AV bill ($178,119) is now paid ahead of it (materials 29 Sep, labour 8 Oct), so we watch the cheque account until Aware pay. Build-up on the Complete AV tab.</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="109">
       <c r="A70" s="110" t="inlineStr">
         <is>
-          <t>2. Complete AV labour and programming ($41,956 inc GST) is held until Aware sign off and we get the handover docs - agreed 28 Sep. Jordan thinks they may push for programming or sub-trade costs. If we agree to any, add them on the Payables tab.</t>
+          <t>2. Complete AV labour and programming ($39,033 inc GST) was released and paid 8 Oct, so INV41565 is fully paid. The $5,334 balance of the quote is still to be invoiced (claim 3). Jordan thinks they may push for programming or sub-trade costs - if we agree to any, add them on the Payables tab.</t>
         </is>
       </c>
     </row>
@@ -7924,23 +7924,23 @@
     </row>
     <row r="14">
       <c r="A14" s="176" t="str">
-        <f>A34</f>
-        <v>Posh Services (Ambius)</v>
+        <f>A21</f>
+        <v>Complete AV Solutions</v>
       </c>
       <c r="B14" s="177" t="str">
-        <f>B34</f>
-        <v>INV21736844 - indoor plants Sep</v>
+        <f>B21</f>
+        <v>INV41565 - Aware seminar room: LABOUR &amp; PROGRAMMING portion - released</v>
       </c>
       <c r="C14" s="178">
-        <f>C34</f>
-        <v>46304</v>
+        <f>C21</f>
+        <v>46291</v>
       </c>
       <c r="D14" s="179">
-        <f>D34</f>
-        <v>245</v>
+        <f>D21</f>
+        <v>39033.020000000004</v>
       </c>
       <c r="E14" s="176" t="str">
-        <f>E34</f>
+        <f>E21</f>
         <v>EFT</v>
       </c>
       <c r="F14" s="180" t="inlineStr">
@@ -7949,14 +7949,14 @@
         </is>
       </c>
       <c r="G14" s="181">
-        <f>G34</f>
+        <f>G21</f>
         <v>46303</v>
       </c>
       <c r="H14" s="182" t="n"/>
       <c r="I14" s="182" t="n"/>
       <c r="J14" s="175" t="inlineStr">
         <is>
-          <t>Posh plants - paid</t>
+          <t>Complete AV labour and programming - hold released, paid</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7970,7 @@
       <c r="C15" s="16" t="n"/>
       <c r="D15" s="142">
         <f>SUM(D6:D14)</f>
-        <v>76418.96999999999</v>
+        <v>115206.98999999999</v>
       </c>
       <c r="E15" s="16" t="n"/>
       <c r="F15" s="16" t="n"/>
@@ -8137,53 +8137,53 @@
       </c>
       <c r="J20" s="175" t="inlineStr">
         <is>
-          <t>PAID 29 Sep (Xero shows the whole bill as paid 8 Oct - see note on the hold).</t>
+          <t>PAID 29 Sep</t>
         </is>
       </c>
     </row>
     <row r="21" ht="72" customHeight="1" s="109">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="170" t="inlineStr">
         <is>
           <t>Complete AV Solutions</t>
         </is>
       </c>
-      <c r="B21" s="110" t="inlineStr">
-        <is>
-          <t>INV41565 - Aware seminar room: LABOUR &amp; PROGRAMMING portion - HELD</t>
-        </is>
-      </c>
-      <c r="C21" s="137" t="n">
+      <c r="B21" s="183" t="inlineStr">
+        <is>
+          <t>INV41565 - Aware seminar room: LABOUR &amp; PROGRAMMING portion - released</t>
+        </is>
+      </c>
+      <c r="C21" s="171" t="n">
         <v>46291</v>
       </c>
-      <c r="D21" s="148">
+      <c r="D21" s="179">
         <f>'Complete AV'!L19-'Complete AV'!L22</f>
         <v>39033.020000000004</v>
       </c>
-      <c r="E21" s="33" t="inlineStr">
+      <c r="E21" s="173" t="inlineStr">
         <is>
           <t>EFT</t>
         </is>
       </c>
-      <c r="F21" s="33" t="inlineStr">
+      <c r="F21" s="173" t="inlineStr">
         <is>
           <t>Equipment purchases</t>
         </is>
       </c>
-      <c r="G21" s="141" t="n">
-        <v>46356</v>
-      </c>
-      <c r="H21" s="18" t="str">
+      <c r="G21" s="171" t="n">
+        <v>46303</v>
+      </c>
+      <c r="H21" s="170">
         <f>IF(G21&lt;Assumptions!$B$5,"Before",IF(G21&gt;Assumptions!$C$48,"After",INT((G21-Assumptions!$B$5)/7)+1))</f>
-        <v>After</v>
-      </c>
-      <c r="I21" s="18" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I21" s="170" t="inlineStr">
         <is>
           <t>Xero bill</t>
         </is>
       </c>
-      <c r="J21" s="115" t="inlineStr">
-        <is>
-          <t>HELD - agreed 28 Sep, released on Aware sign off and handover docs. Xero shows INV41565 fully paid on 8 Oct ($178,119.25) - if the $44,873 did go out, it needs to go into week 2 actuals.</t>
+      <c r="J21" s="175" t="inlineStr">
+        <is>
+          <t>PAID 8 Oct - the hold was released last week. Whole of INV41565 ($178,119.25) is now paid, matches Xero.</t>
         </is>
       </c>
     </row>
@@ -10571,12 +10571,12 @@
     <row r="80" s="109">
       <c r="A80" s="29" t="inlineStr">
         <is>
-          <t>Non-card bills dated past the forecast (Complete AV labour hold, Oct rent, Oct mobiles)</t>
+          <t>Non-card bills dated past the forecast (Oct rent, Oct mobiles)</t>
         </is>
       </c>
       <c r="D80" s="143">
         <f>SUMIFS(D19:D75,E19:E75,"&lt;&gt;Card",G19:G75,"&gt;"&amp;Assumptions!$C$48)</f>
-        <v>69117.8</v>
+        <v>30084.780000000002</v>
       </c>
     </row>
   </sheetData>
@@ -10619,14 +10619,14 @@
     <row r="1" ht="18" customHeight="1" s="109">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Complete AV Solutions - INV41565 - what we're paying and what's held</t>
+          <t>Complete AV Solutions - INV41565 - what we paid and when</t>
         </is>
       </c>
     </row>
     <row r="2" ht="42" customHeight="1" s="109">
       <c r="A2" s="115" t="inlineStr">
         <is>
-          <t>Aware Super seminar room audio upgrade (Q-12140v1, PO-00016902). Bill total $178,119.25 inc GST, dated 1 Sep, due 26 Sep. Agreed 28 Sep (Graham / Jordan): pay the materials now, hold labour and programming until Aware sign off and we get the handover docs. Line items are straight off the bill in Xero.</t>
+          <t>Aware Super seminar room audio upgrade (Q-12140v1, PO-00016902). Bill total $178,119.25 inc GST, dated 1 Sep, due 26 Sep. Agreed 28 Sep (Graham / Jordan): pay the materials now, hold labour and programming until Aware sign off and we get the handover docs. Line items are straight off the bill in Xero. Update 12 Oct: the labour and programming that was held ($39,033.02) was released and paid Thu 8 Oct, so the whole bill is now paid.</t>
         </is>
       </c>
       <c r="G2" s="116" t="inlineStr">
@@ -11577,7 +11577,7 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>HELD - labour and programming (until Aware sign off + handover docs)</t>
+          <t>LABOUR AND PROGRAMMING - was held, released and PAID Thu 8 Oct</t>
         </is>
       </c>
       <c r="B48" s="114" t="n"/>

--- a/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
+++ b/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
@@ -1107,7 +1107,7 @@
       <c r="N8" s="12" t="n"/>
       <c r="O8" s="76" t="inlineStr">
         <is>
-          <t>Week 1 is done and ties to CommBiz. Week 2 actuals are in to Mon 12 Oct only - flag stays 0 until the week closes Wed 14 Oct and the bank balance is keyed.</t>
+          <t>Week 1 is done and reconciles to Xero (flag 1). Week 2 actuals are in to Mon 12 Oct only - flag stays 0 until the week closes Wed 14 Oct and the bank balance is keyed.</t>
         </is>
       </c>
     </row>
@@ -1127,35 +1127,35 @@
       </c>
       <c r="D10" s="119">
         <f>IF(C$8=1,C59,B58)</f>
-        <v>358696.23</v>
+        <v>261747.39999999997</v>
       </c>
       <c r="E10" s="119">
         <f>D10</f>
-        <v>358696.23</v>
+        <v>261747.39999999997</v>
       </c>
       <c r="F10" s="119">
         <f>IF(E$8=1,E59,D58)</f>
-        <v>261282.50999999998</v>
+        <v>263901.67999999993</v>
       </c>
       <c r="G10" s="119">
         <f>F10</f>
-        <v>261282.50999999998</v>
+        <v>263901.67999999993</v>
       </c>
       <c r="H10" s="119">
         <f>IF(G$8=1,G59,F58)</f>
-        <v>495886.79666666663</v>
+        <v>498505.9666666666</v>
       </c>
       <c r="I10" s="119">
         <f>H10</f>
-        <v>495886.79666666663</v>
+        <v>498505.9666666666</v>
       </c>
       <c r="J10" s="119">
         <f>IF(I$8=1,I59,H58)</f>
-        <v>230920.72933333332</v>
+        <v>333107.8993333333</v>
       </c>
       <c r="K10" s="119">
         <f>J10</f>
-        <v>230920.72933333332</v>
+        <v>333107.8993333333</v>
       </c>
       <c r="L10" s="119">
         <f>B10</f>
@@ -1200,8 +1200,8 @@
         <v>134590.91999999998</v>
       </c>
       <c r="C13" s="121">
-        <f>41925.4+6172.39+58024.76+1975.51+1092.3+13046.62+4352.45+13156</f>
-        <v>139745.43</v>
+        <f>41925.4+6172.39+58024.76+1975.51+1092.3+13046.62+4352.45+13156+9350+93.5+627+8043.2</f>
+        <v>157859.13</v>
       </c>
       <c r="D13" s="120">
         <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$45,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$45)</f>
@@ -1232,15 +1232,15 @@
       </c>
       <c r="M13" s="120">
         <f>SUM(C13,E13,G13,I13,K13)</f>
-        <v>282947.7</v>
+        <v>301061.4</v>
       </c>
       <c r="N13" s="120">
         <f>(C13-B13)*C$8+(E13-D13)*E$8+(G13-F13)*G$8+(I13-H13)*I$8+(K13-J13)*K$8</f>
-        <v>5154.510000000009</v>
+        <v>23268.21000000002</v>
       </c>
       <c r="O13" s="108" t="inlineStr">
         <is>
-          <t>Week 2 to 12 Oct: Deloitte $112,683.22 and $18,891.66, CEO Institute $9,086.39, ASX $1,661, Dimensional $506, Ricoh $374 (Xero). Nothing from Aware yet.</t>
+          <t>Week 1 now includes 6-7 Oct: PwC $9,350, CBA Melb $93.50, APA $627, CBA Bris $8,043.20. Week 2 to 12 Oct: Deloitte $112,683.22 and $18,891.66, CEO Institute $9,086.39, ASX $1,661, Dimensional $506, Ricoh $374. Nothing from Aware yet.</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="C15" s="122">
         <f>C13+C14</f>
-        <v>140175.6</v>
+        <v>158289.30000000002</v>
       </c>
       <c r="D15" s="122">
         <f>D13+D14</f>
@@ -1349,11 +1349,11 @@
       </c>
       <c r="M15" s="122">
         <f>M13+M14</f>
-        <v>283377.87</v>
+        <v>301491.57</v>
       </c>
       <c r="N15" s="122">
         <f>N13+N14</f>
-        <v>5584.680000000009</v>
+        <v>23698.38000000002</v>
       </c>
       <c r="O15" s="16" t="n"/>
     </row>
@@ -1393,44 +1393,49 @@
       </c>
       <c r="B19" s="120">
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$44,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$44)</f>
-        <v>0</v>
-      </c>
-      <c r="C19" s="121" t="n"/>
+        <v>85248</v>
+      </c>
+      <c r="C19" s="121">
+        <f>71172.55+9443.5-880</f>
+        <v>79736.05</v>
+      </c>
       <c r="D19" s="120">
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$45,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$45)</f>
-        <v>85248</v>
-      </c>
-      <c r="E19" s="121" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E19" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="F19" s="120">
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$46,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$46)</f>
-        <v>0</v>
+        <v>85248</v>
       </c>
       <c r="G19" s="121" t="n"/>
       <c r="H19" s="120">
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$47,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$47)</f>
-        <v>85248</v>
+        <v>0</v>
       </c>
       <c r="I19" s="121" t="n"/>
       <c r="J19" s="120">
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$48,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$48)</f>
-        <v>0</v>
+        <v>85248</v>
       </c>
       <c r="K19" s="121" t="n"/>
       <c r="L19" s="120">
         <f>SUM(B19,D19,F19,H19,J19)</f>
-        <v>170496</v>
+        <v>255744</v>
       </c>
       <c r="M19" s="120">
         <f>SUM(C19,E19,G19,I19,K19)</f>
-        <v>0</v>
+        <v>79736.05</v>
       </c>
       <c r="N19" s="120">
         <f>(C19-B19)*C$8+(E19-D19)*E$8+(G19-F19)*G$8+(I19-H19)*I$8+(K19-J19)*K$8</f>
-        <v>0</v>
+        <v>-5511.949999999997</v>
       </c>
       <c r="O19" s="108" t="inlineStr">
         <is>
-          <t>Payroll tab - gross x net %. Fortnight is Sat to Fri and the money goes out the Tuesday after: Tue 13 Oct (week 2) and Tue 27 Oct (week 4). The next one is Tue 10 Nov, after this forecast.</t>
+          <t>Payroll tab - gross x net %. Fortnight is Sat to Fri and the money goes out the Tuesday after: Tue 6 Oct (week 1), Tue 20 Oct (week 3) and Tue 3 Nov (week 5). 6 Oct actual is from the Xero bank movement - swap in the ABA figure.</t>
         </is>
       </c>
     </row>
@@ -1442,40 +1447,44 @@
       </c>
       <c r="B20" s="120">
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$44,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$44)</f>
-        <v>0</v>
-      </c>
-      <c r="C20" s="121" t="n"/>
+        <v>13320</v>
+      </c>
+      <c r="C20" s="121" t="n">
+        <v>13083.54</v>
+      </c>
       <c r="D20" s="120">
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$45,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$45)</f>
-        <v>13320</v>
-      </c>
-      <c r="E20" s="121" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E20" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="F20" s="120">
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$46,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$46)</f>
-        <v>0</v>
+        <v>13320</v>
       </c>
       <c r="G20" s="121" t="n"/>
       <c r="H20" s="120">
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$47,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$47)</f>
-        <v>13320</v>
+        <v>0</v>
       </c>
       <c r="I20" s="121" t="n"/>
       <c r="J20" s="120">
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$48,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$48)</f>
-        <v>0</v>
+        <v>13320</v>
       </c>
       <c r="K20" s="121" t="n"/>
       <c r="L20" s="120">
         <f>SUM(B20,D20,F20,H20,J20)</f>
-        <v>26640</v>
+        <v>39960</v>
       </c>
       <c r="M20" s="120">
         <f>SUM(C20,E20,G20,I20,K20)</f>
-        <v>0</v>
+        <v>13083.54</v>
       </c>
       <c r="N20" s="120">
         <f>(C20-B20)*C$8+(E20-D20)*E$8+(G20-F20)*G$8+(I20-H20)*I$8+(K20-J20)*K$8</f>
-        <v>0</v>
+        <v>-236.45999999999913</v>
       </c>
       <c r="O20" s="108" t="inlineStr">
         <is>
@@ -1544,7 +1553,9 @@
         <f>IF(AND(Assumptions!$B$19&gt;=Assumptions!$B$44,Assumptions!$B$19&lt;=Assumptions!$C$44),Assumptions!$B$17+Assumptions!$B$18,0)</f>
         <v>8995</v>
       </c>
-      <c r="C22" s="121" t="n"/>
+      <c r="C22" s="121" t="n">
+        <v>8602.75</v>
+      </c>
       <c r="D22" s="120">
         <f>IF(AND(Assumptions!$B$19&gt;=Assumptions!$B$45,Assumptions!$B$19&lt;=Assumptions!$C$45),Assumptions!$B$17+Assumptions!$B$18,0)</f>
         <v>0</v>
@@ -1573,15 +1584,15 @@
       </c>
       <c r="M22" s="120">
         <f>SUM(C22,E22,G22,I22,K22)</f>
-        <v>0</v>
+        <v>8602.75</v>
       </c>
       <c r="N22" s="120">
         <f>(C22-B22)*C$8+(E22-D22)*E$8+(G22-F22)*G$8+(I22-H22)*I$8+(K22-J22)*K$8</f>
-        <v>-8995</v>
+        <v>-392.25</v>
       </c>
       <c r="O22" s="108" t="inlineStr">
         <is>
-          <t>Sep wages, due 7 Oct. Aug numbers used until the Sep return is lodged ($6,295 NSW + $2,700 other states).</t>
+          <t>Sep wages, due 7 Oct. Paid Wed 7 Oct - $8,602.75 per Xero. Aug numbers were used for the forecast ($6,295 NSW + $2,700 other).</t>
         </is>
       </c>
     </row>
@@ -1593,32 +1604,34 @@
       </c>
       <c r="B23" s="120">
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$44,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$44)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="C23" s="121" t="n"/>
       <c r="D23" s="120">
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$45,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$45)</f>
-        <v>1000</v>
-      </c>
-      <c r="E23" s="121" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="E23" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="F23" s="120">
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$46,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$46)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G23" s="121" t="n"/>
       <c r="H23" s="120">
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$47,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$47)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="I23" s="121" t="n"/>
       <c r="J23" s="120">
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$48,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$48)</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K23" s="121" t="n"/>
       <c r="L23" s="120">
         <f>SUM(B23,D23,F23,H23,J23)</f>
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="M23" s="120">
         <f>SUM(C23,E23,G23,I23,K23)</f>
@@ -1626,11 +1639,11 @@
       </c>
       <c r="N23" s="120">
         <f>(C23-B23)*C$8+(E23-D23)*E$8+(G23-F23)*G$8+(I23-H23)*I$8+(K23-J23)*K$8</f>
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="O23" s="108" t="inlineStr">
         <is>
-          <t>Placeholder. Week 2 actual gets filled on pay day Tue 13 Oct.</t>
+          <t>Placeholder. Expense claims go out with the ABA, so the 6 Oct actual net pay already has them in it.</t>
         </is>
       </c>
     </row>
@@ -1642,15 +1655,15 @@
       </c>
       <c r="B24" s="123">
         <f>B19+B20+B21+B22+B23</f>
-        <v>8995</v>
+        <v>108563</v>
       </c>
       <c r="C24" s="123">
         <f>C19+C20+C21+C22+C23</f>
-        <v>0</v>
+        <v>101422.34</v>
       </c>
       <c r="D24" s="123">
         <f>D19+D20+D21+D22+D23</f>
-        <v>99568</v>
+        <v>0</v>
       </c>
       <c r="E24" s="123">
         <f>E19+E20+E21+E22+E23</f>
@@ -1658,7 +1671,7 @@
       </c>
       <c r="F24" s="123">
         <f>F19+F20+F21+F22+F23</f>
-        <v>0</v>
+        <v>99568</v>
       </c>
       <c r="G24" s="123">
         <f>G19+G20+G21+G22+G23</f>
@@ -1666,7 +1679,7 @@
       </c>
       <c r="H24" s="123">
         <f>H19+H20+H21+H22+H23</f>
-        <v>99568</v>
+        <v>0</v>
       </c>
       <c r="I24" s="123">
         <f>I19+I20+I21+I22+I23</f>
@@ -1674,7 +1687,7 @@
       </c>
       <c r="J24" s="123">
         <f>J19+J20+J21+J22+J23</f>
-        <v>0</v>
+        <v>99568</v>
       </c>
       <c r="K24" s="123">
         <f>K19+K20+K21+K22+K23</f>
@@ -1682,15 +1695,15 @@
       </c>
       <c r="L24" s="123">
         <f>L19+L20+L21+L22+L23</f>
-        <v>208131</v>
+        <v>307699</v>
       </c>
       <c r="M24" s="123">
         <f>M19+M20+M21+M22+M23</f>
-        <v>0</v>
+        <v>101422.34</v>
       </c>
       <c r="N24" s="123">
         <f>N19+N20+N21+N22+N23</f>
-        <v>-8995</v>
+        <v>-7140.659999999996</v>
       </c>
       <c r="O24" s="12" t="n"/>
     </row>
@@ -2193,7 +2206,9 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>1680</v>
       </c>
-      <c r="C38" s="121" t="n"/>
+      <c r="C38" s="121" t="n">
+        <v>880</v>
+      </c>
       <c r="D38" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>1680</v>
@@ -2222,11 +2237,11 @@
       </c>
       <c r="M38" s="120">
         <f>SUM(C38,E38,G38,I38,K38)</f>
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="N38" s="120">
         <f>(C38-B38)*C$8+(E38-D38)*E$8+(G38-F38)*G$8+(I38-H38)*I$8+(K38-J38)*K$8</f>
-        <v>-1680</v>
+        <v>-800</v>
       </c>
       <c r="O38" s="108" t="inlineStr">
         <is>
@@ -2606,7 +2621,9 @@
         <f>Assumptions!$B$37/5</f>
         <v>5000</v>
       </c>
-      <c r="C46" s="121" t="n"/>
+      <c r="C46" s="121" t="n">
+        <v>10000</v>
+      </c>
       <c r="D46" s="120">
         <f>Assumptions!$B$37/5</f>
         <v>5000</v>
@@ -2635,15 +2652,15 @@
       </c>
       <c r="M46" s="120">
         <f>SUM(C46,E46,G46,I46,K46)</f>
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="N46" s="120">
         <f>(C46-B46)*C$8+(E46-D46)*E$8+(G46-F46)*G$8+(I46-H46)*I$8+(K46-J46)*K$8</f>
-        <v>-5000</v>
+        <v>5000</v>
       </c>
       <c r="O46" s="108" t="inlineStr">
         <is>
-          <t>~$25k a month transferred to the PL and DL cards. Covers every Card row on the Payables tab (subscriptions, travel, electricity, Seek, Goget, EH).</t>
+          <t>~$25k a month transferred to the PL and DL cards. Covers every Card row on the Payables tab (subscriptions, travel, electricity, Seek, Goget, EH). Week 1 actual: $10,000 moved to the PL card 7 Oct.</t>
         </is>
       </c>
     </row>
@@ -2733,7 +2750,7 @@
       </c>
       <c r="C49" s="123">
         <f>C35+C36+C37+C38+C39+C40+C41+C42+C43+C44+C45+C46+C47+C48</f>
-        <v>77548.14</v>
+        <v>88428.14</v>
       </c>
       <c r="D49" s="123">
         <f>D35+D36+D37+D38+D39+D40+D41+D42+D43+D44+D45+D46+D47</f>
@@ -2773,11 +2790,11 @@
       </c>
       <c r="M49" s="123">
         <f>M35+M36+M37+M38+M39+M40+M41+M42+M43+M44+M45+M46+M47</f>
-        <v>1430.71</v>
+        <v>12310.71</v>
       </c>
       <c r="N49" s="123">
         <f>N35+N36+N37+N38+N39+N40+N41+N42+N43+N44+N45+N46+N47</f>
-        <v>-14870</v>
+        <v>-3990</v>
       </c>
       <c r="O49" s="12" t="n"/>
     </row>
@@ -2906,15 +2923,15 @@
       </c>
       <c r="B55" s="122">
         <f>B24+B32+B49+B53</f>
-        <v>213633.83</v>
+        <v>313201.82999999996</v>
       </c>
       <c r="C55" s="122">
         <f>C24+C32+C49+C53</f>
-        <v>216634.37</v>
+        <v>328936.71</v>
       </c>
       <c r="D55" s="122">
         <f>D24+D32+D49+D53</f>
-        <v>240109.99</v>
+        <v>140541.99</v>
       </c>
       <c r="E55" s="122">
         <f>E24+E32+E49+E53</f>
@@ -2922,7 +2939,7 @@
       </c>
       <c r="F55" s="122">
         <f>F24+F32+F49+F66</f>
-        <v>60002.060000000005</v>
+        <v>159570.06</v>
       </c>
       <c r="G55" s="122">
         <f>G24+G32+G49+G53</f>
@@ -2930,7 +2947,7 @@
       </c>
       <c r="H55" s="122">
         <f>H24+H32+H49+H53</f>
-        <v>277592.534</v>
+        <v>178024.53399999999</v>
       </c>
       <c r="I55" s="122">
         <f>I24+I32+I49+I53</f>
@@ -2938,7 +2955,7 @@
       </c>
       <c r="J55" s="122">
         <f>J24+J32+J49+J53</f>
-        <v>52650.92</v>
+        <v>152218.92</v>
       </c>
       <c r="K55" s="122">
         <f>K24+K32+K49+K53</f>
@@ -2946,15 +2963,15 @@
       </c>
       <c r="L55" s="122">
         <f>L24+L32+L49+L53</f>
-        <v>843989.3339999999</v>
+        <v>943557.3339999999</v>
       </c>
       <c r="M55" s="122">
         <f>M24+M32+M49+M53</f>
-        <v>258393.89999999997</v>
+        <v>370696.24</v>
       </c>
       <c r="N55" s="122">
         <f>N24+N32+N49+N53</f>
-        <v>-74301.99999999999</v>
+        <v>-61567.65999999998</v>
       </c>
       <c r="O55" s="16" t="n"/>
     </row>
@@ -2966,15 +2983,15 @@
       </c>
       <c r="B57" s="122">
         <f>B15-B55</f>
-        <v>-79042.91</v>
+        <v>-178610.90999999997</v>
       </c>
       <c r="C57" s="122">
         <f>C15-C55</f>
-        <v>-76458.76999999999</v>
+        <v>-170647.41</v>
       </c>
       <c r="D57" s="122">
         <f>D15-D55</f>
-        <v>-97413.72</v>
+        <v>2154.279999999999</v>
       </c>
       <c r="E57" s="122">
         <f>E15-E55</f>
@@ -2990,7 +3007,7 @@
       </c>
       <c r="H57" s="122">
         <f>H15-H55</f>
-        <v>-264966.0673333333</v>
+        <v>-165398.0673333333</v>
       </c>
       <c r="I57" s="122">
         <f>I15-I55</f>
@@ -2998,7 +3015,7 @@
       </c>
       <c r="J57" s="122">
         <f>J15-J55</f>
-        <v>39819.21666666666</v>
+        <v>-59748.783333333355</v>
       </c>
       <c r="K57" s="122">
         <f>K15-K55</f>
@@ -3006,15 +3023,15 @@
       </c>
       <c r="L57" s="122">
         <f>L15-L55</f>
-        <v>-227001.25400000007</v>
+        <v>-326569.2540000001</v>
       </c>
       <c r="M57" s="122">
         <f>M15-M55</f>
-        <v>24983.97000000003</v>
+        <v>-69204.66999999998</v>
       </c>
       <c r="N57" s="122">
         <f>N15-N55</f>
-        <v>79886.68</v>
+        <v>85266.04000000001</v>
       </c>
       <c r="O57" s="16" t="n"/>
     </row>
@@ -3026,15 +3043,15 @@
       </c>
       <c r="B58" s="125">
         <f>B10+B57</f>
-        <v>356112.08999999997</v>
+        <v>256544.09000000003</v>
       </c>
       <c r="C58" s="125">
         <f>C10+C57</f>
-        <v>358696.23</v>
+        <v>264507.58999999997</v>
       </c>
       <c r="D58" s="125">
         <f>D10+D57</f>
-        <v>261282.50999999998</v>
+        <v>263901.67999999993</v>
       </c>
       <c r="E58" s="125" t="str">
         <f>IF(E$8=1,E10+E57,"")</f>
@@ -3042,7 +3059,7 @@
       </c>
       <c r="F58" s="125">
         <f>F10+F57</f>
-        <v>495886.79666666663</v>
+        <v>498505.9666666666</v>
       </c>
       <c r="G58" s="125" t="str">
         <f>IF(G$8=1,G10+G57,"")</f>
@@ -3050,7 +3067,7 @@
       </c>
       <c r="H58" s="125">
         <f>H10+H57</f>
-        <v>230920.72933333332</v>
+        <v>333107.8993333333</v>
       </c>
       <c r="I58" s="125" t="str">
         <f>IF(I$8=1,I10+I57,"")</f>
@@ -3058,7 +3075,7 @@
       </c>
       <c r="J58" s="125">
         <f>J10+J57</f>
-        <v>270739.946</v>
+        <v>273359.1159999999</v>
       </c>
       <c r="K58" s="125" t="str">
         <f>IF(K$8=1,K10+K57,"")</f>
@@ -3066,11 +3083,11 @@
       </c>
       <c r="L58" s="125">
         <f>J58</f>
-        <v>270739.946</v>
+        <v>273359.1159999999</v>
       </c>
       <c r="M58" s="125">
         <f>IF(K$8=1,K58,IF(I$8=1,I58,IF(G$8=1,G58,IF(E$8=1,E58,IF(C$8=1,C58,"")))))</f>
-        <v>358696.23</v>
+        <v>264507.58999999997</v>
       </c>
       <c r="N58" s="26" t="n"/>
       <c r="O58" s="78" t="inlineStr">
@@ -3087,8 +3104,8 @@
       </c>
       <c r="B59" s="10" t="n"/>
       <c r="C59" s="121">
-        <f>88266.06+270430.17</f>
-        <v>358696.23</v>
+        <f>358696.23-86948.83-10000</f>
+        <v>261747.39999999997</v>
       </c>
       <c r="D59" s="10" t="n"/>
       <c r="E59" s="121" t="n"/>
@@ -3103,7 +3120,7 @@
       <c r="N59" s="12" t="n"/>
       <c r="O59" s="79" t="inlineStr">
         <is>
-          <t>Type the real closing balance (cheque + savings) in at the end of each week. Week 2 - key it Wed 14 Oct, then set the flag to 1.</t>
+          <t>Type the real closing balance (cheque + savings) in at the end of each week. Week 1 is worked back from Xero: $358,696.23 at Mon 5 Oct, less the $86,948.83 Xero cash drop over 6-7 Oct and the $10k card transfer - replace with the CommBiz 7 Oct figure. Week 2 - key it Wed 14 Oct, then set the flag to 1.</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3133,7 @@
       <c r="B60" s="10" t="n"/>
       <c r="C60" s="126">
         <f>C58-C59</f>
-        <v>0</v>
+        <v>2760.1900000000023</v>
       </c>
       <c r="D60" s="10" t="n"/>
       <c r="E60" s="126" t="str">
@@ -3143,7 +3160,7 @@
       <c r="N60" s="12" t="n"/>
       <c r="O60" s="76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Should be nil once everything's in. this is a sense check </t>
+          <t>Should be nil once everything's in. Week 1 is about $2.8k unexplained - small card / bank items on 6-7 Oct that aren't on a bill. Clears when the real 7 Oct balance goes in.</t>
         </is>
       </c>
     </row>
@@ -3176,23 +3193,23 @@
       </c>
       <c r="B63" s="120">
         <f>B19+B20+B23</f>
-        <v>0</v>
+        <v>99568</v>
       </c>
       <c r="D63" s="120">
         <f>D19+D20+D23</f>
-        <v>99568</v>
+        <v>0</v>
       </c>
       <c r="F63" s="120">
         <f>F19+F20+F23</f>
-        <v>0</v>
+        <v>99568</v>
       </c>
       <c r="H63" s="120">
         <f>H19+H20+H23</f>
-        <v>99568</v>
+        <v>0</v>
       </c>
       <c r="J63" s="120">
         <f>J19+J20+J23</f>
-        <v>0</v>
+        <v>99568</v>
       </c>
       <c r="O63" s="108" t="n"/>
     </row>
@@ -3204,23 +3221,23 @@
       </c>
       <c r="B64" s="127">
         <f>IF(Payroll!$I$5=0,0,B58/(Payroll!$I$5/2))</f>
-        <v>7.153143379399003</v>
+        <v>5.153143379399004</v>
       </c>
       <c r="D64" s="127">
         <f>IF(Payroll!$I$5=0,0,D58/(Payroll!$I$5/2))</f>
-        <v>5.248322955166318</v>
+        <v>5.300933633295837</v>
       </c>
       <c r="F64" s="127">
         <f>IF(Payroll!$I$5=0,0,F58/(Payroll!$I$5/2))</f>
-        <v>9.960766444373023</v>
+        <v>10.013377122502543</v>
       </c>
       <c r="H64" s="127">
         <f>IF(Payroll!$I$5=0,0,H58/(Payroll!$I$5/2))</f>
-        <v>4.638452702340778</v>
+        <v>6.691063380470298</v>
       </c>
       <c r="J64" s="127">
         <f>IF(Payroll!$I$5=0,0,J58/(Payroll!$I$5/2))</f>
-        <v>5.438292342921421</v>
+        <v>5.490903021050938</v>
       </c>
       <c r="O64" s="108" t="n"/>
     </row>
@@ -3377,7 +3394,7 @@
       </c>
       <c r="C5" s="115" t="inlineStr">
         <is>
-          <t>Mon 28 Sep. Week 1 runs through to Wed 7 Oct so it picks up payroll tax on the 7th, then it's weekly from there (Thu to Wed). Week table is at the bottom of this tab.</t>
+          <t>Mon 28 Sep. Week 1 runs through to Wed 7 Oct so it picks up the 6 Oct pay run and payroll tax on the 7th, then it's weekly from there (Thu to Wed). Week table is at the bottom of this tab.</t>
         </is>
       </c>
     </row>
@@ -3500,45 +3517,45 @@
     <row r="14" ht="24" customHeight="1" s="109">
       <c r="A14" s="18" t="inlineStr">
         <is>
-          <t>Pay date - run 1 (fortnight Sat 26 Sep to Fri 9 Oct)</t>
+          <t>Pay date - run 1 (fortnight Sat 19 Sep to Fri 2 Oct)</t>
         </is>
       </c>
       <c r="B14" s="128" t="n">
-        <v>46308</v>
+        <v>46301</v>
       </c>
       <c r="C14" s="115" t="inlineStr">
         <is>
-          <t>Fortnight is Sat 26 Sep to Fri 9 Oct. Processed Mon 12 Oct, out of the bank Tue 13 Oct (week 2). Xero has the pay run journal dated 8-9 Oct for $101,246 gross - that is the journal date, the money goes on the Tuesday. Super direct debits the same week - payday super since 1 Jul 26.</t>
+          <t>Fortnight Sat 19 Sep to Fri 2 Oct, out of the bank Tue 6 Oct (week 1). Xero bank shows about $79.7k leaving on the 6th and super + payroll tax on the 7th - the pay run journal is just dated 8-9 Oct. Super direct debits the day after - payday super since 1 Jul 26.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>Pay date - run 2 (fortnight Sat 10 Oct to Fri 23 Oct)</t>
+          <t>Pay date - run 2 (fortnight Sat 3 Oct to Fri 16 Oct)</t>
         </is>
       </c>
       <c r="B15" s="128" t="n">
-        <v>46322</v>
+        <v>46315</v>
       </c>
       <c r="C15" s="115" t="inlineStr">
         <is>
-          <t>Tue 27 Oct (week 4).</t>
+          <t>Tue 20 Oct (week 3).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="18" t="inlineStr">
         <is>
-          <t>Pay date - run 3 (fortnight Sat 24 Oct to Fri 6 Nov)</t>
+          <t>Pay date - run 3 (fortnight Sat 17 Oct to Fri 30 Oct)</t>
         </is>
       </c>
       <c r="B16" s="128" t="n">
-        <v>46336</v>
+        <v>46329</v>
       </c>
       <c r="C16" s="115" t="inlineStr">
         <is>
-          <t>Tue 10 Nov - after week 5 (ends Wed 4 Nov), so it does not hit this forecast. Only two pay runs land in October now.</t>
+          <t>Tue 3 Nov (week 5).</t>
         </is>
       </c>
     </row>
@@ -4067,15 +4084,15 @@
     <row r="5" ht="48" customHeight="1" s="109">
       <c r="A5" s="18" t="inlineStr">
         <is>
-          <t>Run 1 - Sat 26 Sep to Fri 9 Oct</t>
+          <t>Run 1 - Sat 19 Sep to Fri 2 Oct</t>
         </is>
       </c>
       <c r="B5" s="128" t="n">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="C5" s="135">
         <f>Assumptions!$B$14</f>
-        <v>46308</v>
+        <v>46301</v>
       </c>
       <c r="D5" s="136">
         <f>Assumptions!$B$9</f>
@@ -4103,22 +4120,22 @@
       </c>
       <c r="J5" s="115" t="inlineStr">
         <is>
-          <t>Timesheets close Fri 9 Oct, processed Mon 12 Oct - approvals, reconcile, finalise with GC, ABA into CommBiz, payroll email to DL. Move the funds from savings Monday. Out of the bank Tue 13 Oct. Xero journal is dated 8-9 Oct ($101,246 gross, $13,084 super).</t>
+          <t>Timesheets closed Fri 2 Oct, Mon 5 Oct was a PH, out of the bank Tue 6 Oct - Xero bank movement says about $79.7k net (78.8% of the $101,246 gross). Super $13,084 and payroll tax $8,603 went Wed 7 Oct. Journal in Xero is dated 8-9 Oct.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" s="109">
       <c r="A6" s="18" t="inlineStr">
         <is>
-          <t>Run 2 - Sat 10 Oct to Fri 23 Oct</t>
+          <t>Run 2 - Sat 3 Oct to Fri 16 Oct</t>
         </is>
       </c>
       <c r="B6" s="128" t="n">
-        <v>46318</v>
+        <v>46311</v>
       </c>
       <c r="C6" s="135">
         <f>Assumptions!$B$15</f>
-        <v>46322</v>
+        <v>46315</v>
       </c>
       <c r="D6" s="136">
         <f>Assumptions!$B$9</f>
@@ -4146,22 +4163,22 @@
       </c>
       <c r="J6" s="115" t="inlineStr">
         <is>
-          <t>Paid Tue 27 Oct. Last run of the month - accrue bonus leave (Checklist step 48). No cash effect.</t>
+          <t>Paid Tue 20 Oct. Last run of the month - accrue bonus leave (Checklist step 48). No cash effect.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="18" t="inlineStr">
         <is>
-          <t>Run 3 - Sat 24 Oct to Fri 6 Nov</t>
+          <t>Run 3 - Sat 17 Oct to Fri 30 Oct</t>
         </is>
       </c>
       <c r="B7" s="128" t="n">
-        <v>46332</v>
+        <v>46325</v>
       </c>
       <c r="C7" s="135">
         <f>Assumptions!$B$16</f>
-        <v>46336</v>
+        <v>46329</v>
       </c>
       <c r="D7" s="136">
         <f>Assumptions!$B$9</f>
@@ -4189,7 +4206,7 @@
       </c>
       <c r="J7" s="115" t="inlineStr">
         <is>
-          <t>Paid Tue 10 Nov - after this forecast, so nothing from it hits the numbers.</t>
+          <t>Paid Tue 3 Nov - lands in week 5.</t>
         </is>
       </c>
     </row>

--- a/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
+++ b/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
@@ -11,7 +11,8 @@
     <sheet name="Payroll" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Receivables" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payables" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Complete AV" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Creditors Run" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Complete AV" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Receivables'!$A$4:$K$56</definedName>
@@ -23,7 +24,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="\$#,##0;\(\$#,##0\);\-"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="ddd\ d\ mmm\ yy"/>
@@ -32,8 +33,9 @@
     <numFmt numFmtId="169" formatCode="d\ mmm\ yy"/>
     <numFmt numFmtId="170" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="171" formatCode="_-[$$-C09]* #,##0.00_-;\-[$$-C09]* #,##0.00_-;_-[$$-C09]* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="172" formatCode="d mmm yy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -165,6 +167,15 @@
       <color theme="0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="FF0000FF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -282,7 +293,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="195">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -525,6 +536,21 @@
     <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -925,7 +951,7 @@
     <row r="3" ht="42" customHeight="1" s="109">
       <c r="A3" s="108" t="inlineStr">
         <is>
-          <t>How this works: the Forecast columns are formulas off the Receivables, Payables, Payroll and Assumptions tabs. Each week, put the actual movements in the yellow Actual column, type in the closing bank balance from CommBiz, and set 'Actuals entered' to 1. The next week then starts from the real bank balance and the difference row shows anything that's been missed.</t>
+          <t>How this works: the Forecast columns are formulas off the Receivables, Payables, Payroll and Assumptions tabs. Each week, put the actual movements in the yellow Actual column, type in the closing bank balance from CommBiz, and set 'Actuals entered' to 1. The next week then starts from the real bank balance and the difference row shows anything that's been missed. The Creditors run row comes off the Creditors Run tab - paste the Xero aged payables detail in there each month.</t>
         </is>
       </c>
     </row>
@@ -1151,11 +1177,11 @@
       </c>
       <c r="J10" s="119">
         <f>IF(I$8=1,I59,H58)</f>
-        <v>333107.8993333333</v>
+        <v>362388.61933333334</v>
       </c>
       <c r="K10" s="119">
         <f>J10</f>
-        <v>333107.8993333333</v>
+        <v>362388.61933333334</v>
       </c>
       <c r="L10" s="119">
         <f>B10</f>
@@ -1721,14 +1747,14 @@
         </is>
       </c>
       <c r="B27" s="124">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
         <v>167794.43</v>
       </c>
       <c r="C27" s="121" t="n">
         <v>139086.23</v>
       </c>
       <c r="D27" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
         <v>43033.020000000004</v>
       </c>
       <c r="E27" s="121">
@@ -1736,23 +1762,23 @@
         <v>70643.31999999999</v>
       </c>
       <c r="F27" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
-        <v>11103.26</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
+        <v>4000</v>
       </c>
       <c r="G27" s="121" t="n"/>
       <c r="H27" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
         <v>4000</v>
       </c>
       <c r="I27" s="121" t="n"/>
       <c r="J27" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
-        <v>14555.92</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
+        <v>4000</v>
       </c>
       <c r="K27" s="121" t="n"/>
       <c r="L27" s="120">
         <f>SUM(B27,D27,F27,H27,J27)</f>
-        <v>240486.63000000003</v>
+        <v>222827.45</v>
       </c>
       <c r="M27" s="120">
         <f>SUM(C27,E27,G27,I27,K27)</f>
@@ -1879,12 +1905,12 @@
         </is>
       </c>
       <c r="B30" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
         <v>6328.8</v>
       </c>
       <c r="C30" s="121" t="n"/>
       <c r="D30" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
         <v>5712.04</v>
       </c>
       <c r="E30" s="121">
@@ -1892,23 +1918,23 @@
         <v>20721.04</v>
       </c>
       <c r="F30" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
         <v>600</v>
       </c>
       <c r="G30" s="121" t="n"/>
       <c r="H30" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
-        <v>21585.43</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
+        <v>600</v>
       </c>
       <c r="I30" s="121" t="n"/>
       <c r="J30" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
-        <v>6328.8</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
+        <v>600</v>
       </c>
       <c r="K30" s="121" t="n"/>
       <c r="L30" s="120">
         <f>SUM(B30,D30,F30,H30,J30)</f>
-        <v>40555.07000000001</v>
+        <v>13840.84</v>
       </c>
       <c r="M30" s="120">
         <f>SUM(C30,E30,G30,I30,K30)</f>
@@ -1931,12 +1957,12 @@
         </is>
       </c>
       <c r="B31" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
       </c>
       <c r="C31" s="121" t="n"/>
       <c r="D31" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
       </c>
       <c r="E31" s="121">
@@ -1944,17 +1970,17 @@
         <v>1277.9</v>
       </c>
       <c r="F31" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
       </c>
       <c r="G31" s="121" t="n"/>
       <c r="H31" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
       </c>
       <c r="I31" s="121" t="n"/>
       <c r="J31" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
       </c>
       <c r="K31" s="121" t="n"/>
@@ -2000,7 +2026,7 @@
       </c>
       <c r="F32" s="123">
         <f>F27+F28+F29+F30+F31</f>
-        <v>27103.260000000002</v>
+        <v>20000</v>
       </c>
       <c r="G32" s="123">
         <f>G27+G28+G29+G30+G31</f>
@@ -2008,7 +2034,7 @@
       </c>
       <c r="H32" s="123">
         <f>H27+H28+H29+H30+H31</f>
-        <v>40985.43</v>
+        <v>20000</v>
       </c>
       <c r="I32" s="123">
         <f>I27+I28+I29+I30+I31</f>
@@ -2016,7 +2042,7 @@
       </c>
       <c r="J32" s="123">
         <f>J27+J28+J29+J30+J31</f>
-        <v>36284.72</v>
+        <v>20000</v>
       </c>
       <c r="K32" s="123">
         <f>K27+K28+K29+K30+K31</f>
@@ -2024,7 +2050,7 @@
       </c>
       <c r="L32" s="123">
         <f>L27+L28+L29+L30+L31</f>
-        <v>358041.7</v>
+        <v>313668.29000000004</v>
       </c>
       <c r="M32" s="123">
         <f>M27+M28+M29+M30+M31</f>
@@ -2050,35 +2076,35 @@
         </is>
       </c>
       <c r="B35" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
         <v>0</v>
       </c>
       <c r="C35" s="121" t="n"/>
       <c r="D35" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
         <v>0</v>
       </c>
       <c r="E35" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
         <v>0</v>
       </c>
       <c r="G35" s="121" t="n"/>
       <c r="H35" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
-        <v>29280.72</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
+        <v>0</v>
       </c>
       <c r="I35" s="121" t="n"/>
       <c r="J35" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
         <v>0</v>
       </c>
       <c r="K35" s="121" t="n"/>
       <c r="L35" s="120">
         <f>SUM(B35,D35,F35,H35,J35)</f>
-        <v>29280.72</v>
+        <v>0</v>
       </c>
       <c r="M35" s="120">
         <f>SUM(C35,E35,G35,I35,K35)</f>
@@ -2101,35 +2127,35 @@
         </is>
       </c>
       <c r="B36" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
         <v>0</v>
       </c>
       <c r="C36" s="121" t="n"/>
       <c r="D36" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
-        <v>692.84</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
+        <v>0</v>
       </c>
       <c r="E36" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
-        <v>13566</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
+        <v>0</v>
       </c>
       <c r="G36" s="121" t="n"/>
       <c r="H36" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
         <v>0</v>
       </c>
       <c r="I36" s="121" t="n"/>
       <c r="J36" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
         <v>0</v>
       </c>
       <c r="K36" s="121" t="n"/>
       <c r="L36" s="120">
         <f>SUM(B36,D36,F36,H36,J36)</f>
-        <v>14258.84</v>
+        <v>0</v>
       </c>
       <c r="M36" s="120">
         <f>SUM(C36,E36,G36,I36,K36)</f>
@@ -2152,35 +2178,35 @@
         </is>
       </c>
       <c r="B37" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
         <v>6600</v>
       </c>
       <c r="C37" s="121" t="n"/>
       <c r="D37" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
         <v>0</v>
       </c>
       <c r="E37" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
-        <v>4675</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
+        <v>0</v>
       </c>
       <c r="G37" s="121" t="n"/>
       <c r="H37" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
         <v>0</v>
       </c>
       <c r="I37" s="121" t="n"/>
       <c r="J37" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
-        <v>4823.5</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
+        <v>0</v>
       </c>
       <c r="K37" s="121" t="n"/>
       <c r="L37" s="120">
         <f>SUM(B37,D37,F37,H37,J37)</f>
-        <v>16098.5</v>
+        <v>6600</v>
       </c>
       <c r="M37" s="120">
         <f>SUM(C37,E37,G37,I37,K37)</f>
@@ -2203,37 +2229,37 @@
         </is>
       </c>
       <c r="B38" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>1680</v>
       </c>
       <c r="C38" s="121" t="n">
         <v>880</v>
       </c>
       <c r="D38" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
-        <v>1680</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
+        <v>800</v>
       </c>
       <c r="E38" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>4650</v>
       </c>
       <c r="G38" s="121" t="n"/>
       <c r="H38" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>800</v>
       </c>
       <c r="I38" s="121" t="n"/>
       <c r="J38" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
-        <v>4732.5</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
+        <v>800</v>
       </c>
       <c r="K38" s="121" t="n"/>
       <c r="L38" s="120">
         <f>SUM(B38,D38,F38,H38,J38)</f>
-        <v>13542.5</v>
+        <v>8730</v>
       </c>
       <c r="M38" s="120">
         <f>SUM(C38,E38,G38,I38,K38)</f>
@@ -2256,29 +2282,29 @@
         </is>
       </c>
       <c r="B39" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>0</v>
       </c>
       <c r="C39" s="121" t="n"/>
       <c r="D39" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>0</v>
       </c>
       <c r="E39" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>2310</v>
       </c>
       <c r="G39" s="121" t="n"/>
       <c r="H39" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>0</v>
       </c>
       <c r="I39" s="121" t="n"/>
       <c r="J39" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>0</v>
       </c>
       <c r="K39" s="121" t="n"/>
@@ -2307,12 +2333,12 @@
         </is>
       </c>
       <c r="B40" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
         <v>0</v>
       </c>
       <c r="C40" s="121" t="n"/>
       <c r="D40" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
         <v>940.11</v>
       </c>
       <c r="E40" s="121">
@@ -2320,23 +2346,23 @@
         <v>940.11</v>
       </c>
       <c r="F40" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
-        <v>101.2</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
+        <v>0</v>
       </c>
       <c r="G40" s="121" t="n"/>
       <c r="H40" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
         <v>0</v>
       </c>
       <c r="I40" s="121" t="n"/>
       <c r="J40" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
         <v>0</v>
       </c>
       <c r="K40" s="121" t="n"/>
       <c r="L40" s="120">
         <f>SUM(B40,D40,F40,H40,J40)</f>
-        <v>1041.31</v>
+        <v>940.11</v>
       </c>
       <c r="M40" s="120">
         <f>SUM(C40,E40,G40,I40,K40)</f>
@@ -2359,29 +2385,29 @@
         </is>
       </c>
       <c r="B41" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
       </c>
       <c r="C41" s="121" t="n"/>
       <c r="D41" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
       </c>
       <c r="E41" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
       </c>
       <c r="G41" s="121" t="n"/>
       <c r="H41" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
       </c>
       <c r="I41" s="121" t="n"/>
       <c r="J41" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
       </c>
       <c r="K41" s="121" t="n"/>
@@ -2410,35 +2436,35 @@
         </is>
       </c>
       <c r="B42" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
         <v>0</v>
       </c>
       <c r="C42" s="121" t="n"/>
       <c r="D42" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
-        <v>66238.98</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
+        <v>0</v>
       </c>
       <c r="E42" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
         <v>0</v>
       </c>
       <c r="G42" s="121" t="n"/>
       <c r="H42" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
         <v>0</v>
       </c>
       <c r="I42" s="121" t="n"/>
       <c r="J42" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
         <v>0</v>
       </c>
       <c r="K42" s="121" t="n"/>
       <c r="L42" s="120">
         <f>SUM(B42,D42,F42,H42,J42)</f>
-        <v>66238.98</v>
+        <v>0</v>
       </c>
       <c r="M42" s="120">
         <f>SUM(C42,E42,G42,I42,K42)</f>
@@ -2461,37 +2487,37 @@
         </is>
       </c>
       <c r="B43" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
         <v>635.6</v>
       </c>
       <c r="C43" s="121" t="n">
         <v>235.6</v>
       </c>
       <c r="D43" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
         <v>645</v>
       </c>
       <c r="E43" s="121" t="n">
         <v>245</v>
       </c>
       <c r="F43" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
         <v>400</v>
       </c>
       <c r="G43" s="121" t="n"/>
       <c r="H43" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
         <v>400</v>
       </c>
       <c r="I43" s="121" t="n"/>
       <c r="J43" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
-        <v>610.2</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
+        <v>400</v>
       </c>
       <c r="K43" s="121" t="n"/>
       <c r="L43" s="120">
         <f>SUM(B43,D43,F43,H43,J43)</f>
-        <v>2690.8</v>
+        <v>2480.6</v>
       </c>
       <c r="M43" s="120">
         <f>SUM(C43,E43,G43,I43,K43)</f>
@@ -2514,29 +2540,29 @@
         </is>
       </c>
       <c r="B44" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
       </c>
       <c r="C44" s="121" t="n"/>
       <c r="D44" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
       </c>
       <c r="E44" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
       </c>
       <c r="G44" s="121" t="n"/>
       <c r="H44" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
       </c>
       <c r="I44" s="121" t="n"/>
       <c r="J44" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
       </c>
       <c r="K44" s="121" t="n"/>
@@ -2671,35 +2697,35 @@
         </is>
       </c>
       <c r="B47" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$44,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$44,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
         <v>0</v>
       </c>
       <c r="C47" s="121" t="n"/>
       <c r="D47" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
         <v>0</v>
       </c>
       <c r="E47" s="121" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
-        <v>996.6</v>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
+        <v>0</v>
       </c>
       <c r="G47" s="121" t="n"/>
       <c r="H47" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
         <v>0</v>
       </c>
       <c r="I47" s="121" t="n"/>
       <c r="J47" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
         <v>0</v>
       </c>
       <c r="K47" s="121" t="n"/>
       <c r="L47" s="120">
         <f>SUM(B47,D47,F47,H47,J47)</f>
-        <v>996.6</v>
+        <v>0</v>
       </c>
       <c r="M47" s="120">
         <f>SUM(C47,E47,G47,I47,K47)</f>
@@ -2716,27 +2742,55 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="117" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Creditors Run </t>
-        </is>
-      </c>
-      <c r="B48" s="120" t="n"/>
+      <c r="A48" s="18" t="inlineStr">
+        <is>
+          <t>Creditors run (Xero aged payables paste)</t>
+        </is>
+      </c>
+      <c r="B48" s="120">
+        <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$44)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$44),'Creditors Run'!$I$11:$I$510),0)</f>
+        <v>0</v>
+      </c>
       <c r="C48" s="121" t="n">
         <v>77302.53999999999</v>
       </c>
-      <c r="D48" s="120" t="n"/>
+      <c r="D48" s="120">
+        <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$45)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$45),'Creditors Run'!$I$11:$I$510),0)</f>
+        <v>67811.82</v>
+      </c>
       <c r="E48" s="121" t="n"/>
-      <c r="F48" s="120" t="n"/>
+      <c r="F48" s="120">
+        <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$46)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$46),'Creditors Run'!$I$11:$I$510),0)</f>
+        <v>26442.059999999998</v>
+      </c>
       <c r="G48" s="121" t="n"/>
-      <c r="H48" s="120" t="n"/>
+      <c r="H48" s="120">
+        <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$47)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$47),'Creditors Run'!$I$11:$I$510),0)</f>
+        <v>20985.43</v>
+      </c>
       <c r="I48" s="121" t="n"/>
-      <c r="J48" s="120" t="n"/>
+      <c r="J48" s="120">
+        <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$48)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$48),'Creditors Run'!$I$11:$I$510),0)</f>
+        <v>25592.92</v>
+      </c>
       <c r="K48" s="121" t="n"/>
-      <c r="L48" s="120" t="n"/>
-      <c r="M48" s="120" t="n"/>
-      <c r="N48" s="120" t="n"/>
-      <c r="O48" s="108" t="n"/>
+      <c r="L48" s="120">
+        <f>SUM(B48,D48,F48,H48,J48)</f>
+        <v>140832.22999999998</v>
+      </c>
+      <c r="M48" s="120">
+        <f>SUM(C48,E48,G48,I48,K48)</f>
+        <v>77302.54</v>
+      </c>
+      <c r="N48" s="120">
+        <f>(C48-B48)*C$8+(E48-D48)*E$8+(G48-F48)*G$8+(I48-H48)*I$8+(K48-J48)*K$8</f>
+        <v>77302.54</v>
+      </c>
+      <c r="O48" s="108" t="inlineStr">
+        <is>
+          <t>Creditors Run tab - paste the Xero aged payables detail in each month and it lands here on the run date (or the date in column L). Week 1 actual is the 1 Oct run. The Payables tab's Xero bill rows drop out of the lines above while this is switched on, so nothing is double counted.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="9" t="inlineStr">
@@ -2745,7 +2799,7 @@
         </is>
       </c>
       <c r="B49" s="123">
-        <f>B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47</f>
+        <f>B35+B36+B37+B38+B39+B40+B41+B42+B43+B44+B45+B46+B47+B48</f>
         <v>15115.6</v>
       </c>
       <c r="C49" s="123">
@@ -2753,48 +2807,48 @@
         <v>88428.14</v>
       </c>
       <c r="D49" s="123">
-        <f>D35+D36+D37+D38+D39+D40+D41+D42+D43+D44+D45+D46+D47</f>
-        <v>76396.93</v>
+        <f>D35+D36+D37+D38+D39+D40+D41+D42+D43+D44+D45+D46+D47+D48</f>
+        <v>76396.93000000001</v>
       </c>
       <c r="E49" s="123">
-        <f>E35+E36+E37+E38+E39+E40+E41+E42+E43+E44+E45+E46+E47</f>
+        <f>E35+E36+E37+E38+E39+E40+E41+E42+E43+E44+E45+E46+E47+E48</f>
         <v>1185.1100000000001</v>
       </c>
       <c r="F49" s="123">
-        <f>F35+F36+F37+F38+F39+F40+F41+F42+F43+F44+F45+F46+F47</f>
-        <v>32898.8</v>
+        <f>F35+F36+F37+F38+F39+F40+F41+F42+F43+F44+F45+F46+F47+F48</f>
+        <v>40002.06</v>
       </c>
       <c r="G49" s="123">
-        <f>G35+G36+G37+G38+G39+G40+G41+G42+G43+G44+G45+G46+G47</f>
+        <f>G35+G36+G37+G38+G39+G40+G41+G42+G43+G44+G45+G46+G47+G48</f>
         <v>0</v>
       </c>
       <c r="H49" s="123">
-        <f>H35+H36+H37+H38+H39+H40+H41+H42+H43+H44+H45+H46+H47</f>
-        <v>36680.72</v>
+        <f>H35+H36+H37+H38+H39+H40+H41+H42+H43+H44+H45+H46+H47+H48</f>
+        <v>28385.43</v>
       </c>
       <c r="I49" s="123">
-        <f>I35+I36+I37+I38+I39+I40+I41+I42+I43+I44+I45+I46+I47</f>
+        <f>I35+I36+I37+I38+I39+I40+I41+I42+I43+I44+I45+I46+I47+I48</f>
         <v>0</v>
       </c>
       <c r="J49" s="123">
-        <f>J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47</f>
-        <v>16366.2</v>
+        <f>J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47+J48</f>
+        <v>32992.92</v>
       </c>
       <c r="K49" s="123">
-        <f>K35+K36+K37+K38+K39+K40+K41+K42+K43+K44+K45+K46+K47</f>
+        <f>K35+K36+K37+K38+K39+K40+K41+K42+K43+K44+K45+K46+K47+K48</f>
         <v>0</v>
       </c>
       <c r="L49" s="123">
-        <f>L35+L36+L37+L38+L39+L40+L41+L42+L43+L44+L45+L46+L47</f>
-        <v>177458.24999999997</v>
+        <f>L35+L36+L37+L38+L39+L40+L41+L42+L43+L44+L45+L46+L47+L48</f>
+        <v>192892.93999999997</v>
       </c>
       <c r="M49" s="123">
-        <f>M35+M36+M37+M38+M39+M40+M41+M42+M43+M44+M45+M46+M47</f>
-        <v>12310.71</v>
+        <f>M35+M36+M37+M38+M39+M40+M41+M42+M43+M44+M45+M46+M47+M48</f>
+        <v>89613.25</v>
       </c>
       <c r="N49" s="123">
-        <f>N35+N36+N37+N38+N39+N40+N41+N42+N43+N44+N45+N46+N47</f>
-        <v>-3990</v>
+        <f>N35+N36+N37+N38+N39+N40+N41+N42+N43+N44+N45+N46+N47+N48</f>
+        <v>73312.54</v>
       </c>
       <c r="O49" s="12" t="n"/>
     </row>
@@ -2931,7 +2985,7 @@
       </c>
       <c r="D55" s="122">
         <f>D24+D32+D49+D53</f>
-        <v>140541.99</v>
+        <v>140541.99000000002</v>
       </c>
       <c r="E55" s="122">
         <f>E24+E32+E49+E53</f>
@@ -2947,7 +3001,7 @@
       </c>
       <c r="H55" s="122">
         <f>H24+H32+H49+H53</f>
-        <v>178024.53399999999</v>
+        <v>148743.81399999998</v>
       </c>
       <c r="I55" s="122">
         <f>I24+I32+I49+I53</f>
@@ -2955,7 +3009,7 @@
       </c>
       <c r="J55" s="122">
         <f>J24+J32+J49+J53</f>
-        <v>152218.92</v>
+        <v>152560.91999999998</v>
       </c>
       <c r="K55" s="122">
         <f>K24+K32+K49+K53</f>
@@ -2963,15 +3017,15 @@
       </c>
       <c r="L55" s="122">
         <f>L24+L32+L49+L53</f>
-        <v>943557.3339999999</v>
+        <v>914618.614</v>
       </c>
       <c r="M55" s="122">
         <f>M24+M32+M49+M53</f>
-        <v>370696.24</v>
+        <v>447998.77999999997</v>
       </c>
       <c r="N55" s="122">
         <f>N24+N32+N49+N53</f>
-        <v>-61567.65999999998</v>
+        <v>15734.880000000012</v>
       </c>
       <c r="O55" s="16" t="n"/>
     </row>
@@ -2991,7 +3045,7 @@
       </c>
       <c r="D57" s="122">
         <f>D15-D55</f>
-        <v>2154.279999999999</v>
+        <v>2154.2799999999697</v>
       </c>
       <c r="E57" s="122">
         <f>E15-E55</f>
@@ -3007,7 +3061,7 @@
       </c>
       <c r="H57" s="122">
         <f>H15-H55</f>
-        <v>-165398.0673333333</v>
+        <v>-136117.3473333333</v>
       </c>
       <c r="I57" s="122">
         <f>I15-I55</f>
@@ -3015,7 +3069,7 @@
       </c>
       <c r="J57" s="122">
         <f>J15-J55</f>
-        <v>-59748.783333333355</v>
+        <v>-60090.783333333326</v>
       </c>
       <c r="K57" s="122">
         <f>K15-K55</f>
@@ -3023,15 +3077,15 @@
       </c>
       <c r="L57" s="122">
         <f>L15-L55</f>
-        <v>-326569.2540000001</v>
+        <v>-297630.5340000001</v>
       </c>
       <c r="M57" s="122">
         <f>M15-M55</f>
-        <v>-69204.66999999998</v>
+        <v>-146507.20999999996</v>
       </c>
       <c r="N57" s="122">
         <f>N15-N55</f>
-        <v>85266.04000000001</v>
+        <v>7963.500000000007</v>
       </c>
       <c r="O57" s="16" t="n"/>
     </row>
@@ -3067,7 +3121,7 @@
       </c>
       <c r="H58" s="125">
         <f>H10+H57</f>
-        <v>333107.8993333333</v>
+        <v>362388.61933333334</v>
       </c>
       <c r="I58" s="125" t="str">
         <f>IF(I$8=1,I10+I57,"")</f>
@@ -3075,7 +3129,7 @@
       </c>
       <c r="J58" s="125">
         <f>J10+J57</f>
-        <v>273359.1159999999</v>
+        <v>302297.836</v>
       </c>
       <c r="K58" s="125" t="str">
         <f>IF(K$8=1,K10+K57,"")</f>
@@ -3083,7 +3137,7 @@
       </c>
       <c r="L58" s="125">
         <f>J58</f>
-        <v>273359.1159999999</v>
+        <v>302297.836</v>
       </c>
       <c r="M58" s="125">
         <f>IF(K$8=1,K58,IF(I$8=1,I58,IF(G$8=1,G58,IF(E$8=1,E58,IF(C$8=1,C58,"")))))</f>
@@ -3233,11 +3287,11 @@
       </c>
       <c r="H64" s="127">
         <f>IF(Payroll!$I$5=0,0,H58/(Payroll!$I$5/2))</f>
-        <v>6.691063380470298</v>
+        <v>7.279218611066474</v>
       </c>
       <c r="J64" s="127">
         <f>IF(Payroll!$I$5=0,0,J58/(Payroll!$I$5/2))</f>
-        <v>5.490903021050938</v>
+        <v>6.072188574642456</v>
       </c>
       <c r="O64" s="108" t="n"/>
     </row>
@@ -3264,7 +3318,7 @@
         </is>
       </c>
       <c r="L66" s="120">
-        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$G$19:$G$75,"&gt;"&amp;Assumptions!$C$48)</f>
+        <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$G$19:$G$75,"&gt;"&amp;Assumptions!$C$48)</f>
         <v>30084.780000000002</v>
       </c>
       <c r="O66" s="108" t="inlineStr">
@@ -7548,6 +7602,7 @@
     <col width="8" customWidth="1" style="109" min="8" max="8"/>
     <col width="14" customWidth="1" style="109" min="9" max="9"/>
     <col width="62" customWidth="1" style="109" min="10" max="10"/>
+    <col width="22" customWidth="1" style="109" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="18" customHeight="1" s="109">
@@ -8065,6 +8120,11 @@
           <t>Notes</t>
         </is>
       </c>
+      <c r="K18" s="113" t="inlineStr">
+        <is>
+          <t>Counted in the category lines? (open Xero bills move to the creditors run)</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="24" customHeight="1" s="109">
       <c r="A19" s="18" t="inlineStr">
@@ -8110,6 +8170,10 @@
           <t>Pay once Aware's Appspace invoice INV-10635 ($23,317) is in (expected 16 Oct)</t>
         </is>
       </c>
+      <c r="K19" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I19="Xero bill",LEFT(J19,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="20" ht="38.25" customHeight="1" s="109">
       <c r="A20" s="170" t="inlineStr">
@@ -8157,6 +8221,10 @@
           <t>PAID 29 Sep</t>
         </is>
       </c>
+      <c r="K20" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I20="Xero bill",LEFT(J20,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="21" ht="72" customHeight="1" s="109">
       <c r="A21" s="170" t="inlineStr">
@@ -8203,6 +8271,10 @@
           <t>PAID 8 Oct - the hold was released last week. Whole of INV41565 ($178,119.25) is now paid, matches Xero.</t>
         </is>
       </c>
+      <c r="K21" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I21="Xero bill",LEFT(J21,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="inlineStr">
@@ -8248,6 +8320,10 @@
           <t>On the due date</t>
         </is>
       </c>
+      <c r="K22" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I22="Xero bill",LEFT(J22,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="18" t="inlineStr">
@@ -8293,6 +8369,10 @@
           <t>Still open in Xero at 12 Oct (the Oct one, 42 of 60, was paid 6 Oct). Pay this week.</t>
         </is>
       </c>
+      <c r="K23" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I23="Xero bill",LEFT(J23,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="170" t="inlineStr">
@@ -8338,6 +8418,10 @@
           <t>PAID 29 Sep - PL card</t>
         </is>
       </c>
+      <c r="K24" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I24="Xero bill",LEFT(J24,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="inlineStr">
@@ -8383,6 +8467,10 @@
           <t>DD via the PL card</t>
         </is>
       </c>
+      <c r="K25" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I25="Xero bill",LEFT(J25,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="170" t="inlineStr">
@@ -8428,6 +8516,10 @@
           <t>PAID 8 Oct</t>
         </is>
       </c>
+      <c r="K26" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I26="Xero bill",LEFT(J26,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="170" t="inlineStr">
@@ -8473,6 +8565,10 @@
           <t>PAID 22 Sep - PL card</t>
         </is>
       </c>
+      <c r="K27" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I27="Xero bill",LEFT(J27,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="28" ht="25.5" customHeight="1" s="109">
       <c r="A28" s="170" t="inlineStr">
@@ -8518,6 +8614,10 @@
           <t>PAID 1 Oct</t>
         </is>
       </c>
+      <c r="K28" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I28="Xero bill",LEFT(J28,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="inlineStr">
@@ -8563,6 +8663,10 @@
           <t>On the due date. Oct rent gets invoiced ~22 Oct, due ~22 Nov</t>
         </is>
       </c>
+      <c r="K29" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I29="Xero bill",LEFT(J29,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="170" t="inlineStr">
@@ -8608,6 +8712,10 @@
           <t>PAID 18 Sep - card</t>
         </is>
       </c>
+      <c r="K30" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I30="Xero bill",LEFT(J30,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="170" t="inlineStr">
@@ -8653,6 +8761,10 @@
           <t>PAID 23 Sep - card</t>
         </is>
       </c>
+      <c r="K31" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I31="Xero bill",LEFT(J31,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="170" t="inlineStr">
@@ -8698,6 +8810,10 @@
           <t>PAID 8 Oct - BPAY</t>
         </is>
       </c>
+      <c r="K32" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I32="Xero bill",LEFT(J32,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="inlineStr">
@@ -8743,6 +8859,10 @@
           <t>GC said hold until he confirms. Assumed released week 4</t>
         </is>
       </c>
+      <c r="K33" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I33="Xero bill",LEFT(J33,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="170" t="inlineStr">
@@ -8788,6 +8908,10 @@
           <t>PAID 8 Oct</t>
         </is>
       </c>
+      <c r="K34" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I34="Xero bill",LEFT(J34,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="170" t="inlineStr">
@@ -8833,6 +8957,10 @@
           <t>PAID 30 Sep - DD</t>
         </is>
       </c>
+      <c r="K35" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I35="Xero bill",LEFT(J35,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="170" t="inlineStr">
@@ -8878,6 +9006,10 @@
           <t>PAID 1 Oct</t>
         </is>
       </c>
+      <c r="K36" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I36="Xero bill",LEFT(J36,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="170" t="inlineStr">
@@ -8923,6 +9055,10 @@
           <t>PAID 18 Sep - card</t>
         </is>
       </c>
+      <c r="K37" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I37="Xero bill",LEFT(J37,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="170" t="inlineStr">
@@ -8968,6 +9104,10 @@
           <t>PAID 1 Oct</t>
         </is>
       </c>
+      <c r="K38" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I38="Xero bill",LEFT(J38,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="170" t="inlineStr">
@@ -9013,6 +9153,10 @@
           <t>PAID 22 Sep - card</t>
         </is>
       </c>
+      <c r="K39" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I39="Xero bill",LEFT(J39,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="170" t="inlineStr">
@@ -9058,6 +9202,10 @@
           <t>Refunded 24 Sep - card</t>
         </is>
       </c>
+      <c r="K40" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I40="Xero bill",LEFT(J40,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="170" t="inlineStr">
@@ -9103,6 +9251,10 @@
           <t>PAID - card</t>
         </is>
       </c>
+      <c r="K41" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I41="Xero bill",LEFT(J41,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="170" t="inlineStr">
@@ -9148,6 +9300,10 @@
           <t>PAID 17 Sep - card</t>
         </is>
       </c>
+      <c r="K42" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I42="Xero bill",LEFT(J42,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="170" t="inlineStr">
@@ -9193,6 +9349,10 @@
           <t>PAID 24 Sep - card</t>
         </is>
       </c>
+      <c r="K43" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I43="Xero bill",LEFT(J43,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="inlineStr">
@@ -9238,6 +9398,10 @@
           <t>DD on the due date</t>
         </is>
       </c>
+      <c r="K44" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I44="Xero bill",LEFT(J44,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="inlineStr">
@@ -9283,6 +9447,10 @@
           <t>DD on the due date</t>
         </is>
       </c>
+      <c r="K45" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I45="Xero bill",LEFT(J45,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="inlineStr">
@@ -9328,6 +9496,10 @@
           <t>On the due date</t>
         </is>
       </c>
+      <c r="K46" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I46="Xero bill",LEFT(J46,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="inlineStr">
@@ -9373,6 +9545,10 @@
           <t>Template $3,850 a month. Nothing paid in Xero to 12 Oct - check if the Oct invoice has come in.</t>
         </is>
       </c>
+      <c r="K47" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I47="Xero bill",LEFT(J47,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="inlineStr">
@@ -9418,6 +9594,10 @@
           <t>On the due date, 31 Oct</t>
         </is>
       </c>
+      <c r="K48" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I48="Xero bill",LEFT(J48,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="170" t="inlineStr">
@@ -9463,6 +9643,10 @@
           <t>PAID 8 Oct (INV-19664)</t>
         </is>
       </c>
+      <c r="K49" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I49="Xero bill",LEFT(J49,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="170" t="inlineStr">
@@ -9508,6 +9692,10 @@
           <t>PAID 6 Oct</t>
         </is>
       </c>
+      <c r="K50" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I50="Xero bill",LEFT(J50,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="18" t="inlineStr">
@@ -9553,6 +9741,10 @@
           <t>Quarterly, due 8 Oct. No bill in Xero at 12 Oct - check with DL.</t>
         </is>
       </c>
+      <c r="K51" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I51="Xero bill",LEFT(J51,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="170" t="inlineStr">
@@ -9598,6 +9790,10 @@
           <t>PAID 8 Oct - BPAY (TTI20227626284, $136)</t>
         </is>
       </c>
+      <c r="K52" s="170" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I52="Xero bill",LEFT(J52,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="18" t="inlineStr">
@@ -9643,6 +9839,10 @@
           <t>Open - PL card, in the card line</t>
         </is>
       </c>
+      <c r="K53" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I53="Xero bill",LEFT(J53,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="18" t="inlineStr">
@@ -9688,6 +9888,10 @@
           <t>Open - PL card, in the card line</t>
         </is>
       </c>
+      <c r="K54" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I54="Xero bill",LEFT(J54,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="18" t="inlineStr">
@@ -9733,6 +9937,10 @@
           <t>PL card</t>
         </is>
       </c>
+      <c r="K55" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I55="Xero bill",LEFT(J55,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="18" t="inlineStr">
@@ -9778,6 +9986,10 @@
           <t>PL card</t>
         </is>
       </c>
+      <c r="K56" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I56="Xero bill",LEFT(J56,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="18" t="inlineStr">
@@ -9823,6 +10035,10 @@
           <t>PL card</t>
         </is>
       </c>
+      <c r="K57" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I57="Xero bill",LEFT(J57,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="18" t="inlineStr">
@@ -9868,6 +10084,10 @@
           <t>PL / DL cards - approx</t>
         </is>
       </c>
+      <c r="K58" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I58="Xero bill",LEFT(J58,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="18" t="inlineStr">
@@ -9913,6 +10133,10 @@
           <t>Invoiced ~22 Oct, due ~22 Nov - after this forecast</t>
         </is>
       </c>
+      <c r="K59" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I59="Xero bill",LEFT(J59,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="18" t="inlineStr">
@@ -9958,6 +10182,10 @@
           <t>Due 8 Nov - after this forecast</t>
         </is>
       </c>
+      <c r="K60" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I60="Xero bill",LEFT(J60,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
     </row>
     <row r="61" s="109">
       <c r="A61" s="18" t="inlineStr">
@@ -10003,6 +10231,10 @@
           <t>Annual renewal, GC approved. Due Wed 14 Oct - all six Brookvale bills go in one payment.</t>
         </is>
       </c>
+      <c r="K61" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I61="Xero bill",LEFT(J61,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="62" s="109">
       <c r="A62" s="18" t="inlineStr">
@@ -10048,6 +10280,10 @@
           <t>Annual renewal, GC approved.</t>
         </is>
       </c>
+      <c r="K62" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I62="Xero bill",LEFT(J62,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="63" s="109">
       <c r="A63" s="18" t="inlineStr">
@@ -10093,6 +10329,10 @@
           <t>Annual renewal, GC approved.</t>
         </is>
       </c>
+      <c r="K63" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I63="Xero bill",LEFT(J63,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="64" s="109">
       <c r="A64" s="18" t="inlineStr">
@@ -10138,6 +10378,10 @@
           <t>Annual renewal, GC approved.</t>
         </is>
       </c>
+      <c r="K64" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I64="Xero bill",LEFT(J64,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="18" t="inlineStr">
@@ -10183,6 +10427,10 @@
           <t>Annual renewal, GC approved.</t>
         </is>
       </c>
+      <c r="K65" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I65="Xero bill",LEFT(J65,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="18" t="inlineStr">
@@ -10228,6 +10476,10 @@
           <t>Annual renewal, GC approved.</t>
         </is>
       </c>
+      <c r="K66" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I66="Xero bill",LEFT(J66,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="18" t="inlineStr">
@@ -10273,6 +10525,10 @@
           <t>Due Sun 1 Nov, pay Mon 2 Nov (week 5).</t>
         </is>
       </c>
+      <c r="K67" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I67="Xero bill",LEFT(J67,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="18" t="inlineStr">
@@ -10318,6 +10574,10 @@
           <t>Due Sun 1 Nov, pay Mon 2 Nov (week 5).</t>
         </is>
       </c>
+      <c r="K68" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I68="Xero bill",LEFT(J68,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="18" t="inlineStr">
@@ -10363,6 +10623,10 @@
           <t>DL approved. On the due date (week 5).</t>
         </is>
       </c>
+      <c r="K69" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I69="Xero bill",LEFT(J69,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="18" t="inlineStr">
@@ -10408,6 +10672,10 @@
           <t>DL approved. On the due date (week 5).</t>
         </is>
       </c>
+      <c r="K70" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I70="Xero bill",LEFT(J70,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="18" t="inlineStr">
@@ -10453,6 +10721,10 @@
           <t>Direct debit</t>
         </is>
       </c>
+      <c r="K71" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I71="Xero bill",LEFT(J71,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="18" t="inlineStr">
@@ -10498,6 +10770,10 @@
           <t>BPAY on the due date</t>
         </is>
       </c>
+      <c r="K72" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I72="Xero bill",LEFT(J72,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="18" t="inlineStr">
@@ -10542,6 +10818,22 @@
         <is>
           <t>PL card</t>
         </is>
+      </c>
+      <c r="K73" s="18" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I73="Xero bill",LEFT(J73,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>No - in the creditors run</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="K74" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I74="Xero bill",LEFT(J74,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="K75" t="str">
+        <f>IF(AND('Creditors Run'!$B$5=1,I75="Xero bill",LEFT(J75,4)&lt;&gt;"PAID"),"No - in the creditors run","Yes")</f>
+        <v>Yes</v>
       </c>
     </row>
     <row r="77" s="109">
@@ -10612,6 +10904,6996 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N510"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" style="109" min="1" max="1"/>
+    <col width="9" customWidth="1" style="109" min="2" max="2"/>
+    <col width="16" customWidth="1" style="109" min="3" max="3"/>
+    <col width="9" customWidth="1" style="109" min="4" max="4"/>
+    <col width="52" customWidth="1" style="109" min="5" max="5"/>
+    <col width="8" customWidth="1" style="109" min="6" max="6"/>
+    <col width="13" customWidth="1" style="109" min="7" max="7"/>
+    <col width="11" customWidth="1" style="109" min="8" max="8"/>
+    <col width="12" customWidth="1" style="109" min="9" max="9"/>
+    <col width="12" customWidth="1" style="109" min="10" max="10"/>
+    <col width="16" customWidth="1" style="109" min="11" max="11"/>
+    <col width="13" customWidth="1" style="109" min="12" max="12"/>
+    <col width="10" customWidth="1" style="109" min="13" max="13"/>
+    <col width="12" customWidth="1" style="109" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Creditors run - paste the Xero aged payables detail straight in</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="62" customHeight="1" s="109">
+      <c r="A2" s="184" t="inlineStr">
+        <is>
+          <t>How it works: run the aged payables detail in Xero, export it, and paste the lines in from row 11 (columns A to K, same order as the report). Anything with a date in column A and a number in Gross gets counted - the contact and total lines the report adds are ignored. Every bill goes out on the run date in B4 unless you type a date in L, and an x in M leaves a line out (card bills - they sit in the card line). With B5 at 1 the Cash Flow Creditors run row takes these numbers and the Payables tab stops counting its Xero bill rows, so nothing is counted twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Creditors run pay date</t>
+        </is>
+      </c>
+      <c r="B4" s="192" t="n">
+        <v>46328</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mon 2 Nov (1 Nov is a Sunday). Change it each month. Anything with its own date in column L ignores this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Use this paste for the forecast? (1 = yes, 0 = use the Payables tab rows instead)</t>
+        </is>
+      </c>
+      <c r="B5" s="186" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total open per the paste (what the forecast uses, before any x)</t>
+        </is>
+      </c>
+      <c r="B6" s="187">
+        <f>SUMPRODUCT((A11:A510&lt;&gt;"")*ISNUMBER(I11:I510),I11:I510)</f>
+        <v>144499.05</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report total per Xero (type it from the bottom of the report)</t>
+        </is>
+      </c>
+      <c r="B7" s="188" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Difference - should be nil</t>
+        </is>
+      </c>
+      <c r="B8" s="187" t="str">
+        <f>IF(B7="","",B6-B7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" s="109">
+      <c r="A10" s="189" t="inlineStr">
+        <is>
+          <t>Invoice Date</t>
+        </is>
+      </c>
+      <c r="B10" s="189" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C10" s="189" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="D10" s="189" t="inlineStr">
+        <is>
+          <t>Item Code</t>
+        </is>
+      </c>
+      <c r="E10" s="189" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="F10" s="189" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="G10" s="189" t="inlineStr">
+        <is>
+          <t>Unit Price (ex)</t>
+        </is>
+      </c>
+      <c r="H10" s="189" t="inlineStr">
+        <is>
+          <t>GST</t>
+        </is>
+      </c>
+      <c r="I10" s="189" t="inlineStr">
+        <is>
+          <t>Gross</t>
+        </is>
+      </c>
+      <c r="J10" s="189" t="inlineStr">
+        <is>
+          <t>Invoice Total</t>
+        </is>
+      </c>
+      <c r="K10" s="189" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L10" s="189" t="inlineStr">
+        <is>
+          <t>Pay on (optional)</t>
+        </is>
+      </c>
+      <c r="M10" s="189" t="inlineStr">
+        <is>
+          <t>Exclude (x)</t>
+        </is>
+      </c>
+      <c r="N10" s="189" t="inlineStr">
+        <is>
+          <t>Pay date used</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="193" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>INV950936412</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Equipment purchases for 26052701 Aware SYD 28.06 Equipment [PO-00016916]</t>
+        </is>
+      </c>
+      <c r="G11" s="187" t="n">
+        <v>6457.51</v>
+      </c>
+      <c r="H11" s="187" t="n">
+        <v>645.75</v>
+      </c>
+      <c r="I11" s="187" t="n">
+        <v>7103.26</v>
+      </c>
+      <c r="J11" s="187" t="n">
+        <v>7103.26</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L11" s="192" t="n">
+        <v>46314</v>
+      </c>
+      <c r="N11" s="193">
+        <f>IF(L11="",$B$4,L11)</f>
+        <v>46314</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="193" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INV00133660</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Annual Appspace licensing subscription (12 months) for 26091401 Aware Super [PO-00016941]</t>
+        </is>
+      </c>
+      <c r="G12" s="187" t="n">
+        <v>19077.66</v>
+      </c>
+      <c r="H12" s="187" t="n">
+        <v>1907.77</v>
+      </c>
+      <c r="I12" s="187" t="n">
+        <v>20985.43</v>
+      </c>
+      <c r="J12" s="187" t="n">
+        <v>20985.43</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L12" s="192" t="n">
+        <v>46318</v>
+      </c>
+      <c r="N12" s="193">
+        <f>IF(L12="",$B$4,L12)</f>
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="193" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INV15775235</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Ricoh printing services September 2026 [paid via DD]</t>
+        </is>
+      </c>
+      <c r="G13" s="187" t="n">
+        <v>191.09</v>
+      </c>
+      <c r="H13" s="187" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="I13" s="187" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="J13" s="187" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L13" s="192" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N13" s="193">
+        <f>IF(L13="",$B$4,L13)</f>
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>INV1918336</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Brookvale - annual removable / electronic equipment insurance [GC App]</t>
+        </is>
+      </c>
+      <c r="G14" s="187" t="n">
+        <v>10300.62</v>
+      </c>
+      <c r="H14" s="187" t="n">
+        <v>982.54</v>
+      </c>
+      <c r="I14" s="187" t="n">
+        <v>11283.16</v>
+      </c>
+      <c r="J14" s="187" t="n">
+        <v>11283.16</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L14" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N14" s="193">
+        <f>IF(L14="",$B$4,L14)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>INV1920113</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Brookvale - annual business pack insurance [GC App]</t>
+        </is>
+      </c>
+      <c r="G15" s="187" t="n">
+        <v>3211.96</v>
+      </c>
+      <c r="H15" s="187" t="n">
+        <v>298.57</v>
+      </c>
+      <c r="I15" s="187" t="n">
+        <v>3510.52</v>
+      </c>
+      <c r="J15" s="187" t="n">
+        <v>3510.52</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L15" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N15" s="193">
+        <f>IF(L15="",$B$4,L15)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INV1914759</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Brookvale - annual corporate travel insurance [GC App]</t>
+        </is>
+      </c>
+      <c r="G16" s="187" t="n">
+        <v>1246.49</v>
+      </c>
+      <c r="H16" s="187" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="I16" s="187" t="n">
+        <v>1342.24</v>
+      </c>
+      <c r="J16" s="187" t="n">
+        <v>1342.24</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L16" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N16" s="193">
+        <f>IF(L16="",$B$4,L16)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INV1918436</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Brookvale - Mecon annual contract works insurance [GC App]</t>
+        </is>
+      </c>
+      <c r="G17" s="187" t="n">
+        <v>7338.73</v>
+      </c>
+      <c r="H17" s="187" t="n">
+        <v>681.66</v>
+      </c>
+      <c r="I17" s="187" t="n">
+        <v>8020.39</v>
+      </c>
+      <c r="J17" s="187" t="n">
+        <v>8020.39</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L17" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N17" s="193">
+        <f>IF(L17="",$B$4,L17)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>INV1920058</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Brookvale - annual management liability insurance [GC App]</t>
+        </is>
+      </c>
+      <c r="G18" s="187" t="n">
+        <v>6195.64</v>
+      </c>
+      <c r="H18" s="187" t="n">
+        <v>582.5700000000001</v>
+      </c>
+      <c r="I18" s="187" t="n">
+        <v>6778.21</v>
+      </c>
+      <c r="J18" s="187" t="n">
+        <v>6778.21</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L18" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N18" s="193">
+        <f>IF(L18="",$B$4,L18)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>INV1918462</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Brookvale - annual IT liability insurance [GC App]</t>
+        </is>
+      </c>
+      <c r="G19" s="187" t="n">
+        <v>32254.45</v>
+      </c>
+      <c r="H19" s="187" t="n">
+        <v>3050.02</v>
+      </c>
+      <c r="I19" s="187" t="n">
+        <v>35304.46</v>
+      </c>
+      <c r="J19" s="187" t="n">
+        <v>35304.46</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L19" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N19" s="193">
+        <f>IF(L19="",$B$4,L19)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="193" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>INV-0060</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Spacera - Aware Super national support agreement October [PO-00016885]</t>
+        </is>
+      </c>
+      <c r="G20" s="187" t="n">
+        <v>5208</v>
+      </c>
+      <c r="H20" s="187" t="n">
+        <v>520.8</v>
+      </c>
+      <c r="I20" s="187" t="n">
+        <v>5728.8</v>
+      </c>
+      <c r="J20" s="187" t="n">
+        <v>5728.8</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L20" s="192" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N20" s="193">
+        <f>IF(L20="",$B$4,L20)</f>
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>INV01049843</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Employment Hero subs renewal September 2026 [paid via PL CC]</t>
+        </is>
+      </c>
+      <c r="G21" s="187" t="n">
+        <v>2044.4</v>
+      </c>
+      <c r="H21" s="187" t="n">
+        <v>204.44</v>
+      </c>
+      <c r="I21" s="187" t="n">
+        <v>2248.84</v>
+      </c>
+      <c r="J21" s="187" t="n">
+        <v>2248.84</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L21" s="192" t="n"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N21" s="193">
+        <f>IF(L21="",$B$4,L21)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INV7200</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Luminous - CTS 20 logo anniversary, balance of project fees [DL App]</t>
+        </is>
+      </c>
+      <c r="G22" s="187" t="n">
+        <v>4385</v>
+      </c>
+      <c r="H22" s="187" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="I22" s="187" t="n">
+        <v>4823.5</v>
+      </c>
+      <c r="J22" s="187" t="n">
+        <v>4823.5</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L22" s="192" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N22" s="193">
+        <f>IF(L22="",$B$4,L22)</f>
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>INV10498230926</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Goget September 2026 [paid via PL CC]</t>
+        </is>
+      </c>
+      <c r="G23" s="187" t="n">
+        <v>572.29</v>
+      </c>
+      <c r="H23" s="187" t="n">
+        <v>57.23</v>
+      </c>
+      <c r="I23" s="187" t="n">
+        <v>629.52</v>
+      </c>
+      <c r="J23" s="187" t="n">
+        <v>629.52</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L23" s="192" t="n"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N23" s="193">
+        <f>IF(L23="",$B$4,L23)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="193" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INV179820</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>First Focus - CORE intelligent managed services October 2026 [paid via DD]</t>
+        </is>
+      </c>
+      <c r="G24" s="187" t="n">
+        <v>12332.73</v>
+      </c>
+      <c r="H24" s="187" t="n">
+        <v>1233.29</v>
+      </c>
+      <c r="I24" s="187" t="n">
+        <v>13566</v>
+      </c>
+      <c r="J24" s="187" t="n">
+        <v>13566</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L24" s="192" t="n">
+        <v>46310</v>
+      </c>
+      <c r="N24" s="193">
+        <f>IF(L24="",$B$4,L24)</f>
+        <v>46310</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="193" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>INV000599632521</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Optus - Lugstein home internet October 2026 [BPAY]</t>
+        </is>
+      </c>
+      <c r="G25" s="187" t="n">
+        <v>92</v>
+      </c>
+      <c r="H25" s="187" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I25" s="187" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="J25" s="187" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L25" s="192" t="n">
+        <v>46315</v>
+      </c>
+      <c r="N25" s="193">
+        <f>IF(L25="",$B$4,L25)</f>
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="193" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>INV-0120</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RJW - digital growth marketing October 2026</t>
+        </is>
+      </c>
+      <c r="G26" s="187" t="n">
+        <v>4250</v>
+      </c>
+      <c r="H26" s="187" t="n">
+        <v>425</v>
+      </c>
+      <c r="I26" s="187" t="n">
+        <v>4675</v>
+      </c>
+      <c r="J26" s="187" t="n">
+        <v>4675</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L26" s="192" t="n">
+        <v>46316</v>
+      </c>
+      <c r="N26" s="193">
+        <f>IF(L26="",$B$4,L26)</f>
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>INV457214</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Contact Group - equipment purchases for 2605605 DTTL Hobart AV fitout [PO-00016935]</t>
+        </is>
+      </c>
+      <c r="G27" s="187" t="n">
+        <v>821.25</v>
+      </c>
+      <c r="H27" s="187" t="n">
+        <v>82.13</v>
+      </c>
+      <c r="I27" s="187" t="n">
+        <v>903.38</v>
+      </c>
+      <c r="J27" s="187" t="n">
+        <v>903.38</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L27" s="192" t="n">
+        <v>46328</v>
+      </c>
+      <c r="N27" s="193">
+        <f>IF(L27="",$B$4,L27)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>INV457215</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Contact Group - equipment &amp; labour for 2605605 DTTL Hobart AV fitout [PO-00016921]</t>
+        </is>
+      </c>
+      <c r="G28" s="187" t="n">
+        <v>8775</v>
+      </c>
+      <c r="H28" s="187" t="n">
+        <v>877.54</v>
+      </c>
+      <c r="I28" s="187" t="n">
+        <v>9652.540000000001</v>
+      </c>
+      <c r="J28" s="187" t="n">
+        <v>9652.540000000001</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L28" s="192" t="n">
+        <v>46328</v>
+      </c>
+      <c r="N28" s="193">
+        <f>IF(L28="",$B$4,L28)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="193" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>INV180546</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>First Focus - managed services Azure October 2026 [paid via DD]</t>
+        </is>
+      </c>
+      <c r="G29" s="187" t="n">
+        <v>629.85</v>
+      </c>
+      <c r="H29" s="187" t="n">
+        <v>62.99</v>
+      </c>
+      <c r="I29" s="187" t="n">
+        <v>692.84</v>
+      </c>
+      <c r="J29" s="187" t="n">
+        <v>692.84</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L29" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N29" s="193">
+        <f>IF(L29="",$B$4,L29)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="193" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INV2026/USA-09032</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Flatworld - Seek data entry September 2026 [paid via PL CC]</t>
+        </is>
+      </c>
+      <c r="G30" s="187" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="H30" s="187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="187" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="J30" s="187" t="n">
+        <v>92.20999999999999</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L30" s="192" t="n"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N30" s="193">
+        <f>IF(L30="",$B$4,L30)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="193" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INV00004009</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Easton Belle - legal fees, general commercial file [DL App]</t>
+        </is>
+      </c>
+      <c r="G31" s="187" t="n">
+        <v>3575</v>
+      </c>
+      <c r="H31" s="187" t="n">
+        <v>357.5</v>
+      </c>
+      <c r="I31" s="187" t="n">
+        <v>3932.5</v>
+      </c>
+      <c r="J31" s="187" t="n">
+        <v>3932.5</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L31" s="192" t="n">
+        <v>46325</v>
+      </c>
+      <c r="N31" s="193">
+        <f>IF(L31="",$B$4,L31)</f>
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="193" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>INV260412412804</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Energy Australia - electricity 23 Aug to 21 Sep [DD via PL CC]</t>
+        </is>
+      </c>
+      <c r="G32" s="187" t="n">
+        <v>632.95</v>
+      </c>
+      <c r="H32" s="187" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="I32" s="187" t="n">
+        <v>696.25</v>
+      </c>
+      <c r="J32" s="187" t="n">
+        <v>696.25</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L32" s="192" t="n"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N32" s="193">
+        <f>IF(L32="",$B$4,L32)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="193" t="n">
+        <v>46275</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>INV-18315</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Persona Health - fitness for duty assessment (GC to confirm)</t>
+        </is>
+      </c>
+      <c r="G33" s="187" t="n">
+        <v>906</v>
+      </c>
+      <c r="H33" s="187" t="n">
+        <v>90.59999999999999</v>
+      </c>
+      <c r="I33" s="187" t="n">
+        <v>996.6</v>
+      </c>
+      <c r="J33" s="187" t="n">
+        <v>996.6</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L33" s="192" t="n">
+        <v>46316</v>
+      </c>
+      <c r="N33" s="193">
+        <f>IF(L33="",$B$4,L33)</f>
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="193" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>41 of 60</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Employsure September 2026</t>
+        </is>
+      </c>
+      <c r="G34" s="187" t="n">
+        <v>800</v>
+      </c>
+      <c r="H34" s="187" t="n">
+        <v>80</v>
+      </c>
+      <c r="I34" s="187" t="n">
+        <v>880</v>
+      </c>
+      <c r="J34" s="187" t="n">
+        <v>880</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L34" s="192" t="n">
+        <v>46309</v>
+      </c>
+      <c r="N34" s="193">
+        <f>IF(L34="",$B$4,L34)</f>
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="193" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ASIC</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>ASIC - balance of the aged payables report at 12 Oct (check the actual bill)</t>
+        </is>
+      </c>
+      <c r="G35" s="187" t="n">
+        <v>342</v>
+      </c>
+      <c r="H35" s="187" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="187" t="n">
+        <v>342</v>
+      </c>
+      <c r="J35" s="187" t="n">
+        <v>342</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Awaiting Payment</t>
+        </is>
+      </c>
+      <c r="L35" s="192" t="n">
+        <v>46328</v>
+      </c>
+      <c r="N35" s="193">
+        <f>IF(L35="",$B$4,L35)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="193" t="n"/>
+      <c r="G36" s="187" t="n"/>
+      <c r="H36" s="187" t="n"/>
+      <c r="I36" s="187" t="n"/>
+      <c r="J36" s="187" t="n"/>
+      <c r="L36" s="192" t="n"/>
+      <c r="N36" s="193">
+        <f>IF(L36="",$B$4,L36)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="194" t="inlineStr">
+        <is>
+          <t>Rows 11 to 35 are the open bills in Xero at 12 Oct ($144,499.05) typed in the report layout so the forecast has something to work from. Next month, clear them and paste the new report over the top.</t>
+        </is>
+      </c>
+      <c r="G37" s="187" t="n"/>
+      <c r="H37" s="187" t="n"/>
+      <c r="I37" s="187" t="n"/>
+      <c r="J37" s="187" t="n"/>
+      <c r="L37" s="192" t="n"/>
+      <c r="N37" s="193">
+        <f>IF(L37="",$B$4,L37)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="193" t="n"/>
+      <c r="G38" s="187" t="n"/>
+      <c r="H38" s="187" t="n"/>
+      <c r="I38" s="187" t="n"/>
+      <c r="J38" s="187" t="n"/>
+      <c r="L38" s="192" t="n"/>
+      <c r="N38" s="193">
+        <f>IF(L38="",$B$4,L38)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="193" t="n"/>
+      <c r="G39" s="187" t="n"/>
+      <c r="H39" s="187" t="n"/>
+      <c r="I39" s="187" t="n"/>
+      <c r="J39" s="187" t="n"/>
+      <c r="L39" s="192" t="n"/>
+      <c r="N39" s="193">
+        <f>IF(L39="",$B$4,L39)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="193" t="n"/>
+      <c r="G40" s="187" t="n"/>
+      <c r="H40" s="187" t="n"/>
+      <c r="I40" s="187" t="n"/>
+      <c r="J40" s="187" t="n"/>
+      <c r="L40" s="192" t="n"/>
+      <c r="N40" s="193">
+        <f>IF(L40="",$B$4,L40)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="193" t="n"/>
+      <c r="G41" s="187" t="n"/>
+      <c r="H41" s="187" t="n"/>
+      <c r="I41" s="187" t="n"/>
+      <c r="J41" s="187" t="n"/>
+      <c r="L41" s="192" t="n"/>
+      <c r="N41" s="193">
+        <f>IF(L41="",$B$4,L41)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="193" t="n"/>
+      <c r="G42" s="187" t="n"/>
+      <c r="H42" s="187" t="n"/>
+      <c r="I42" s="187" t="n"/>
+      <c r="J42" s="187" t="n"/>
+      <c r="L42" s="192" t="n"/>
+      <c r="N42" s="193">
+        <f>IF(L42="",$B$4,L42)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="193" t="n"/>
+      <c r="G43" s="187" t="n"/>
+      <c r="H43" s="187" t="n"/>
+      <c r="I43" s="187" t="n"/>
+      <c r="J43" s="187" t="n"/>
+      <c r="L43" s="192" t="n"/>
+      <c r="N43" s="193">
+        <f>IF(L43="",$B$4,L43)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="193" t="n"/>
+      <c r="G44" s="187" t="n"/>
+      <c r="H44" s="187" t="n"/>
+      <c r="I44" s="187" t="n"/>
+      <c r="J44" s="187" t="n"/>
+      <c r="L44" s="192" t="n"/>
+      <c r="N44" s="193">
+        <f>IF(L44="",$B$4,L44)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="193" t="n"/>
+      <c r="G45" s="187" t="n"/>
+      <c r="H45" s="187" t="n"/>
+      <c r="I45" s="187" t="n"/>
+      <c r="J45" s="187" t="n"/>
+      <c r="L45" s="192" t="n"/>
+      <c r="N45" s="193">
+        <f>IF(L45="",$B$4,L45)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="193" t="n"/>
+      <c r="G46" s="187" t="n"/>
+      <c r="H46" s="187" t="n"/>
+      <c r="I46" s="187" t="n"/>
+      <c r="J46" s="187" t="n"/>
+      <c r="L46" s="192" t="n"/>
+      <c r="N46" s="193">
+        <f>IF(L46="",$B$4,L46)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="193" t="n"/>
+      <c r="G47" s="187" t="n"/>
+      <c r="H47" s="187" t="n"/>
+      <c r="I47" s="187" t="n"/>
+      <c r="J47" s="187" t="n"/>
+      <c r="L47" s="192" t="n"/>
+      <c r="N47" s="193">
+        <f>IF(L47="",$B$4,L47)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="193" t="n"/>
+      <c r="G48" s="187" t="n"/>
+      <c r="H48" s="187" t="n"/>
+      <c r="I48" s="187" t="n"/>
+      <c r="J48" s="187" t="n"/>
+      <c r="L48" s="192" t="n"/>
+      <c r="N48" s="193">
+        <f>IF(L48="",$B$4,L48)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="193" t="n"/>
+      <c r="G49" s="187" t="n"/>
+      <c r="H49" s="187" t="n"/>
+      <c r="I49" s="187" t="n"/>
+      <c r="J49" s="187" t="n"/>
+      <c r="L49" s="192" t="n"/>
+      <c r="N49" s="193">
+        <f>IF(L49="",$B$4,L49)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="193" t="n"/>
+      <c r="G50" s="187" t="n"/>
+      <c r="H50" s="187" t="n"/>
+      <c r="I50" s="187" t="n"/>
+      <c r="J50" s="187" t="n"/>
+      <c r="L50" s="192" t="n"/>
+      <c r="N50" s="193">
+        <f>IF(L50="",$B$4,L50)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="193" t="n"/>
+      <c r="G51" s="187" t="n"/>
+      <c r="H51" s="187" t="n"/>
+      <c r="I51" s="187" t="n"/>
+      <c r="J51" s="187" t="n"/>
+      <c r="L51" s="192" t="n"/>
+      <c r="N51" s="193">
+        <f>IF(L51="",$B$4,L51)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="193" t="n"/>
+      <c r="G52" s="187" t="n"/>
+      <c r="H52" s="187" t="n"/>
+      <c r="I52" s="187" t="n"/>
+      <c r="J52" s="187" t="n"/>
+      <c r="L52" s="192" t="n"/>
+      <c r="N52" s="193">
+        <f>IF(L52="",$B$4,L52)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="193" t="n"/>
+      <c r="G53" s="187" t="n"/>
+      <c r="H53" s="187" t="n"/>
+      <c r="I53" s="187" t="n"/>
+      <c r="J53" s="187" t="n"/>
+      <c r="L53" s="192" t="n"/>
+      <c r="N53" s="193">
+        <f>IF(L53="",$B$4,L53)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="193" t="n"/>
+      <c r="G54" s="187" t="n"/>
+      <c r="H54" s="187" t="n"/>
+      <c r="I54" s="187" t="n"/>
+      <c r="J54" s="187" t="n"/>
+      <c r="L54" s="192" t="n"/>
+      <c r="N54" s="193">
+        <f>IF(L54="",$B$4,L54)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="193" t="n"/>
+      <c r="G55" s="187" t="n"/>
+      <c r="H55" s="187" t="n"/>
+      <c r="I55" s="187" t="n"/>
+      <c r="J55" s="187" t="n"/>
+      <c r="L55" s="192" t="n"/>
+      <c r="N55" s="193">
+        <f>IF(L55="",$B$4,L55)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="193" t="n"/>
+      <c r="G56" s="187" t="n"/>
+      <c r="H56" s="187" t="n"/>
+      <c r="I56" s="187" t="n"/>
+      <c r="J56" s="187" t="n"/>
+      <c r="L56" s="192" t="n"/>
+      <c r="N56" s="193">
+        <f>IF(L56="",$B$4,L56)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="193" t="n"/>
+      <c r="G57" s="187" t="n"/>
+      <c r="H57" s="187" t="n"/>
+      <c r="I57" s="187" t="n"/>
+      <c r="J57" s="187" t="n"/>
+      <c r="L57" s="192" t="n"/>
+      <c r="N57" s="193">
+        <f>IF(L57="",$B$4,L57)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="193" t="n"/>
+      <c r="G58" s="187" t="n"/>
+      <c r="H58" s="187" t="n"/>
+      <c r="I58" s="187" t="n"/>
+      <c r="J58" s="187" t="n"/>
+      <c r="L58" s="192" t="n"/>
+      <c r="N58" s="193">
+        <f>IF(L58="",$B$4,L58)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="193" t="n"/>
+      <c r="G59" s="187" t="n"/>
+      <c r="H59" s="187" t="n"/>
+      <c r="I59" s="187" t="n"/>
+      <c r="J59" s="187" t="n"/>
+      <c r="L59" s="192" t="n"/>
+      <c r="N59" s="193">
+        <f>IF(L59="",$B$4,L59)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="193" t="n"/>
+      <c r="G60" s="187" t="n"/>
+      <c r="H60" s="187" t="n"/>
+      <c r="I60" s="187" t="n"/>
+      <c r="J60" s="187" t="n"/>
+      <c r="L60" s="192" t="n"/>
+      <c r="N60" s="193">
+        <f>IF(L60="",$B$4,L60)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="193" t="n"/>
+      <c r="G61" s="187" t="n"/>
+      <c r="H61" s="187" t="n"/>
+      <c r="I61" s="187" t="n"/>
+      <c r="J61" s="187" t="n"/>
+      <c r="L61" s="192" t="n"/>
+      <c r="N61" s="193">
+        <f>IF(L61="",$B$4,L61)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="193" t="n"/>
+      <c r="G62" s="187" t="n"/>
+      <c r="H62" s="187" t="n"/>
+      <c r="I62" s="187" t="n"/>
+      <c r="J62" s="187" t="n"/>
+      <c r="L62" s="192" t="n"/>
+      <c r="N62" s="193">
+        <f>IF(L62="",$B$4,L62)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="193" t="n"/>
+      <c r="G63" s="187" t="n"/>
+      <c r="H63" s="187" t="n"/>
+      <c r="I63" s="187" t="n"/>
+      <c r="J63" s="187" t="n"/>
+      <c r="L63" s="192" t="n"/>
+      <c r="N63" s="193">
+        <f>IF(L63="",$B$4,L63)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="193" t="n"/>
+      <c r="G64" s="187" t="n"/>
+      <c r="H64" s="187" t="n"/>
+      <c r="I64" s="187" t="n"/>
+      <c r="J64" s="187" t="n"/>
+      <c r="L64" s="192" t="n"/>
+      <c r="N64" s="193">
+        <f>IF(L64="",$B$4,L64)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="193" t="n"/>
+      <c r="G65" s="187" t="n"/>
+      <c r="H65" s="187" t="n"/>
+      <c r="I65" s="187" t="n"/>
+      <c r="J65" s="187" t="n"/>
+      <c r="L65" s="192" t="n"/>
+      <c r="N65" s="193">
+        <f>IF(L65="",$B$4,L65)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="193" t="n"/>
+      <c r="G66" s="187" t="n"/>
+      <c r="H66" s="187" t="n"/>
+      <c r="I66" s="187" t="n"/>
+      <c r="J66" s="187" t="n"/>
+      <c r="L66" s="192" t="n"/>
+      <c r="N66" s="193">
+        <f>IF(L66="",$B$4,L66)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="193" t="n"/>
+      <c r="G67" s="187" t="n"/>
+      <c r="H67" s="187" t="n"/>
+      <c r="I67" s="187" t="n"/>
+      <c r="J67" s="187" t="n"/>
+      <c r="L67" s="192" t="n"/>
+      <c r="N67" s="193">
+        <f>IF(L67="",$B$4,L67)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="193" t="n"/>
+      <c r="G68" s="187" t="n"/>
+      <c r="H68" s="187" t="n"/>
+      <c r="I68" s="187" t="n"/>
+      <c r="J68" s="187" t="n"/>
+      <c r="L68" s="192" t="n"/>
+      <c r="N68" s="193">
+        <f>IF(L68="",$B$4,L68)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="193" t="n"/>
+      <c r="G69" s="187" t="n"/>
+      <c r="H69" s="187" t="n"/>
+      <c r="I69" s="187" t="n"/>
+      <c r="J69" s="187" t="n"/>
+      <c r="L69" s="192" t="n"/>
+      <c r="N69" s="193">
+        <f>IF(L69="",$B$4,L69)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="193" t="n"/>
+      <c r="G70" s="187" t="n"/>
+      <c r="H70" s="187" t="n"/>
+      <c r="I70" s="187" t="n"/>
+      <c r="J70" s="187" t="n"/>
+      <c r="L70" s="192" t="n"/>
+      <c r="N70" s="193">
+        <f>IF(L70="",$B$4,L70)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="193" t="n"/>
+      <c r="G71" s="187" t="n"/>
+      <c r="H71" s="187" t="n"/>
+      <c r="I71" s="187" t="n"/>
+      <c r="J71" s="187" t="n"/>
+      <c r="L71" s="192" t="n"/>
+      <c r="N71" s="193">
+        <f>IF(L71="",$B$4,L71)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="193" t="n"/>
+      <c r="G72" s="187" t="n"/>
+      <c r="H72" s="187" t="n"/>
+      <c r="I72" s="187" t="n"/>
+      <c r="J72" s="187" t="n"/>
+      <c r="L72" s="192" t="n"/>
+      <c r="N72" s="193">
+        <f>IF(L72="",$B$4,L72)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="193" t="n"/>
+      <c r="G73" s="187" t="n"/>
+      <c r="H73" s="187" t="n"/>
+      <c r="I73" s="187" t="n"/>
+      <c r="J73" s="187" t="n"/>
+      <c r="L73" s="192" t="n"/>
+      <c r="N73" s="193">
+        <f>IF(L73="",$B$4,L73)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="193" t="n"/>
+      <c r="G74" s="187" t="n"/>
+      <c r="H74" s="187" t="n"/>
+      <c r="I74" s="187" t="n"/>
+      <c r="J74" s="187" t="n"/>
+      <c r="L74" s="192" t="n"/>
+      <c r="N74" s="193">
+        <f>IF(L74="",$B$4,L74)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="193" t="n"/>
+      <c r="G75" s="187" t="n"/>
+      <c r="H75" s="187" t="n"/>
+      <c r="I75" s="187" t="n"/>
+      <c r="J75" s="187" t="n"/>
+      <c r="L75" s="192" t="n"/>
+      <c r="N75" s="193">
+        <f>IF(L75="",$B$4,L75)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="193" t="n"/>
+      <c r="G76" s="187" t="n"/>
+      <c r="H76" s="187" t="n"/>
+      <c r="I76" s="187" t="n"/>
+      <c r="J76" s="187" t="n"/>
+      <c r="L76" s="192" t="n"/>
+      <c r="N76" s="193">
+        <f>IF(L76="",$B$4,L76)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="193" t="n"/>
+      <c r="G77" s="187" t="n"/>
+      <c r="H77" s="187" t="n"/>
+      <c r="I77" s="187" t="n"/>
+      <c r="J77" s="187" t="n"/>
+      <c r="L77" s="192" t="n"/>
+      <c r="N77" s="193">
+        <f>IF(L77="",$B$4,L77)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="193" t="n"/>
+      <c r="G78" s="187" t="n"/>
+      <c r="H78" s="187" t="n"/>
+      <c r="I78" s="187" t="n"/>
+      <c r="J78" s="187" t="n"/>
+      <c r="L78" s="192" t="n"/>
+      <c r="N78" s="193">
+        <f>IF(L78="",$B$4,L78)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="193" t="n"/>
+      <c r="G79" s="187" t="n"/>
+      <c r="H79" s="187" t="n"/>
+      <c r="I79" s="187" t="n"/>
+      <c r="J79" s="187" t="n"/>
+      <c r="L79" s="192" t="n"/>
+      <c r="N79" s="193">
+        <f>IF(L79="",$B$4,L79)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="193" t="n"/>
+      <c r="G80" s="187" t="n"/>
+      <c r="H80" s="187" t="n"/>
+      <c r="I80" s="187" t="n"/>
+      <c r="J80" s="187" t="n"/>
+      <c r="L80" s="192" t="n"/>
+      <c r="N80" s="193">
+        <f>IF(L80="",$B$4,L80)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="193" t="n"/>
+      <c r="G81" s="187" t="n"/>
+      <c r="H81" s="187" t="n"/>
+      <c r="I81" s="187" t="n"/>
+      <c r="J81" s="187" t="n"/>
+      <c r="L81" s="192" t="n"/>
+      <c r="N81" s="193">
+        <f>IF(L81="",$B$4,L81)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="193" t="n"/>
+      <c r="G82" s="187" t="n"/>
+      <c r="H82" s="187" t="n"/>
+      <c r="I82" s="187" t="n"/>
+      <c r="J82" s="187" t="n"/>
+      <c r="L82" s="192" t="n"/>
+      <c r="N82" s="193">
+        <f>IF(L82="",$B$4,L82)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="193" t="n"/>
+      <c r="G83" s="187" t="n"/>
+      <c r="H83" s="187" t="n"/>
+      <c r="I83" s="187" t="n"/>
+      <c r="J83" s="187" t="n"/>
+      <c r="L83" s="192" t="n"/>
+      <c r="N83" s="193">
+        <f>IF(L83="",$B$4,L83)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="193" t="n"/>
+      <c r="G84" s="187" t="n"/>
+      <c r="H84" s="187" t="n"/>
+      <c r="I84" s="187" t="n"/>
+      <c r="J84" s="187" t="n"/>
+      <c r="L84" s="192" t="n"/>
+      <c r="N84" s="193">
+        <f>IF(L84="",$B$4,L84)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="193" t="n"/>
+      <c r="G85" s="187" t="n"/>
+      <c r="H85" s="187" t="n"/>
+      <c r="I85" s="187" t="n"/>
+      <c r="J85" s="187" t="n"/>
+      <c r="L85" s="192" t="n"/>
+      <c r="N85" s="193">
+        <f>IF(L85="",$B$4,L85)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="193" t="n"/>
+      <c r="G86" s="187" t="n"/>
+      <c r="H86" s="187" t="n"/>
+      <c r="I86" s="187" t="n"/>
+      <c r="J86" s="187" t="n"/>
+      <c r="L86" s="192" t="n"/>
+      <c r="N86" s="193">
+        <f>IF(L86="",$B$4,L86)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="193" t="n"/>
+      <c r="G87" s="187" t="n"/>
+      <c r="H87" s="187" t="n"/>
+      <c r="I87" s="187" t="n"/>
+      <c r="J87" s="187" t="n"/>
+      <c r="L87" s="192" t="n"/>
+      <c r="N87" s="193">
+        <f>IF(L87="",$B$4,L87)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="193" t="n"/>
+      <c r="G88" s="187" t="n"/>
+      <c r="H88" s="187" t="n"/>
+      <c r="I88" s="187" t="n"/>
+      <c r="J88" s="187" t="n"/>
+      <c r="L88" s="192" t="n"/>
+      <c r="N88" s="193">
+        <f>IF(L88="",$B$4,L88)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="193" t="n"/>
+      <c r="G89" s="187" t="n"/>
+      <c r="H89" s="187" t="n"/>
+      <c r="I89" s="187" t="n"/>
+      <c r="J89" s="187" t="n"/>
+      <c r="L89" s="192" t="n"/>
+      <c r="N89" s="193">
+        <f>IF(L89="",$B$4,L89)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="193" t="n"/>
+      <c r="G90" s="187" t="n"/>
+      <c r="H90" s="187" t="n"/>
+      <c r="I90" s="187" t="n"/>
+      <c r="J90" s="187" t="n"/>
+      <c r="L90" s="192" t="n"/>
+      <c r="N90" s="193">
+        <f>IF(L90="",$B$4,L90)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="193" t="n"/>
+      <c r="G91" s="187" t="n"/>
+      <c r="H91" s="187" t="n"/>
+      <c r="I91" s="187" t="n"/>
+      <c r="J91" s="187" t="n"/>
+      <c r="L91" s="192" t="n"/>
+      <c r="N91" s="193">
+        <f>IF(L91="",$B$4,L91)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="193" t="n"/>
+      <c r="G92" s="187" t="n"/>
+      <c r="H92" s="187" t="n"/>
+      <c r="I92" s="187" t="n"/>
+      <c r="J92" s="187" t="n"/>
+      <c r="L92" s="192" t="n"/>
+      <c r="N92" s="193">
+        <f>IF(L92="",$B$4,L92)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="193" t="n"/>
+      <c r="G93" s="187" t="n"/>
+      <c r="H93" s="187" t="n"/>
+      <c r="I93" s="187" t="n"/>
+      <c r="J93" s="187" t="n"/>
+      <c r="L93" s="192" t="n"/>
+      <c r="N93" s="193">
+        <f>IF(L93="",$B$4,L93)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="193" t="n"/>
+      <c r="G94" s="187" t="n"/>
+      <c r="H94" s="187" t="n"/>
+      <c r="I94" s="187" t="n"/>
+      <c r="J94" s="187" t="n"/>
+      <c r="L94" s="192" t="n"/>
+      <c r="N94" s="193">
+        <f>IF(L94="",$B$4,L94)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="193" t="n"/>
+      <c r="G95" s="187" t="n"/>
+      <c r="H95" s="187" t="n"/>
+      <c r="I95" s="187" t="n"/>
+      <c r="J95" s="187" t="n"/>
+      <c r="L95" s="192" t="n"/>
+      <c r="N95" s="193">
+        <f>IF(L95="",$B$4,L95)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="193" t="n"/>
+      <c r="G96" s="187" t="n"/>
+      <c r="H96" s="187" t="n"/>
+      <c r="I96" s="187" t="n"/>
+      <c r="J96" s="187" t="n"/>
+      <c r="L96" s="192" t="n"/>
+      <c r="N96" s="193">
+        <f>IF(L96="",$B$4,L96)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="193" t="n"/>
+      <c r="G97" s="187" t="n"/>
+      <c r="H97" s="187" t="n"/>
+      <c r="I97" s="187" t="n"/>
+      <c r="J97" s="187" t="n"/>
+      <c r="L97" s="192" t="n"/>
+      <c r="N97" s="193">
+        <f>IF(L97="",$B$4,L97)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="193" t="n"/>
+      <c r="G98" s="187" t="n"/>
+      <c r="H98" s="187" t="n"/>
+      <c r="I98" s="187" t="n"/>
+      <c r="J98" s="187" t="n"/>
+      <c r="L98" s="192" t="n"/>
+      <c r="N98" s="193">
+        <f>IF(L98="",$B$4,L98)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="193" t="n"/>
+      <c r="G99" s="187" t="n"/>
+      <c r="H99" s="187" t="n"/>
+      <c r="I99" s="187" t="n"/>
+      <c r="J99" s="187" t="n"/>
+      <c r="L99" s="192" t="n"/>
+      <c r="N99" s="193">
+        <f>IF(L99="",$B$4,L99)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="193" t="n"/>
+      <c r="G100" s="187" t="n"/>
+      <c r="H100" s="187" t="n"/>
+      <c r="I100" s="187" t="n"/>
+      <c r="J100" s="187" t="n"/>
+      <c r="L100" s="192" t="n"/>
+      <c r="N100" s="193">
+        <f>IF(L100="",$B$4,L100)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="193" t="n"/>
+      <c r="G101" s="187" t="n"/>
+      <c r="H101" s="187" t="n"/>
+      <c r="I101" s="187" t="n"/>
+      <c r="J101" s="187" t="n"/>
+      <c r="L101" s="192" t="n"/>
+      <c r="N101" s="193">
+        <f>IF(L101="",$B$4,L101)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="193" t="n"/>
+      <c r="G102" s="187" t="n"/>
+      <c r="H102" s="187" t="n"/>
+      <c r="I102" s="187" t="n"/>
+      <c r="J102" s="187" t="n"/>
+      <c r="L102" s="192" t="n"/>
+      <c r="N102" s="193">
+        <f>IF(L102="",$B$4,L102)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="193" t="n"/>
+      <c r="G103" s="187" t="n"/>
+      <c r="H103" s="187" t="n"/>
+      <c r="I103" s="187" t="n"/>
+      <c r="J103" s="187" t="n"/>
+      <c r="L103" s="192" t="n"/>
+      <c r="N103" s="193">
+        <f>IF(L103="",$B$4,L103)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="193" t="n"/>
+      <c r="G104" s="187" t="n"/>
+      <c r="H104" s="187" t="n"/>
+      <c r="I104" s="187" t="n"/>
+      <c r="J104" s="187" t="n"/>
+      <c r="L104" s="192" t="n"/>
+      <c r="N104" s="193">
+        <f>IF(L104="",$B$4,L104)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="193" t="n"/>
+      <c r="G105" s="187" t="n"/>
+      <c r="H105" s="187" t="n"/>
+      <c r="I105" s="187" t="n"/>
+      <c r="J105" s="187" t="n"/>
+      <c r="L105" s="192" t="n"/>
+      <c r="N105" s="193">
+        <f>IF(L105="",$B$4,L105)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="193" t="n"/>
+      <c r="G106" s="187" t="n"/>
+      <c r="H106" s="187" t="n"/>
+      <c r="I106" s="187" t="n"/>
+      <c r="J106" s="187" t="n"/>
+      <c r="L106" s="192" t="n"/>
+      <c r="N106" s="193">
+        <f>IF(L106="",$B$4,L106)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="193" t="n"/>
+      <c r="G107" s="187" t="n"/>
+      <c r="H107" s="187" t="n"/>
+      <c r="I107" s="187" t="n"/>
+      <c r="J107" s="187" t="n"/>
+      <c r="L107" s="192" t="n"/>
+      <c r="N107" s="193">
+        <f>IF(L107="",$B$4,L107)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="193" t="n"/>
+      <c r="G108" s="187" t="n"/>
+      <c r="H108" s="187" t="n"/>
+      <c r="I108" s="187" t="n"/>
+      <c r="J108" s="187" t="n"/>
+      <c r="L108" s="192" t="n"/>
+      <c r="N108" s="193">
+        <f>IF(L108="",$B$4,L108)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="193" t="n"/>
+      <c r="G109" s="187" t="n"/>
+      <c r="H109" s="187" t="n"/>
+      <c r="I109" s="187" t="n"/>
+      <c r="J109" s="187" t="n"/>
+      <c r="L109" s="192" t="n"/>
+      <c r="N109" s="193">
+        <f>IF(L109="",$B$4,L109)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="193" t="n"/>
+      <c r="G110" s="187" t="n"/>
+      <c r="H110" s="187" t="n"/>
+      <c r="I110" s="187" t="n"/>
+      <c r="J110" s="187" t="n"/>
+      <c r="L110" s="192" t="n"/>
+      <c r="N110" s="193">
+        <f>IF(L110="",$B$4,L110)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="193" t="n"/>
+      <c r="G111" s="187" t="n"/>
+      <c r="H111" s="187" t="n"/>
+      <c r="I111" s="187" t="n"/>
+      <c r="J111" s="187" t="n"/>
+      <c r="L111" s="192" t="n"/>
+      <c r="N111" s="193">
+        <f>IF(L111="",$B$4,L111)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="193" t="n"/>
+      <c r="G112" s="187" t="n"/>
+      <c r="H112" s="187" t="n"/>
+      <c r="I112" s="187" t="n"/>
+      <c r="J112" s="187" t="n"/>
+      <c r="L112" s="192" t="n"/>
+      <c r="N112" s="193">
+        <f>IF(L112="",$B$4,L112)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="193" t="n"/>
+      <c r="G113" s="187" t="n"/>
+      <c r="H113" s="187" t="n"/>
+      <c r="I113" s="187" t="n"/>
+      <c r="J113" s="187" t="n"/>
+      <c r="L113" s="192" t="n"/>
+      <c r="N113" s="193">
+        <f>IF(L113="",$B$4,L113)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="193" t="n"/>
+      <c r="G114" s="187" t="n"/>
+      <c r="H114" s="187" t="n"/>
+      <c r="I114" s="187" t="n"/>
+      <c r="J114" s="187" t="n"/>
+      <c r="L114" s="192" t="n"/>
+      <c r="N114" s="193">
+        <f>IF(L114="",$B$4,L114)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="193" t="n"/>
+      <c r="G115" s="187" t="n"/>
+      <c r="H115" s="187" t="n"/>
+      <c r="I115" s="187" t="n"/>
+      <c r="J115" s="187" t="n"/>
+      <c r="L115" s="192" t="n"/>
+      <c r="N115" s="193">
+        <f>IF(L115="",$B$4,L115)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="193" t="n"/>
+      <c r="G116" s="187" t="n"/>
+      <c r="H116" s="187" t="n"/>
+      <c r="I116" s="187" t="n"/>
+      <c r="J116" s="187" t="n"/>
+      <c r="L116" s="192" t="n"/>
+      <c r="N116" s="193">
+        <f>IF(L116="",$B$4,L116)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="193" t="n"/>
+      <c r="G117" s="187" t="n"/>
+      <c r="H117" s="187" t="n"/>
+      <c r="I117" s="187" t="n"/>
+      <c r="J117" s="187" t="n"/>
+      <c r="L117" s="192" t="n"/>
+      <c r="N117" s="193">
+        <f>IF(L117="",$B$4,L117)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="193" t="n"/>
+      <c r="G118" s="187" t="n"/>
+      <c r="H118" s="187" t="n"/>
+      <c r="I118" s="187" t="n"/>
+      <c r="J118" s="187" t="n"/>
+      <c r="L118" s="192" t="n"/>
+      <c r="N118" s="193">
+        <f>IF(L118="",$B$4,L118)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="193" t="n"/>
+      <c r="G119" s="187" t="n"/>
+      <c r="H119" s="187" t="n"/>
+      <c r="I119" s="187" t="n"/>
+      <c r="J119" s="187" t="n"/>
+      <c r="L119" s="192" t="n"/>
+      <c r="N119" s="193">
+        <f>IF(L119="",$B$4,L119)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="193" t="n"/>
+      <c r="G120" s="187" t="n"/>
+      <c r="H120" s="187" t="n"/>
+      <c r="I120" s="187" t="n"/>
+      <c r="J120" s="187" t="n"/>
+      <c r="L120" s="192" t="n"/>
+      <c r="N120" s="193">
+        <f>IF(L120="",$B$4,L120)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="193" t="n"/>
+      <c r="G121" s="187" t="n"/>
+      <c r="H121" s="187" t="n"/>
+      <c r="I121" s="187" t="n"/>
+      <c r="J121" s="187" t="n"/>
+      <c r="L121" s="192" t="n"/>
+      <c r="N121" s="193">
+        <f>IF(L121="",$B$4,L121)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="193" t="n"/>
+      <c r="G122" s="187" t="n"/>
+      <c r="H122" s="187" t="n"/>
+      <c r="I122" s="187" t="n"/>
+      <c r="J122" s="187" t="n"/>
+      <c r="L122" s="192" t="n"/>
+      <c r="N122" s="193">
+        <f>IF(L122="",$B$4,L122)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="193" t="n"/>
+      <c r="G123" s="187" t="n"/>
+      <c r="H123" s="187" t="n"/>
+      <c r="I123" s="187" t="n"/>
+      <c r="J123" s="187" t="n"/>
+      <c r="L123" s="192" t="n"/>
+      <c r="N123" s="193">
+        <f>IF(L123="",$B$4,L123)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="193" t="n"/>
+      <c r="G124" s="187" t="n"/>
+      <c r="H124" s="187" t="n"/>
+      <c r="I124" s="187" t="n"/>
+      <c r="J124" s="187" t="n"/>
+      <c r="L124" s="192" t="n"/>
+      <c r="N124" s="193">
+        <f>IF(L124="",$B$4,L124)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="193" t="n"/>
+      <c r="G125" s="187" t="n"/>
+      <c r="H125" s="187" t="n"/>
+      <c r="I125" s="187" t="n"/>
+      <c r="J125" s="187" t="n"/>
+      <c r="L125" s="192" t="n"/>
+      <c r="N125" s="193">
+        <f>IF(L125="",$B$4,L125)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="193" t="n"/>
+      <c r="G126" s="187" t="n"/>
+      <c r="H126" s="187" t="n"/>
+      <c r="I126" s="187" t="n"/>
+      <c r="J126" s="187" t="n"/>
+      <c r="L126" s="192" t="n"/>
+      <c r="N126" s="193">
+        <f>IF(L126="",$B$4,L126)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="193" t="n"/>
+      <c r="G127" s="187" t="n"/>
+      <c r="H127" s="187" t="n"/>
+      <c r="I127" s="187" t="n"/>
+      <c r="J127" s="187" t="n"/>
+      <c r="L127" s="192" t="n"/>
+      <c r="N127" s="193">
+        <f>IF(L127="",$B$4,L127)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="193" t="n"/>
+      <c r="G128" s="187" t="n"/>
+      <c r="H128" s="187" t="n"/>
+      <c r="I128" s="187" t="n"/>
+      <c r="J128" s="187" t="n"/>
+      <c r="L128" s="192" t="n"/>
+      <c r="N128" s="193">
+        <f>IF(L128="",$B$4,L128)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="193" t="n"/>
+      <c r="G129" s="187" t="n"/>
+      <c r="H129" s="187" t="n"/>
+      <c r="I129" s="187" t="n"/>
+      <c r="J129" s="187" t="n"/>
+      <c r="L129" s="192" t="n"/>
+      <c r="N129" s="193">
+        <f>IF(L129="",$B$4,L129)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="193" t="n"/>
+      <c r="G130" s="187" t="n"/>
+      <c r="H130" s="187" t="n"/>
+      <c r="I130" s="187" t="n"/>
+      <c r="J130" s="187" t="n"/>
+      <c r="L130" s="192" t="n"/>
+      <c r="N130" s="193">
+        <f>IF(L130="",$B$4,L130)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="193" t="n"/>
+      <c r="G131" s="187" t="n"/>
+      <c r="H131" s="187" t="n"/>
+      <c r="I131" s="187" t="n"/>
+      <c r="J131" s="187" t="n"/>
+      <c r="L131" s="192" t="n"/>
+      <c r="N131" s="193">
+        <f>IF(L131="",$B$4,L131)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="193" t="n"/>
+      <c r="G132" s="187" t="n"/>
+      <c r="H132" s="187" t="n"/>
+      <c r="I132" s="187" t="n"/>
+      <c r="J132" s="187" t="n"/>
+      <c r="L132" s="192" t="n"/>
+      <c r="N132" s="193">
+        <f>IF(L132="",$B$4,L132)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="193" t="n"/>
+      <c r="G133" s="187" t="n"/>
+      <c r="H133" s="187" t="n"/>
+      <c r="I133" s="187" t="n"/>
+      <c r="J133" s="187" t="n"/>
+      <c r="L133" s="192" t="n"/>
+      <c r="N133" s="193">
+        <f>IF(L133="",$B$4,L133)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="193" t="n"/>
+      <c r="G134" s="187" t="n"/>
+      <c r="H134" s="187" t="n"/>
+      <c r="I134" s="187" t="n"/>
+      <c r="J134" s="187" t="n"/>
+      <c r="L134" s="192" t="n"/>
+      <c r="N134" s="193">
+        <f>IF(L134="",$B$4,L134)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="193" t="n"/>
+      <c r="G135" s="187" t="n"/>
+      <c r="H135" s="187" t="n"/>
+      <c r="I135" s="187" t="n"/>
+      <c r="J135" s="187" t="n"/>
+      <c r="L135" s="192" t="n"/>
+      <c r="N135" s="193">
+        <f>IF(L135="",$B$4,L135)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="193" t="n"/>
+      <c r="G136" s="187" t="n"/>
+      <c r="H136" s="187" t="n"/>
+      <c r="I136" s="187" t="n"/>
+      <c r="J136" s="187" t="n"/>
+      <c r="L136" s="192" t="n"/>
+      <c r="N136" s="193">
+        <f>IF(L136="",$B$4,L136)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="193" t="n"/>
+      <c r="G137" s="187" t="n"/>
+      <c r="H137" s="187" t="n"/>
+      <c r="I137" s="187" t="n"/>
+      <c r="J137" s="187" t="n"/>
+      <c r="L137" s="192" t="n"/>
+      <c r="N137" s="193">
+        <f>IF(L137="",$B$4,L137)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="193" t="n"/>
+      <c r="G138" s="187" t="n"/>
+      <c r="H138" s="187" t="n"/>
+      <c r="I138" s="187" t="n"/>
+      <c r="J138" s="187" t="n"/>
+      <c r="L138" s="192" t="n"/>
+      <c r="N138" s="193">
+        <f>IF(L138="",$B$4,L138)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="193" t="n"/>
+      <c r="G139" s="187" t="n"/>
+      <c r="H139" s="187" t="n"/>
+      <c r="I139" s="187" t="n"/>
+      <c r="J139" s="187" t="n"/>
+      <c r="L139" s="192" t="n"/>
+      <c r="N139" s="193">
+        <f>IF(L139="",$B$4,L139)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="193" t="n"/>
+      <c r="G140" s="187" t="n"/>
+      <c r="H140" s="187" t="n"/>
+      <c r="I140" s="187" t="n"/>
+      <c r="J140" s="187" t="n"/>
+      <c r="L140" s="192" t="n"/>
+      <c r="N140" s="193">
+        <f>IF(L140="",$B$4,L140)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="193" t="n"/>
+      <c r="G141" s="187" t="n"/>
+      <c r="H141" s="187" t="n"/>
+      <c r="I141" s="187" t="n"/>
+      <c r="J141" s="187" t="n"/>
+      <c r="L141" s="192" t="n"/>
+      <c r="N141" s="193">
+        <f>IF(L141="",$B$4,L141)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="193" t="n"/>
+      <c r="G142" s="187" t="n"/>
+      <c r="H142" s="187" t="n"/>
+      <c r="I142" s="187" t="n"/>
+      <c r="J142" s="187" t="n"/>
+      <c r="L142" s="192" t="n"/>
+      <c r="N142" s="193">
+        <f>IF(L142="",$B$4,L142)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="193" t="n"/>
+      <c r="G143" s="187" t="n"/>
+      <c r="H143" s="187" t="n"/>
+      <c r="I143" s="187" t="n"/>
+      <c r="J143" s="187" t="n"/>
+      <c r="L143" s="192" t="n"/>
+      <c r="N143" s="193">
+        <f>IF(L143="",$B$4,L143)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="193" t="n"/>
+      <c r="G144" s="187" t="n"/>
+      <c r="H144" s="187" t="n"/>
+      <c r="I144" s="187" t="n"/>
+      <c r="J144" s="187" t="n"/>
+      <c r="L144" s="192" t="n"/>
+      <c r="N144" s="193">
+        <f>IF(L144="",$B$4,L144)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="193" t="n"/>
+      <c r="G145" s="187" t="n"/>
+      <c r="H145" s="187" t="n"/>
+      <c r="I145" s="187" t="n"/>
+      <c r="J145" s="187" t="n"/>
+      <c r="L145" s="192" t="n"/>
+      <c r="N145" s="193">
+        <f>IF(L145="",$B$4,L145)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="193" t="n"/>
+      <c r="G146" s="187" t="n"/>
+      <c r="H146" s="187" t="n"/>
+      <c r="I146" s="187" t="n"/>
+      <c r="J146" s="187" t="n"/>
+      <c r="L146" s="192" t="n"/>
+      <c r="N146" s="193">
+        <f>IF(L146="",$B$4,L146)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="193" t="n"/>
+      <c r="G147" s="187" t="n"/>
+      <c r="H147" s="187" t="n"/>
+      <c r="I147" s="187" t="n"/>
+      <c r="J147" s="187" t="n"/>
+      <c r="L147" s="192" t="n"/>
+      <c r="N147" s="193">
+        <f>IF(L147="",$B$4,L147)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="193" t="n"/>
+      <c r="G148" s="187" t="n"/>
+      <c r="H148" s="187" t="n"/>
+      <c r="I148" s="187" t="n"/>
+      <c r="J148" s="187" t="n"/>
+      <c r="L148" s="192" t="n"/>
+      <c r="N148" s="193">
+        <f>IF(L148="",$B$4,L148)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="193" t="n"/>
+      <c r="G149" s="187" t="n"/>
+      <c r="H149" s="187" t="n"/>
+      <c r="I149" s="187" t="n"/>
+      <c r="J149" s="187" t="n"/>
+      <c r="L149" s="192" t="n"/>
+      <c r="N149" s="193">
+        <f>IF(L149="",$B$4,L149)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="193" t="n"/>
+      <c r="G150" s="187" t="n"/>
+      <c r="H150" s="187" t="n"/>
+      <c r="I150" s="187" t="n"/>
+      <c r="J150" s="187" t="n"/>
+      <c r="L150" s="192" t="n"/>
+      <c r="N150" s="193">
+        <f>IF(L150="",$B$4,L150)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="193" t="n"/>
+      <c r="G151" s="187" t="n"/>
+      <c r="H151" s="187" t="n"/>
+      <c r="I151" s="187" t="n"/>
+      <c r="J151" s="187" t="n"/>
+      <c r="L151" s="192" t="n"/>
+      <c r="N151" s="193">
+        <f>IF(L151="",$B$4,L151)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="193" t="n"/>
+      <c r="G152" s="187" t="n"/>
+      <c r="H152" s="187" t="n"/>
+      <c r="I152" s="187" t="n"/>
+      <c r="J152" s="187" t="n"/>
+      <c r="L152" s="192" t="n"/>
+      <c r="N152" s="193">
+        <f>IF(L152="",$B$4,L152)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="193" t="n"/>
+      <c r="G153" s="187" t="n"/>
+      <c r="H153" s="187" t="n"/>
+      <c r="I153" s="187" t="n"/>
+      <c r="J153" s="187" t="n"/>
+      <c r="L153" s="192" t="n"/>
+      <c r="N153" s="193">
+        <f>IF(L153="",$B$4,L153)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="193" t="n"/>
+      <c r="G154" s="187" t="n"/>
+      <c r="H154" s="187" t="n"/>
+      <c r="I154" s="187" t="n"/>
+      <c r="J154" s="187" t="n"/>
+      <c r="L154" s="192" t="n"/>
+      <c r="N154" s="193">
+        <f>IF(L154="",$B$4,L154)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="193" t="n"/>
+      <c r="G155" s="187" t="n"/>
+      <c r="H155" s="187" t="n"/>
+      <c r="I155" s="187" t="n"/>
+      <c r="J155" s="187" t="n"/>
+      <c r="L155" s="192" t="n"/>
+      <c r="N155" s="193">
+        <f>IF(L155="",$B$4,L155)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="193" t="n"/>
+      <c r="G156" s="187" t="n"/>
+      <c r="H156" s="187" t="n"/>
+      <c r="I156" s="187" t="n"/>
+      <c r="J156" s="187" t="n"/>
+      <c r="L156" s="192" t="n"/>
+      <c r="N156" s="193">
+        <f>IF(L156="",$B$4,L156)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="193" t="n"/>
+      <c r="G157" s="187" t="n"/>
+      <c r="H157" s="187" t="n"/>
+      <c r="I157" s="187" t="n"/>
+      <c r="J157" s="187" t="n"/>
+      <c r="L157" s="192" t="n"/>
+      <c r="N157" s="193">
+        <f>IF(L157="",$B$4,L157)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="193" t="n"/>
+      <c r="G158" s="187" t="n"/>
+      <c r="H158" s="187" t="n"/>
+      <c r="I158" s="187" t="n"/>
+      <c r="J158" s="187" t="n"/>
+      <c r="L158" s="192" t="n"/>
+      <c r="N158" s="193">
+        <f>IF(L158="",$B$4,L158)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="193" t="n"/>
+      <c r="G159" s="187" t="n"/>
+      <c r="H159" s="187" t="n"/>
+      <c r="I159" s="187" t="n"/>
+      <c r="J159" s="187" t="n"/>
+      <c r="L159" s="192" t="n"/>
+      <c r="N159" s="193">
+        <f>IF(L159="",$B$4,L159)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="193" t="n"/>
+      <c r="G160" s="187" t="n"/>
+      <c r="H160" s="187" t="n"/>
+      <c r="I160" s="187" t="n"/>
+      <c r="J160" s="187" t="n"/>
+      <c r="L160" s="192" t="n"/>
+      <c r="N160" s="193">
+        <f>IF(L160="",$B$4,L160)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="193" t="n"/>
+      <c r="G161" s="187" t="n"/>
+      <c r="H161" s="187" t="n"/>
+      <c r="I161" s="187" t="n"/>
+      <c r="J161" s="187" t="n"/>
+      <c r="L161" s="192" t="n"/>
+      <c r="N161" s="193">
+        <f>IF(L161="",$B$4,L161)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="193" t="n"/>
+      <c r="G162" s="187" t="n"/>
+      <c r="H162" s="187" t="n"/>
+      <c r="I162" s="187" t="n"/>
+      <c r="J162" s="187" t="n"/>
+      <c r="L162" s="192" t="n"/>
+      <c r="N162" s="193">
+        <f>IF(L162="",$B$4,L162)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="193" t="n"/>
+      <c r="G163" s="187" t="n"/>
+      <c r="H163" s="187" t="n"/>
+      <c r="I163" s="187" t="n"/>
+      <c r="J163" s="187" t="n"/>
+      <c r="L163" s="192" t="n"/>
+      <c r="N163" s="193">
+        <f>IF(L163="",$B$4,L163)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="193" t="n"/>
+      <c r="G164" s="187" t="n"/>
+      <c r="H164" s="187" t="n"/>
+      <c r="I164" s="187" t="n"/>
+      <c r="J164" s="187" t="n"/>
+      <c r="L164" s="192" t="n"/>
+      <c r="N164" s="193">
+        <f>IF(L164="",$B$4,L164)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="193" t="n"/>
+      <c r="G165" s="187" t="n"/>
+      <c r="H165" s="187" t="n"/>
+      <c r="I165" s="187" t="n"/>
+      <c r="J165" s="187" t="n"/>
+      <c r="L165" s="192" t="n"/>
+      <c r="N165" s="193">
+        <f>IF(L165="",$B$4,L165)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="193" t="n"/>
+      <c r="G166" s="187" t="n"/>
+      <c r="H166" s="187" t="n"/>
+      <c r="I166" s="187" t="n"/>
+      <c r="J166" s="187" t="n"/>
+      <c r="L166" s="192" t="n"/>
+      <c r="N166" s="193">
+        <f>IF(L166="",$B$4,L166)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="193" t="n"/>
+      <c r="G167" s="187" t="n"/>
+      <c r="H167" s="187" t="n"/>
+      <c r="I167" s="187" t="n"/>
+      <c r="J167" s="187" t="n"/>
+      <c r="L167" s="192" t="n"/>
+      <c r="N167" s="193">
+        <f>IF(L167="",$B$4,L167)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="193" t="n"/>
+      <c r="G168" s="187" t="n"/>
+      <c r="H168" s="187" t="n"/>
+      <c r="I168" s="187" t="n"/>
+      <c r="J168" s="187" t="n"/>
+      <c r="L168" s="192" t="n"/>
+      <c r="N168" s="193">
+        <f>IF(L168="",$B$4,L168)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="193" t="n"/>
+      <c r="G169" s="187" t="n"/>
+      <c r="H169" s="187" t="n"/>
+      <c r="I169" s="187" t="n"/>
+      <c r="J169" s="187" t="n"/>
+      <c r="L169" s="192" t="n"/>
+      <c r="N169" s="193">
+        <f>IF(L169="",$B$4,L169)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="193" t="n"/>
+      <c r="G170" s="187" t="n"/>
+      <c r="H170" s="187" t="n"/>
+      <c r="I170" s="187" t="n"/>
+      <c r="J170" s="187" t="n"/>
+      <c r="L170" s="192" t="n"/>
+      <c r="N170" s="193">
+        <f>IF(L170="",$B$4,L170)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="193" t="n"/>
+      <c r="G171" s="187" t="n"/>
+      <c r="H171" s="187" t="n"/>
+      <c r="I171" s="187" t="n"/>
+      <c r="J171" s="187" t="n"/>
+      <c r="L171" s="192" t="n"/>
+      <c r="N171" s="193">
+        <f>IF(L171="",$B$4,L171)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="193" t="n"/>
+      <c r="G172" s="187" t="n"/>
+      <c r="H172" s="187" t="n"/>
+      <c r="I172" s="187" t="n"/>
+      <c r="J172" s="187" t="n"/>
+      <c r="L172" s="192" t="n"/>
+      <c r="N172" s="193">
+        <f>IF(L172="",$B$4,L172)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="193" t="n"/>
+      <c r="G173" s="187" t="n"/>
+      <c r="H173" s="187" t="n"/>
+      <c r="I173" s="187" t="n"/>
+      <c r="J173" s="187" t="n"/>
+      <c r="L173" s="192" t="n"/>
+      <c r="N173" s="193">
+        <f>IF(L173="",$B$4,L173)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="193" t="n"/>
+      <c r="G174" s="187" t="n"/>
+      <c r="H174" s="187" t="n"/>
+      <c r="I174" s="187" t="n"/>
+      <c r="J174" s="187" t="n"/>
+      <c r="L174" s="192" t="n"/>
+      <c r="N174" s="193">
+        <f>IF(L174="",$B$4,L174)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="193" t="n"/>
+      <c r="G175" s="187" t="n"/>
+      <c r="H175" s="187" t="n"/>
+      <c r="I175" s="187" t="n"/>
+      <c r="J175" s="187" t="n"/>
+      <c r="L175" s="192" t="n"/>
+      <c r="N175" s="193">
+        <f>IF(L175="",$B$4,L175)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="193" t="n"/>
+      <c r="G176" s="187" t="n"/>
+      <c r="H176" s="187" t="n"/>
+      <c r="I176" s="187" t="n"/>
+      <c r="J176" s="187" t="n"/>
+      <c r="L176" s="192" t="n"/>
+      <c r="N176" s="193">
+        <f>IF(L176="",$B$4,L176)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="193" t="n"/>
+      <c r="G177" s="187" t="n"/>
+      <c r="H177" s="187" t="n"/>
+      <c r="I177" s="187" t="n"/>
+      <c r="J177" s="187" t="n"/>
+      <c r="L177" s="192" t="n"/>
+      <c r="N177" s="193">
+        <f>IF(L177="",$B$4,L177)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="193" t="n"/>
+      <c r="G178" s="187" t="n"/>
+      <c r="H178" s="187" t="n"/>
+      <c r="I178" s="187" t="n"/>
+      <c r="J178" s="187" t="n"/>
+      <c r="L178" s="192" t="n"/>
+      <c r="N178" s="193">
+        <f>IF(L178="",$B$4,L178)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="193" t="n"/>
+      <c r="G179" s="187" t="n"/>
+      <c r="H179" s="187" t="n"/>
+      <c r="I179" s="187" t="n"/>
+      <c r="J179" s="187" t="n"/>
+      <c r="L179" s="192" t="n"/>
+      <c r="N179" s="193">
+        <f>IF(L179="",$B$4,L179)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="193" t="n"/>
+      <c r="G180" s="187" t="n"/>
+      <c r="H180" s="187" t="n"/>
+      <c r="I180" s="187" t="n"/>
+      <c r="J180" s="187" t="n"/>
+      <c r="L180" s="192" t="n"/>
+      <c r="N180" s="193">
+        <f>IF(L180="",$B$4,L180)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="193" t="n"/>
+      <c r="G181" s="187" t="n"/>
+      <c r="H181" s="187" t="n"/>
+      <c r="I181" s="187" t="n"/>
+      <c r="J181" s="187" t="n"/>
+      <c r="L181" s="192" t="n"/>
+      <c r="N181" s="193">
+        <f>IF(L181="",$B$4,L181)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="193" t="n"/>
+      <c r="G182" s="187" t="n"/>
+      <c r="H182" s="187" t="n"/>
+      <c r="I182" s="187" t="n"/>
+      <c r="J182" s="187" t="n"/>
+      <c r="L182" s="192" t="n"/>
+      <c r="N182" s="193">
+        <f>IF(L182="",$B$4,L182)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="193" t="n"/>
+      <c r="G183" s="187" t="n"/>
+      <c r="H183" s="187" t="n"/>
+      <c r="I183" s="187" t="n"/>
+      <c r="J183" s="187" t="n"/>
+      <c r="L183" s="192" t="n"/>
+      <c r="N183" s="193">
+        <f>IF(L183="",$B$4,L183)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="193" t="n"/>
+      <c r="G184" s="187" t="n"/>
+      <c r="H184" s="187" t="n"/>
+      <c r="I184" s="187" t="n"/>
+      <c r="J184" s="187" t="n"/>
+      <c r="L184" s="192" t="n"/>
+      <c r="N184" s="193">
+        <f>IF(L184="",$B$4,L184)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="193" t="n"/>
+      <c r="G185" s="187" t="n"/>
+      <c r="H185" s="187" t="n"/>
+      <c r="I185" s="187" t="n"/>
+      <c r="J185" s="187" t="n"/>
+      <c r="L185" s="192" t="n"/>
+      <c r="N185" s="193">
+        <f>IF(L185="",$B$4,L185)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="193" t="n"/>
+      <c r="G186" s="187" t="n"/>
+      <c r="H186" s="187" t="n"/>
+      <c r="I186" s="187" t="n"/>
+      <c r="J186" s="187" t="n"/>
+      <c r="L186" s="192" t="n"/>
+      <c r="N186" s="193">
+        <f>IF(L186="",$B$4,L186)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="193" t="n"/>
+      <c r="G187" s="187" t="n"/>
+      <c r="H187" s="187" t="n"/>
+      <c r="I187" s="187" t="n"/>
+      <c r="J187" s="187" t="n"/>
+      <c r="L187" s="192" t="n"/>
+      <c r="N187" s="193">
+        <f>IF(L187="",$B$4,L187)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="193" t="n"/>
+      <c r="G188" s="187" t="n"/>
+      <c r="H188" s="187" t="n"/>
+      <c r="I188" s="187" t="n"/>
+      <c r="J188" s="187" t="n"/>
+      <c r="L188" s="192" t="n"/>
+      <c r="N188" s="193">
+        <f>IF(L188="",$B$4,L188)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="193" t="n"/>
+      <c r="G189" s="187" t="n"/>
+      <c r="H189" s="187" t="n"/>
+      <c r="I189" s="187" t="n"/>
+      <c r="J189" s="187" t="n"/>
+      <c r="L189" s="192" t="n"/>
+      <c r="N189" s="193">
+        <f>IF(L189="",$B$4,L189)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="193" t="n"/>
+      <c r="G190" s="187" t="n"/>
+      <c r="H190" s="187" t="n"/>
+      <c r="I190" s="187" t="n"/>
+      <c r="J190" s="187" t="n"/>
+      <c r="L190" s="192" t="n"/>
+      <c r="N190" s="193">
+        <f>IF(L190="",$B$4,L190)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="193" t="n"/>
+      <c r="G191" s="187" t="n"/>
+      <c r="H191" s="187" t="n"/>
+      <c r="I191" s="187" t="n"/>
+      <c r="J191" s="187" t="n"/>
+      <c r="L191" s="192" t="n"/>
+      <c r="N191" s="193">
+        <f>IF(L191="",$B$4,L191)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="193" t="n"/>
+      <c r="G192" s="187" t="n"/>
+      <c r="H192" s="187" t="n"/>
+      <c r="I192" s="187" t="n"/>
+      <c r="J192" s="187" t="n"/>
+      <c r="L192" s="192" t="n"/>
+      <c r="N192" s="193">
+        <f>IF(L192="",$B$4,L192)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="193" t="n"/>
+      <c r="G193" s="187" t="n"/>
+      <c r="H193" s="187" t="n"/>
+      <c r="I193" s="187" t="n"/>
+      <c r="J193" s="187" t="n"/>
+      <c r="L193" s="192" t="n"/>
+      <c r="N193" s="193">
+        <f>IF(L193="",$B$4,L193)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="193" t="n"/>
+      <c r="G194" s="187" t="n"/>
+      <c r="H194" s="187" t="n"/>
+      <c r="I194" s="187" t="n"/>
+      <c r="J194" s="187" t="n"/>
+      <c r="L194" s="192" t="n"/>
+      <c r="N194" s="193">
+        <f>IF(L194="",$B$4,L194)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="193" t="n"/>
+      <c r="G195" s="187" t="n"/>
+      <c r="H195" s="187" t="n"/>
+      <c r="I195" s="187" t="n"/>
+      <c r="J195" s="187" t="n"/>
+      <c r="L195" s="192" t="n"/>
+      <c r="N195" s="193">
+        <f>IF(L195="",$B$4,L195)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="193" t="n"/>
+      <c r="G196" s="187" t="n"/>
+      <c r="H196" s="187" t="n"/>
+      <c r="I196" s="187" t="n"/>
+      <c r="J196" s="187" t="n"/>
+      <c r="L196" s="192" t="n"/>
+      <c r="N196" s="193">
+        <f>IF(L196="",$B$4,L196)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="193" t="n"/>
+      <c r="G197" s="187" t="n"/>
+      <c r="H197" s="187" t="n"/>
+      <c r="I197" s="187" t="n"/>
+      <c r="J197" s="187" t="n"/>
+      <c r="L197" s="192" t="n"/>
+      <c r="N197" s="193">
+        <f>IF(L197="",$B$4,L197)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="193" t="n"/>
+      <c r="G198" s="187" t="n"/>
+      <c r="H198" s="187" t="n"/>
+      <c r="I198" s="187" t="n"/>
+      <c r="J198" s="187" t="n"/>
+      <c r="L198" s="192" t="n"/>
+      <c r="N198" s="193">
+        <f>IF(L198="",$B$4,L198)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="193" t="n"/>
+      <c r="G199" s="187" t="n"/>
+      <c r="H199" s="187" t="n"/>
+      <c r="I199" s="187" t="n"/>
+      <c r="J199" s="187" t="n"/>
+      <c r="L199" s="192" t="n"/>
+      <c r="N199" s="193">
+        <f>IF(L199="",$B$4,L199)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="193" t="n"/>
+      <c r="G200" s="187" t="n"/>
+      <c r="H200" s="187" t="n"/>
+      <c r="I200" s="187" t="n"/>
+      <c r="J200" s="187" t="n"/>
+      <c r="L200" s="192" t="n"/>
+      <c r="N200" s="193">
+        <f>IF(L200="",$B$4,L200)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="193" t="n"/>
+      <c r="G201" s="187" t="n"/>
+      <c r="H201" s="187" t="n"/>
+      <c r="I201" s="187" t="n"/>
+      <c r="J201" s="187" t="n"/>
+      <c r="L201" s="192" t="n"/>
+      <c r="N201" s="193">
+        <f>IF(L201="",$B$4,L201)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="193" t="n"/>
+      <c r="G202" s="187" t="n"/>
+      <c r="H202" s="187" t="n"/>
+      <c r="I202" s="187" t="n"/>
+      <c r="J202" s="187" t="n"/>
+      <c r="L202" s="192" t="n"/>
+      <c r="N202" s="193">
+        <f>IF(L202="",$B$4,L202)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="193" t="n"/>
+      <c r="G203" s="187" t="n"/>
+      <c r="H203" s="187" t="n"/>
+      <c r="I203" s="187" t="n"/>
+      <c r="J203" s="187" t="n"/>
+      <c r="L203" s="192" t="n"/>
+      <c r="N203" s="193">
+        <f>IF(L203="",$B$4,L203)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="193" t="n"/>
+      <c r="G204" s="187" t="n"/>
+      <c r="H204" s="187" t="n"/>
+      <c r="I204" s="187" t="n"/>
+      <c r="J204" s="187" t="n"/>
+      <c r="L204" s="192" t="n"/>
+      <c r="N204" s="193">
+        <f>IF(L204="",$B$4,L204)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="193" t="n"/>
+      <c r="G205" s="187" t="n"/>
+      <c r="H205" s="187" t="n"/>
+      <c r="I205" s="187" t="n"/>
+      <c r="J205" s="187" t="n"/>
+      <c r="L205" s="192" t="n"/>
+      <c r="N205" s="193">
+        <f>IF(L205="",$B$4,L205)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="193" t="n"/>
+      <c r="G206" s="187" t="n"/>
+      <c r="H206" s="187" t="n"/>
+      <c r="I206" s="187" t="n"/>
+      <c r="J206" s="187" t="n"/>
+      <c r="L206" s="192" t="n"/>
+      <c r="N206" s="193">
+        <f>IF(L206="",$B$4,L206)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="193" t="n"/>
+      <c r="G207" s="187" t="n"/>
+      <c r="H207" s="187" t="n"/>
+      <c r="I207" s="187" t="n"/>
+      <c r="J207" s="187" t="n"/>
+      <c r="L207" s="192" t="n"/>
+      <c r="N207" s="193">
+        <f>IF(L207="",$B$4,L207)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="193" t="n"/>
+      <c r="G208" s="187" t="n"/>
+      <c r="H208" s="187" t="n"/>
+      <c r="I208" s="187" t="n"/>
+      <c r="J208" s="187" t="n"/>
+      <c r="L208" s="192" t="n"/>
+      <c r="N208" s="193">
+        <f>IF(L208="",$B$4,L208)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="193" t="n"/>
+      <c r="G209" s="187" t="n"/>
+      <c r="H209" s="187" t="n"/>
+      <c r="I209" s="187" t="n"/>
+      <c r="J209" s="187" t="n"/>
+      <c r="L209" s="192" t="n"/>
+      <c r="N209" s="193">
+        <f>IF(L209="",$B$4,L209)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="193" t="n"/>
+      <c r="G210" s="187" t="n"/>
+      <c r="H210" s="187" t="n"/>
+      <c r="I210" s="187" t="n"/>
+      <c r="J210" s="187" t="n"/>
+      <c r="L210" s="192" t="n"/>
+      <c r="N210" s="193">
+        <f>IF(L210="",$B$4,L210)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="193" t="n"/>
+      <c r="G211" s="187" t="n"/>
+      <c r="H211" s="187" t="n"/>
+      <c r="I211" s="187" t="n"/>
+      <c r="J211" s="187" t="n"/>
+      <c r="L211" s="192" t="n"/>
+      <c r="N211" s="193">
+        <f>IF(L211="",$B$4,L211)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="193" t="n"/>
+      <c r="G212" s="187" t="n"/>
+      <c r="H212" s="187" t="n"/>
+      <c r="I212" s="187" t="n"/>
+      <c r="J212" s="187" t="n"/>
+      <c r="L212" s="192" t="n"/>
+      <c r="N212" s="193">
+        <f>IF(L212="",$B$4,L212)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="193" t="n"/>
+      <c r="G213" s="187" t="n"/>
+      <c r="H213" s="187" t="n"/>
+      <c r="I213" s="187" t="n"/>
+      <c r="J213" s="187" t="n"/>
+      <c r="L213" s="192" t="n"/>
+      <c r="N213" s="193">
+        <f>IF(L213="",$B$4,L213)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="193" t="n"/>
+      <c r="G214" s="187" t="n"/>
+      <c r="H214" s="187" t="n"/>
+      <c r="I214" s="187" t="n"/>
+      <c r="J214" s="187" t="n"/>
+      <c r="L214" s="192" t="n"/>
+      <c r="N214" s="193">
+        <f>IF(L214="",$B$4,L214)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="193" t="n"/>
+      <c r="G215" s="187" t="n"/>
+      <c r="H215" s="187" t="n"/>
+      <c r="I215" s="187" t="n"/>
+      <c r="J215" s="187" t="n"/>
+      <c r="L215" s="192" t="n"/>
+      <c r="N215" s="193">
+        <f>IF(L215="",$B$4,L215)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="193" t="n"/>
+      <c r="G216" s="187" t="n"/>
+      <c r="H216" s="187" t="n"/>
+      <c r="I216" s="187" t="n"/>
+      <c r="J216" s="187" t="n"/>
+      <c r="L216" s="192" t="n"/>
+      <c r="N216" s="193">
+        <f>IF(L216="",$B$4,L216)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="193" t="n"/>
+      <c r="G217" s="187" t="n"/>
+      <c r="H217" s="187" t="n"/>
+      <c r="I217" s="187" t="n"/>
+      <c r="J217" s="187" t="n"/>
+      <c r="L217" s="192" t="n"/>
+      <c r="N217" s="193">
+        <f>IF(L217="",$B$4,L217)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="193" t="n"/>
+      <c r="G218" s="187" t="n"/>
+      <c r="H218" s="187" t="n"/>
+      <c r="I218" s="187" t="n"/>
+      <c r="J218" s="187" t="n"/>
+      <c r="L218" s="192" t="n"/>
+      <c r="N218" s="193">
+        <f>IF(L218="",$B$4,L218)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="193" t="n"/>
+      <c r="G219" s="187" t="n"/>
+      <c r="H219" s="187" t="n"/>
+      <c r="I219" s="187" t="n"/>
+      <c r="J219" s="187" t="n"/>
+      <c r="L219" s="192" t="n"/>
+      <c r="N219" s="193">
+        <f>IF(L219="",$B$4,L219)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="193" t="n"/>
+      <c r="G220" s="187" t="n"/>
+      <c r="H220" s="187" t="n"/>
+      <c r="I220" s="187" t="n"/>
+      <c r="J220" s="187" t="n"/>
+      <c r="L220" s="192" t="n"/>
+      <c r="N220" s="193">
+        <f>IF(L220="",$B$4,L220)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="193" t="n"/>
+      <c r="G221" s="187" t="n"/>
+      <c r="H221" s="187" t="n"/>
+      <c r="I221" s="187" t="n"/>
+      <c r="J221" s="187" t="n"/>
+      <c r="L221" s="192" t="n"/>
+      <c r="N221" s="193">
+        <f>IF(L221="",$B$4,L221)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="193" t="n"/>
+      <c r="G222" s="187" t="n"/>
+      <c r="H222" s="187" t="n"/>
+      <c r="I222" s="187" t="n"/>
+      <c r="J222" s="187" t="n"/>
+      <c r="L222" s="192" t="n"/>
+      <c r="N222" s="193">
+        <f>IF(L222="",$B$4,L222)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="193" t="n"/>
+      <c r="G223" s="187" t="n"/>
+      <c r="H223" s="187" t="n"/>
+      <c r="I223" s="187" t="n"/>
+      <c r="J223" s="187" t="n"/>
+      <c r="L223" s="192" t="n"/>
+      <c r="N223" s="193">
+        <f>IF(L223="",$B$4,L223)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="193" t="n"/>
+      <c r="G224" s="187" t="n"/>
+      <c r="H224" s="187" t="n"/>
+      <c r="I224" s="187" t="n"/>
+      <c r="J224" s="187" t="n"/>
+      <c r="L224" s="192" t="n"/>
+      <c r="N224" s="193">
+        <f>IF(L224="",$B$4,L224)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="193" t="n"/>
+      <c r="G225" s="187" t="n"/>
+      <c r="H225" s="187" t="n"/>
+      <c r="I225" s="187" t="n"/>
+      <c r="J225" s="187" t="n"/>
+      <c r="L225" s="192" t="n"/>
+      <c r="N225" s="193">
+        <f>IF(L225="",$B$4,L225)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="193" t="n"/>
+      <c r="G226" s="187" t="n"/>
+      <c r="H226" s="187" t="n"/>
+      <c r="I226" s="187" t="n"/>
+      <c r="J226" s="187" t="n"/>
+      <c r="L226" s="192" t="n"/>
+      <c r="N226" s="193">
+        <f>IF(L226="",$B$4,L226)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="193" t="n"/>
+      <c r="G227" s="187" t="n"/>
+      <c r="H227" s="187" t="n"/>
+      <c r="I227" s="187" t="n"/>
+      <c r="J227" s="187" t="n"/>
+      <c r="L227" s="192" t="n"/>
+      <c r="N227" s="193">
+        <f>IF(L227="",$B$4,L227)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="193" t="n"/>
+      <c r="G228" s="187" t="n"/>
+      <c r="H228" s="187" t="n"/>
+      <c r="I228" s="187" t="n"/>
+      <c r="J228" s="187" t="n"/>
+      <c r="L228" s="192" t="n"/>
+      <c r="N228" s="193">
+        <f>IF(L228="",$B$4,L228)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="193" t="n"/>
+      <c r="G229" s="187" t="n"/>
+      <c r="H229" s="187" t="n"/>
+      <c r="I229" s="187" t="n"/>
+      <c r="J229" s="187" t="n"/>
+      <c r="L229" s="192" t="n"/>
+      <c r="N229" s="193">
+        <f>IF(L229="",$B$4,L229)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="193" t="n"/>
+      <c r="G230" s="187" t="n"/>
+      <c r="H230" s="187" t="n"/>
+      <c r="I230" s="187" t="n"/>
+      <c r="J230" s="187" t="n"/>
+      <c r="L230" s="192" t="n"/>
+      <c r="N230" s="193">
+        <f>IF(L230="",$B$4,L230)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="193" t="n"/>
+      <c r="G231" s="187" t="n"/>
+      <c r="H231" s="187" t="n"/>
+      <c r="I231" s="187" t="n"/>
+      <c r="J231" s="187" t="n"/>
+      <c r="L231" s="192" t="n"/>
+      <c r="N231" s="193">
+        <f>IF(L231="",$B$4,L231)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="193" t="n"/>
+      <c r="G232" s="187" t="n"/>
+      <c r="H232" s="187" t="n"/>
+      <c r="I232" s="187" t="n"/>
+      <c r="J232" s="187" t="n"/>
+      <c r="L232" s="192" t="n"/>
+      <c r="N232" s="193">
+        <f>IF(L232="",$B$4,L232)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="193" t="n"/>
+      <c r="G233" s="187" t="n"/>
+      <c r="H233" s="187" t="n"/>
+      <c r="I233" s="187" t="n"/>
+      <c r="J233" s="187" t="n"/>
+      <c r="L233" s="192" t="n"/>
+      <c r="N233" s="193">
+        <f>IF(L233="",$B$4,L233)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="193" t="n"/>
+      <c r="G234" s="187" t="n"/>
+      <c r="H234" s="187" t="n"/>
+      <c r="I234" s="187" t="n"/>
+      <c r="J234" s="187" t="n"/>
+      <c r="L234" s="192" t="n"/>
+      <c r="N234" s="193">
+        <f>IF(L234="",$B$4,L234)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="193" t="n"/>
+      <c r="G235" s="187" t="n"/>
+      <c r="H235" s="187" t="n"/>
+      <c r="I235" s="187" t="n"/>
+      <c r="J235" s="187" t="n"/>
+      <c r="L235" s="192" t="n"/>
+      <c r="N235" s="193">
+        <f>IF(L235="",$B$4,L235)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="193" t="n"/>
+      <c r="G236" s="187" t="n"/>
+      <c r="H236" s="187" t="n"/>
+      <c r="I236" s="187" t="n"/>
+      <c r="J236" s="187" t="n"/>
+      <c r="L236" s="192" t="n"/>
+      <c r="N236" s="193">
+        <f>IF(L236="",$B$4,L236)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="193" t="n"/>
+      <c r="G237" s="187" t="n"/>
+      <c r="H237" s="187" t="n"/>
+      <c r="I237" s="187" t="n"/>
+      <c r="J237" s="187" t="n"/>
+      <c r="L237" s="192" t="n"/>
+      <c r="N237" s="193">
+        <f>IF(L237="",$B$4,L237)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="193" t="n"/>
+      <c r="G238" s="187" t="n"/>
+      <c r="H238" s="187" t="n"/>
+      <c r="I238" s="187" t="n"/>
+      <c r="J238" s="187" t="n"/>
+      <c r="L238" s="192" t="n"/>
+      <c r="N238" s="193">
+        <f>IF(L238="",$B$4,L238)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="193" t="n"/>
+      <c r="G239" s="187" t="n"/>
+      <c r="H239" s="187" t="n"/>
+      <c r="I239" s="187" t="n"/>
+      <c r="J239" s="187" t="n"/>
+      <c r="L239" s="192" t="n"/>
+      <c r="N239" s="193">
+        <f>IF(L239="",$B$4,L239)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="193" t="n"/>
+      <c r="G240" s="187" t="n"/>
+      <c r="H240" s="187" t="n"/>
+      <c r="I240" s="187" t="n"/>
+      <c r="J240" s="187" t="n"/>
+      <c r="L240" s="192" t="n"/>
+      <c r="N240" s="193">
+        <f>IF(L240="",$B$4,L240)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="193" t="n"/>
+      <c r="G241" s="187" t="n"/>
+      <c r="H241" s="187" t="n"/>
+      <c r="I241" s="187" t="n"/>
+      <c r="J241" s="187" t="n"/>
+      <c r="L241" s="192" t="n"/>
+      <c r="N241" s="193">
+        <f>IF(L241="",$B$4,L241)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="193" t="n"/>
+      <c r="G242" s="187" t="n"/>
+      <c r="H242" s="187" t="n"/>
+      <c r="I242" s="187" t="n"/>
+      <c r="J242" s="187" t="n"/>
+      <c r="L242" s="192" t="n"/>
+      <c r="N242" s="193">
+        <f>IF(L242="",$B$4,L242)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="193" t="n"/>
+      <c r="G243" s="187" t="n"/>
+      <c r="H243" s="187" t="n"/>
+      <c r="I243" s="187" t="n"/>
+      <c r="J243" s="187" t="n"/>
+      <c r="L243" s="192" t="n"/>
+      <c r="N243" s="193">
+        <f>IF(L243="",$B$4,L243)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="193" t="n"/>
+      <c r="G244" s="187" t="n"/>
+      <c r="H244" s="187" t="n"/>
+      <c r="I244" s="187" t="n"/>
+      <c r="J244" s="187" t="n"/>
+      <c r="L244" s="192" t="n"/>
+      <c r="N244" s="193">
+        <f>IF(L244="",$B$4,L244)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="193" t="n"/>
+      <c r="G245" s="187" t="n"/>
+      <c r="H245" s="187" t="n"/>
+      <c r="I245" s="187" t="n"/>
+      <c r="J245" s="187" t="n"/>
+      <c r="L245" s="192" t="n"/>
+      <c r="N245" s="193">
+        <f>IF(L245="",$B$4,L245)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="193" t="n"/>
+      <c r="G246" s="187" t="n"/>
+      <c r="H246" s="187" t="n"/>
+      <c r="I246" s="187" t="n"/>
+      <c r="J246" s="187" t="n"/>
+      <c r="L246" s="192" t="n"/>
+      <c r="N246" s="193">
+        <f>IF(L246="",$B$4,L246)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="193" t="n"/>
+      <c r="G247" s="187" t="n"/>
+      <c r="H247" s="187" t="n"/>
+      <c r="I247" s="187" t="n"/>
+      <c r="J247" s="187" t="n"/>
+      <c r="L247" s="192" t="n"/>
+      <c r="N247" s="193">
+        <f>IF(L247="",$B$4,L247)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="193" t="n"/>
+      <c r="G248" s="187" t="n"/>
+      <c r="H248" s="187" t="n"/>
+      <c r="I248" s="187" t="n"/>
+      <c r="J248" s="187" t="n"/>
+      <c r="L248" s="192" t="n"/>
+      <c r="N248" s="193">
+        <f>IF(L248="",$B$4,L248)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="193" t="n"/>
+      <c r="G249" s="187" t="n"/>
+      <c r="H249" s="187" t="n"/>
+      <c r="I249" s="187" t="n"/>
+      <c r="J249" s="187" t="n"/>
+      <c r="L249" s="192" t="n"/>
+      <c r="N249" s="193">
+        <f>IF(L249="",$B$4,L249)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="193" t="n"/>
+      <c r="G250" s="187" t="n"/>
+      <c r="H250" s="187" t="n"/>
+      <c r="I250" s="187" t="n"/>
+      <c r="J250" s="187" t="n"/>
+      <c r="L250" s="192" t="n"/>
+      <c r="N250" s="193">
+        <f>IF(L250="",$B$4,L250)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="193" t="n"/>
+      <c r="G251" s="187" t="n"/>
+      <c r="H251" s="187" t="n"/>
+      <c r="I251" s="187" t="n"/>
+      <c r="J251" s="187" t="n"/>
+      <c r="L251" s="192" t="n"/>
+      <c r="N251" s="193">
+        <f>IF(L251="",$B$4,L251)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="193" t="n"/>
+      <c r="G252" s="187" t="n"/>
+      <c r="H252" s="187" t="n"/>
+      <c r="I252" s="187" t="n"/>
+      <c r="J252" s="187" t="n"/>
+      <c r="L252" s="192" t="n"/>
+      <c r="N252" s="193">
+        <f>IF(L252="",$B$4,L252)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="193" t="n"/>
+      <c r="G253" s="187" t="n"/>
+      <c r="H253" s="187" t="n"/>
+      <c r="I253" s="187" t="n"/>
+      <c r="J253" s="187" t="n"/>
+      <c r="L253" s="192" t="n"/>
+      <c r="N253" s="193">
+        <f>IF(L253="",$B$4,L253)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="193" t="n"/>
+      <c r="G254" s="187" t="n"/>
+      <c r="H254" s="187" t="n"/>
+      <c r="I254" s="187" t="n"/>
+      <c r="J254" s="187" t="n"/>
+      <c r="L254" s="192" t="n"/>
+      <c r="N254" s="193">
+        <f>IF(L254="",$B$4,L254)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="193" t="n"/>
+      <c r="G255" s="187" t="n"/>
+      <c r="H255" s="187" t="n"/>
+      <c r="I255" s="187" t="n"/>
+      <c r="J255" s="187" t="n"/>
+      <c r="L255" s="192" t="n"/>
+      <c r="N255" s="193">
+        <f>IF(L255="",$B$4,L255)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="193" t="n"/>
+      <c r="G256" s="187" t="n"/>
+      <c r="H256" s="187" t="n"/>
+      <c r="I256" s="187" t="n"/>
+      <c r="J256" s="187" t="n"/>
+      <c r="L256" s="192" t="n"/>
+      <c r="N256" s="193">
+        <f>IF(L256="",$B$4,L256)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="193" t="n"/>
+      <c r="G257" s="187" t="n"/>
+      <c r="H257" s="187" t="n"/>
+      <c r="I257" s="187" t="n"/>
+      <c r="J257" s="187" t="n"/>
+      <c r="L257" s="192" t="n"/>
+      <c r="N257" s="193">
+        <f>IF(L257="",$B$4,L257)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="193" t="n"/>
+      <c r="G258" s="187" t="n"/>
+      <c r="H258" s="187" t="n"/>
+      <c r="I258" s="187" t="n"/>
+      <c r="J258" s="187" t="n"/>
+      <c r="L258" s="192" t="n"/>
+      <c r="N258" s="193">
+        <f>IF(L258="",$B$4,L258)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="193" t="n"/>
+      <c r="G259" s="187" t="n"/>
+      <c r="H259" s="187" t="n"/>
+      <c r="I259" s="187" t="n"/>
+      <c r="J259" s="187" t="n"/>
+      <c r="L259" s="192" t="n"/>
+      <c r="N259" s="193">
+        <f>IF(L259="",$B$4,L259)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="193" t="n"/>
+      <c r="G260" s="187" t="n"/>
+      <c r="H260" s="187" t="n"/>
+      <c r="I260" s="187" t="n"/>
+      <c r="J260" s="187" t="n"/>
+      <c r="L260" s="192" t="n"/>
+      <c r="N260" s="193">
+        <f>IF(L260="",$B$4,L260)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="193" t="n"/>
+      <c r="G261" s="187" t="n"/>
+      <c r="H261" s="187" t="n"/>
+      <c r="I261" s="187" t="n"/>
+      <c r="J261" s="187" t="n"/>
+      <c r="L261" s="192" t="n"/>
+      <c r="N261" s="193">
+        <f>IF(L261="",$B$4,L261)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="193" t="n"/>
+      <c r="G262" s="187" t="n"/>
+      <c r="H262" s="187" t="n"/>
+      <c r="I262" s="187" t="n"/>
+      <c r="J262" s="187" t="n"/>
+      <c r="L262" s="192" t="n"/>
+      <c r="N262" s="193">
+        <f>IF(L262="",$B$4,L262)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="193" t="n"/>
+      <c r="G263" s="187" t="n"/>
+      <c r="H263" s="187" t="n"/>
+      <c r="I263" s="187" t="n"/>
+      <c r="J263" s="187" t="n"/>
+      <c r="L263" s="192" t="n"/>
+      <c r="N263" s="193">
+        <f>IF(L263="",$B$4,L263)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="193" t="n"/>
+      <c r="G264" s="187" t="n"/>
+      <c r="H264" s="187" t="n"/>
+      <c r="I264" s="187" t="n"/>
+      <c r="J264" s="187" t="n"/>
+      <c r="L264" s="192" t="n"/>
+      <c r="N264" s="193">
+        <f>IF(L264="",$B$4,L264)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="193" t="n"/>
+      <c r="G265" s="187" t="n"/>
+      <c r="H265" s="187" t="n"/>
+      <c r="I265" s="187" t="n"/>
+      <c r="J265" s="187" t="n"/>
+      <c r="L265" s="192" t="n"/>
+      <c r="N265" s="193">
+        <f>IF(L265="",$B$4,L265)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="193" t="n"/>
+      <c r="G266" s="187" t="n"/>
+      <c r="H266" s="187" t="n"/>
+      <c r="I266" s="187" t="n"/>
+      <c r="J266" s="187" t="n"/>
+      <c r="L266" s="192" t="n"/>
+      <c r="N266" s="193">
+        <f>IF(L266="",$B$4,L266)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="193" t="n"/>
+      <c r="G267" s="187" t="n"/>
+      <c r="H267" s="187" t="n"/>
+      <c r="I267" s="187" t="n"/>
+      <c r="J267" s="187" t="n"/>
+      <c r="L267" s="192" t="n"/>
+      <c r="N267" s="193">
+        <f>IF(L267="",$B$4,L267)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="193" t="n"/>
+      <c r="G268" s="187" t="n"/>
+      <c r="H268" s="187" t="n"/>
+      <c r="I268" s="187" t="n"/>
+      <c r="J268" s="187" t="n"/>
+      <c r="L268" s="192" t="n"/>
+      <c r="N268" s="193">
+        <f>IF(L268="",$B$4,L268)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="193" t="n"/>
+      <c r="G269" s="187" t="n"/>
+      <c r="H269" s="187" t="n"/>
+      <c r="I269" s="187" t="n"/>
+      <c r="J269" s="187" t="n"/>
+      <c r="L269" s="192" t="n"/>
+      <c r="N269" s="193">
+        <f>IF(L269="",$B$4,L269)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="193" t="n"/>
+      <c r="G270" s="187" t="n"/>
+      <c r="H270" s="187" t="n"/>
+      <c r="I270" s="187" t="n"/>
+      <c r="J270" s="187" t="n"/>
+      <c r="L270" s="192" t="n"/>
+      <c r="N270" s="193">
+        <f>IF(L270="",$B$4,L270)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="193" t="n"/>
+      <c r="G271" s="187" t="n"/>
+      <c r="H271" s="187" t="n"/>
+      <c r="I271" s="187" t="n"/>
+      <c r="J271" s="187" t="n"/>
+      <c r="L271" s="192" t="n"/>
+      <c r="N271" s="193">
+        <f>IF(L271="",$B$4,L271)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="193" t="n"/>
+      <c r="G272" s="187" t="n"/>
+      <c r="H272" s="187" t="n"/>
+      <c r="I272" s="187" t="n"/>
+      <c r="J272" s="187" t="n"/>
+      <c r="L272" s="192" t="n"/>
+      <c r="N272" s="193">
+        <f>IF(L272="",$B$4,L272)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="193" t="n"/>
+      <c r="G273" s="187" t="n"/>
+      <c r="H273" s="187" t="n"/>
+      <c r="I273" s="187" t="n"/>
+      <c r="J273" s="187" t="n"/>
+      <c r="L273" s="192" t="n"/>
+      <c r="N273" s="193">
+        <f>IF(L273="",$B$4,L273)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="193" t="n"/>
+      <c r="G274" s="187" t="n"/>
+      <c r="H274" s="187" t="n"/>
+      <c r="I274" s="187" t="n"/>
+      <c r="J274" s="187" t="n"/>
+      <c r="L274" s="192" t="n"/>
+      <c r="N274" s="193">
+        <f>IF(L274="",$B$4,L274)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="193" t="n"/>
+      <c r="G275" s="187" t="n"/>
+      <c r="H275" s="187" t="n"/>
+      <c r="I275" s="187" t="n"/>
+      <c r="J275" s="187" t="n"/>
+      <c r="L275" s="192" t="n"/>
+      <c r="N275" s="193">
+        <f>IF(L275="",$B$4,L275)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="193" t="n"/>
+      <c r="G276" s="187" t="n"/>
+      <c r="H276" s="187" t="n"/>
+      <c r="I276" s="187" t="n"/>
+      <c r="J276" s="187" t="n"/>
+      <c r="L276" s="192" t="n"/>
+      <c r="N276" s="193">
+        <f>IF(L276="",$B$4,L276)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="193" t="n"/>
+      <c r="G277" s="187" t="n"/>
+      <c r="H277" s="187" t="n"/>
+      <c r="I277" s="187" t="n"/>
+      <c r="J277" s="187" t="n"/>
+      <c r="L277" s="192" t="n"/>
+      <c r="N277" s="193">
+        <f>IF(L277="",$B$4,L277)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="193" t="n"/>
+      <c r="G278" s="187" t="n"/>
+      <c r="H278" s="187" t="n"/>
+      <c r="I278" s="187" t="n"/>
+      <c r="J278" s="187" t="n"/>
+      <c r="L278" s="192" t="n"/>
+      <c r="N278" s="193">
+        <f>IF(L278="",$B$4,L278)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="193" t="n"/>
+      <c r="G279" s="187" t="n"/>
+      <c r="H279" s="187" t="n"/>
+      <c r="I279" s="187" t="n"/>
+      <c r="J279" s="187" t="n"/>
+      <c r="L279" s="192" t="n"/>
+      <c r="N279" s="193">
+        <f>IF(L279="",$B$4,L279)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="193" t="n"/>
+      <c r="G280" s="187" t="n"/>
+      <c r="H280" s="187" t="n"/>
+      <c r="I280" s="187" t="n"/>
+      <c r="J280" s="187" t="n"/>
+      <c r="L280" s="192" t="n"/>
+      <c r="N280" s="193">
+        <f>IF(L280="",$B$4,L280)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="193" t="n"/>
+      <c r="G281" s="187" t="n"/>
+      <c r="H281" s="187" t="n"/>
+      <c r="I281" s="187" t="n"/>
+      <c r="J281" s="187" t="n"/>
+      <c r="L281" s="192" t="n"/>
+      <c r="N281" s="193">
+        <f>IF(L281="",$B$4,L281)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="193" t="n"/>
+      <c r="G282" s="187" t="n"/>
+      <c r="H282" s="187" t="n"/>
+      <c r="I282" s="187" t="n"/>
+      <c r="J282" s="187" t="n"/>
+      <c r="L282" s="192" t="n"/>
+      <c r="N282" s="193">
+        <f>IF(L282="",$B$4,L282)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="193" t="n"/>
+      <c r="G283" s="187" t="n"/>
+      <c r="H283" s="187" t="n"/>
+      <c r="I283" s="187" t="n"/>
+      <c r="J283" s="187" t="n"/>
+      <c r="L283" s="192" t="n"/>
+      <c r="N283" s="193">
+        <f>IF(L283="",$B$4,L283)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="193" t="n"/>
+      <c r="G284" s="187" t="n"/>
+      <c r="H284" s="187" t="n"/>
+      <c r="I284" s="187" t="n"/>
+      <c r="J284" s="187" t="n"/>
+      <c r="L284" s="192" t="n"/>
+      <c r="N284" s="193">
+        <f>IF(L284="",$B$4,L284)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="193" t="n"/>
+      <c r="G285" s="187" t="n"/>
+      <c r="H285" s="187" t="n"/>
+      <c r="I285" s="187" t="n"/>
+      <c r="J285" s="187" t="n"/>
+      <c r="L285" s="192" t="n"/>
+      <c r="N285" s="193">
+        <f>IF(L285="",$B$4,L285)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="193" t="n"/>
+      <c r="G286" s="187" t="n"/>
+      <c r="H286" s="187" t="n"/>
+      <c r="I286" s="187" t="n"/>
+      <c r="J286" s="187" t="n"/>
+      <c r="L286" s="192" t="n"/>
+      <c r="N286" s="193">
+        <f>IF(L286="",$B$4,L286)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="193" t="n"/>
+      <c r="G287" s="187" t="n"/>
+      <c r="H287" s="187" t="n"/>
+      <c r="I287" s="187" t="n"/>
+      <c r="J287" s="187" t="n"/>
+      <c r="L287" s="192" t="n"/>
+      <c r="N287" s="193">
+        <f>IF(L287="",$B$4,L287)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="193" t="n"/>
+      <c r="G288" s="187" t="n"/>
+      <c r="H288" s="187" t="n"/>
+      <c r="I288" s="187" t="n"/>
+      <c r="J288" s="187" t="n"/>
+      <c r="L288" s="192" t="n"/>
+      <c r="N288" s="193">
+        <f>IF(L288="",$B$4,L288)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="193" t="n"/>
+      <c r="G289" s="187" t="n"/>
+      <c r="H289" s="187" t="n"/>
+      <c r="I289" s="187" t="n"/>
+      <c r="J289" s="187" t="n"/>
+      <c r="L289" s="192" t="n"/>
+      <c r="N289" s="193">
+        <f>IF(L289="",$B$4,L289)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="193" t="n"/>
+      <c r="G290" s="187" t="n"/>
+      <c r="H290" s="187" t="n"/>
+      <c r="I290" s="187" t="n"/>
+      <c r="J290" s="187" t="n"/>
+      <c r="L290" s="192" t="n"/>
+      <c r="N290" s="193">
+        <f>IF(L290="",$B$4,L290)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="193" t="n"/>
+      <c r="G291" s="187" t="n"/>
+      <c r="H291" s="187" t="n"/>
+      <c r="I291" s="187" t="n"/>
+      <c r="J291" s="187" t="n"/>
+      <c r="L291" s="192" t="n"/>
+      <c r="N291" s="193">
+        <f>IF(L291="",$B$4,L291)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="193" t="n"/>
+      <c r="G292" s="187" t="n"/>
+      <c r="H292" s="187" t="n"/>
+      <c r="I292" s="187" t="n"/>
+      <c r="J292" s="187" t="n"/>
+      <c r="L292" s="192" t="n"/>
+      <c r="N292" s="193">
+        <f>IF(L292="",$B$4,L292)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="193" t="n"/>
+      <c r="G293" s="187" t="n"/>
+      <c r="H293" s="187" t="n"/>
+      <c r="I293" s="187" t="n"/>
+      <c r="J293" s="187" t="n"/>
+      <c r="L293" s="192" t="n"/>
+      <c r="N293" s="193">
+        <f>IF(L293="",$B$4,L293)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="193" t="n"/>
+      <c r="G294" s="187" t="n"/>
+      <c r="H294" s="187" t="n"/>
+      <c r="I294" s="187" t="n"/>
+      <c r="J294" s="187" t="n"/>
+      <c r="L294" s="192" t="n"/>
+      <c r="N294" s="193">
+        <f>IF(L294="",$B$4,L294)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="193" t="n"/>
+      <c r="G295" s="187" t="n"/>
+      <c r="H295" s="187" t="n"/>
+      <c r="I295" s="187" t="n"/>
+      <c r="J295" s="187" t="n"/>
+      <c r="L295" s="192" t="n"/>
+      <c r="N295" s="193">
+        <f>IF(L295="",$B$4,L295)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="193" t="n"/>
+      <c r="G296" s="187" t="n"/>
+      <c r="H296" s="187" t="n"/>
+      <c r="I296" s="187" t="n"/>
+      <c r="J296" s="187" t="n"/>
+      <c r="L296" s="192" t="n"/>
+      <c r="N296" s="193">
+        <f>IF(L296="",$B$4,L296)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="193" t="n"/>
+      <c r="G297" s="187" t="n"/>
+      <c r="H297" s="187" t="n"/>
+      <c r="I297" s="187" t="n"/>
+      <c r="J297" s="187" t="n"/>
+      <c r="L297" s="192" t="n"/>
+      <c r="N297" s="193">
+        <f>IF(L297="",$B$4,L297)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="193" t="n"/>
+      <c r="G298" s="187" t="n"/>
+      <c r="H298" s="187" t="n"/>
+      <c r="I298" s="187" t="n"/>
+      <c r="J298" s="187" t="n"/>
+      <c r="L298" s="192" t="n"/>
+      <c r="N298" s="193">
+        <f>IF(L298="",$B$4,L298)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="193" t="n"/>
+      <c r="G299" s="187" t="n"/>
+      <c r="H299" s="187" t="n"/>
+      <c r="I299" s="187" t="n"/>
+      <c r="J299" s="187" t="n"/>
+      <c r="L299" s="192" t="n"/>
+      <c r="N299" s="193">
+        <f>IF(L299="",$B$4,L299)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="193" t="n"/>
+      <c r="G300" s="187" t="n"/>
+      <c r="H300" s="187" t="n"/>
+      <c r="I300" s="187" t="n"/>
+      <c r="J300" s="187" t="n"/>
+      <c r="L300" s="192" t="n"/>
+      <c r="N300" s="193">
+        <f>IF(L300="",$B$4,L300)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="193" t="n"/>
+      <c r="G301" s="187" t="n"/>
+      <c r="H301" s="187" t="n"/>
+      <c r="I301" s="187" t="n"/>
+      <c r="J301" s="187" t="n"/>
+      <c r="L301" s="192" t="n"/>
+      <c r="N301" s="193">
+        <f>IF(L301="",$B$4,L301)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="193" t="n"/>
+      <c r="G302" s="187" t="n"/>
+      <c r="H302" s="187" t="n"/>
+      <c r="I302" s="187" t="n"/>
+      <c r="J302" s="187" t="n"/>
+      <c r="L302" s="192" t="n"/>
+      <c r="N302" s="193">
+        <f>IF(L302="",$B$4,L302)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="193" t="n"/>
+      <c r="G303" s="187" t="n"/>
+      <c r="H303" s="187" t="n"/>
+      <c r="I303" s="187" t="n"/>
+      <c r="J303" s="187" t="n"/>
+      <c r="L303" s="192" t="n"/>
+      <c r="N303" s="193">
+        <f>IF(L303="",$B$4,L303)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="193" t="n"/>
+      <c r="G304" s="187" t="n"/>
+      <c r="H304" s="187" t="n"/>
+      <c r="I304" s="187" t="n"/>
+      <c r="J304" s="187" t="n"/>
+      <c r="L304" s="192" t="n"/>
+      <c r="N304" s="193">
+        <f>IF(L304="",$B$4,L304)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="193" t="n"/>
+      <c r="G305" s="187" t="n"/>
+      <c r="H305" s="187" t="n"/>
+      <c r="I305" s="187" t="n"/>
+      <c r="J305" s="187" t="n"/>
+      <c r="L305" s="192" t="n"/>
+      <c r="N305" s="193">
+        <f>IF(L305="",$B$4,L305)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="193" t="n"/>
+      <c r="G306" s="187" t="n"/>
+      <c r="H306" s="187" t="n"/>
+      <c r="I306" s="187" t="n"/>
+      <c r="J306" s="187" t="n"/>
+      <c r="L306" s="192" t="n"/>
+      <c r="N306" s="193">
+        <f>IF(L306="",$B$4,L306)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="193" t="n"/>
+      <c r="G307" s="187" t="n"/>
+      <c r="H307" s="187" t="n"/>
+      <c r="I307" s="187" t="n"/>
+      <c r="J307" s="187" t="n"/>
+      <c r="L307" s="192" t="n"/>
+      <c r="N307" s="193">
+        <f>IF(L307="",$B$4,L307)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="193" t="n"/>
+      <c r="G308" s="187" t="n"/>
+      <c r="H308" s="187" t="n"/>
+      <c r="I308" s="187" t="n"/>
+      <c r="J308" s="187" t="n"/>
+      <c r="L308" s="192" t="n"/>
+      <c r="N308" s="193">
+        <f>IF(L308="",$B$4,L308)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="193" t="n"/>
+      <c r="G309" s="187" t="n"/>
+      <c r="H309" s="187" t="n"/>
+      <c r="I309" s="187" t="n"/>
+      <c r="J309" s="187" t="n"/>
+      <c r="L309" s="192" t="n"/>
+      <c r="N309" s="193">
+        <f>IF(L309="",$B$4,L309)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="193" t="n"/>
+      <c r="G310" s="187" t="n"/>
+      <c r="H310" s="187" t="n"/>
+      <c r="I310" s="187" t="n"/>
+      <c r="J310" s="187" t="n"/>
+      <c r="L310" s="192" t="n"/>
+      <c r="N310" s="193">
+        <f>IF(L310="",$B$4,L310)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="193" t="n"/>
+      <c r="G311" s="187" t="n"/>
+      <c r="H311" s="187" t="n"/>
+      <c r="I311" s="187" t="n"/>
+      <c r="J311" s="187" t="n"/>
+      <c r="L311" s="192" t="n"/>
+      <c r="N311" s="193">
+        <f>IF(L311="",$B$4,L311)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="193" t="n"/>
+      <c r="G312" s="187" t="n"/>
+      <c r="H312" s="187" t="n"/>
+      <c r="I312" s="187" t="n"/>
+      <c r="J312" s="187" t="n"/>
+      <c r="L312" s="192" t="n"/>
+      <c r="N312" s="193">
+        <f>IF(L312="",$B$4,L312)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="193" t="n"/>
+      <c r="G313" s="187" t="n"/>
+      <c r="H313" s="187" t="n"/>
+      <c r="I313" s="187" t="n"/>
+      <c r="J313" s="187" t="n"/>
+      <c r="L313" s="192" t="n"/>
+      <c r="N313" s="193">
+        <f>IF(L313="",$B$4,L313)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="193" t="n"/>
+      <c r="G314" s="187" t="n"/>
+      <c r="H314" s="187" t="n"/>
+      <c r="I314" s="187" t="n"/>
+      <c r="J314" s="187" t="n"/>
+      <c r="L314" s="192" t="n"/>
+      <c r="N314" s="193">
+        <f>IF(L314="",$B$4,L314)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="193" t="n"/>
+      <c r="G315" s="187" t="n"/>
+      <c r="H315" s="187" t="n"/>
+      <c r="I315" s="187" t="n"/>
+      <c r="J315" s="187" t="n"/>
+      <c r="L315" s="192" t="n"/>
+      <c r="N315" s="193">
+        <f>IF(L315="",$B$4,L315)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="193" t="n"/>
+      <c r="G316" s="187" t="n"/>
+      <c r="H316" s="187" t="n"/>
+      <c r="I316" s="187" t="n"/>
+      <c r="J316" s="187" t="n"/>
+      <c r="L316" s="192" t="n"/>
+      <c r="N316" s="193">
+        <f>IF(L316="",$B$4,L316)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="193" t="n"/>
+      <c r="G317" s="187" t="n"/>
+      <c r="H317" s="187" t="n"/>
+      <c r="I317" s="187" t="n"/>
+      <c r="J317" s="187" t="n"/>
+      <c r="L317" s="192" t="n"/>
+      <c r="N317" s="193">
+        <f>IF(L317="",$B$4,L317)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="193" t="n"/>
+      <c r="G318" s="187" t="n"/>
+      <c r="H318" s="187" t="n"/>
+      <c r="I318" s="187" t="n"/>
+      <c r="J318" s="187" t="n"/>
+      <c r="L318" s="192" t="n"/>
+      <c r="N318" s="193">
+        <f>IF(L318="",$B$4,L318)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="193" t="n"/>
+      <c r="G319" s="187" t="n"/>
+      <c r="H319" s="187" t="n"/>
+      <c r="I319" s="187" t="n"/>
+      <c r="J319" s="187" t="n"/>
+      <c r="L319" s="192" t="n"/>
+      <c r="N319" s="193">
+        <f>IF(L319="",$B$4,L319)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="193" t="n"/>
+      <c r="G320" s="187" t="n"/>
+      <c r="H320" s="187" t="n"/>
+      <c r="I320" s="187" t="n"/>
+      <c r="J320" s="187" t="n"/>
+      <c r="L320" s="192" t="n"/>
+      <c r="N320" s="193">
+        <f>IF(L320="",$B$4,L320)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="193" t="n"/>
+      <c r="G321" s="187" t="n"/>
+      <c r="H321" s="187" t="n"/>
+      <c r="I321" s="187" t="n"/>
+      <c r="J321" s="187" t="n"/>
+      <c r="L321" s="192" t="n"/>
+      <c r="N321" s="193">
+        <f>IF(L321="",$B$4,L321)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="193" t="n"/>
+      <c r="G322" s="187" t="n"/>
+      <c r="H322" s="187" t="n"/>
+      <c r="I322" s="187" t="n"/>
+      <c r="J322" s="187" t="n"/>
+      <c r="L322" s="192" t="n"/>
+      <c r="N322" s="193">
+        <f>IF(L322="",$B$4,L322)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="193" t="n"/>
+      <c r="G323" s="187" t="n"/>
+      <c r="H323" s="187" t="n"/>
+      <c r="I323" s="187" t="n"/>
+      <c r="J323" s="187" t="n"/>
+      <c r="L323" s="192" t="n"/>
+      <c r="N323" s="193">
+        <f>IF(L323="",$B$4,L323)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="193" t="n"/>
+      <c r="G324" s="187" t="n"/>
+      <c r="H324" s="187" t="n"/>
+      <c r="I324" s="187" t="n"/>
+      <c r="J324" s="187" t="n"/>
+      <c r="L324" s="192" t="n"/>
+      <c r="N324" s="193">
+        <f>IF(L324="",$B$4,L324)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="193" t="n"/>
+      <c r="G325" s="187" t="n"/>
+      <c r="H325" s="187" t="n"/>
+      <c r="I325" s="187" t="n"/>
+      <c r="J325" s="187" t="n"/>
+      <c r="L325" s="192" t="n"/>
+      <c r="N325" s="193">
+        <f>IF(L325="",$B$4,L325)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="193" t="n"/>
+      <c r="G326" s="187" t="n"/>
+      <c r="H326" s="187" t="n"/>
+      <c r="I326" s="187" t="n"/>
+      <c r="J326" s="187" t="n"/>
+      <c r="L326" s="192" t="n"/>
+      <c r="N326" s="193">
+        <f>IF(L326="",$B$4,L326)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="193" t="n"/>
+      <c r="G327" s="187" t="n"/>
+      <c r="H327" s="187" t="n"/>
+      <c r="I327" s="187" t="n"/>
+      <c r="J327" s="187" t="n"/>
+      <c r="L327" s="192" t="n"/>
+      <c r="N327" s="193">
+        <f>IF(L327="",$B$4,L327)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="193" t="n"/>
+      <c r="G328" s="187" t="n"/>
+      <c r="H328" s="187" t="n"/>
+      <c r="I328" s="187" t="n"/>
+      <c r="J328" s="187" t="n"/>
+      <c r="L328" s="192" t="n"/>
+      <c r="N328" s="193">
+        <f>IF(L328="",$B$4,L328)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="193" t="n"/>
+      <c r="G329" s="187" t="n"/>
+      <c r="H329" s="187" t="n"/>
+      <c r="I329" s="187" t="n"/>
+      <c r="J329" s="187" t="n"/>
+      <c r="L329" s="192" t="n"/>
+      <c r="N329" s="193">
+        <f>IF(L329="",$B$4,L329)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="193" t="n"/>
+      <c r="G330" s="187" t="n"/>
+      <c r="H330" s="187" t="n"/>
+      <c r="I330" s="187" t="n"/>
+      <c r="J330" s="187" t="n"/>
+      <c r="L330" s="192" t="n"/>
+      <c r="N330" s="193">
+        <f>IF(L330="",$B$4,L330)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="193" t="n"/>
+      <c r="G331" s="187" t="n"/>
+      <c r="H331" s="187" t="n"/>
+      <c r="I331" s="187" t="n"/>
+      <c r="J331" s="187" t="n"/>
+      <c r="L331" s="192" t="n"/>
+      <c r="N331" s="193">
+        <f>IF(L331="",$B$4,L331)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="193" t="n"/>
+      <c r="G332" s="187" t="n"/>
+      <c r="H332" s="187" t="n"/>
+      <c r="I332" s="187" t="n"/>
+      <c r="J332" s="187" t="n"/>
+      <c r="L332" s="192" t="n"/>
+      <c r="N332" s="193">
+        <f>IF(L332="",$B$4,L332)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="193" t="n"/>
+      <c r="G333" s="187" t="n"/>
+      <c r="H333" s="187" t="n"/>
+      <c r="I333" s="187" t="n"/>
+      <c r="J333" s="187" t="n"/>
+      <c r="L333" s="192" t="n"/>
+      <c r="N333" s="193">
+        <f>IF(L333="",$B$4,L333)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="193" t="n"/>
+      <c r="G334" s="187" t="n"/>
+      <c r="H334" s="187" t="n"/>
+      <c r="I334" s="187" t="n"/>
+      <c r="J334" s="187" t="n"/>
+      <c r="L334" s="192" t="n"/>
+      <c r="N334" s="193">
+        <f>IF(L334="",$B$4,L334)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="193" t="n"/>
+      <c r="G335" s="187" t="n"/>
+      <c r="H335" s="187" t="n"/>
+      <c r="I335" s="187" t="n"/>
+      <c r="J335" s="187" t="n"/>
+      <c r="L335" s="192" t="n"/>
+      <c r="N335" s="193">
+        <f>IF(L335="",$B$4,L335)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="193" t="n"/>
+      <c r="G336" s="187" t="n"/>
+      <c r="H336" s="187" t="n"/>
+      <c r="I336" s="187" t="n"/>
+      <c r="J336" s="187" t="n"/>
+      <c r="L336" s="192" t="n"/>
+      <c r="N336" s="193">
+        <f>IF(L336="",$B$4,L336)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="193" t="n"/>
+      <c r="G337" s="187" t="n"/>
+      <c r="H337" s="187" t="n"/>
+      <c r="I337" s="187" t="n"/>
+      <c r="J337" s="187" t="n"/>
+      <c r="L337" s="192" t="n"/>
+      <c r="N337" s="193">
+        <f>IF(L337="",$B$4,L337)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="193" t="n"/>
+      <c r="G338" s="187" t="n"/>
+      <c r="H338" s="187" t="n"/>
+      <c r="I338" s="187" t="n"/>
+      <c r="J338" s="187" t="n"/>
+      <c r="L338" s="192" t="n"/>
+      <c r="N338" s="193">
+        <f>IF(L338="",$B$4,L338)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="193" t="n"/>
+      <c r="G339" s="187" t="n"/>
+      <c r="H339" s="187" t="n"/>
+      <c r="I339" s="187" t="n"/>
+      <c r="J339" s="187" t="n"/>
+      <c r="L339" s="192" t="n"/>
+      <c r="N339" s="193">
+        <f>IF(L339="",$B$4,L339)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="193" t="n"/>
+      <c r="G340" s="187" t="n"/>
+      <c r="H340" s="187" t="n"/>
+      <c r="I340" s="187" t="n"/>
+      <c r="J340" s="187" t="n"/>
+      <c r="L340" s="192" t="n"/>
+      <c r="N340" s="193">
+        <f>IF(L340="",$B$4,L340)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="193" t="n"/>
+      <c r="G341" s="187" t="n"/>
+      <c r="H341" s="187" t="n"/>
+      <c r="I341" s="187" t="n"/>
+      <c r="J341" s="187" t="n"/>
+      <c r="L341" s="192" t="n"/>
+      <c r="N341" s="193">
+        <f>IF(L341="",$B$4,L341)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="193" t="n"/>
+      <c r="G342" s="187" t="n"/>
+      <c r="H342" s="187" t="n"/>
+      <c r="I342" s="187" t="n"/>
+      <c r="J342" s="187" t="n"/>
+      <c r="L342" s="192" t="n"/>
+      <c r="N342" s="193">
+        <f>IF(L342="",$B$4,L342)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="193" t="n"/>
+      <c r="G343" s="187" t="n"/>
+      <c r="H343" s="187" t="n"/>
+      <c r="I343" s="187" t="n"/>
+      <c r="J343" s="187" t="n"/>
+      <c r="L343" s="192" t="n"/>
+      <c r="N343" s="193">
+        <f>IF(L343="",$B$4,L343)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="193" t="n"/>
+      <c r="G344" s="187" t="n"/>
+      <c r="H344" s="187" t="n"/>
+      <c r="I344" s="187" t="n"/>
+      <c r="J344" s="187" t="n"/>
+      <c r="L344" s="192" t="n"/>
+      <c r="N344" s="193">
+        <f>IF(L344="",$B$4,L344)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="193" t="n"/>
+      <c r="G345" s="187" t="n"/>
+      <c r="H345" s="187" t="n"/>
+      <c r="I345" s="187" t="n"/>
+      <c r="J345" s="187" t="n"/>
+      <c r="L345" s="192" t="n"/>
+      <c r="N345" s="193">
+        <f>IF(L345="",$B$4,L345)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="193" t="n"/>
+      <c r="G346" s="187" t="n"/>
+      <c r="H346" s="187" t="n"/>
+      <c r="I346" s="187" t="n"/>
+      <c r="J346" s="187" t="n"/>
+      <c r="L346" s="192" t="n"/>
+      <c r="N346" s="193">
+        <f>IF(L346="",$B$4,L346)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="193" t="n"/>
+      <c r="G347" s="187" t="n"/>
+      <c r="H347" s="187" t="n"/>
+      <c r="I347" s="187" t="n"/>
+      <c r="J347" s="187" t="n"/>
+      <c r="L347" s="192" t="n"/>
+      <c r="N347" s="193">
+        <f>IF(L347="",$B$4,L347)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="193" t="n"/>
+      <c r="G348" s="187" t="n"/>
+      <c r="H348" s="187" t="n"/>
+      <c r="I348" s="187" t="n"/>
+      <c r="J348" s="187" t="n"/>
+      <c r="L348" s="192" t="n"/>
+      <c r="N348" s="193">
+        <f>IF(L348="",$B$4,L348)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="193" t="n"/>
+      <c r="G349" s="187" t="n"/>
+      <c r="H349" s="187" t="n"/>
+      <c r="I349" s="187" t="n"/>
+      <c r="J349" s="187" t="n"/>
+      <c r="L349" s="192" t="n"/>
+      <c r="N349" s="193">
+        <f>IF(L349="",$B$4,L349)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="193" t="n"/>
+      <c r="G350" s="187" t="n"/>
+      <c r="H350" s="187" t="n"/>
+      <c r="I350" s="187" t="n"/>
+      <c r="J350" s="187" t="n"/>
+      <c r="L350" s="192" t="n"/>
+      <c r="N350" s="193">
+        <f>IF(L350="",$B$4,L350)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="193" t="n"/>
+      <c r="G351" s="187" t="n"/>
+      <c r="H351" s="187" t="n"/>
+      <c r="I351" s="187" t="n"/>
+      <c r="J351" s="187" t="n"/>
+      <c r="L351" s="192" t="n"/>
+      <c r="N351" s="193">
+        <f>IF(L351="",$B$4,L351)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="193" t="n"/>
+      <c r="G352" s="187" t="n"/>
+      <c r="H352" s="187" t="n"/>
+      <c r="I352" s="187" t="n"/>
+      <c r="J352" s="187" t="n"/>
+      <c r="L352" s="192" t="n"/>
+      <c r="N352" s="193">
+        <f>IF(L352="",$B$4,L352)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="193" t="n"/>
+      <c r="G353" s="187" t="n"/>
+      <c r="H353" s="187" t="n"/>
+      <c r="I353" s="187" t="n"/>
+      <c r="J353" s="187" t="n"/>
+      <c r="L353" s="192" t="n"/>
+      <c r="N353" s="193">
+        <f>IF(L353="",$B$4,L353)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="193" t="n"/>
+      <c r="G354" s="187" t="n"/>
+      <c r="H354" s="187" t="n"/>
+      <c r="I354" s="187" t="n"/>
+      <c r="J354" s="187" t="n"/>
+      <c r="L354" s="192" t="n"/>
+      <c r="N354" s="193">
+        <f>IF(L354="",$B$4,L354)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="193" t="n"/>
+      <c r="G355" s="187" t="n"/>
+      <c r="H355" s="187" t="n"/>
+      <c r="I355" s="187" t="n"/>
+      <c r="J355" s="187" t="n"/>
+      <c r="L355" s="192" t="n"/>
+      <c r="N355" s="193">
+        <f>IF(L355="",$B$4,L355)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="193" t="n"/>
+      <c r="G356" s="187" t="n"/>
+      <c r="H356" s="187" t="n"/>
+      <c r="I356" s="187" t="n"/>
+      <c r="J356" s="187" t="n"/>
+      <c r="L356" s="192" t="n"/>
+      <c r="N356" s="193">
+        <f>IF(L356="",$B$4,L356)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="193" t="n"/>
+      <c r="G357" s="187" t="n"/>
+      <c r="H357" s="187" t="n"/>
+      <c r="I357" s="187" t="n"/>
+      <c r="J357" s="187" t="n"/>
+      <c r="L357" s="192" t="n"/>
+      <c r="N357" s="193">
+        <f>IF(L357="",$B$4,L357)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="193" t="n"/>
+      <c r="G358" s="187" t="n"/>
+      <c r="H358" s="187" t="n"/>
+      <c r="I358" s="187" t="n"/>
+      <c r="J358" s="187" t="n"/>
+      <c r="L358" s="192" t="n"/>
+      <c r="N358" s="193">
+        <f>IF(L358="",$B$4,L358)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="193" t="n"/>
+      <c r="G359" s="187" t="n"/>
+      <c r="H359" s="187" t="n"/>
+      <c r="I359" s="187" t="n"/>
+      <c r="J359" s="187" t="n"/>
+      <c r="L359" s="192" t="n"/>
+      <c r="N359" s="193">
+        <f>IF(L359="",$B$4,L359)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="193" t="n"/>
+      <c r="G360" s="187" t="n"/>
+      <c r="H360" s="187" t="n"/>
+      <c r="I360" s="187" t="n"/>
+      <c r="J360" s="187" t="n"/>
+      <c r="L360" s="192" t="n"/>
+      <c r="N360" s="193">
+        <f>IF(L360="",$B$4,L360)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="193" t="n"/>
+      <c r="G361" s="187" t="n"/>
+      <c r="H361" s="187" t="n"/>
+      <c r="I361" s="187" t="n"/>
+      <c r="J361" s="187" t="n"/>
+      <c r="L361" s="192" t="n"/>
+      <c r="N361" s="193">
+        <f>IF(L361="",$B$4,L361)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="193" t="n"/>
+      <c r="G362" s="187" t="n"/>
+      <c r="H362" s="187" t="n"/>
+      <c r="I362" s="187" t="n"/>
+      <c r="J362" s="187" t="n"/>
+      <c r="L362" s="192" t="n"/>
+      <c r="N362" s="193">
+        <f>IF(L362="",$B$4,L362)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="193" t="n"/>
+      <c r="G363" s="187" t="n"/>
+      <c r="H363" s="187" t="n"/>
+      <c r="I363" s="187" t="n"/>
+      <c r="J363" s="187" t="n"/>
+      <c r="L363" s="192" t="n"/>
+      <c r="N363" s="193">
+        <f>IF(L363="",$B$4,L363)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="193" t="n"/>
+      <c r="G364" s="187" t="n"/>
+      <c r="H364" s="187" t="n"/>
+      <c r="I364" s="187" t="n"/>
+      <c r="J364" s="187" t="n"/>
+      <c r="L364" s="192" t="n"/>
+      <c r="N364" s="193">
+        <f>IF(L364="",$B$4,L364)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="193" t="n"/>
+      <c r="G365" s="187" t="n"/>
+      <c r="H365" s="187" t="n"/>
+      <c r="I365" s="187" t="n"/>
+      <c r="J365" s="187" t="n"/>
+      <c r="L365" s="192" t="n"/>
+      <c r="N365" s="193">
+        <f>IF(L365="",$B$4,L365)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="193" t="n"/>
+      <c r="G366" s="187" t="n"/>
+      <c r="H366" s="187" t="n"/>
+      <c r="I366" s="187" t="n"/>
+      <c r="J366" s="187" t="n"/>
+      <c r="L366" s="192" t="n"/>
+      <c r="N366" s="193">
+        <f>IF(L366="",$B$4,L366)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="193" t="n"/>
+      <c r="G367" s="187" t="n"/>
+      <c r="H367" s="187" t="n"/>
+      <c r="I367" s="187" t="n"/>
+      <c r="J367" s="187" t="n"/>
+      <c r="L367" s="192" t="n"/>
+      <c r="N367" s="193">
+        <f>IF(L367="",$B$4,L367)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="193" t="n"/>
+      <c r="G368" s="187" t="n"/>
+      <c r="H368" s="187" t="n"/>
+      <c r="I368" s="187" t="n"/>
+      <c r="J368" s="187" t="n"/>
+      <c r="L368" s="192" t="n"/>
+      <c r="N368" s="193">
+        <f>IF(L368="",$B$4,L368)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="193" t="n"/>
+      <c r="G369" s="187" t="n"/>
+      <c r="H369" s="187" t="n"/>
+      <c r="I369" s="187" t="n"/>
+      <c r="J369" s="187" t="n"/>
+      <c r="L369" s="192" t="n"/>
+      <c r="N369" s="193">
+        <f>IF(L369="",$B$4,L369)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="193" t="n"/>
+      <c r="G370" s="187" t="n"/>
+      <c r="H370" s="187" t="n"/>
+      <c r="I370" s="187" t="n"/>
+      <c r="J370" s="187" t="n"/>
+      <c r="L370" s="192" t="n"/>
+      <c r="N370" s="193">
+        <f>IF(L370="",$B$4,L370)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="193" t="n"/>
+      <c r="G371" s="187" t="n"/>
+      <c r="H371" s="187" t="n"/>
+      <c r="I371" s="187" t="n"/>
+      <c r="J371" s="187" t="n"/>
+      <c r="L371" s="192" t="n"/>
+      <c r="N371" s="193">
+        <f>IF(L371="",$B$4,L371)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="193" t="n"/>
+      <c r="G372" s="187" t="n"/>
+      <c r="H372" s="187" t="n"/>
+      <c r="I372" s="187" t="n"/>
+      <c r="J372" s="187" t="n"/>
+      <c r="L372" s="192" t="n"/>
+      <c r="N372" s="193">
+        <f>IF(L372="",$B$4,L372)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="193" t="n"/>
+      <c r="G373" s="187" t="n"/>
+      <c r="H373" s="187" t="n"/>
+      <c r="I373" s="187" t="n"/>
+      <c r="J373" s="187" t="n"/>
+      <c r="L373" s="192" t="n"/>
+      <c r="N373" s="193">
+        <f>IF(L373="",$B$4,L373)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="193" t="n"/>
+      <c r="G374" s="187" t="n"/>
+      <c r="H374" s="187" t="n"/>
+      <c r="I374" s="187" t="n"/>
+      <c r="J374" s="187" t="n"/>
+      <c r="L374" s="192" t="n"/>
+      <c r="N374" s="193">
+        <f>IF(L374="",$B$4,L374)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="193" t="n"/>
+      <c r="G375" s="187" t="n"/>
+      <c r="H375" s="187" t="n"/>
+      <c r="I375" s="187" t="n"/>
+      <c r="J375" s="187" t="n"/>
+      <c r="L375" s="192" t="n"/>
+      <c r="N375" s="193">
+        <f>IF(L375="",$B$4,L375)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="193" t="n"/>
+      <c r="G376" s="187" t="n"/>
+      <c r="H376" s="187" t="n"/>
+      <c r="I376" s="187" t="n"/>
+      <c r="J376" s="187" t="n"/>
+      <c r="L376" s="192" t="n"/>
+      <c r="N376" s="193">
+        <f>IF(L376="",$B$4,L376)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="193" t="n"/>
+      <c r="G377" s="187" t="n"/>
+      <c r="H377" s="187" t="n"/>
+      <c r="I377" s="187" t="n"/>
+      <c r="J377" s="187" t="n"/>
+      <c r="L377" s="192" t="n"/>
+      <c r="N377" s="193">
+        <f>IF(L377="",$B$4,L377)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="193" t="n"/>
+      <c r="G378" s="187" t="n"/>
+      <c r="H378" s="187" t="n"/>
+      <c r="I378" s="187" t="n"/>
+      <c r="J378" s="187" t="n"/>
+      <c r="L378" s="192" t="n"/>
+      <c r="N378" s="193">
+        <f>IF(L378="",$B$4,L378)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="193" t="n"/>
+      <c r="G379" s="187" t="n"/>
+      <c r="H379" s="187" t="n"/>
+      <c r="I379" s="187" t="n"/>
+      <c r="J379" s="187" t="n"/>
+      <c r="L379" s="192" t="n"/>
+      <c r="N379" s="193">
+        <f>IF(L379="",$B$4,L379)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="193" t="n"/>
+      <c r="G380" s="187" t="n"/>
+      <c r="H380" s="187" t="n"/>
+      <c r="I380" s="187" t="n"/>
+      <c r="J380" s="187" t="n"/>
+      <c r="L380" s="192" t="n"/>
+      <c r="N380" s="193">
+        <f>IF(L380="",$B$4,L380)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="193" t="n"/>
+      <c r="G381" s="187" t="n"/>
+      <c r="H381" s="187" t="n"/>
+      <c r="I381" s="187" t="n"/>
+      <c r="J381" s="187" t="n"/>
+      <c r="L381" s="192" t="n"/>
+      <c r="N381" s="193">
+        <f>IF(L381="",$B$4,L381)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="193" t="n"/>
+      <c r="G382" s="187" t="n"/>
+      <c r="H382" s="187" t="n"/>
+      <c r="I382" s="187" t="n"/>
+      <c r="J382" s="187" t="n"/>
+      <c r="L382" s="192" t="n"/>
+      <c r="N382" s="193">
+        <f>IF(L382="",$B$4,L382)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="193" t="n"/>
+      <c r="G383" s="187" t="n"/>
+      <c r="H383" s="187" t="n"/>
+      <c r="I383" s="187" t="n"/>
+      <c r="J383" s="187" t="n"/>
+      <c r="L383" s="192" t="n"/>
+      <c r="N383" s="193">
+        <f>IF(L383="",$B$4,L383)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="193" t="n"/>
+      <c r="G384" s="187" t="n"/>
+      <c r="H384" s="187" t="n"/>
+      <c r="I384" s="187" t="n"/>
+      <c r="J384" s="187" t="n"/>
+      <c r="L384" s="192" t="n"/>
+      <c r="N384" s="193">
+        <f>IF(L384="",$B$4,L384)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="193" t="n"/>
+      <c r="G385" s="187" t="n"/>
+      <c r="H385" s="187" t="n"/>
+      <c r="I385" s="187" t="n"/>
+      <c r="J385" s="187" t="n"/>
+      <c r="L385" s="192" t="n"/>
+      <c r="N385" s="193">
+        <f>IF(L385="",$B$4,L385)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="193" t="n"/>
+      <c r="G386" s="187" t="n"/>
+      <c r="H386" s="187" t="n"/>
+      <c r="I386" s="187" t="n"/>
+      <c r="J386" s="187" t="n"/>
+      <c r="L386" s="192" t="n"/>
+      <c r="N386" s="193">
+        <f>IF(L386="",$B$4,L386)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="193" t="n"/>
+      <c r="G387" s="187" t="n"/>
+      <c r="H387" s="187" t="n"/>
+      <c r="I387" s="187" t="n"/>
+      <c r="J387" s="187" t="n"/>
+      <c r="L387" s="192" t="n"/>
+      <c r="N387" s="193">
+        <f>IF(L387="",$B$4,L387)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" s="193" t="n"/>
+      <c r="G388" s="187" t="n"/>
+      <c r="H388" s="187" t="n"/>
+      <c r="I388" s="187" t="n"/>
+      <c r="J388" s="187" t="n"/>
+      <c r="L388" s="192" t="n"/>
+      <c r="N388" s="193">
+        <f>IF(L388="",$B$4,L388)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" s="193" t="n"/>
+      <c r="G389" s="187" t="n"/>
+      <c r="H389" s="187" t="n"/>
+      <c r="I389" s="187" t="n"/>
+      <c r="J389" s="187" t="n"/>
+      <c r="L389" s="192" t="n"/>
+      <c r="N389" s="193">
+        <f>IF(L389="",$B$4,L389)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" s="193" t="n"/>
+      <c r="G390" s="187" t="n"/>
+      <c r="H390" s="187" t="n"/>
+      <c r="I390" s="187" t="n"/>
+      <c r="J390" s="187" t="n"/>
+      <c r="L390" s="192" t="n"/>
+      <c r="N390" s="193">
+        <f>IF(L390="",$B$4,L390)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="193" t="n"/>
+      <c r="G391" s="187" t="n"/>
+      <c r="H391" s="187" t="n"/>
+      <c r="I391" s="187" t="n"/>
+      <c r="J391" s="187" t="n"/>
+      <c r="L391" s="192" t="n"/>
+      <c r="N391" s="193">
+        <f>IF(L391="",$B$4,L391)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="193" t="n"/>
+      <c r="G392" s="187" t="n"/>
+      <c r="H392" s="187" t="n"/>
+      <c r="I392" s="187" t="n"/>
+      <c r="J392" s="187" t="n"/>
+      <c r="L392" s="192" t="n"/>
+      <c r="N392" s="193">
+        <f>IF(L392="",$B$4,L392)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="193" t="n"/>
+      <c r="G393" s="187" t="n"/>
+      <c r="H393" s="187" t="n"/>
+      <c r="I393" s="187" t="n"/>
+      <c r="J393" s="187" t="n"/>
+      <c r="L393" s="192" t="n"/>
+      <c r="N393" s="193">
+        <f>IF(L393="",$B$4,L393)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="193" t="n"/>
+      <c r="G394" s="187" t="n"/>
+      <c r="H394" s="187" t="n"/>
+      <c r="I394" s="187" t="n"/>
+      <c r="J394" s="187" t="n"/>
+      <c r="L394" s="192" t="n"/>
+      <c r="N394" s="193">
+        <f>IF(L394="",$B$4,L394)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="193" t="n"/>
+      <c r="G395" s="187" t="n"/>
+      <c r="H395" s="187" t="n"/>
+      <c r="I395" s="187" t="n"/>
+      <c r="J395" s="187" t="n"/>
+      <c r="L395" s="192" t="n"/>
+      <c r="N395" s="193">
+        <f>IF(L395="",$B$4,L395)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="193" t="n"/>
+      <c r="G396" s="187" t="n"/>
+      <c r="H396" s="187" t="n"/>
+      <c r="I396" s="187" t="n"/>
+      <c r="J396" s="187" t="n"/>
+      <c r="L396" s="192" t="n"/>
+      <c r="N396" s="193">
+        <f>IF(L396="",$B$4,L396)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="193" t="n"/>
+      <c r="G397" s="187" t="n"/>
+      <c r="H397" s="187" t="n"/>
+      <c r="I397" s="187" t="n"/>
+      <c r="J397" s="187" t="n"/>
+      <c r="L397" s="192" t="n"/>
+      <c r="N397" s="193">
+        <f>IF(L397="",$B$4,L397)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="193" t="n"/>
+      <c r="G398" s="187" t="n"/>
+      <c r="H398" s="187" t="n"/>
+      <c r="I398" s="187" t="n"/>
+      <c r="J398" s="187" t="n"/>
+      <c r="L398" s="192" t="n"/>
+      <c r="N398" s="193">
+        <f>IF(L398="",$B$4,L398)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="193" t="n"/>
+      <c r="G399" s="187" t="n"/>
+      <c r="H399" s="187" t="n"/>
+      <c r="I399" s="187" t="n"/>
+      <c r="J399" s="187" t="n"/>
+      <c r="L399" s="192" t="n"/>
+      <c r="N399" s="193">
+        <f>IF(L399="",$B$4,L399)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" s="193" t="n"/>
+      <c r="G400" s="187" t="n"/>
+      <c r="H400" s="187" t="n"/>
+      <c r="I400" s="187" t="n"/>
+      <c r="J400" s="187" t="n"/>
+      <c r="L400" s="192" t="n"/>
+      <c r="N400" s="193">
+        <f>IF(L400="",$B$4,L400)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="193" t="n"/>
+      <c r="G401" s="187" t="n"/>
+      <c r="H401" s="187" t="n"/>
+      <c r="I401" s="187" t="n"/>
+      <c r="J401" s="187" t="n"/>
+      <c r="L401" s="192" t="n"/>
+      <c r="N401" s="193">
+        <f>IF(L401="",$B$4,L401)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" s="193" t="n"/>
+      <c r="G402" s="187" t="n"/>
+      <c r="H402" s="187" t="n"/>
+      <c r="I402" s="187" t="n"/>
+      <c r="J402" s="187" t="n"/>
+      <c r="L402" s="192" t="n"/>
+      <c r="N402" s="193">
+        <f>IF(L402="",$B$4,L402)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="193" t="n"/>
+      <c r="G403" s="187" t="n"/>
+      <c r="H403" s="187" t="n"/>
+      <c r="I403" s="187" t="n"/>
+      <c r="J403" s="187" t="n"/>
+      <c r="L403" s="192" t="n"/>
+      <c r="N403" s="193">
+        <f>IF(L403="",$B$4,L403)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="193" t="n"/>
+      <c r="G404" s="187" t="n"/>
+      <c r="H404" s="187" t="n"/>
+      <c r="I404" s="187" t="n"/>
+      <c r="J404" s="187" t="n"/>
+      <c r="L404" s="192" t="n"/>
+      <c r="N404" s="193">
+        <f>IF(L404="",$B$4,L404)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="193" t="n"/>
+      <c r="G405" s="187" t="n"/>
+      <c r="H405" s="187" t="n"/>
+      <c r="I405" s="187" t="n"/>
+      <c r="J405" s="187" t="n"/>
+      <c r="L405" s="192" t="n"/>
+      <c r="N405" s="193">
+        <f>IF(L405="",$B$4,L405)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="193" t="n"/>
+      <c r="G406" s="187" t="n"/>
+      <c r="H406" s="187" t="n"/>
+      <c r="I406" s="187" t="n"/>
+      <c r="J406" s="187" t="n"/>
+      <c r="L406" s="192" t="n"/>
+      <c r="N406" s="193">
+        <f>IF(L406="",$B$4,L406)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="193" t="n"/>
+      <c r="G407" s="187" t="n"/>
+      <c r="H407" s="187" t="n"/>
+      <c r="I407" s="187" t="n"/>
+      <c r="J407" s="187" t="n"/>
+      <c r="L407" s="192" t="n"/>
+      <c r="N407" s="193">
+        <f>IF(L407="",$B$4,L407)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" s="193" t="n"/>
+      <c r="G408" s="187" t="n"/>
+      <c r="H408" s="187" t="n"/>
+      <c r="I408" s="187" t="n"/>
+      <c r="J408" s="187" t="n"/>
+      <c r="L408" s="192" t="n"/>
+      <c r="N408" s="193">
+        <f>IF(L408="",$B$4,L408)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="193" t="n"/>
+      <c r="G409" s="187" t="n"/>
+      <c r="H409" s="187" t="n"/>
+      <c r="I409" s="187" t="n"/>
+      <c r="J409" s="187" t="n"/>
+      <c r="L409" s="192" t="n"/>
+      <c r="N409" s="193">
+        <f>IF(L409="",$B$4,L409)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="193" t="n"/>
+      <c r="G410" s="187" t="n"/>
+      <c r="H410" s="187" t="n"/>
+      <c r="I410" s="187" t="n"/>
+      <c r="J410" s="187" t="n"/>
+      <c r="L410" s="192" t="n"/>
+      <c r="N410" s="193">
+        <f>IF(L410="",$B$4,L410)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" s="193" t="n"/>
+      <c r="G411" s="187" t="n"/>
+      <c r="H411" s="187" t="n"/>
+      <c r="I411" s="187" t="n"/>
+      <c r="J411" s="187" t="n"/>
+      <c r="L411" s="192" t="n"/>
+      <c r="N411" s="193">
+        <f>IF(L411="",$B$4,L411)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" s="193" t="n"/>
+      <c r="G412" s="187" t="n"/>
+      <c r="H412" s="187" t="n"/>
+      <c r="I412" s="187" t="n"/>
+      <c r="J412" s="187" t="n"/>
+      <c r="L412" s="192" t="n"/>
+      <c r="N412" s="193">
+        <f>IF(L412="",$B$4,L412)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" s="193" t="n"/>
+      <c r="G413" s="187" t="n"/>
+      <c r="H413" s="187" t="n"/>
+      <c r="I413" s="187" t="n"/>
+      <c r="J413" s="187" t="n"/>
+      <c r="L413" s="192" t="n"/>
+      <c r="N413" s="193">
+        <f>IF(L413="",$B$4,L413)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="193" t="n"/>
+      <c r="G414" s="187" t="n"/>
+      <c r="H414" s="187" t="n"/>
+      <c r="I414" s="187" t="n"/>
+      <c r="J414" s="187" t="n"/>
+      <c r="L414" s="192" t="n"/>
+      <c r="N414" s="193">
+        <f>IF(L414="",$B$4,L414)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" s="193" t="n"/>
+      <c r="G415" s="187" t="n"/>
+      <c r="H415" s="187" t="n"/>
+      <c r="I415" s="187" t="n"/>
+      <c r="J415" s="187" t="n"/>
+      <c r="L415" s="192" t="n"/>
+      <c r="N415" s="193">
+        <f>IF(L415="",$B$4,L415)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="193" t="n"/>
+      <c r="G416" s="187" t="n"/>
+      <c r="H416" s="187" t="n"/>
+      <c r="I416" s="187" t="n"/>
+      <c r="J416" s="187" t="n"/>
+      <c r="L416" s="192" t="n"/>
+      <c r="N416" s="193">
+        <f>IF(L416="",$B$4,L416)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="193" t="n"/>
+      <c r="G417" s="187" t="n"/>
+      <c r="H417" s="187" t="n"/>
+      <c r="I417" s="187" t="n"/>
+      <c r="J417" s="187" t="n"/>
+      <c r="L417" s="192" t="n"/>
+      <c r="N417" s="193">
+        <f>IF(L417="",$B$4,L417)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="193" t="n"/>
+      <c r="G418" s="187" t="n"/>
+      <c r="H418" s="187" t="n"/>
+      <c r="I418" s="187" t="n"/>
+      <c r="J418" s="187" t="n"/>
+      <c r="L418" s="192" t="n"/>
+      <c r="N418" s="193">
+        <f>IF(L418="",$B$4,L418)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="193" t="n"/>
+      <c r="G419" s="187" t="n"/>
+      <c r="H419" s="187" t="n"/>
+      <c r="I419" s="187" t="n"/>
+      <c r="J419" s="187" t="n"/>
+      <c r="L419" s="192" t="n"/>
+      <c r="N419" s="193">
+        <f>IF(L419="",$B$4,L419)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="193" t="n"/>
+      <c r="G420" s="187" t="n"/>
+      <c r="H420" s="187" t="n"/>
+      <c r="I420" s="187" t="n"/>
+      <c r="J420" s="187" t="n"/>
+      <c r="L420" s="192" t="n"/>
+      <c r="N420" s="193">
+        <f>IF(L420="",$B$4,L420)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" s="193" t="n"/>
+      <c r="G421" s="187" t="n"/>
+      <c r="H421" s="187" t="n"/>
+      <c r="I421" s="187" t="n"/>
+      <c r="J421" s="187" t="n"/>
+      <c r="L421" s="192" t="n"/>
+      <c r="N421" s="193">
+        <f>IF(L421="",$B$4,L421)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" s="193" t="n"/>
+      <c r="G422" s="187" t="n"/>
+      <c r="H422" s="187" t="n"/>
+      <c r="I422" s="187" t="n"/>
+      <c r="J422" s="187" t="n"/>
+      <c r="L422" s="192" t="n"/>
+      <c r="N422" s="193">
+        <f>IF(L422="",$B$4,L422)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" s="193" t="n"/>
+      <c r="G423" s="187" t="n"/>
+      <c r="H423" s="187" t="n"/>
+      <c r="I423" s="187" t="n"/>
+      <c r="J423" s="187" t="n"/>
+      <c r="L423" s="192" t="n"/>
+      <c r="N423" s="193">
+        <f>IF(L423="",$B$4,L423)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="193" t="n"/>
+      <c r="G424" s="187" t="n"/>
+      <c r="H424" s="187" t="n"/>
+      <c r="I424" s="187" t="n"/>
+      <c r="J424" s="187" t="n"/>
+      <c r="L424" s="192" t="n"/>
+      <c r="N424" s="193">
+        <f>IF(L424="",$B$4,L424)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="193" t="n"/>
+      <c r="G425" s="187" t="n"/>
+      <c r="H425" s="187" t="n"/>
+      <c r="I425" s="187" t="n"/>
+      <c r="J425" s="187" t="n"/>
+      <c r="L425" s="192" t="n"/>
+      <c r="N425" s="193">
+        <f>IF(L425="",$B$4,L425)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" s="193" t="n"/>
+      <c r="G426" s="187" t="n"/>
+      <c r="H426" s="187" t="n"/>
+      <c r="I426" s="187" t="n"/>
+      <c r="J426" s="187" t="n"/>
+      <c r="L426" s="192" t="n"/>
+      <c r="N426" s="193">
+        <f>IF(L426="",$B$4,L426)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="193" t="n"/>
+      <c r="G427" s="187" t="n"/>
+      <c r="H427" s="187" t="n"/>
+      <c r="I427" s="187" t="n"/>
+      <c r="J427" s="187" t="n"/>
+      <c r="L427" s="192" t="n"/>
+      <c r="N427" s="193">
+        <f>IF(L427="",$B$4,L427)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="193" t="n"/>
+      <c r="G428" s="187" t="n"/>
+      <c r="H428" s="187" t="n"/>
+      <c r="I428" s="187" t="n"/>
+      <c r="J428" s="187" t="n"/>
+      <c r="L428" s="192" t="n"/>
+      <c r="N428" s="193">
+        <f>IF(L428="",$B$4,L428)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="193" t="n"/>
+      <c r="G429" s="187" t="n"/>
+      <c r="H429" s="187" t="n"/>
+      <c r="I429" s="187" t="n"/>
+      <c r="J429" s="187" t="n"/>
+      <c r="L429" s="192" t="n"/>
+      <c r="N429" s="193">
+        <f>IF(L429="",$B$4,L429)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="193" t="n"/>
+      <c r="G430" s="187" t="n"/>
+      <c r="H430" s="187" t="n"/>
+      <c r="I430" s="187" t="n"/>
+      <c r="J430" s="187" t="n"/>
+      <c r="L430" s="192" t="n"/>
+      <c r="N430" s="193">
+        <f>IF(L430="",$B$4,L430)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" s="193" t="n"/>
+      <c r="G431" s="187" t="n"/>
+      <c r="H431" s="187" t="n"/>
+      <c r="I431" s="187" t="n"/>
+      <c r="J431" s="187" t="n"/>
+      <c r="L431" s="192" t="n"/>
+      <c r="N431" s="193">
+        <f>IF(L431="",$B$4,L431)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="193" t="n"/>
+      <c r="G432" s="187" t="n"/>
+      <c r="H432" s="187" t="n"/>
+      <c r="I432" s="187" t="n"/>
+      <c r="J432" s="187" t="n"/>
+      <c r="L432" s="192" t="n"/>
+      <c r="N432" s="193">
+        <f>IF(L432="",$B$4,L432)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" s="193" t="n"/>
+      <c r="G433" s="187" t="n"/>
+      <c r="H433" s="187" t="n"/>
+      <c r="I433" s="187" t="n"/>
+      <c r="J433" s="187" t="n"/>
+      <c r="L433" s="192" t="n"/>
+      <c r="N433" s="193">
+        <f>IF(L433="",$B$4,L433)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="193" t="n"/>
+      <c r="G434" s="187" t="n"/>
+      <c r="H434" s="187" t="n"/>
+      <c r="I434" s="187" t="n"/>
+      <c r="J434" s="187" t="n"/>
+      <c r="L434" s="192" t="n"/>
+      <c r="N434" s="193">
+        <f>IF(L434="",$B$4,L434)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="193" t="n"/>
+      <c r="G435" s="187" t="n"/>
+      <c r="H435" s="187" t="n"/>
+      <c r="I435" s="187" t="n"/>
+      <c r="J435" s="187" t="n"/>
+      <c r="L435" s="192" t="n"/>
+      <c r="N435" s="193">
+        <f>IF(L435="",$B$4,L435)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="193" t="n"/>
+      <c r="G436" s="187" t="n"/>
+      <c r="H436" s="187" t="n"/>
+      <c r="I436" s="187" t="n"/>
+      <c r="J436" s="187" t="n"/>
+      <c r="L436" s="192" t="n"/>
+      <c r="N436" s="193">
+        <f>IF(L436="",$B$4,L436)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="193" t="n"/>
+      <c r="G437" s="187" t="n"/>
+      <c r="H437" s="187" t="n"/>
+      <c r="I437" s="187" t="n"/>
+      <c r="J437" s="187" t="n"/>
+      <c r="L437" s="192" t="n"/>
+      <c r="N437" s="193">
+        <f>IF(L437="",$B$4,L437)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="193" t="n"/>
+      <c r="G438" s="187" t="n"/>
+      <c r="H438" s="187" t="n"/>
+      <c r="I438" s="187" t="n"/>
+      <c r="J438" s="187" t="n"/>
+      <c r="L438" s="192" t="n"/>
+      <c r="N438" s="193">
+        <f>IF(L438="",$B$4,L438)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="193" t="n"/>
+      <c r="G439" s="187" t="n"/>
+      <c r="H439" s="187" t="n"/>
+      <c r="I439" s="187" t="n"/>
+      <c r="J439" s="187" t="n"/>
+      <c r="L439" s="192" t="n"/>
+      <c r="N439" s="193">
+        <f>IF(L439="",$B$4,L439)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="193" t="n"/>
+      <c r="G440" s="187" t="n"/>
+      <c r="H440" s="187" t="n"/>
+      <c r="I440" s="187" t="n"/>
+      <c r="J440" s="187" t="n"/>
+      <c r="L440" s="192" t="n"/>
+      <c r="N440" s="193">
+        <f>IF(L440="",$B$4,L440)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="193" t="n"/>
+      <c r="G441" s="187" t="n"/>
+      <c r="H441" s="187" t="n"/>
+      <c r="I441" s="187" t="n"/>
+      <c r="J441" s="187" t="n"/>
+      <c r="L441" s="192" t="n"/>
+      <c r="N441" s="193">
+        <f>IF(L441="",$B$4,L441)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="193" t="n"/>
+      <c r="G442" s="187" t="n"/>
+      <c r="H442" s="187" t="n"/>
+      <c r="I442" s="187" t="n"/>
+      <c r="J442" s="187" t="n"/>
+      <c r="L442" s="192" t="n"/>
+      <c r="N442" s="193">
+        <f>IF(L442="",$B$4,L442)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" s="193" t="n"/>
+      <c r="G443" s="187" t="n"/>
+      <c r="H443" s="187" t="n"/>
+      <c r="I443" s="187" t="n"/>
+      <c r="J443" s="187" t="n"/>
+      <c r="L443" s="192" t="n"/>
+      <c r="N443" s="193">
+        <f>IF(L443="",$B$4,L443)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="193" t="n"/>
+      <c r="G444" s="187" t="n"/>
+      <c r="H444" s="187" t="n"/>
+      <c r="I444" s="187" t="n"/>
+      <c r="J444" s="187" t="n"/>
+      <c r="L444" s="192" t="n"/>
+      <c r="N444" s="193">
+        <f>IF(L444="",$B$4,L444)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" s="193" t="n"/>
+      <c r="G445" s="187" t="n"/>
+      <c r="H445" s="187" t="n"/>
+      <c r="I445" s="187" t="n"/>
+      <c r="J445" s="187" t="n"/>
+      <c r="L445" s="192" t="n"/>
+      <c r="N445" s="193">
+        <f>IF(L445="",$B$4,L445)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" s="193" t="n"/>
+      <c r="G446" s="187" t="n"/>
+      <c r="H446" s="187" t="n"/>
+      <c r="I446" s="187" t="n"/>
+      <c r="J446" s="187" t="n"/>
+      <c r="L446" s="192" t="n"/>
+      <c r="N446" s="193">
+        <f>IF(L446="",$B$4,L446)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" s="193" t="n"/>
+      <c r="G447" s="187" t="n"/>
+      <c r="H447" s="187" t="n"/>
+      <c r="I447" s="187" t="n"/>
+      <c r="J447" s="187" t="n"/>
+      <c r="L447" s="192" t="n"/>
+      <c r="N447" s="193">
+        <f>IF(L447="",$B$4,L447)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="193" t="n"/>
+      <c r="G448" s="187" t="n"/>
+      <c r="H448" s="187" t="n"/>
+      <c r="I448" s="187" t="n"/>
+      <c r="J448" s="187" t="n"/>
+      <c r="L448" s="192" t="n"/>
+      <c r="N448" s="193">
+        <f>IF(L448="",$B$4,L448)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="193" t="n"/>
+      <c r="G449" s="187" t="n"/>
+      <c r="H449" s="187" t="n"/>
+      <c r="I449" s="187" t="n"/>
+      <c r="J449" s="187" t="n"/>
+      <c r="L449" s="192" t="n"/>
+      <c r="N449" s="193">
+        <f>IF(L449="",$B$4,L449)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" s="193" t="n"/>
+      <c r="G450" s="187" t="n"/>
+      <c r="H450" s="187" t="n"/>
+      <c r="I450" s="187" t="n"/>
+      <c r="J450" s="187" t="n"/>
+      <c r="L450" s="192" t="n"/>
+      <c r="N450" s="193">
+        <f>IF(L450="",$B$4,L450)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="193" t="n"/>
+      <c r="G451" s="187" t="n"/>
+      <c r="H451" s="187" t="n"/>
+      <c r="I451" s="187" t="n"/>
+      <c r="J451" s="187" t="n"/>
+      <c r="L451" s="192" t="n"/>
+      <c r="N451" s="193">
+        <f>IF(L451="",$B$4,L451)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="193" t="n"/>
+      <c r="G452" s="187" t="n"/>
+      <c r="H452" s="187" t="n"/>
+      <c r="I452" s="187" t="n"/>
+      <c r="J452" s="187" t="n"/>
+      <c r="L452" s="192" t="n"/>
+      <c r="N452" s="193">
+        <f>IF(L452="",$B$4,L452)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="193" t="n"/>
+      <c r="G453" s="187" t="n"/>
+      <c r="H453" s="187" t="n"/>
+      <c r="I453" s="187" t="n"/>
+      <c r="J453" s="187" t="n"/>
+      <c r="L453" s="192" t="n"/>
+      <c r="N453" s="193">
+        <f>IF(L453="",$B$4,L453)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="193" t="n"/>
+      <c r="G454" s="187" t="n"/>
+      <c r="H454" s="187" t="n"/>
+      <c r="I454" s="187" t="n"/>
+      <c r="J454" s="187" t="n"/>
+      <c r="L454" s="192" t="n"/>
+      <c r="N454" s="193">
+        <f>IF(L454="",$B$4,L454)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="193" t="n"/>
+      <c r="G455" s="187" t="n"/>
+      <c r="H455" s="187" t="n"/>
+      <c r="I455" s="187" t="n"/>
+      <c r="J455" s="187" t="n"/>
+      <c r="L455" s="192" t="n"/>
+      <c r="N455" s="193">
+        <f>IF(L455="",$B$4,L455)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="193" t="n"/>
+      <c r="G456" s="187" t="n"/>
+      <c r="H456" s="187" t="n"/>
+      <c r="I456" s="187" t="n"/>
+      <c r="J456" s="187" t="n"/>
+      <c r="L456" s="192" t="n"/>
+      <c r="N456" s="193">
+        <f>IF(L456="",$B$4,L456)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="193" t="n"/>
+      <c r="G457" s="187" t="n"/>
+      <c r="H457" s="187" t="n"/>
+      <c r="I457" s="187" t="n"/>
+      <c r="J457" s="187" t="n"/>
+      <c r="L457" s="192" t="n"/>
+      <c r="N457" s="193">
+        <f>IF(L457="",$B$4,L457)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" s="193" t="n"/>
+      <c r="G458" s="187" t="n"/>
+      <c r="H458" s="187" t="n"/>
+      <c r="I458" s="187" t="n"/>
+      <c r="J458" s="187" t="n"/>
+      <c r="L458" s="192" t="n"/>
+      <c r="N458" s="193">
+        <f>IF(L458="",$B$4,L458)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" s="193" t="n"/>
+      <c r="G459" s="187" t="n"/>
+      <c r="H459" s="187" t="n"/>
+      <c r="I459" s="187" t="n"/>
+      <c r="J459" s="187" t="n"/>
+      <c r="L459" s="192" t="n"/>
+      <c r="N459" s="193">
+        <f>IF(L459="",$B$4,L459)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" s="193" t="n"/>
+      <c r="G460" s="187" t="n"/>
+      <c r="H460" s="187" t="n"/>
+      <c r="I460" s="187" t="n"/>
+      <c r="J460" s="187" t="n"/>
+      <c r="L460" s="192" t="n"/>
+      <c r="N460" s="193">
+        <f>IF(L460="",$B$4,L460)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="193" t="n"/>
+      <c r="G461" s="187" t="n"/>
+      <c r="H461" s="187" t="n"/>
+      <c r="I461" s="187" t="n"/>
+      <c r="J461" s="187" t="n"/>
+      <c r="L461" s="192" t="n"/>
+      <c r="N461" s="193">
+        <f>IF(L461="",$B$4,L461)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="193" t="n"/>
+      <c r="G462" s="187" t="n"/>
+      <c r="H462" s="187" t="n"/>
+      <c r="I462" s="187" t="n"/>
+      <c r="J462" s="187" t="n"/>
+      <c r="L462" s="192" t="n"/>
+      <c r="N462" s="193">
+        <f>IF(L462="",$B$4,L462)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="193" t="n"/>
+      <c r="G463" s="187" t="n"/>
+      <c r="H463" s="187" t="n"/>
+      <c r="I463" s="187" t="n"/>
+      <c r="J463" s="187" t="n"/>
+      <c r="L463" s="192" t="n"/>
+      <c r="N463" s="193">
+        <f>IF(L463="",$B$4,L463)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="193" t="n"/>
+      <c r="G464" s="187" t="n"/>
+      <c r="H464" s="187" t="n"/>
+      <c r="I464" s="187" t="n"/>
+      <c r="J464" s="187" t="n"/>
+      <c r="L464" s="192" t="n"/>
+      <c r="N464" s="193">
+        <f>IF(L464="",$B$4,L464)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="193" t="n"/>
+      <c r="G465" s="187" t="n"/>
+      <c r="H465" s="187" t="n"/>
+      <c r="I465" s="187" t="n"/>
+      <c r="J465" s="187" t="n"/>
+      <c r="L465" s="192" t="n"/>
+      <c r="N465" s="193">
+        <f>IF(L465="",$B$4,L465)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="193" t="n"/>
+      <c r="G466" s="187" t="n"/>
+      <c r="H466" s="187" t="n"/>
+      <c r="I466" s="187" t="n"/>
+      <c r="J466" s="187" t="n"/>
+      <c r="L466" s="192" t="n"/>
+      <c r="N466" s="193">
+        <f>IF(L466="",$B$4,L466)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" s="193" t="n"/>
+      <c r="G467" s="187" t="n"/>
+      <c r="H467" s="187" t="n"/>
+      <c r="I467" s="187" t="n"/>
+      <c r="J467" s="187" t="n"/>
+      <c r="L467" s="192" t="n"/>
+      <c r="N467" s="193">
+        <f>IF(L467="",$B$4,L467)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="193" t="n"/>
+      <c r="G468" s="187" t="n"/>
+      <c r="H468" s="187" t="n"/>
+      <c r="I468" s="187" t="n"/>
+      <c r="J468" s="187" t="n"/>
+      <c r="L468" s="192" t="n"/>
+      <c r="N468" s="193">
+        <f>IF(L468="",$B$4,L468)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" s="193" t="n"/>
+      <c r="G469" s="187" t="n"/>
+      <c r="H469" s="187" t="n"/>
+      <c r="I469" s="187" t="n"/>
+      <c r="J469" s="187" t="n"/>
+      <c r="L469" s="192" t="n"/>
+      <c r="N469" s="193">
+        <f>IF(L469="",$B$4,L469)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="193" t="n"/>
+      <c r="G470" s="187" t="n"/>
+      <c r="H470" s="187" t="n"/>
+      <c r="I470" s="187" t="n"/>
+      <c r="J470" s="187" t="n"/>
+      <c r="L470" s="192" t="n"/>
+      <c r="N470" s="193">
+        <f>IF(L470="",$B$4,L470)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" s="193" t="n"/>
+      <c r="G471" s="187" t="n"/>
+      <c r="H471" s="187" t="n"/>
+      <c r="I471" s="187" t="n"/>
+      <c r="J471" s="187" t="n"/>
+      <c r="L471" s="192" t="n"/>
+      <c r="N471" s="193">
+        <f>IF(L471="",$B$4,L471)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="193" t="n"/>
+      <c r="G472" s="187" t="n"/>
+      <c r="H472" s="187" t="n"/>
+      <c r="I472" s="187" t="n"/>
+      <c r="J472" s="187" t="n"/>
+      <c r="L472" s="192" t="n"/>
+      <c r="N472" s="193">
+        <f>IF(L472="",$B$4,L472)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="193" t="n"/>
+      <c r="G473" s="187" t="n"/>
+      <c r="H473" s="187" t="n"/>
+      <c r="I473" s="187" t="n"/>
+      <c r="J473" s="187" t="n"/>
+      <c r="L473" s="192" t="n"/>
+      <c r="N473" s="193">
+        <f>IF(L473="",$B$4,L473)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="193" t="n"/>
+      <c r="G474" s="187" t="n"/>
+      <c r="H474" s="187" t="n"/>
+      <c r="I474" s="187" t="n"/>
+      <c r="J474" s="187" t="n"/>
+      <c r="L474" s="192" t="n"/>
+      <c r="N474" s="193">
+        <f>IF(L474="",$B$4,L474)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="193" t="n"/>
+      <c r="G475" s="187" t="n"/>
+      <c r="H475" s="187" t="n"/>
+      <c r="I475" s="187" t="n"/>
+      <c r="J475" s="187" t="n"/>
+      <c r="L475" s="192" t="n"/>
+      <c r="N475" s="193">
+        <f>IF(L475="",$B$4,L475)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="193" t="n"/>
+      <c r="G476" s="187" t="n"/>
+      <c r="H476" s="187" t="n"/>
+      <c r="I476" s="187" t="n"/>
+      <c r="J476" s="187" t="n"/>
+      <c r="L476" s="192" t="n"/>
+      <c r="N476" s="193">
+        <f>IF(L476="",$B$4,L476)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="193" t="n"/>
+      <c r="G477" s="187" t="n"/>
+      <c r="H477" s="187" t="n"/>
+      <c r="I477" s="187" t="n"/>
+      <c r="J477" s="187" t="n"/>
+      <c r="L477" s="192" t="n"/>
+      <c r="N477" s="193">
+        <f>IF(L477="",$B$4,L477)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="193" t="n"/>
+      <c r="G478" s="187" t="n"/>
+      <c r="H478" s="187" t="n"/>
+      <c r="I478" s="187" t="n"/>
+      <c r="J478" s="187" t="n"/>
+      <c r="L478" s="192" t="n"/>
+      <c r="N478" s="193">
+        <f>IF(L478="",$B$4,L478)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" s="193" t="n"/>
+      <c r="G479" s="187" t="n"/>
+      <c r="H479" s="187" t="n"/>
+      <c r="I479" s="187" t="n"/>
+      <c r="J479" s="187" t="n"/>
+      <c r="L479" s="192" t="n"/>
+      <c r="N479" s="193">
+        <f>IF(L479="",$B$4,L479)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="193" t="n"/>
+      <c r="G480" s="187" t="n"/>
+      <c r="H480" s="187" t="n"/>
+      <c r="I480" s="187" t="n"/>
+      <c r="J480" s="187" t="n"/>
+      <c r="L480" s="192" t="n"/>
+      <c r="N480" s="193">
+        <f>IF(L480="",$B$4,L480)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="193" t="n"/>
+      <c r="G481" s="187" t="n"/>
+      <c r="H481" s="187" t="n"/>
+      <c r="I481" s="187" t="n"/>
+      <c r="J481" s="187" t="n"/>
+      <c r="L481" s="192" t="n"/>
+      <c r="N481" s="193">
+        <f>IF(L481="",$B$4,L481)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="193" t="n"/>
+      <c r="G482" s="187" t="n"/>
+      <c r="H482" s="187" t="n"/>
+      <c r="I482" s="187" t="n"/>
+      <c r="J482" s="187" t="n"/>
+      <c r="L482" s="192" t="n"/>
+      <c r="N482" s="193">
+        <f>IF(L482="",$B$4,L482)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="193" t="n"/>
+      <c r="G483" s="187" t="n"/>
+      <c r="H483" s="187" t="n"/>
+      <c r="I483" s="187" t="n"/>
+      <c r="J483" s="187" t="n"/>
+      <c r="L483" s="192" t="n"/>
+      <c r="N483" s="193">
+        <f>IF(L483="",$B$4,L483)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="193" t="n"/>
+      <c r="G484" s="187" t="n"/>
+      <c r="H484" s="187" t="n"/>
+      <c r="I484" s="187" t="n"/>
+      <c r="J484" s="187" t="n"/>
+      <c r="L484" s="192" t="n"/>
+      <c r="N484" s="193">
+        <f>IF(L484="",$B$4,L484)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="193" t="n"/>
+      <c r="G485" s="187" t="n"/>
+      <c r="H485" s="187" t="n"/>
+      <c r="I485" s="187" t="n"/>
+      <c r="J485" s="187" t="n"/>
+      <c r="L485" s="192" t="n"/>
+      <c r="N485" s="193">
+        <f>IF(L485="",$B$4,L485)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="193" t="n"/>
+      <c r="G486" s="187" t="n"/>
+      <c r="H486" s="187" t="n"/>
+      <c r="I486" s="187" t="n"/>
+      <c r="J486" s="187" t="n"/>
+      <c r="L486" s="192" t="n"/>
+      <c r="N486" s="193">
+        <f>IF(L486="",$B$4,L486)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="193" t="n"/>
+      <c r="G487" s="187" t="n"/>
+      <c r="H487" s="187" t="n"/>
+      <c r="I487" s="187" t="n"/>
+      <c r="J487" s="187" t="n"/>
+      <c r="L487" s="192" t="n"/>
+      <c r="N487" s="193">
+        <f>IF(L487="",$B$4,L487)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="193" t="n"/>
+      <c r="G488" s="187" t="n"/>
+      <c r="H488" s="187" t="n"/>
+      <c r="I488" s="187" t="n"/>
+      <c r="J488" s="187" t="n"/>
+      <c r="L488" s="192" t="n"/>
+      <c r="N488" s="193">
+        <f>IF(L488="",$B$4,L488)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="193" t="n"/>
+      <c r="G489" s="187" t="n"/>
+      <c r="H489" s="187" t="n"/>
+      <c r="I489" s="187" t="n"/>
+      <c r="J489" s="187" t="n"/>
+      <c r="L489" s="192" t="n"/>
+      <c r="N489" s="193">
+        <f>IF(L489="",$B$4,L489)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="193" t="n"/>
+      <c r="G490" s="187" t="n"/>
+      <c r="H490" s="187" t="n"/>
+      <c r="I490" s="187" t="n"/>
+      <c r="J490" s="187" t="n"/>
+      <c r="L490" s="192" t="n"/>
+      <c r="N490" s="193">
+        <f>IF(L490="",$B$4,L490)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="193" t="n"/>
+      <c r="G491" s="187" t="n"/>
+      <c r="H491" s="187" t="n"/>
+      <c r="I491" s="187" t="n"/>
+      <c r="J491" s="187" t="n"/>
+      <c r="L491" s="192" t="n"/>
+      <c r="N491" s="193">
+        <f>IF(L491="",$B$4,L491)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="193" t="n"/>
+      <c r="G492" s="187" t="n"/>
+      <c r="H492" s="187" t="n"/>
+      <c r="I492" s="187" t="n"/>
+      <c r="J492" s="187" t="n"/>
+      <c r="L492" s="192" t="n"/>
+      <c r="N492" s="193">
+        <f>IF(L492="",$B$4,L492)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="193" t="n"/>
+      <c r="G493" s="187" t="n"/>
+      <c r="H493" s="187" t="n"/>
+      <c r="I493" s="187" t="n"/>
+      <c r="J493" s="187" t="n"/>
+      <c r="L493" s="192" t="n"/>
+      <c r="N493" s="193">
+        <f>IF(L493="",$B$4,L493)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="193" t="n"/>
+      <c r="G494" s="187" t="n"/>
+      <c r="H494" s="187" t="n"/>
+      <c r="I494" s="187" t="n"/>
+      <c r="J494" s="187" t="n"/>
+      <c r="L494" s="192" t="n"/>
+      <c r="N494" s="193">
+        <f>IF(L494="",$B$4,L494)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="193" t="n"/>
+      <c r="G495" s="187" t="n"/>
+      <c r="H495" s="187" t="n"/>
+      <c r="I495" s="187" t="n"/>
+      <c r="J495" s="187" t="n"/>
+      <c r="L495" s="192" t="n"/>
+      <c r="N495" s="193">
+        <f>IF(L495="",$B$4,L495)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="193" t="n"/>
+      <c r="G496" s="187" t="n"/>
+      <c r="H496" s="187" t="n"/>
+      <c r="I496" s="187" t="n"/>
+      <c r="J496" s="187" t="n"/>
+      <c r="L496" s="192" t="n"/>
+      <c r="N496" s="193">
+        <f>IF(L496="",$B$4,L496)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="193" t="n"/>
+      <c r="G497" s="187" t="n"/>
+      <c r="H497" s="187" t="n"/>
+      <c r="I497" s="187" t="n"/>
+      <c r="J497" s="187" t="n"/>
+      <c r="L497" s="192" t="n"/>
+      <c r="N497" s="193">
+        <f>IF(L497="",$B$4,L497)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="193" t="n"/>
+      <c r="G498" s="187" t="n"/>
+      <c r="H498" s="187" t="n"/>
+      <c r="I498" s="187" t="n"/>
+      <c r="J498" s="187" t="n"/>
+      <c r="L498" s="192" t="n"/>
+      <c r="N498" s="193">
+        <f>IF(L498="",$B$4,L498)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="193" t="n"/>
+      <c r="G499" s="187" t="n"/>
+      <c r="H499" s="187" t="n"/>
+      <c r="I499" s="187" t="n"/>
+      <c r="J499" s="187" t="n"/>
+      <c r="L499" s="192" t="n"/>
+      <c r="N499" s="193">
+        <f>IF(L499="",$B$4,L499)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="193" t="n"/>
+      <c r="G500" s="187" t="n"/>
+      <c r="H500" s="187" t="n"/>
+      <c r="I500" s="187" t="n"/>
+      <c r="J500" s="187" t="n"/>
+      <c r="L500" s="192" t="n"/>
+      <c r="N500" s="193">
+        <f>IF(L500="",$B$4,L500)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="193" t="n"/>
+      <c r="G501" s="187" t="n"/>
+      <c r="H501" s="187" t="n"/>
+      <c r="I501" s="187" t="n"/>
+      <c r="J501" s="187" t="n"/>
+      <c r="L501" s="192" t="n"/>
+      <c r="N501" s="193">
+        <f>IF(L501="",$B$4,L501)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" s="193" t="n"/>
+      <c r="G502" s="187" t="n"/>
+      <c r="H502" s="187" t="n"/>
+      <c r="I502" s="187" t="n"/>
+      <c r="J502" s="187" t="n"/>
+      <c r="L502" s="192" t="n"/>
+      <c r="N502" s="193">
+        <f>IF(L502="",$B$4,L502)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="193" t="n"/>
+      <c r="G503" s="187" t="n"/>
+      <c r="H503" s="187" t="n"/>
+      <c r="I503" s="187" t="n"/>
+      <c r="J503" s="187" t="n"/>
+      <c r="L503" s="192" t="n"/>
+      <c r="N503" s="193">
+        <f>IF(L503="",$B$4,L503)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="193" t="n"/>
+      <c r="G504" s="187" t="n"/>
+      <c r="H504" s="187" t="n"/>
+      <c r="I504" s="187" t="n"/>
+      <c r="J504" s="187" t="n"/>
+      <c r="L504" s="192" t="n"/>
+      <c r="N504" s="193">
+        <f>IF(L504="",$B$4,L504)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="193" t="n"/>
+      <c r="G505" s="187" t="n"/>
+      <c r="H505" s="187" t="n"/>
+      <c r="I505" s="187" t="n"/>
+      <c r="J505" s="187" t="n"/>
+      <c r="L505" s="192" t="n"/>
+      <c r="N505" s="193">
+        <f>IF(L505="",$B$4,L505)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="193" t="n"/>
+      <c r="G506" s="187" t="n"/>
+      <c r="H506" s="187" t="n"/>
+      <c r="I506" s="187" t="n"/>
+      <c r="J506" s="187" t="n"/>
+      <c r="L506" s="192" t="n"/>
+      <c r="N506" s="193">
+        <f>IF(L506="",$B$4,L506)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="193" t="n"/>
+      <c r="G507" s="187" t="n"/>
+      <c r="H507" s="187" t="n"/>
+      <c r="I507" s="187" t="n"/>
+      <c r="J507" s="187" t="n"/>
+      <c r="L507" s="192" t="n"/>
+      <c r="N507" s="193">
+        <f>IF(L507="",$B$4,L507)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="193" t="n"/>
+      <c r="G508" s="187" t="n"/>
+      <c r="H508" s="187" t="n"/>
+      <c r="I508" s="187" t="n"/>
+      <c r="J508" s="187" t="n"/>
+      <c r="L508" s="192" t="n"/>
+      <c r="N508" s="193">
+        <f>IF(L508="",$B$4,L508)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="193" t="n"/>
+      <c r="G509" s="187" t="n"/>
+      <c r="H509" s="187" t="n"/>
+      <c r="I509" s="187" t="n"/>
+      <c r="J509" s="187" t="n"/>
+      <c r="L509" s="192" t="n"/>
+      <c r="N509" s="193">
+        <f>IF(L509="",$B$4,L509)</f>
+        <v>46328</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="193" t="n"/>
+      <c r="G510" s="187" t="n"/>
+      <c r="H510" s="187" t="n"/>
+      <c r="I510" s="187" t="n"/>
+      <c r="J510" s="187" t="n"/>
+      <c r="L510" s="192" t="n"/>
+      <c r="N510" s="193">
+        <f>IF(L510="",$B$4,L510)</f>
+        <v>46328</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:N2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
+++ b/cashflow/CTS Cash Flow Forecast - 12102026.xlsx
@@ -1114,15 +1114,15 @@
       </c>
       <c r="D8" s="10" t="n"/>
       <c r="E8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="10" t="n"/>
       <c r="I8" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" s="10" t="n"/>
       <c r="K8" s="11" t="n">
@@ -1133,7 +1133,7 @@
       <c r="N8" s="12" t="n"/>
       <c r="O8" s="76" t="inlineStr">
         <is>
-          <t>Week 1 is done and reconciles to Xero (flag 1). Week 2 actuals are in to Mon 12 Oct only - flag stays 0 until the week closes Wed 14 Oct and the bank balance is keyed.</t>
+          <t>Weeks 1 to 4 are done (flag 1). Weeks 2 to 4 are built off the Xero cash P&amp;L, grossed up for GST, with the bank balance worked back from Xero total cash. Week 5 runs to 4 Nov and is in the 29 Oct forecast file.</t>
         </is>
       </c>
     </row>
@@ -1161,27 +1161,27 @@
       </c>
       <c r="F10" s="119">
         <f>IF(E$8=1,E59,D58)</f>
-        <v>263901.67999999993</v>
+        <v>579568.07</v>
       </c>
       <c r="G10" s="119">
         <f>F10</f>
-        <v>263901.67999999993</v>
+        <v>579568.07</v>
       </c>
       <c r="H10" s="119">
         <f>IF(G$8=1,G59,F58)</f>
-        <v>498505.9666666666</v>
+        <v>455481.91000000003</v>
       </c>
       <c r="I10" s="119">
         <f>H10</f>
-        <v>498505.9666666666</v>
+        <v>455481.91000000003</v>
       </c>
       <c r="J10" s="119">
         <f>IF(I$8=1,I59,H58)</f>
-        <v>362388.61933333334</v>
+        <v>439930.67999999993</v>
       </c>
       <c r="K10" s="119">
         <f>J10</f>
-        <v>362388.61933333334</v>
+        <v>439930.67999999993</v>
       </c>
       <c r="L10" s="119">
         <f>B10</f>
@@ -1234,19 +1234,25 @@
         <v>142696.27</v>
       </c>
       <c r="E13" s="121">
-        <f>112683.22+18891.66+9086.39+1661+506+374</f>
-        <v>143202.27000000002</v>
+        <f>ROUND(369617.53*1.1,2)</f>
+        <v>406579.28</v>
       </c>
       <c r="F13" s="120">
         <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$46,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$46)+Assumptions!$B$39/3</f>
         <v>234604.28666666668</v>
       </c>
-      <c r="G13" s="121" t="n"/>
+      <c r="G13" s="121">
+        <f>ROUND(103182.08*1.1,2)</f>
+        <v>113500.29</v>
+      </c>
       <c r="H13" s="120">
         <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$47,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$47)+Assumptions!$B$39/3</f>
         <v>12626.466666666667</v>
       </c>
-      <c r="I13" s="121" t="n"/>
+      <c r="I13" s="121">
+        <f>ROUND(17509*1.1,2)</f>
+        <v>19259.9</v>
+      </c>
       <c r="J13" s="120">
         <f>SUMIFS(Receivables!$F$5:$F$65,Receivables!$H$5:$H$65,"&gt;="&amp;Assumptions!$B$48,Receivables!$H$5:$H$65,"&lt;="&amp;Assumptions!$C$48)+Assumptions!$B$39/3</f>
         <v>91870.13666666666</v>
@@ -1258,15 +1264,15 @@
       </c>
       <c r="M13" s="120">
         <f>SUM(C13,E13,G13,I13,K13)</f>
-        <v>301061.4</v>
+        <v>697198.6000000001</v>
       </c>
       <c r="N13" s="120">
         <f>(C13-B13)*C$8+(E13-D13)*E$8+(G13-F13)*G$8+(I13-H13)*I$8+(K13-J13)*K$8</f>
-        <v>23268.21000000002</v>
+        <v>172680.65666666668</v>
       </c>
       <c r="O13" s="108" t="inlineStr">
         <is>
-          <t>Week 1 now includes 6-7 Oct: PwC $9,350, CBA Melb $93.50, APA $627, CBA Bris $8,043.20. Week 2 to 12 Oct: Deloitte $112,683.22 and $18,891.66, CEO Institute $9,086.39, ASX $1,661, Dimensional $506, Ricoh $374. Nothing from Aware yet.</t>
+          <t>Week 2: Aware $225,887 landed Tue 13 Oct, plus Deloitte, CEO Institute, ASX. Week 3: CBA Sep contract invoices (15 Oct), Aware Appspace $23,317, ICC, Bankwest. Week 4: Aware maintenance $12,100 and the Perth USB-C job (27 Oct), RSNSW. All from Xero cash P&amp;L x 1.1.</t>
         </is>
       </c>
     </row>
@@ -1294,12 +1300,16 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="G14" s="121" t="n"/>
+      <c r="G14" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H14" s="120">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="I14" s="121" t="n"/>
+      <c r="I14" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J14" s="120">
         <f>Assumptions!$B$40</f>
         <v>600</v>
@@ -1343,7 +1353,7 @@
       </c>
       <c r="E15" s="122">
         <f>E13+E14</f>
-        <v>143202.27000000002</v>
+        <v>406579.28</v>
       </c>
       <c r="F15" s="122">
         <f>F13+F14</f>
@@ -1351,7 +1361,7 @@
       </c>
       <c r="G15" s="122">
         <f>G13+G14</f>
-        <v>0</v>
+        <v>113500.29</v>
       </c>
       <c r="H15" s="122">
         <f>H13+H14</f>
@@ -1359,7 +1369,7 @@
       </c>
       <c r="I15" s="122">
         <f>I13+I14</f>
-        <v>0</v>
+        <v>19259.9</v>
       </c>
       <c r="J15" s="122">
         <f>J13+J14</f>
@@ -1375,11 +1385,11 @@
       </c>
       <c r="M15" s="122">
         <f>M13+M14</f>
-        <v>301491.57</v>
+        <v>697628.7700000001</v>
       </c>
       <c r="N15" s="122">
         <f>N13+N14</f>
-        <v>23698.38000000002</v>
+        <v>173110.8266666667</v>
       </c>
       <c r="O15" s="16" t="n"/>
     </row>
@@ -1436,12 +1446,17 @@
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$46,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$46)</f>
         <v>85248</v>
       </c>
-      <c r="G19" s="121" t="n"/>
+      <c r="G19" s="121">
+        <f>ROUND(111704.13*Assumptions!$B$10,2)</f>
+        <v>85788.77</v>
+      </c>
       <c r="H19" s="120">
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$47,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$47)</f>
         <v>0</v>
       </c>
-      <c r="I19" s="121" t="n"/>
+      <c r="I19" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J19" s="120">
         <f>SUMIFS(Payroll!$E$5:$E$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$48,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$48)</f>
         <v>85248</v>
@@ -1453,15 +1468,15 @@
       </c>
       <c r="M19" s="120">
         <f>SUM(C19,E19,G19,I19,K19)</f>
-        <v>79736.05</v>
+        <v>165524.82</v>
       </c>
       <c r="N19" s="120">
         <f>(C19-B19)*C$8+(E19-D19)*E$8+(G19-F19)*G$8+(I19-H19)*I$8+(K19-J19)*K$8</f>
-        <v>-5511.949999999997</v>
+        <v>-4971.179999999993</v>
       </c>
       <c r="O19" s="108" t="inlineStr">
         <is>
-          <t>Payroll tab - gross x net %. Fortnight is Sat to Fri and the money goes out the Tuesday after: Tue 6 Oct (week 1), Tue 20 Oct (week 3) and Tue 3 Nov (week 5). 6 Oct actual is from the Xero bank movement - swap in the ABA figure.</t>
+          <t>Payroll tab - gross x net %. Pay runs Tue 6 Oct (week 1, $79.7k from the bank) and Tue 20 Oct (week 3, $111,704 gross per Xero, net at 78.8% - swap in the ABA figure). Next one Tue 3 Nov is in the new file.</t>
         </is>
       </c>
     </row>
@@ -1489,12 +1504,16 @@
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$46,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$46)</f>
         <v>13320</v>
       </c>
-      <c r="G20" s="121" t="n"/>
+      <c r="G20" s="121" t="n">
+        <v>14214.47</v>
+      </c>
       <c r="H20" s="120">
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$47,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$47)</f>
         <v>0</v>
       </c>
-      <c r="I20" s="121" t="n"/>
+      <c r="I20" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J20" s="120">
         <f>SUMIFS(Payroll!$G$5:$G$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$48,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$48)</f>
         <v>13320</v>
@@ -1506,15 +1525,15 @@
       </c>
       <c r="M20" s="120">
         <f>SUM(C20,E20,G20,I20,K20)</f>
-        <v>13083.54</v>
+        <v>27298.010000000002</v>
       </c>
       <c r="N20" s="120">
         <f>(C20-B20)*C$8+(E20-D20)*E$8+(G20-F20)*G$8+(I20-H20)*I$8+(K20-J20)*K$8</f>
-        <v>-236.45999999999913</v>
+        <v>658.0100000000002</v>
       </c>
       <c r="O20" s="108" t="inlineStr">
         <is>
-          <t>Gross x 12%. EH direct debits it in the pay run week.</t>
+          <t>Gross x 12%. Actuals are the super in the Xero pay run journals ($13,084 on 7 Oct, $14,214 on 21 Oct).</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1559,16 @@
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="G21" s="121" t="n"/>
+      <c r="G21" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H21" s="120">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="I21" s="121" t="n"/>
+      <c r="I21" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J21" s="120">
         <f>0</f>
         <v>0</v>
@@ -1593,12 +1616,16 @@
         <f>IF(AND(Assumptions!$B$19&gt;=Assumptions!$B$46,Assumptions!$B$19&lt;=Assumptions!$C$46),Assumptions!$B$17+Assumptions!$B$18,0)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="121" t="n"/>
+      <c r="G22" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H22" s="120">
         <f>IF(AND(Assumptions!$B$19&gt;=Assumptions!$B$47,Assumptions!$B$19&lt;=Assumptions!$C$47),Assumptions!$B$17+Assumptions!$B$18,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="121" t="n"/>
+      <c r="I22" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J22" s="120">
         <f>IF(AND(Assumptions!$B$19&gt;=Assumptions!$B$48,Assumptions!$B$19&lt;=Assumptions!$C$48),Assumptions!$B$17+Assumptions!$B$18,0)</f>
         <v>0</v>
@@ -1644,12 +1671,16 @@
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$46,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$46)</f>
         <v>1000</v>
       </c>
-      <c r="G23" s="121" t="n"/>
+      <c r="G23" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H23" s="120">
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$47,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$47)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="121" t="n"/>
+      <c r="I23" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J23" s="120">
         <f>SUMIFS(Payroll!$H$5:$H$7,Payroll!$C$5:$C$7,"&gt;="&amp;Assumptions!$B$48,Payroll!$C$5:$C$7,"&lt;="&amp;Assumptions!$C$48)</f>
         <v>1000</v>
@@ -1665,7 +1696,7 @@
       </c>
       <c r="N23" s="120">
         <f>(C23-B23)*C$8+(E23-D23)*E$8+(G23-F23)*G$8+(I23-H23)*I$8+(K23-J23)*K$8</f>
-        <v>-1000</v>
+        <v>-2000</v>
       </c>
       <c r="O23" s="108" t="inlineStr">
         <is>
@@ -1701,7 +1732,7 @@
       </c>
       <c r="G24" s="123">
         <f>G19+G20+G21+G22+G23</f>
-        <v>0</v>
+        <v>100003.24</v>
       </c>
       <c r="H24" s="123">
         <f>H19+H20+H21+H22+H23</f>
@@ -1725,11 +1756,11 @@
       </c>
       <c r="M24" s="123">
         <f>M19+M20+M21+M22+M23</f>
-        <v>101422.34</v>
+        <v>201425.58000000002</v>
       </c>
       <c r="N24" s="123">
         <f>N19+N20+N21+N22+N23</f>
-        <v>-7140.659999999996</v>
+        <v>-6705.419999999993</v>
       </c>
       <c r="O24" s="12" t="n"/>
     </row>
@@ -1765,12 +1796,18 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
         <v>4000</v>
       </c>
-      <c r="G27" s="121" t="n"/>
+      <c r="G27" s="121">
+        <f>ROUND(80501.16*1.1,2)</f>
+        <v>88551.28</v>
+      </c>
       <c r="H27" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
         <v>4000</v>
       </c>
-      <c r="I27" s="121" t="n"/>
+      <c r="I27" s="121">
+        <f>ROUND(11382*1.1,2)</f>
+        <v>12520.2</v>
+      </c>
       <c r="J27" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Equipment purchases")+Assumptions!$B$29/5</f>
         <v>4000</v>
@@ -1782,15 +1819,15 @@
       </c>
       <c r="M27" s="120">
         <f>SUM(C27,E27,G27,I27,K27)</f>
-        <v>209729.55</v>
+        <v>310801.02999999997</v>
       </c>
       <c r="N27" s="120">
         <f>(C27-B27)*C$8+(E27-D27)*E$8+(G27-F27)*G$8+(I27-H27)*I$8+(K27-J27)*K$8</f>
-        <v>-28708.199999999983</v>
+        <v>91973.58</v>
       </c>
       <c r="O27" s="108" t="inlineStr">
         <is>
-          <t>139k was paid on the 29/09/2026. Remittance (Complete AV) table  under GC approvals was send on the 29/09. Week 2 to 12 Oct: LiveU SDI/modems $26,004 plus small items ($28,737 ex GST per Xero cash P&amp;L). Complete AV labour and programming $39,033.02 was released and paid 8 Oct - whole bill now paid.</t>
+          <t>139k materials paid 29 Sep, labour $39,033 released and paid 8 Oct. Week 3 actual $88.6k is the equipment purchases in Xero cash P&amp;L 15-21 Oct - a lot bigger than the estimate, worth a look at what it was.</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1854,18 @@
         <f>Assumptions!$B$27/5</f>
         <v>8000</v>
       </c>
-      <c r="G28" s="121" t="n"/>
+      <c r="G28" s="121">
+        <f>ROUND((9090+1628.4)*1.1,2)</f>
+        <v>11790.24</v>
+      </c>
       <c r="H28" s="120">
         <f>Assumptions!$B$27/5</f>
         <v>8000</v>
       </c>
-      <c r="I28" s="121" t="n"/>
+      <c r="I28" s="121">
+        <f>ROUND(3055*1.1,2)</f>
+        <v>3360.5</v>
+      </c>
       <c r="J28" s="120">
         <f>Assumptions!$B$27/5</f>
         <v>8000</v>
@@ -1834,11 +1877,11 @@
       </c>
       <c r="M28" s="120">
         <f>SUM(C28,E28,G28,I28,K28)</f>
-        <v>9510.18</v>
+        <v>24660.92</v>
       </c>
       <c r="N28" s="120">
         <f>(C28-B28)*C$8+(E28-D28)*E$8+(G28-F28)*G$8+(I28-H28)*I$8+(K28-J28)*K$8</f>
-        <v>-8000</v>
+        <v>-7339.08</v>
       </c>
       <c r="O28" s="108" t="inlineStr">
         <is>
@@ -1869,12 +1912,18 @@
         <f>Assumptions!$B$28/5</f>
         <v>6000</v>
       </c>
-      <c r="G29" s="121" t="n"/>
+      <c r="G29" s="121">
+        <f>ROUND((4167.5+42.5+9.73)*1.1,2)</f>
+        <v>4641.7</v>
+      </c>
       <c r="H29" s="120">
         <f>Assumptions!$B$28/5</f>
         <v>6000</v>
       </c>
-      <c r="I29" s="121" t="n"/>
+      <c r="I29" s="121">
+        <f>ROUND((2630+43.75)*1.1,2)</f>
+        <v>2941.13</v>
+      </c>
       <c r="J29" s="120">
         <f>Assumptions!$B$28/5</f>
         <v>6000</v>
@@ -1886,11 +1935,11 @@
       </c>
       <c r="M29" s="120">
         <f>SUM(C29,E29,G29,I29,K29)</f>
-        <v>15724.52</v>
+        <v>23307.350000000002</v>
       </c>
       <c r="N29" s="120">
         <f>(C29-B29)*C$8+(E29-D29)*E$8+(G29-F29)*G$8+(I29-H29)*I$8+(K29-J29)*K$8</f>
-        <v>-6000</v>
+        <v>-692.6499999999996</v>
       </c>
       <c r="O29" s="108" t="inlineStr">
         <is>
@@ -1914,19 +1963,23 @@
         <v>5712.04</v>
       </c>
       <c r="E30" s="121">
-        <f>ROUND(18837.31*1.1,2)</f>
-        <v>20721.04</v>
+        <f>ROUND(19053.3*1.1,2)</f>
+        <v>20958.63</v>
       </c>
       <c r="F30" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
         <v>600</v>
       </c>
-      <c r="G30" s="121" t="n"/>
+      <c r="G30" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H30" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
         <v>600</v>
       </c>
-      <c r="I30" s="121" t="n"/>
+      <c r="I30" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J30" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Client subscriptions")+Assumptions!$B$31/5</f>
         <v>600</v>
@@ -1938,11 +1991,11 @@
       </c>
       <c r="M30" s="120">
         <f>SUM(C30,E30,G30,I30,K30)</f>
-        <v>20721.04</v>
+        <v>20958.63</v>
       </c>
       <c r="N30" s="120">
         <f>(C30-B30)*C$8+(E30-D30)*E$8+(G30-F30)*G$8+(I30-H30)*I$8+(K30-J30)*K$8</f>
-        <v>-6328.8</v>
+        <v>7717.790000000001</v>
       </c>
       <c r="O30" s="108" t="inlineStr">
         <is>
@@ -1966,19 +2019,25 @@
         <v>1400</v>
       </c>
       <c r="E31" s="121">
-        <f>ROUND((1115.04+46.69)*1.1,2)</f>
-        <v>1277.9</v>
+        <f>ROUND((1115.04+560.9+46.69)*1.1,2)</f>
+        <v>1894.89</v>
       </c>
       <c r="F31" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
       </c>
-      <c r="G31" s="121" t="n"/>
+      <c r="G31" s="121">
+        <f>ROUND((2525.5+2214.76+1132+834.55)*1.1,2)</f>
+        <v>7377.49</v>
+      </c>
       <c r="H31" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
       </c>
-      <c r="I31" s="121" t="n"/>
+      <c r="I31" s="121">
+        <f>ROUND((658+361.82)*1.1,2)</f>
+        <v>1121.8</v>
+      </c>
       <c r="J31" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Direct travel &amp; freight")+Assumptions!$B$30/5</f>
         <v>1400</v>
@@ -1990,11 +2049,11 @@
       </c>
       <c r="M31" s="120">
         <f>SUM(C31,E31,G31,I31,K31)</f>
-        <v>1277.9</v>
+        <v>10394.179999999998</v>
       </c>
       <c r="N31" s="120">
         <f>(C31-B31)*C$8+(E31-D31)*E$8+(G31-F31)*G$8+(I31-H31)*I$8+(K31-J31)*K$8</f>
-        <v>-1400</v>
+        <v>4794.18</v>
       </c>
       <c r="O31" s="108" t="inlineStr">
         <is>
@@ -2022,7 +2081,7 @@
       </c>
       <c r="E32" s="123">
         <f>E27+E28+E29+E30+E31</f>
-        <v>117876.95999999999</v>
+        <v>118731.54000000001</v>
       </c>
       <c r="F32" s="123">
         <f>F27+F28+F29+F30+F31</f>
@@ -2030,7 +2089,7 @@
       </c>
       <c r="G32" s="123">
         <f>G27+G28+G29+G30+G31</f>
-        <v>0</v>
+        <v>112360.71</v>
       </c>
       <c r="H32" s="123">
         <f>H27+H28+H29+H30+H31</f>
@@ -2038,7 +2097,7 @@
       </c>
       <c r="I32" s="123">
         <f>I27+I28+I29+I30+I31</f>
-        <v>0</v>
+        <v>19943.63</v>
       </c>
       <c r="J32" s="123">
         <f>J27+J28+J29+J30+J31</f>
@@ -2054,11 +2113,11 @@
       </c>
       <c r="M32" s="123">
         <f>M27+M28+M29+M30+M31</f>
-        <v>256963.18999999997</v>
+        <v>390122.1099999999</v>
       </c>
       <c r="N32" s="123">
         <f>N27+N28+N29+N30+N31</f>
-        <v>-50436.999999999985</v>
+        <v>96453.82</v>
       </c>
       <c r="O32" s="12" t="n"/>
     </row>
@@ -2091,12 +2150,16 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
         <v>0</v>
       </c>
-      <c r="G35" s="121" t="n"/>
+      <c r="G35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H35" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
         <v>0</v>
       </c>
-      <c r="I35" s="121" t="n"/>
+      <c r="I35" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J35" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Rent")</f>
         <v>0</v>
@@ -2142,12 +2205,17 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
         <v>0</v>
       </c>
-      <c r="G36" s="121" t="n"/>
+      <c r="G36" s="121">
+        <f>ROUND(9178.55*1.1,2)</f>
+        <v>10096.41</v>
+      </c>
       <c r="H36" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
         <v>0</v>
       </c>
-      <c r="I36" s="121" t="n"/>
+      <c r="I36" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J36" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"IT support")</f>
         <v>0</v>
@@ -2159,11 +2227,11 @@
       </c>
       <c r="M36" s="120">
         <f>SUM(C36,E36,G36,I36,K36)</f>
-        <v>0</v>
+        <v>10096.41</v>
       </c>
       <c r="N36" s="120">
         <f>(C36-B36)*C$8+(E36-D36)*E$8+(G36-F36)*G$8+(I36-H36)*I$8+(K36-J36)*K$8</f>
-        <v>0</v>
+        <v>10096.41</v>
       </c>
       <c r="O36" s="108" t="inlineStr">
         <is>
@@ -2193,12 +2261,18 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
         <v>0</v>
       </c>
-      <c r="G37" s="121" t="n"/>
+      <c r="G37" s="121">
+        <f>ROUND(4250*1.1,2)</f>
+        <v>4675</v>
+      </c>
       <c r="H37" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
         <v>0</v>
       </c>
-      <c r="I37" s="121" t="n"/>
+      <c r="I37" s="121">
+        <f>ROUND(4385*1.1,2)</f>
+        <v>4823.5</v>
+      </c>
       <c r="J37" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Advertising")</f>
         <v>0</v>
@@ -2210,11 +2284,11 @@
       </c>
       <c r="M37" s="120">
         <f>SUM(C37,E37,G37,I37,K37)</f>
-        <v>0</v>
+        <v>9498.5</v>
       </c>
       <c r="N37" s="120">
         <f>(C37-B37)*C$8+(E37-D37)*E$8+(G37-F37)*G$8+(I37-H37)*I$8+(K37-J37)*K$8</f>
-        <v>-6600</v>
+        <v>2898.5</v>
       </c>
       <c r="O37" s="108" t="inlineStr">
         <is>
@@ -2246,12 +2320,16 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>4650</v>
       </c>
-      <c r="G38" s="121" t="n"/>
+      <c r="G38" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H38" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>800</v>
       </c>
-      <c r="I38" s="121" t="n"/>
+      <c r="I38" s="121" t="n">
+        <v>342</v>
+      </c>
       <c r="J38" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Professional fees")+Assumptions!$B$33/5</f>
         <v>800</v>
@@ -2263,11 +2341,11 @@
       </c>
       <c r="M38" s="120">
         <f>SUM(C38,E38,G38,I38,K38)</f>
-        <v>880</v>
+        <v>1222</v>
       </c>
       <c r="N38" s="120">
         <f>(C38-B38)*C$8+(E38-D38)*E$8+(G38-F38)*G$8+(I38-H38)*I$8+(K38-J38)*K$8</f>
-        <v>-800</v>
+        <v>-6708</v>
       </c>
       <c r="O38" s="108" t="inlineStr">
         <is>
@@ -2290,19 +2368,25 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$45,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$45,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>0</v>
       </c>
-      <c r="E39" s="121" t="n">
-        <v>0</v>
+      <c r="E39" s="121">
+        <f>ROUND(629.85*1.1,2)</f>
+        <v>692.84</v>
       </c>
       <c r="F39" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>2310</v>
       </c>
-      <c r="G39" s="121" t="n"/>
+      <c r="G39" s="121">
+        <f>ROUND(3154.18*1.1,2)</f>
+        <v>3469.6</v>
+      </c>
       <c r="H39" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>0</v>
       </c>
-      <c r="I39" s="121" t="n"/>
+      <c r="I39" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J39" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Dues &amp; subscriptions")</f>
         <v>0</v>
@@ -2314,11 +2398,11 @@
       </c>
       <c r="M39" s="120">
         <f>SUM(C39,E39,G39,I39,K39)</f>
-        <v>0</v>
+        <v>4162.44</v>
       </c>
       <c r="N39" s="120">
         <f>(C39-B39)*C$8+(E39-D39)*E$8+(G39-F39)*G$8+(I39-H39)*I$8+(K39-J39)*K$8</f>
-        <v>0</v>
+        <v>1852.44</v>
       </c>
       <c r="O39" s="108" t="inlineStr">
         <is>
@@ -2349,12 +2433,17 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
         <v>0</v>
       </c>
-      <c r="G40" s="121" t="n"/>
+      <c r="G40" s="121">
+        <f>ROUND(92*1.1,2)</f>
+        <v>101.2</v>
+      </c>
       <c r="H40" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
         <v>0</v>
       </c>
-      <c r="I40" s="121" t="n"/>
+      <c r="I40" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J40" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Telephone &amp; internet")</f>
         <v>0</v>
@@ -2366,11 +2455,11 @@
       </c>
       <c r="M40" s="120">
         <f>SUM(C40,E40,G40,I40,K40)</f>
-        <v>940.11</v>
+        <v>1041.31</v>
       </c>
       <c r="N40" s="120">
         <f>(C40-B40)*C$8+(E40-D40)*E$8+(G40-F40)*G$8+(I40-H40)*I$8+(K40-J40)*K$8</f>
-        <v>0</v>
+        <v>101.2</v>
       </c>
       <c r="O40" s="108" t="inlineStr">
         <is>
@@ -2400,12 +2489,17 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
       </c>
-      <c r="G41" s="121" t="n"/>
+      <c r="G41" s="121">
+        <f>ROUND(906*1.1,2)</f>
+        <v>996.6</v>
+      </c>
       <c r="H41" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
       </c>
-      <c r="I41" s="121" t="n"/>
+      <c r="I41" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J41" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Recruitment")+Assumptions!$B$32/5</f>
         <v>1000</v>
@@ -2417,11 +2511,11 @@
       </c>
       <c r="M41" s="120">
         <f>SUM(C41,E41,G41,I41,K41)</f>
-        <v>0</v>
+        <v>996.6</v>
       </c>
       <c r="N41" s="120">
         <f>(C41-B41)*C$8+(E41-D41)*E$8+(G41-F41)*G$8+(I41-H41)*I$8+(K41-J41)*K$8</f>
-        <v>-1000</v>
+        <v>-3003.4</v>
       </c>
       <c r="O41" s="108" t="inlineStr">
         <is>
@@ -2451,12 +2545,16 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
         <v>0</v>
       </c>
-      <c r="G42" s="121" t="n"/>
+      <c r="G42" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H42" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
         <v>0</v>
       </c>
-      <c r="I42" s="121" t="n"/>
+      <c r="I42" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J42" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Insurance")+Assumptions!$B$34/5</f>
         <v>0</v>
@@ -2476,7 +2574,7 @@
       </c>
       <c r="O42" s="108" t="inlineStr">
         <is>
-          <t>Brookvale annual renewals $66,239 due Wed 14 Oct (six bills, GC approved) - Payables tab. Was a $3k a month estimate, now nil on top.</t>
+          <t>Brookvale $66,239 was in the week 2 forecast but has not been paid - still open in Xero at 29 Oct, due 30 Oct. It is in the 2 Nov creditors run in the new file.</t>
         </is>
       </c>
     </row>
@@ -2504,12 +2602,17 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
         <v>400</v>
       </c>
-      <c r="G43" s="121" t="n"/>
+      <c r="G43" s="121">
+        <f>ROUND((44.04+31.82+27.93+12.95+6.1)*1.1,2)</f>
+        <v>135.12</v>
+      </c>
       <c r="H43" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
         <v>400</v>
       </c>
-      <c r="I43" s="121" t="n"/>
+      <c r="I43" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J43" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Office")+Assumptions!$B$35/5</f>
         <v>400</v>
@@ -2521,11 +2624,11 @@
       </c>
       <c r="M43" s="120">
         <f>SUM(C43,E43,G43,I43,K43)</f>
-        <v>480.6</v>
+        <v>615.72</v>
       </c>
       <c r="N43" s="120">
         <f>(C43-B43)*C$8+(E43-D43)*E$8+(G43-F43)*G$8+(I43-H43)*I$8+(K43-J43)*K$8</f>
-        <v>-400</v>
+        <v>-1464.88</v>
       </c>
       <c r="O43" s="108" t="inlineStr">
         <is>
@@ -2555,12 +2658,16 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
       </c>
-      <c r="G44" s="121" t="n"/>
+      <c r="G44" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H44" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
       </c>
-      <c r="I44" s="121" t="n"/>
+      <c r="I44" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J44" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Electricity")</f>
         <v>0</v>
@@ -2608,12 +2715,17 @@
         <f>Assumptions!$B$36/5</f>
         <v>200</v>
       </c>
-      <c r="G45" s="121" t="n"/>
+      <c r="G45" s="121">
+        <f>ROUND(139.89*1.1,2)+36.86</f>
+        <v>190.74</v>
+      </c>
       <c r="H45" s="120">
         <f>Assumptions!$B$36/5</f>
         <v>200</v>
       </c>
-      <c r="I45" s="121" t="n"/>
+      <c r="I45" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J45" s="120">
         <f>Assumptions!$B$36/5</f>
         <v>200</v>
@@ -2625,11 +2737,11 @@
       </c>
       <c r="M45" s="120">
         <f>SUM(C45,E45,G45,I45,K45)</f>
-        <v>10</v>
+        <v>200.74</v>
       </c>
       <c r="N45" s="120">
         <f>(C45-B45)*C$8+(E45-D45)*E$8+(G45-F45)*G$8+(I45-H45)*I$8+(K45-J45)*K$8</f>
-        <v>-190</v>
+        <v>-599.26</v>
       </c>
       <c r="O45" s="108" t="inlineStr">
         <is>
@@ -2661,12 +2773,16 @@
         <f>Assumptions!$B$37/5</f>
         <v>5000</v>
       </c>
-      <c r="G46" s="121" t="n"/>
+      <c r="G46" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H46" s="120">
         <f>Assumptions!$B$37/5</f>
         <v>5000</v>
       </c>
-      <c r="I46" s="121" t="n"/>
+      <c r="I46" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J46" s="120">
         <f>Assumptions!$B$37/5</f>
         <v>5000</v>
@@ -2682,11 +2798,11 @@
       </c>
       <c r="N46" s="120">
         <f>(C46-B46)*C$8+(E46-D46)*E$8+(G46-F46)*G$8+(I46-H46)*I$8+(K46-J46)*K$8</f>
-        <v>5000</v>
+        <v>-10000</v>
       </c>
       <c r="O46" s="108" t="inlineStr">
         <is>
-          <t>~$25k a month transferred to the PL and DL cards. Covers every Card row on the Payables tab (subscriptions, travel, electricity, Seek, Goget, EH). Week 1 actual: $10,000 moved to the PL card 7 Oct.</t>
+          <t>~$25k a month to the PL and DL cards. Weeks 2 to 4 actuals are nil here because the card spend is already inside the category lines (Xero cash P&amp;L includes what the cards paid). Only the $10k transfer on 7 Oct is shown, in week 1.</t>
         </is>
       </c>
     </row>
@@ -2712,12 +2828,17 @@
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$46,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$46,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
         <v>0</v>
       </c>
-      <c r="G47" s="121" t="n"/>
+      <c r="G47" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H47" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$47,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$47,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
         <v>0</v>
       </c>
-      <c r="I47" s="121" t="n"/>
+      <c r="I47" s="121">
+        <f>ROUND(360*1.1,2)</f>
+        <v>396</v>
+      </c>
       <c r="J47" s="120">
         <f>SUMIFS(Payables!$D$19:$D$75,Payables!$K$19:$K$75,"Yes",Payables!$G$19:$G$75,"&gt;="&amp;Assumptions!$B$48,Payables!$G$19:$G$75,"&lt;="&amp;Assumptions!$C$48,Payables!$E$19:$E$75,"&lt;&gt;Card",Payables!$F$19:$F$75,"Other")</f>
         <v>0</v>
@@ -2729,11 +2850,11 @@
       </c>
       <c r="M47" s="120">
         <f>SUM(C47,E47,G47,I47,K47)</f>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="N47" s="120">
         <f>(C47-B47)*C$8+(E47-D47)*E$8+(G47-F47)*G$8+(I47-H47)*I$8+(K47-J47)*K$8</f>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="O47" s="108" t="inlineStr">
         <is>
@@ -2758,17 +2879,23 @@
         <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$45)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$45),'Creditors Run'!$I$11:$I$510),0)</f>
         <v>67811.82</v>
       </c>
-      <c r="E48" s="121" t="n"/>
+      <c r="E48" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="F48" s="120">
         <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$46)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$46),'Creditors Run'!$I$11:$I$510),0)</f>
         <v>26442.059999999998</v>
       </c>
-      <c r="G48" s="121" t="n"/>
+      <c r="G48" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H48" s="120">
         <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$47)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$47),'Creditors Run'!$I$11:$I$510),0)</f>
         <v>20985.43</v>
       </c>
-      <c r="I48" s="121" t="n"/>
+      <c r="I48" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J48" s="120">
         <f>IF('Creditors Run'!$B$5=1,SUMPRODUCT(('Creditors Run'!$A$11:$A$510&lt;&gt;"")*ISNUMBER('Creditors Run'!$I$11:$I$510)*('Creditors Run'!$M$11:$M$510="")*('Creditors Run'!$N$11:$N$510&gt;=Assumptions!$B$48)*('Creditors Run'!$N$11:$N$510&lt;=Assumptions!$C$48),'Creditors Run'!$I$11:$I$510),0)</f>
         <v>25592.92</v>
@@ -2784,11 +2911,11 @@
       </c>
       <c r="N48" s="120">
         <f>(C48-B48)*C$8+(E48-D48)*E$8+(G48-F48)*G$8+(I48-H48)*I$8+(K48-J48)*K$8</f>
-        <v>77302.54</v>
+        <v>-37936.77000000001</v>
       </c>
       <c r="O48" s="108" t="inlineStr">
         <is>
-          <t>Creditors Run tab - paste the Xero aged payables detail in each month and it lands here on the run date (or the date in column L). Week 1 actual is the 1 Oct run. The Payables tab's Xero bill rows drop out of the lines above while this is switched on, so nothing is double counted.</t>
+          <t>Creditors Run tab. Week 1 actual is the 1 Oct run ($77,303). No run in weeks 2 to 4 - bills were paid one by one and sit in their category lines.</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2939,7 @@
       </c>
       <c r="E49" s="123">
         <f>E35+E36+E37+E38+E39+E40+E41+E42+E43+E44+E45+E46+E47+E48</f>
-        <v>1185.1100000000001</v>
+        <v>1877.95</v>
       </c>
       <c r="F49" s="123">
         <f>F35+F36+F37+F38+F39+F40+F41+F42+F43+F44+F45+F46+F47+F48</f>
@@ -2820,7 +2947,7 @@
       </c>
       <c r="G49" s="123">
         <f>G35+G36+G37+G38+G39+G40+G41+G42+G43+G44+G45+G46+G47+G48</f>
-        <v>0</v>
+        <v>19664.67</v>
       </c>
       <c r="H49" s="123">
         <f>H35+H36+H37+H38+H39+H40+H41+H42+H43+H44+H45+H46+H47+H48</f>
@@ -2828,7 +2955,7 @@
       </c>
       <c r="I49" s="123">
         <f>I35+I36+I37+I38+I39+I40+I41+I42+I43+I44+I45+I46+I47+I48</f>
-        <v>0</v>
+        <v>5561.5</v>
       </c>
       <c r="J49" s="123">
         <f>J35+J36+J37+J38+J39+J40+J41+J42+J43+J44+J45+J46+J47+J48</f>
@@ -2844,11 +2971,11 @@
       </c>
       <c r="M49" s="123">
         <f>M35+M36+M37+M38+M39+M40+M41+M42+M43+M44+M45+M46+M47+M48</f>
-        <v>89613.25</v>
+        <v>115532.26</v>
       </c>
       <c r="N49" s="123">
         <f>N35+N36+N37+N38+N39+N40+N41+N42+N43+N44+N45+N46+N47+N48</f>
-        <v>73312.54</v>
+        <v>-44367.76000000001</v>
       </c>
       <c r="O49" s="12" t="n"/>
     </row>
@@ -2881,12 +3008,16 @@
         <f>IF(AND(Assumptions!$B$25&gt;=Assumptions!$B$46,Assumptions!$B$25&lt;=Assumptions!$C$46),Assumptions!$B$21*(Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24),0)</f>
         <v>0</v>
       </c>
-      <c r="G52" s="121" t="n"/>
+      <c r="G52" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="H52" s="120">
         <f>IF(AND(Assumptions!$B$25&gt;=Assumptions!$B$47,Assumptions!$B$25&lt;=Assumptions!$C$47),Assumptions!$B$21*(Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24),0)</f>
         <v>100358.38399999999</v>
       </c>
-      <c r="I52" s="121" t="n"/>
+      <c r="I52" s="121" t="n">
+        <v>0</v>
+      </c>
       <c r="J52" s="120">
         <f>IF(AND(Assumptions!$B$25&gt;=Assumptions!$B$48,Assumptions!$B$25&lt;=Assumptions!$C$48),Assumptions!$B$21*(Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24),0)</f>
         <v>0</v>
@@ -2902,11 +3033,11 @@
       </c>
       <c r="N52" s="120">
         <f>(C52-B52)*C$8+(E52-D52)*E$8+(G52-F52)*G$8+(I52-H52)*I$8+(K52-J52)*K$8</f>
-        <v>0</v>
+        <v>-100358.38399999999</v>
       </c>
       <c r="O52" s="108" t="str">
-        <f>"Q1 BAS est. "&amp;TEXT(Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24,"$#,##0")&amp;" (Sep PAYG "&amp;TEXT(Assumptions!$B$22,"$#,##0")&amp;" + GST est "&amp;TEXT(Assumptions!$B$23,"$#,##0")&amp;" + instalment "&amp;TEXT(Assumptions!$B$24,"$#,##0")&amp;"), due "&amp;TEXT(Assumptions!$B$25,"d mmm")&amp;". Toggle on Assumptions = "&amp;Assumptions!$B$21&amp;" (1 = in the forecast)."</f>
-        <v>Q1 BAS est. $100,358 (Sep PAYG $50,358 + GST est $50,000 + instalment $0,), due 28 Oct. Toggle on Assumptions = 1 (1 = in the forecast).</v>
+        <f>"Q1 BAS est. "&amp;TEXT(Assumptions!$B$22+Assumptions!$B$23+Assumptions!$B$24,"$#,##0")&amp;" was in week 4 (28 Oct) but did not go out - Xero bank is flat 28 to 29 Oct. Carried into the 29 Oct forecast as 25 Nov through the agent."</f>
+        <v>Q1 BAS est. $100,358 was in week 4 (28 Oct) but did not go out - Xero bank is flat 28 to 29 Oct. Carried into the 29 Oct forecast as 25 Nov through the agent.</v>
       </c>
     </row>
     <row r="53">
@@ -2965,7 +3096,7 @@
       </c>
       <c r="N53" s="123">
         <f>N52</f>
-        <v>0</v>
+        <v>-100358.38399999999</v>
       </c>
       <c r="O53" s="12" t="n"/>
     </row>
@@ -2989,7 +3120,7 @@
       </c>
       <c r="E55" s="122">
         <f>E24+E32+E49+E53</f>
-        <v>119062.06999999999</v>
+        <v>120609.49</v>
       </c>
       <c r="F55" s="122">
         <f>F24+F32+F49+F66</f>
@@ -2997,7 +3128,7 @@
       </c>
       <c r="G55" s="122">
         <f>G24+G32+G49+G53</f>
-        <v>0</v>
+        <v>232028.62</v>
       </c>
       <c r="H55" s="122">
         <f>H24+H32+H49+H53</f>
@@ -3005,7 +3136,7 @@
       </c>
       <c r="I55" s="122">
         <f>I24+I32+I49+I53</f>
-        <v>0</v>
+        <v>25505.13</v>
       </c>
       <c r="J55" s="122">
         <f>J24+J32+J49+J53</f>
@@ -3021,11 +3152,11 @@
       </c>
       <c r="M55" s="122">
         <f>M24+M32+M49+M53</f>
-        <v>447998.77999999997</v>
+        <v>707079.95</v>
       </c>
       <c r="N55" s="122">
         <f>N24+N32+N49+N53</f>
-        <v>15734.880000000012</v>
+        <v>-54977.74399999999</v>
       </c>
       <c r="O55" s="16" t="n"/>
     </row>
@@ -3049,7 +3180,7 @@
       </c>
       <c r="E57" s="122">
         <f>E15-E55</f>
-        <v>24140.200000000026</v>
+        <v>285969.79000000004</v>
       </c>
       <c r="F57" s="122">
         <f>F15-F68</f>
@@ -3057,7 +3188,7 @@
       </c>
       <c r="G57" s="122">
         <f>G15-G55</f>
-        <v>0</v>
+        <v>-118528.33</v>
       </c>
       <c r="H57" s="122">
         <f>H15-H55</f>
@@ -3065,7 +3196,7 @@
       </c>
       <c r="I57" s="122">
         <f>I15-I55</f>
-        <v>0</v>
+        <v>-6245.23</v>
       </c>
       <c r="J57" s="122">
         <f>J15-J55</f>
@@ -3081,11 +3212,11 @@
       </c>
       <c r="M57" s="122">
         <f>M15-M55</f>
-        <v>-146507.20999999996</v>
+        <v>-9451.179999999818</v>
       </c>
       <c r="N57" s="122">
         <f>N15-N55</f>
-        <v>7963.500000000007</v>
+        <v>228088.57066666667</v>
       </c>
       <c r="O57" s="16" t="n"/>
     </row>
@@ -3107,29 +3238,29 @@
         <f>D10+D57</f>
         <v>263901.67999999993</v>
       </c>
-      <c r="E58" s="125" t="str">
+      <c r="E58" s="125">
         <f>IF(E$8=1,E10+E57,"")</f>
-        <v/>
+        <v>547717.19</v>
       </c>
       <c r="F58" s="125">
         <f>F10+F57</f>
-        <v>498505.9666666666</v>
-      </c>
-      <c r="G58" s="125" t="str">
+        <v>814172.3566666667</v>
+      </c>
+      <c r="G58" s="125">
         <f>IF(G$8=1,G10+G57,"")</f>
-        <v/>
+        <v>461039.73999999993</v>
       </c>
       <c r="H58" s="125">
         <f>H10+H57</f>
-        <v>362388.61933333334</v>
-      </c>
-      <c r="I58" s="125" t="str">
+        <v>319364.5626666667</v>
+      </c>
+      <c r="I58" s="125">
         <f>IF(I$8=1,I10+I57,"")</f>
-        <v/>
+        <v>449236.68000000005</v>
       </c>
       <c r="J58" s="125">
         <f>J10+J57</f>
-        <v>302297.836</v>
+        <v>379839.8966666666</v>
       </c>
       <c r="K58" s="125" t="str">
         <f>IF(K$8=1,K10+K57,"")</f>
@@ -3137,11 +3268,11 @@
       </c>
       <c r="L58" s="125">
         <f>J58</f>
-        <v>302297.836</v>
+        <v>379839.8966666666</v>
       </c>
       <c r="M58" s="125">
         <f>IF(K$8=1,K58,IF(I$8=1,I58,IF(G$8=1,G58,IF(E$8=1,E58,IF(C$8=1,C58,"")))))</f>
-        <v>264507.58999999997</v>
+        <v>449236.68000000005</v>
       </c>
       <c r="N58" s="26" t="n"/>
       <c r="O58" s="78" t="inlineStr">
@@ -3162,11 +3293,20 @@
         <v>261747.39999999997</v>
       </c>
       <c r="D59" s="10" t="n"/>
-      <c r="E59" s="121" t="n"/>
+      <c r="E59" s="121">
+        <f>1036314.34-456746.27</f>
+        <v>579568.07</v>
+      </c>
       <c r="F59" s="10" t="n"/>
-      <c r="G59" s="121" t="n"/>
+      <c r="G59" s="121">
+        <f>912228.18-456746.27</f>
+        <v>455481.91000000003</v>
+      </c>
       <c r="H59" s="10" t="n"/>
-      <c r="I59" s="121" t="n"/>
+      <c r="I59" s="121">
+        <f>896676.95-456746.27</f>
+        <v>439930.67999999993</v>
+      </c>
       <c r="J59" s="10" t="n"/>
       <c r="K59" s="121" t="n"/>
       <c r="L59" s="12" t="n"/>
@@ -3174,7 +3314,7 @@
       <c r="N59" s="12" t="n"/>
       <c r="O59" s="79" t="inlineStr">
         <is>
-          <t>Type the real closing balance (cheque + savings) in at the end of each week. Week 1 is worked back from Xero: $358,696.23 at Mon 5 Oct, less the $86,948.83 Xero cash drop over 6-7 Oct and the $10k card transfer - replace with the CommBiz 7 Oct figure. Week 2 - key it Wed 14 Oct, then set the flag to 1.</t>
+          <t>Weeks 2 to 4 are worked back from Xero total cash less the other accounts ($456,746, the gap on 5 Oct). Replace each with the CommBiz cheque + savings figure at 14, 21 and 28 Oct. Week 1 is the same method off 7 Oct.</t>
         </is>
       </c>
     </row>
@@ -3190,19 +3330,19 @@
         <v>2760.1900000000023</v>
       </c>
       <c r="D60" s="10" t="n"/>
-      <c r="E60" s="126" t="str">
+      <c r="E60" s="126">
         <f>IF(E$8=1,E58-E59,"")</f>
-        <v/>
+        <v>-31850.880000000005</v>
       </c>
       <c r="F60" s="10" t="n"/>
-      <c r="G60" s="126" t="str">
+      <c r="G60" s="126">
         <f>IF(G$8=1,G58-G59,"")</f>
-        <v/>
+        <v>5557.8299999999</v>
       </c>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="126" t="str">
+      <c r="I60" s="126">
         <f>IF(I$8=1,I58-I59,"")</f>
-        <v/>
+        <v>9306.000000000116</v>
       </c>
       <c r="J60" s="10" t="n"/>
       <c r="K60" s="126" t="str">
@@ -3214,7 +3354,7 @@
       <c r="N60" s="12" t="n"/>
       <c r="O60" s="76" t="inlineStr">
         <is>
-          <t>Should be nil once everything's in. Week 1 is about $2.8k unexplained - small card / bank items on 6-7 Oct that aren't on a bill. Clears when the real 7 Oct balance goes in.</t>
+          <t>Should be nil once everything's in. Weeks 2 to 4 show the gap between the Xero P&amp;L method and the bank - card spend, transfers and anything not on a bill. The CommBiz balances will tighten it.</t>
         </is>
       </c>
     </row>
@@ -3283,15 +3423,15 @@
       </c>
       <c r="F64" s="127">
         <f>IF(Payroll!$I$5=0,0,F58/(Payroll!$I$5/2))</f>
-        <v>10.013377122502543</v>
+        <v>16.354096831646046</v>
       </c>
       <c r="H64" s="127">
         <f>IF(Payroll!$I$5=0,0,H58/(Payroll!$I$5/2))</f>
-        <v>7.279218611066474</v>
+        <v>6.415004070919707</v>
       </c>
       <c r="J64" s="127">
         <f>IF(Payroll!$I$5=0,0,J58/(Payroll!$I$5/2))</f>
-        <v>6.072188574642456</v>
+        <v>7.629758490010176</v>
       </c>
       <c r="O64" s="108" t="n"/>
     </row>
@@ -3351,7 +3491,7 @@
     <row r="69" ht="15.75" customHeight="1" s="109">
       <c r="A69" s="110" t="inlineStr">
         <is>
-          <t>1. Aware Super $225,887 (INV-10596) is the big one - still not paid at 12 Oct and now expected 9 Nov, after this forecast. The whole Complete AV bill ($178,119) is now paid ahead of it (materials 29 Sep, labour 8 Oct), so we watch the cheque account until Aware pay. Build-up on the Complete AV tab.</t>
+          <t>1. Aware Super paid the $225,887 on 13 Oct and everything else by 27 Oct - risk cleared. The whole Complete AV bill ($178,119) went out ahead of it. Build-up on the Complete AV tab.</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3512,7 @@
     <row r="72" ht="15.75" customHeight="1" s="109">
       <c r="A72" s="110" t="inlineStr">
         <is>
-          <t>4. BAS - Sep quarter (Sep PAYG ~$50k + GST est ~$50k + any instalment) is due 28 Oct as we lodge it ourselves - it's in week 4. Swap the GST estimate for the activity statement figure once it's run.</t>
+          <t>4. BAS - Sep quarter (~$96k) did not go out on 28 Oct. Confirm whether it is lodged through the agent (25 Nov) - it is in the 29 Oct forecast on that date. Swap the GST estimate for the activity statement figure.</t>
         </is>
       </c>
     </row>
